--- a/artfynd/A 45833-2025 artfynd.xlsx
+++ b/artfynd/A 45833-2025 artfynd.xlsx
@@ -1277,32 +1277,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129035054</v>
+        <v>129035014</v>
       </c>
       <c r="B8" t="n">
-        <v>98651</v>
+        <v>57723</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>569126</v>
+        <v>569455</v>
       </c>
       <c r="R8" t="n">
-        <v>6949570</v>
+        <v>6949703</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>13 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1379,7 +1379,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129035014</v>
+        <v>129035013</v>
       </c>
       <c r="B9" t="n">
         <v>57723</v>
@@ -1417,7 +1417,7 @@
         <v>569455</v>
       </c>
       <c r="R9" t="n">
-        <v>6949703</v>
+        <v>6949716</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1481,32 +1481,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129035013</v>
+        <v>129035054</v>
       </c>
       <c r="B10" t="n">
-        <v>57723</v>
+        <v>98651</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>569455</v>
+        <v>569126</v>
       </c>
       <c r="R10" t="n">
-        <v>6949716</v>
+        <v>6949570</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>13 ex</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1782,10 +1782,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129034630</v>
+        <v>129034577</v>
       </c>
       <c r="B13" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1793,21 +1793,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1817,10 +1817,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569231</v>
+        <v>569496</v>
       </c>
       <c r="R13" t="n">
-        <v>6949559</v>
+        <v>6949627</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1853,6 +1853,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1879,10 +1884,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129034577</v>
+        <v>129034630</v>
       </c>
       <c r="B14" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1890,21 +1895,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1914,10 +1919,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569496</v>
+        <v>569231</v>
       </c>
       <c r="R14" t="n">
-        <v>6949627</v>
+        <v>6949559</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1950,11 +1955,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Äldre ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -4879,32 +4879,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129035011</v>
+        <v>129034607</v>
       </c>
       <c r="B44" t="n">
-        <v>57723</v>
+        <v>98651</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4914,10 +4914,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>569442</v>
+        <v>569317</v>
       </c>
       <c r="R44" t="n">
-        <v>6949783</v>
+        <v>6949549</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>31 stycken</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4981,32 +4981,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129034575</v>
+        <v>129035041</v>
       </c>
       <c r="B45" t="n">
-        <v>57723</v>
+        <v>98651</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5016,10 +5016,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>569448</v>
+        <v>569262</v>
       </c>
       <c r="R45" t="n">
-        <v>6949625</v>
+        <v>6949524</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Färska ringhack på Tall av tretåig hackspett</t>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5083,32 +5083,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129034607</v>
+        <v>129035011</v>
       </c>
       <c r="B46" t="n">
-        <v>98651</v>
+        <v>57723</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5118,10 +5118,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>569317</v>
+        <v>569442</v>
       </c>
       <c r="R46" t="n">
-        <v>6949549</v>
+        <v>6949783</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>31 stycken</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5185,32 +5185,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129035041</v>
+        <v>129034575</v>
       </c>
       <c r="B47" t="n">
-        <v>98651</v>
+        <v>57723</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5220,10 +5220,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>569262</v>
+        <v>569448</v>
       </c>
       <c r="R47" t="n">
-        <v>6949524</v>
+        <v>6949625</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5260,7 +5260,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>5 ex</t>
+          <t>Färska ringhack på Tall av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5981,10 +5981,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129035028</v>
+        <v>129034581</v>
       </c>
       <c r="B55" t="n">
-        <v>91805</v>
+        <v>57883</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5992,21 +5992,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6016,10 +6016,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>569192</v>
+        <v>569223</v>
       </c>
       <c r="R55" t="n">
-        <v>6949509</v>
+        <v>6949401</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6052,6 +6052,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Sågs och gjorde övriga läten</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6078,10 +6083,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129035008</v>
+        <v>129035028</v>
       </c>
       <c r="B56" t="n">
-        <v>91520</v>
+        <v>91805</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6089,21 +6094,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6113,10 +6118,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>569216</v>
+        <v>569192</v>
       </c>
       <c r="R56" t="n">
-        <v>6949430</v>
+        <v>6949509</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6175,10 +6180,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129034581</v>
+        <v>129035008</v>
       </c>
       <c r="B57" t="n">
-        <v>57883</v>
+        <v>91520</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6186,21 +6191,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6210,10 +6215,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>569223</v>
+        <v>569216</v>
       </c>
       <c r="R57" t="n">
-        <v>6949401</v>
+        <v>6949430</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6246,11 +6251,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Sågs och gjorde övriga läten</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7980,32 +7980,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129034650</v>
+        <v>129034645</v>
       </c>
       <c r="B75" t="n">
-        <v>98651</v>
+        <v>92811</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8015,10 +8015,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>569303</v>
+        <v>569196</v>
       </c>
       <c r="R75" t="n">
-        <v>6949537</v>
+        <v>6949411</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8055,7 +8055,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>30 stycken ( finns eventuellt mer )</t>
+          <t>4 färska exemplar 3 äldre exemplar</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8082,32 +8082,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129034605</v>
+        <v>129034642</v>
       </c>
       <c r="B76" t="n">
-        <v>98651</v>
+        <v>92811</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8117,10 +8117,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>569305</v>
+        <v>569283</v>
       </c>
       <c r="R76" t="n">
-        <v>6949538</v>
+        <v>6949655</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8157,7 +8157,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>21 knärot</t>
+          <t>7 äldre exemplar</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8184,32 +8184,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129026691</v>
+        <v>129034598</v>
       </c>
       <c r="B77" t="n">
-        <v>91805</v>
+        <v>97522</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8219,10 +8219,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>569195</v>
+        <v>569460</v>
       </c>
       <c r="R77" t="n">
-        <v>6949487</v>
+        <v>6949629</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8281,32 +8281,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129034645</v>
+        <v>129026691</v>
       </c>
       <c r="B78" t="n">
-        <v>92811</v>
+        <v>91805</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8316,10 +8316,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>569196</v>
+        <v>569195</v>
       </c>
       <c r="R78" t="n">
-        <v>6949411</v>
+        <v>6949487</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8352,11 +8352,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>4 färska exemplar 3 äldre exemplar</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8383,32 +8378,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129034642</v>
+        <v>129034650</v>
       </c>
       <c r="B79" t="n">
-        <v>92811</v>
+        <v>98651</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8418,10 +8413,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>569283</v>
+        <v>569303</v>
       </c>
       <c r="R79" t="n">
-        <v>6949655</v>
+        <v>6949537</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8458,7 +8453,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>7 äldre exemplar</t>
+          <t>30 stycken ( finns eventuellt mer )</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8485,32 +8480,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129034598</v>
+        <v>129034605</v>
       </c>
       <c r="B80" t="n">
-        <v>97522</v>
+        <v>98651</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8520,10 +8515,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>569460</v>
+        <v>569305</v>
       </c>
       <c r="R80" t="n">
-        <v>6949629</v>
+        <v>6949538</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8556,6 +8551,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>21 knärot</t>
         </is>
       </c>
       <c r="AD80" t="b">

--- a/artfynd/A 45833-2025 artfynd.xlsx
+++ b/artfynd/A 45833-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129034627</v>
+        <v>129034612</v>
       </c>
       <c r="B2" t="n">
-        <v>79034</v>
+        <v>98656</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569482</v>
+        <v>569243</v>
       </c>
       <c r="R2" t="n">
-        <v>6949676</v>
+        <v>6949558</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>30  exemplar ca</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129034612</v>
+        <v>129035046</v>
       </c>
       <c r="B3" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569243</v>
+        <v>569127</v>
       </c>
       <c r="R3" t="n">
-        <v>6949558</v>
+        <v>6949602</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>30  exemplar ca</t>
+          <t>13 ex</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129035046</v>
+        <v>129035043</v>
       </c>
       <c r="B4" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -909,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569127</v>
+        <v>569204</v>
       </c>
       <c r="R4" t="n">
-        <v>6949602</v>
+        <v>6949533</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,7 +954,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>13 ex</t>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,32 +981,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129035043</v>
+        <v>129034627</v>
       </c>
       <c r="B5" t="n">
-        <v>98651</v>
+        <v>79034</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569204</v>
+        <v>569482</v>
       </c>
       <c r="R5" t="n">
-        <v>6949533</v>
+        <v>6949676</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1047,11 +1052,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>10 ex</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1078,32 +1078,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129035039</v>
+        <v>129035030</v>
       </c>
       <c r="B6" t="n">
-        <v>98651</v>
+        <v>97527</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>569394</v>
+        <v>569424</v>
       </c>
       <c r="R6" t="n">
-        <v>6949664</v>
+        <v>6949671</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1149,11 +1149,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1180,32 +1175,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129035030</v>
+        <v>129035039</v>
       </c>
       <c r="B7" t="n">
-        <v>97522</v>
+        <v>98656</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>569424</v>
+        <v>569394</v>
       </c>
       <c r="R7" t="n">
-        <v>6949671</v>
+        <v>6949664</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1251,6 +1246,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1277,7 +1277,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129035014</v>
+        <v>129035013</v>
       </c>
       <c r="B8" t="n">
         <v>57723</v>
@@ -1315,7 +1315,7 @@
         <v>569455</v>
       </c>
       <c r="R8" t="n">
-        <v>6949703</v>
+        <v>6949716</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1379,7 +1379,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129035013</v>
+        <v>129035014</v>
       </c>
       <c r="B9" t="n">
         <v>57723</v>
@@ -1417,7 +1417,7 @@
         <v>569455</v>
       </c>
       <c r="R9" t="n">
-        <v>6949716</v>
+        <v>6949703</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1484,7 +1484,7 @@
         <v>129035054</v>
       </c>
       <c r="B10" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>129034648</v>
       </c>
       <c r="B11" t="n">
-        <v>96770</v>
+        <v>96775</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1680,32 +1680,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129034594</v>
+        <v>129035055</v>
       </c>
       <c r="B12" t="n">
-        <v>91805</v>
+        <v>98656</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1715,10 +1715,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569203</v>
+        <v>569221</v>
       </c>
       <c r="R12" t="n">
-        <v>6949498</v>
+        <v>6949406</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>11 exemplar</t>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1782,32 +1782,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129034577</v>
+        <v>129035042</v>
       </c>
       <c r="B13" t="n">
-        <v>57723</v>
+        <v>98656</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1817,10 +1817,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569496</v>
+        <v>569200</v>
       </c>
       <c r="R13" t="n">
-        <v>6949627</v>
+        <v>6949533</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1857,7 +1857,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på tall</t>
+          <t>30 ex</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1884,10 +1884,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129034630</v>
+        <v>129034594</v>
       </c>
       <c r="B14" t="n">
-        <v>79034</v>
+        <v>91808</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1895,21 +1895,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1919,10 +1919,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569231</v>
+        <v>569203</v>
       </c>
       <c r="R14" t="n">
-        <v>6949559</v>
+        <v>6949498</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1955,6 +1955,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>11 exemplar</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1981,32 +1986,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129035055</v>
+        <v>129034630</v>
       </c>
       <c r="B15" t="n">
-        <v>98651</v>
+        <v>79034</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2016,10 +2021,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>569221</v>
+        <v>569231</v>
       </c>
       <c r="R15" t="n">
-        <v>6949406</v>
+        <v>6949559</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2052,11 +2057,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>25 ex</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2083,32 +2083,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129035042</v>
+        <v>129034577</v>
       </c>
       <c r="B16" t="n">
-        <v>98651</v>
+        <v>57723</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>569200</v>
+        <v>569496</v>
       </c>
       <c r="R16" t="n">
-        <v>6949533</v>
+        <v>6949627</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>30 ex</t>
+          <t>Äldre ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2185,32 +2185,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129035009</v>
+        <v>129035059</v>
       </c>
       <c r="B17" t="n">
-        <v>57723</v>
+        <v>92816</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2220,10 +2220,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>569314</v>
+        <v>569273</v>
       </c>
       <c r="R17" t="n">
-        <v>6949502</v>
+        <v>6949537</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2256,11 +2256,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2287,10 +2282,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129035019</v>
+        <v>129034629</v>
       </c>
       <c r="B18" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2298,21 +2293,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2322,10 +2317,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>569117</v>
+        <v>569247</v>
       </c>
       <c r="R18" t="n">
-        <v>6949581</v>
+        <v>6949558</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2358,11 +2353,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2389,7 +2379,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129034580</v>
+        <v>129035009</v>
       </c>
       <c r="B19" t="n">
         <v>57723</v>
@@ -2424,10 +2414,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>569396</v>
+        <v>569314</v>
       </c>
       <c r="R19" t="n">
-        <v>6949738</v>
+        <v>6949502</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2464,7 +2454,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Äldre ringhack på Tall</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2491,32 +2481,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129034620</v>
+        <v>129034580</v>
       </c>
       <c r="B20" t="n">
-        <v>98651</v>
+        <v>57723</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2526,10 +2516,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>569195</v>
+        <v>569396</v>
       </c>
       <c r="R20" t="n">
-        <v>6949410</v>
+        <v>6949738</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2566,7 +2556,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Blommande knärot 1 exemplar + 21 övriga exemplar blommar ej</t>
+          <t>Äldre ringhack på Tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2593,32 +2583,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129035059</v>
+        <v>129035019</v>
       </c>
       <c r="B21" t="n">
-        <v>92811</v>
+        <v>57723</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2628,10 +2618,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>569273</v>
+        <v>569117</v>
       </c>
       <c r="R21" t="n">
-        <v>6949537</v>
+        <v>6949581</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2664,6 +2654,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2690,32 +2685,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129034629</v>
+        <v>129034620</v>
       </c>
       <c r="B22" t="n">
-        <v>79034</v>
+        <v>98656</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2725,10 +2720,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>569247</v>
+        <v>569195</v>
       </c>
       <c r="R22" t="n">
-        <v>6949558</v>
+        <v>6949410</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2761,6 +2756,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Blommande knärot 1 exemplar + 21 övriga exemplar blommar ej</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2787,10 +2787,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129035025</v>
+        <v>129034592</v>
       </c>
       <c r="B23" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569388</v>
+        <v>569205</v>
       </c>
       <c r="R23" t="n">
-        <v>6949665</v>
+        <v>6949497</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2858,6 +2858,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>1 x</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2884,10 +2889,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129034647</v>
+        <v>129034591</v>
       </c>
       <c r="B24" t="n">
-        <v>88920</v>
+        <v>91808</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2895,21 +2900,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2919,10 +2924,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569247</v>
+        <v>569203</v>
       </c>
       <c r="R24" t="n">
-        <v>6949558</v>
+        <v>6949513</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2955,6 +2960,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>11 ex</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2981,32 +2991,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129034623</v>
+        <v>129034647</v>
       </c>
       <c r="B25" t="n">
-        <v>98651</v>
+        <v>88923</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>510</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3016,10 +3026,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569253</v>
+        <v>569247</v>
       </c>
       <c r="R25" t="n">
-        <v>6949425</v>
+        <v>6949558</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3052,11 +3062,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>74 stycken</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3083,10 +3088,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129034592</v>
+        <v>129035004</v>
       </c>
       <c r="B26" t="n">
-        <v>91805</v>
+        <v>91523</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3094,21 +3099,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3118,10 +3123,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569205</v>
+        <v>569152</v>
       </c>
       <c r="R26" t="n">
-        <v>6949497</v>
+        <v>6949557</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3154,11 +3159,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>1 x</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3185,10 +3185,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129034591</v>
+        <v>129035025</v>
       </c>
       <c r="B27" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3220,10 +3220,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>569203</v>
+        <v>569388</v>
       </c>
       <c r="R27" t="n">
-        <v>6949513</v>
+        <v>6949665</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3256,11 +3256,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>11 ex</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3287,10 +3282,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129035004</v>
+        <v>129035005</v>
       </c>
       <c r="B28" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3322,10 +3317,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>569152</v>
+        <v>569188</v>
       </c>
       <c r="R28" t="n">
-        <v>6949557</v>
+        <v>6949496</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3384,10 +3379,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129035005</v>
+        <v>129034625</v>
       </c>
       <c r="B29" t="n">
-        <v>91520</v>
+        <v>79034</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3395,21 +3390,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3419,10 +3414,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>569188</v>
+        <v>569479</v>
       </c>
       <c r="R29" t="n">
-        <v>6949496</v>
+        <v>6949657</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3481,32 +3476,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129034625</v>
+        <v>129034623</v>
       </c>
       <c r="B30" t="n">
-        <v>79034</v>
+        <v>98656</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3516,10 +3511,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>569479</v>
+        <v>569253</v>
       </c>
       <c r="R30" t="n">
-        <v>6949657</v>
+        <v>6949425</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3552,6 +3547,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>74 stycken</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3581,7 +3581,7 @@
         <v>129034637</v>
       </c>
       <c r="B31" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3675,10 +3675,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129035058</v>
+        <v>129035031</v>
       </c>
       <c r="B32" t="n">
-        <v>79034</v>
+        <v>80139</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3686,21 +3686,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3710,10 +3710,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>569388</v>
+        <v>569125</v>
       </c>
       <c r="R32" t="n">
-        <v>6949647</v>
+        <v>6949570</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3772,10 +3772,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129035031</v>
+        <v>129034578</v>
       </c>
       <c r="B33" t="n">
-        <v>80139</v>
+        <v>57723</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3783,21 +3783,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3807,10 +3807,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>569125</v>
+        <v>569420</v>
       </c>
       <c r="R33" t="n">
-        <v>6949570</v>
+        <v>6949723</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3843,6 +3843,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3869,10 +3874,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129034578</v>
+        <v>129035058</v>
       </c>
       <c r="B34" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3880,21 +3885,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3904,10 +3909,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>569420</v>
+        <v>569388</v>
       </c>
       <c r="R34" t="n">
-        <v>6949723</v>
+        <v>6949647</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3940,11 +3945,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3974,7 +3974,7 @@
         <v>129035051</v>
       </c>
       <c r="B35" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4073,32 +4073,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129034602</v>
+        <v>129035020</v>
       </c>
       <c r="B36" t="n">
-        <v>98651</v>
+        <v>57723</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4108,10 +4108,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>569301</v>
+        <v>569171</v>
       </c>
       <c r="R36" t="n">
-        <v>6949480</v>
+        <v>6949543</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>22 stycken</t>
+          <t>Äldre ringhack på granhögstubbe</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4175,32 +4175,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129035040</v>
+        <v>129035015</v>
       </c>
       <c r="B37" t="n">
-        <v>98651</v>
+        <v>57723</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4210,10 +4210,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>569386</v>
+        <v>569454</v>
       </c>
       <c r="R37" t="n">
-        <v>6949657</v>
+        <v>6949698</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4250,7 +4250,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>9 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4277,10 +4277,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129035045</v>
+        <v>129034602</v>
       </c>
       <c r="B38" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4312,10 +4312,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>569130</v>
+        <v>569301</v>
       </c>
       <c r="R38" t="n">
-        <v>6949603</v>
+        <v>6949480</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>14 ex</t>
+          <t>22 stycken</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4379,32 +4379,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129034634</v>
+        <v>129035040</v>
       </c>
       <c r="B39" t="n">
-        <v>79034</v>
+        <v>98656</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4414,10 +4414,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>569200</v>
+        <v>569386</v>
       </c>
       <c r="R39" t="n">
-        <v>6949411</v>
+        <v>6949657</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4450,6 +4450,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>9 ex</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4476,32 +4481,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129035015</v>
+        <v>129035045</v>
       </c>
       <c r="B40" t="n">
-        <v>57723</v>
+        <v>98656</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4511,10 +4516,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>569454</v>
+        <v>569130</v>
       </c>
       <c r="R40" t="n">
-        <v>6949698</v>
+        <v>6949603</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4551,7 +4556,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>14 ex</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4578,10 +4583,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129035020</v>
+        <v>129034634</v>
       </c>
       <c r="B41" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4589,21 +4594,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4613,10 +4618,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>569171</v>
+        <v>569200</v>
       </c>
       <c r="R41" t="n">
-        <v>6949543</v>
+        <v>6949411</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4649,11 +4654,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på granhögstubbe</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4683,7 +4683,7 @@
         <v>129034643</v>
       </c>
       <c r="B42" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4785,7 +4785,7 @@
         <v>129035063</v>
       </c>
       <c r="B43" t="n">
-        <v>96770</v>
+        <v>96775</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4879,32 +4879,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129034607</v>
+        <v>129034575</v>
       </c>
       <c r="B44" t="n">
-        <v>98651</v>
+        <v>57723</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4914,10 +4914,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>569317</v>
+        <v>569448</v>
       </c>
       <c r="R44" t="n">
-        <v>6949549</v>
+        <v>6949625</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>31 stycken</t>
+          <t>Färska ringhack på Tall av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4981,32 +4981,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129035041</v>
+        <v>129035011</v>
       </c>
       <c r="B45" t="n">
-        <v>98651</v>
+        <v>57723</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5016,10 +5016,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>569262</v>
+        <v>569442</v>
       </c>
       <c r="R45" t="n">
-        <v>6949524</v>
+        <v>6949783</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>5 ex</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5083,32 +5083,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129035011</v>
+        <v>129034607</v>
       </c>
       <c r="B46" t="n">
-        <v>57723</v>
+        <v>98656</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5118,10 +5118,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>569442</v>
+        <v>569317</v>
       </c>
       <c r="R46" t="n">
-        <v>6949783</v>
+        <v>6949549</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>31 stycken</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5185,32 +5185,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129034575</v>
+        <v>129035041</v>
       </c>
       <c r="B47" t="n">
-        <v>57723</v>
+        <v>98656</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5220,10 +5220,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>569448</v>
+        <v>569262</v>
       </c>
       <c r="R47" t="n">
-        <v>6949625</v>
+        <v>6949524</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5260,7 +5260,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Färska ringhack på Tall av tretåig hackspett</t>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5287,10 +5287,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129034632</v>
+        <v>129035022</v>
       </c>
       <c r="B48" t="n">
-        <v>79034</v>
+        <v>91808</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5298,21 +5298,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5322,10 +5322,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>569237</v>
+        <v>569423</v>
       </c>
       <c r="R48" t="n">
-        <v>6949442</v>
+        <v>6949656</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5384,32 +5384,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129035062</v>
+        <v>129034597</v>
       </c>
       <c r="B49" t="n">
-        <v>96770</v>
+        <v>91808</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2869</v>
+        <v>658</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5419,10 +5419,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>569478</v>
+        <v>569221</v>
       </c>
       <c r="R49" t="n">
-        <v>6949666</v>
+        <v>6949499</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5455,6 +5455,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>8 exemplar</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5481,10 +5486,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129035022</v>
+        <v>129035002</v>
       </c>
       <c r="B50" t="n">
-        <v>91805</v>
+        <v>91523</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5492,21 +5497,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5516,10 +5521,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>569423</v>
+        <v>569405</v>
       </c>
       <c r="R50" t="n">
-        <v>6949656</v>
+        <v>6949685</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5578,10 +5583,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129034597</v>
+        <v>129035016</v>
       </c>
       <c r="B51" t="n">
-        <v>91805</v>
+        <v>57723</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5589,21 +5594,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5613,10 +5618,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>569221</v>
+        <v>569435</v>
       </c>
       <c r="R51" t="n">
-        <v>6949499</v>
+        <v>6949665</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5653,7 +5658,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>8 exemplar</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5680,32 +5685,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129035002</v>
+        <v>129034616</v>
       </c>
       <c r="B52" t="n">
-        <v>91520</v>
+        <v>98656</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5715,10 +5720,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>569405</v>
+        <v>569223</v>
       </c>
       <c r="R52" t="n">
-        <v>6949685</v>
+        <v>6949465</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5751,6 +5756,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>10 stycken</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5777,32 +5787,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129035016</v>
+        <v>129035062</v>
       </c>
       <c r="B53" t="n">
-        <v>57723</v>
+        <v>96775</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5812,10 +5822,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>569435</v>
+        <v>569478</v>
       </c>
       <c r="R53" t="n">
-        <v>6949665</v>
+        <v>6949666</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5848,11 +5858,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5879,32 +5884,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129034616</v>
+        <v>129034632</v>
       </c>
       <c r="B54" t="n">
-        <v>98651</v>
+        <v>79034</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5914,10 +5919,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>569223</v>
+        <v>569237</v>
       </c>
       <c r="R54" t="n">
-        <v>6949465</v>
+        <v>6949442</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5950,11 +5955,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>10 stycken</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5981,10 +5981,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129034581</v>
+        <v>129034600</v>
       </c>
       <c r="B55" t="n">
-        <v>57883</v>
+        <v>80139</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5992,21 +5992,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6016,10 +6016,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>569223</v>
+        <v>569481</v>
       </c>
       <c r="R55" t="n">
-        <v>6949401</v>
+        <v>6949674</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Sågs och gjorde övriga läten</t>
+          <t>Apothecier antal 1</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6083,32 +6083,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129035028</v>
+        <v>129034610</v>
       </c>
       <c r="B56" t="n">
-        <v>91805</v>
+        <v>98656</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6118,10 +6118,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>569192</v>
+        <v>569282</v>
       </c>
       <c r="R56" t="n">
-        <v>6949509</v>
+        <v>6949567</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6154,6 +6154,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ca 100 stycken</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6180,32 +6185,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129035008</v>
+        <v>129034614</v>
       </c>
       <c r="B57" t="n">
-        <v>91520</v>
+        <v>98656</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6215,10 +6220,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>569216</v>
+        <v>569237</v>
       </c>
       <c r="R57" t="n">
-        <v>6949430</v>
+        <v>6949556</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6251,6 +6256,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>5 stycken</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6277,10 +6287,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129034600</v>
+        <v>129034581</v>
       </c>
       <c r="B58" t="n">
-        <v>80139</v>
+        <v>57883</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6288,21 +6298,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6312,10 +6322,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>569481</v>
+        <v>569223</v>
       </c>
       <c r="R58" t="n">
-        <v>6949674</v>
+        <v>6949401</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6352,7 +6362,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Apothecier antal 1</t>
+          <t>Sågs och gjorde övriga läten</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6379,32 +6389,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129034610</v>
+        <v>129035028</v>
       </c>
       <c r="B59" t="n">
-        <v>98651</v>
+        <v>91808</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6414,10 +6424,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>569282</v>
+        <v>569192</v>
       </c>
       <c r="R59" t="n">
-        <v>6949567</v>
+        <v>6949509</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6450,11 +6460,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ca 100 stycken</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6481,32 +6486,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129034614</v>
+        <v>129035008</v>
       </c>
       <c r="B60" t="n">
-        <v>98651</v>
+        <v>91523</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6516,10 +6521,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>569237</v>
+        <v>569216</v>
       </c>
       <c r="R60" t="n">
-        <v>6949556</v>
+        <v>6949430</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6552,11 +6557,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>5 stycken</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6586,7 +6586,7 @@
         <v>129034586</v>
       </c>
       <c r="B61" t="n">
-        <v>91975</v>
+        <v>91978</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6683,7 +6683,7 @@
         <v>129035024</v>
       </c>
       <c r="B62" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6777,32 +6777,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129035003</v>
+        <v>129034624</v>
       </c>
       <c r="B63" t="n">
-        <v>91520</v>
+        <v>105719</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6812,10 +6812,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>569164</v>
+        <v>569234</v>
       </c>
       <c r="R63" t="n">
-        <v>6949559</v>
+        <v>6949440</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6848,6 +6848,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>9 exemplar</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6874,10 +6879,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129034587</v>
+        <v>129035003</v>
       </c>
       <c r="B64" t="n">
-        <v>91805</v>
+        <v>91523</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6885,21 +6890,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6909,10 +6914,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>569463</v>
+        <v>569164</v>
       </c>
       <c r="R64" t="n">
-        <v>6949711</v>
+        <v>6949559</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6971,10 +6976,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129035021</v>
+        <v>129034587</v>
       </c>
       <c r="B65" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7006,10 +7011,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>569446</v>
+        <v>569463</v>
       </c>
       <c r="R65" t="n">
-        <v>6949629</v>
+        <v>6949711</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7068,10 +7073,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129034574</v>
+        <v>129035021</v>
       </c>
       <c r="B66" t="n">
-        <v>91520</v>
+        <v>91808</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7079,21 +7084,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7103,10 +7108,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>569461</v>
+        <v>569446</v>
       </c>
       <c r="R66" t="n">
-        <v>6949706</v>
+        <v>6949629</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7165,49 +7170,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129027791</v>
+        <v>129034574</v>
       </c>
       <c r="B67" t="n">
-        <v>98651</v>
+        <v>91523</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Sandsjömyran, Mpd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>569308</v>
+        <v>569461</v>
       </c>
       <c r="R67" t="n">
-        <v>6949546</v>
+        <v>6949706</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7266,45 +7267,49 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129034624</v>
+        <v>129027791</v>
       </c>
       <c r="B68" t="n">
-        <v>105714</v>
+        <v>98656</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Sandsjömyran, Mpd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>569234</v>
+        <v>569308</v>
       </c>
       <c r="R68" t="n">
-        <v>6949440</v>
+        <v>6949546</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7337,11 +7342,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>9 exemplar</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7371,7 +7371,7 @@
         <v>129035035</v>
       </c>
       <c r="B69" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7470,10 +7470,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129034639</v>
+        <v>129035060</v>
       </c>
       <c r="B70" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7505,10 +7505,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>569398</v>
+        <v>569208</v>
       </c>
       <c r="R70" t="n">
-        <v>6949741</v>
+        <v>6949415</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7545,7 +7545,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>6 äldre exemplar och 1 färsk fruktkropp</t>
+          <t>20 ex minst</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7572,10 +7572,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129035060</v>
+        <v>129034639</v>
       </c>
       <c r="B71" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7607,10 +7607,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>569208</v>
+        <v>569398</v>
       </c>
       <c r="R71" t="n">
-        <v>6949415</v>
+        <v>6949741</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7647,7 +7647,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>20 ex minst</t>
+          <t>6 äldre exemplar och 1 färsk fruktkropp</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7881,7 +7881,7 @@
         <v>129035037</v>
       </c>
       <c r="B74" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7980,32 +7980,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129034645</v>
+        <v>129026691</v>
       </c>
       <c r="B75" t="n">
-        <v>92811</v>
+        <v>91808</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8015,10 +8015,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>569196</v>
+        <v>569195</v>
       </c>
       <c r="R75" t="n">
-        <v>6949411</v>
+        <v>6949487</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8051,11 +8051,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>4 färska exemplar 3 äldre exemplar</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8082,10 +8077,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129034642</v>
+        <v>129034645</v>
       </c>
       <c r="B76" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8117,10 +8112,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>569283</v>
+        <v>569196</v>
       </c>
       <c r="R76" t="n">
-        <v>6949655</v>
+        <v>6949411</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8157,7 +8152,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>7 äldre exemplar</t>
+          <t>4 färska exemplar 3 äldre exemplar</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8184,10 +8179,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129034598</v>
+        <v>129034642</v>
       </c>
       <c r="B77" t="n">
-        <v>97522</v>
+        <v>92816</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8195,21 +8190,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8219,10 +8214,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>569460</v>
+        <v>569283</v>
       </c>
       <c r="R77" t="n">
-        <v>6949629</v>
+        <v>6949655</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8255,6 +8250,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>7 äldre exemplar</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8281,32 +8281,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129026691</v>
+        <v>129034650</v>
       </c>
       <c r="B78" t="n">
-        <v>91805</v>
+        <v>98656</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8316,10 +8316,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>569195</v>
+        <v>569303</v>
       </c>
       <c r="R78" t="n">
-        <v>6949487</v>
+        <v>6949537</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8352,6 +8352,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>30 stycken ( finns eventuellt mer )</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8378,10 +8383,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129034650</v>
+        <v>129034605</v>
       </c>
       <c r="B79" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8413,10 +8418,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>569303</v>
+        <v>569305</v>
       </c>
       <c r="R79" t="n">
-        <v>6949537</v>
+        <v>6949538</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8453,7 +8458,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>30 stycken ( finns eventuellt mer )</t>
+          <t>21 knärot</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8480,32 +8485,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129034605</v>
+        <v>129034598</v>
       </c>
       <c r="B80" t="n">
-        <v>98651</v>
+        <v>97527</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8515,10 +8520,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>569305</v>
+        <v>569460</v>
       </c>
       <c r="R80" t="n">
-        <v>6949538</v>
+        <v>6949629</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8551,11 +8556,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>21 knärot</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8582,10 +8582,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129034640</v>
+        <v>129035061</v>
       </c>
       <c r="B81" t="n">
-        <v>92811</v>
+        <v>96775</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8593,21 +8593,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4364</v>
+        <v>2869</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8617,10 +8617,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>569213</v>
+        <v>569333</v>
       </c>
       <c r="R81" t="n">
-        <v>6949414</v>
+        <v>6949607</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8653,11 +8653,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>16 exemplar</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8684,10 +8679,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129035061</v>
+        <v>129034640</v>
       </c>
       <c r="B82" t="n">
-        <v>96770</v>
+        <v>92816</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8695,21 +8690,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2869</v>
+        <v>4364</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8719,10 +8714,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>569333</v>
+        <v>569213</v>
       </c>
       <c r="R82" t="n">
-        <v>6949607</v>
+        <v>6949414</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8755,6 +8750,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>16 exemplar</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8781,32 +8781,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129035007</v>
+        <v>129035001</v>
       </c>
       <c r="B83" t="n">
-        <v>91520</v>
+        <v>91488</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8816,10 +8816,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>569225</v>
+        <v>569232</v>
       </c>
       <c r="R83" t="n">
-        <v>6949424</v>
+        <v>6949444</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8878,10 +8878,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129035057</v>
+        <v>129035012</v>
       </c>
       <c r="B84" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8889,21 +8889,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8913,10 +8913,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>569464</v>
+        <v>569435</v>
       </c>
       <c r="R84" t="n">
-        <v>6949648</v>
+        <v>6949783</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8949,6 +8949,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8975,32 +8980,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129035001</v>
+        <v>129035007</v>
       </c>
       <c r="B85" t="n">
-        <v>91485</v>
+        <v>91523</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9010,10 +9015,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>569232</v>
+        <v>569225</v>
       </c>
       <c r="R85" t="n">
-        <v>6949444</v>
+        <v>6949424</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9072,10 +9077,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129035012</v>
+        <v>129035057</v>
       </c>
       <c r="B86" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9083,21 +9088,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9107,10 +9112,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>569435</v>
+        <v>569464</v>
       </c>
       <c r="R86" t="n">
-        <v>6949783</v>
+        <v>6949648</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9143,11 +9148,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9177,7 +9177,7 @@
         <v>129035047</v>
       </c>
       <c r="B87" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         <v>129034604</v>
       </c>
       <c r="B88" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9381,7 +9381,7 @@
         <v>129034618</v>
       </c>
       <c r="B89" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9483,7 +9483,7 @@
         <v>129035023</v>
       </c>
       <c r="B90" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         <v>129035027</v>
       </c>
       <c r="B91" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         <v>129034589</v>
       </c>
       <c r="B92" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9774,7 +9774,7 @@
         <v>129035029</v>
       </c>
       <c r="B93" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9871,7 +9871,7 @@
         <v>129035038</v>
       </c>
       <c r="B94" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9973,7 +9973,7 @@
         <v>129035050</v>
       </c>
       <c r="B95" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10075,7 +10075,7 @@
         <v>129034621</v>
       </c>
       <c r="B96" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10271,7 +10271,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129035010</v>
+        <v>129035017</v>
       </c>
       <c r="B98" t="n">
         <v>57723</v>
@@ -10306,10 +10306,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>569465</v>
+        <v>569192</v>
       </c>
       <c r="R98" t="n">
-        <v>6949606</v>
+        <v>6949518</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10346,7 +10346,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10373,7 +10373,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129035017</v>
+        <v>129035010</v>
       </c>
       <c r="B99" t="n">
         <v>57723</v>
@@ -10408,10 +10408,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>569192</v>
+        <v>569465</v>
       </c>
       <c r="R99" t="n">
-        <v>6949518</v>
+        <v>6949606</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10448,7 +10448,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10475,32 +10475,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129034609</v>
+        <v>129035056</v>
       </c>
       <c r="B100" t="n">
-        <v>98651</v>
+        <v>105719</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10510,10 +10510,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>569458</v>
+        <v>569201</v>
       </c>
       <c r="R100" t="n">
-        <v>6949777</v>
+        <v>6949530</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10546,11 +10546,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>48 stycken</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10577,10 +10572,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129035036</v>
+        <v>129034609</v>
       </c>
       <c r="B101" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10612,10 +10607,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>569330</v>
+        <v>569458</v>
       </c>
       <c r="R101" t="n">
-        <v>6949564</v>
+        <v>6949777</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10652,7 +10647,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>8 ex</t>
+          <t>48 stycken</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10679,10 +10674,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129035052</v>
+        <v>129035036</v>
       </c>
       <c r="B102" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10714,10 +10709,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>569405</v>
+        <v>569330</v>
       </c>
       <c r="R102" t="n">
-        <v>6949641</v>
+        <v>6949564</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10754,7 +10749,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>70 ex</t>
+          <t>8 ex</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10781,32 +10776,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129035056</v>
+        <v>129035052</v>
       </c>
       <c r="B103" t="n">
-        <v>105714</v>
+        <v>98656</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10816,10 +10811,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>569201</v>
+        <v>569405</v>
       </c>
       <c r="R103" t="n">
-        <v>6949530</v>
+        <v>6949641</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10852,6 +10847,11 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>70 ex</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10881,7 +10881,7 @@
         <v>129035026</v>
       </c>
       <c r="B104" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>129035006</v>
       </c>
       <c r="B105" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11075,7 +11075,7 @@
         <v>129027886</v>
       </c>
       <c r="B106" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
         <v>129035048</v>
       </c>
       <c r="B107" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11274,7 +11274,7 @@
         <v>129035053</v>
       </c>
       <c r="B108" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>129035049</v>
       </c>
       <c r="B109" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11478,7 +11478,7 @@
         <v>129035044</v>
       </c>
       <c r="B110" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
         <v>129035033</v>
       </c>
       <c r="B111" t="n">
-        <v>91721</v>
+        <v>91724</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11677,7 +11677,7 @@
         <v>129035032</v>
       </c>
       <c r="B112" t="n">
-        <v>91721</v>
+        <v>91724</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>

--- a/artfynd/A 45833-2025 artfynd.xlsx
+++ b/artfynd/A 45833-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129034612</v>
       </c>
       <c r="B2" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129035046</v>
       </c>
       <c r="B3" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129035043</v>
       </c>
       <c r="B4" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>129034627</v>
       </c>
       <c r="B5" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,32 +1078,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129035030</v>
+        <v>129035039</v>
       </c>
       <c r="B6" t="n">
-        <v>97527</v>
+        <v>98659</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>569424</v>
+        <v>569394</v>
       </c>
       <c r="R6" t="n">
-        <v>6949671</v>
+        <v>6949664</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1149,6 +1149,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1175,32 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129035039</v>
+        <v>129035030</v>
       </c>
       <c r="B7" t="n">
-        <v>98656</v>
+        <v>97530</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>569394</v>
+        <v>569424</v>
       </c>
       <c r="R7" t="n">
-        <v>6949664</v>
+        <v>6949671</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1246,11 +1251,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1277,32 +1277,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129035013</v>
+        <v>129035054</v>
       </c>
       <c r="B8" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>569455</v>
+        <v>569126</v>
       </c>
       <c r="R8" t="n">
-        <v>6949716</v>
+        <v>6949570</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>13 ex</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1379,7 +1379,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129035014</v>
+        <v>129035013</v>
       </c>
       <c r="B9" t="n">
         <v>57723</v>
@@ -1417,7 +1417,7 @@
         <v>569455</v>
       </c>
       <c r="R9" t="n">
-        <v>6949703</v>
+        <v>6949716</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1481,32 +1481,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129035054</v>
+        <v>129035014</v>
       </c>
       <c r="B10" t="n">
-        <v>98656</v>
+        <v>57723</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>569126</v>
+        <v>569455</v>
       </c>
       <c r="R10" t="n">
-        <v>6949570</v>
+        <v>6949703</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>13 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1586,7 +1586,7 @@
         <v>129034648</v>
       </c>
       <c r="B11" t="n">
-        <v>96775</v>
+        <v>96778</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1680,32 +1680,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129035055</v>
+        <v>129034630</v>
       </c>
       <c r="B12" t="n">
-        <v>98656</v>
+        <v>79035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1715,10 +1715,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569221</v>
+        <v>569231</v>
       </c>
       <c r="R12" t="n">
-        <v>6949406</v>
+        <v>6949559</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1751,11 +1751,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>25 ex</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1782,32 +1777,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129035042</v>
+        <v>129034577</v>
       </c>
       <c r="B13" t="n">
-        <v>98656</v>
+        <v>57723</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1817,10 +1812,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569200</v>
+        <v>569496</v>
       </c>
       <c r="R13" t="n">
-        <v>6949533</v>
+        <v>6949627</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1857,7 +1852,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>30 ex</t>
+          <t>Äldre ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1884,32 +1879,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129034594</v>
+        <v>129035055</v>
       </c>
       <c r="B14" t="n">
-        <v>91808</v>
+        <v>98659</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1919,10 +1914,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569203</v>
+        <v>569221</v>
       </c>
       <c r="R14" t="n">
-        <v>6949498</v>
+        <v>6949406</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1959,7 +1954,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>11 exemplar</t>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1986,32 +1981,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129034630</v>
+        <v>129035042</v>
       </c>
       <c r="B15" t="n">
-        <v>79034</v>
+        <v>98659</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2021,10 +2016,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>569231</v>
+        <v>569200</v>
       </c>
       <c r="R15" t="n">
-        <v>6949559</v>
+        <v>6949533</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2057,6 +2052,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>30 ex</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2083,10 +2083,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129034577</v>
+        <v>129034594</v>
       </c>
       <c r="B16" t="n">
-        <v>57723</v>
+        <v>91811</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2094,21 +2094,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>569496</v>
+        <v>569203</v>
       </c>
       <c r="R16" t="n">
-        <v>6949627</v>
+        <v>6949498</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på tall</t>
+          <t>11 exemplar</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2185,32 +2185,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129035059</v>
+        <v>129034629</v>
       </c>
       <c r="B17" t="n">
-        <v>92816</v>
+        <v>79035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2220,10 +2220,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>569273</v>
+        <v>569247</v>
       </c>
       <c r="R17" t="n">
-        <v>6949537</v>
+        <v>6949558</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2282,32 +2282,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129034629</v>
+        <v>129034620</v>
       </c>
       <c r="B18" t="n">
-        <v>79034</v>
+        <v>98659</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2317,10 +2317,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>569247</v>
+        <v>569195</v>
       </c>
       <c r="R18" t="n">
-        <v>6949558</v>
+        <v>6949410</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2353,6 +2353,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Blommande knärot 1 exemplar + 21 övriga exemplar blommar ej</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2379,32 +2384,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129035009</v>
+        <v>129035059</v>
       </c>
       <c r="B19" t="n">
-        <v>57723</v>
+        <v>92819</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2414,10 +2419,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>569314</v>
+        <v>569273</v>
       </c>
       <c r="R19" t="n">
-        <v>6949502</v>
+        <v>6949537</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2450,11 +2455,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2481,7 +2481,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129034580</v>
+        <v>129035009</v>
       </c>
       <c r="B20" t="n">
         <v>57723</v>
@@ -2516,10 +2516,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>569396</v>
+        <v>569314</v>
       </c>
       <c r="R20" t="n">
-        <v>6949738</v>
+        <v>6949502</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Äldre ringhack på Tall</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2583,7 +2583,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129035019</v>
+        <v>129034580</v>
       </c>
       <c r="B21" t="n">
         <v>57723</v>
@@ -2618,10 +2618,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>569117</v>
+        <v>569396</v>
       </c>
       <c r="R21" t="n">
-        <v>6949581</v>
+        <v>6949738</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Äldre ringhack på Tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2685,32 +2685,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129034620</v>
+        <v>129035019</v>
       </c>
       <c r="B22" t="n">
-        <v>98656</v>
+        <v>57723</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2720,10 +2720,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>569195</v>
+        <v>569117</v>
       </c>
       <c r="R22" t="n">
-        <v>6949410</v>
+        <v>6949581</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2760,7 +2760,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Blommande knärot 1 exemplar + 21 övriga exemplar blommar ej</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2787,10 +2787,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129034592</v>
+        <v>129034625</v>
       </c>
       <c r="B23" t="n">
-        <v>91808</v>
+        <v>79035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2798,21 +2798,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569205</v>
+        <v>569479</v>
       </c>
       <c r="R23" t="n">
-        <v>6949497</v>
+        <v>6949657</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2858,11 +2858,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>1 x</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2889,10 +2884,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129034591</v>
+        <v>129034592</v>
       </c>
       <c r="B24" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2924,10 +2919,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569203</v>
+        <v>569205</v>
       </c>
       <c r="R24" t="n">
-        <v>6949513</v>
+        <v>6949497</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2964,7 +2959,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>11 ex</t>
+          <t>1 x</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2991,10 +2986,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129034647</v>
+        <v>129034591</v>
       </c>
       <c r="B25" t="n">
-        <v>88923</v>
+        <v>91811</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3002,21 +2997,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3026,10 +3021,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569247</v>
+        <v>569203</v>
       </c>
       <c r="R25" t="n">
-        <v>6949558</v>
+        <v>6949513</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3062,6 +3057,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>11 ex</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3088,10 +3088,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129035004</v>
+        <v>129034647</v>
       </c>
       <c r="B26" t="n">
-        <v>91523</v>
+        <v>88926</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3099,21 +3099,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3123,10 +3123,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569152</v>
+        <v>569247</v>
       </c>
       <c r="R26" t="n">
-        <v>6949557</v>
+        <v>6949558</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3188,7 +3188,7 @@
         <v>129035025</v>
       </c>
       <c r="B27" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3282,10 +3282,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129035005</v>
+        <v>129035004</v>
       </c>
       <c r="B28" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3317,10 +3317,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>569188</v>
+        <v>569152</v>
       </c>
       <c r="R28" t="n">
-        <v>6949496</v>
+        <v>6949557</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3379,10 +3379,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129034625</v>
+        <v>129035005</v>
       </c>
       <c r="B29" t="n">
-        <v>79034</v>
+        <v>91526</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3390,21 +3390,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3414,10 +3414,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>569479</v>
+        <v>569188</v>
       </c>
       <c r="R29" t="n">
-        <v>6949657</v>
+        <v>6949496</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3479,7 +3479,7 @@
         <v>129034623</v>
       </c>
       <c r="B30" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>129034637</v>
       </c>
       <c r="B31" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3675,10 +3675,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129035031</v>
+        <v>129035058</v>
       </c>
       <c r="B32" t="n">
-        <v>80139</v>
+        <v>79035</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3686,21 +3686,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3710,10 +3710,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>569125</v>
+        <v>569388</v>
       </c>
       <c r="R32" t="n">
-        <v>6949570</v>
+        <v>6949647</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3772,10 +3772,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129034578</v>
+        <v>129035031</v>
       </c>
       <c r="B33" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3783,21 +3783,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3807,10 +3807,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>569420</v>
+        <v>569125</v>
       </c>
       <c r="R33" t="n">
-        <v>6949723</v>
+        <v>6949570</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3843,11 +3843,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3874,10 +3869,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129035058</v>
+        <v>129034578</v>
       </c>
       <c r="B34" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3885,21 +3880,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3909,10 +3904,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>569388</v>
+        <v>569420</v>
       </c>
       <c r="R34" t="n">
-        <v>6949647</v>
+        <v>6949723</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3945,6 +3940,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3974,7 +3974,7 @@
         <v>129035051</v>
       </c>
       <c r="B35" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4277,32 +4277,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129034602</v>
+        <v>129034634</v>
       </c>
       <c r="B38" t="n">
-        <v>98656</v>
+        <v>79035</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4312,10 +4312,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>569301</v>
+        <v>569200</v>
       </c>
       <c r="R38" t="n">
-        <v>6949480</v>
+        <v>6949411</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4348,11 +4348,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>22 stycken</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4379,10 +4374,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129035040</v>
+        <v>129034602</v>
       </c>
       <c r="B39" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4414,10 +4409,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>569386</v>
+        <v>569301</v>
       </c>
       <c r="R39" t="n">
-        <v>6949657</v>
+        <v>6949480</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4454,7 +4449,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>9 ex</t>
+          <t>22 stycken</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4481,10 +4476,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129035045</v>
+        <v>129035040</v>
       </c>
       <c r="B40" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4516,10 +4511,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>569130</v>
+        <v>569386</v>
       </c>
       <c r="R40" t="n">
-        <v>6949603</v>
+        <v>6949657</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4556,7 +4551,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>14 ex</t>
+          <t>9 ex</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4583,32 +4578,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129034634</v>
+        <v>129035045</v>
       </c>
       <c r="B41" t="n">
-        <v>79034</v>
+        <v>98659</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4618,10 +4613,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>569200</v>
+        <v>569130</v>
       </c>
       <c r="R41" t="n">
-        <v>6949411</v>
+        <v>6949603</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4654,6 +4649,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>14 ex</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4680,10 +4680,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129034643</v>
+        <v>129035063</v>
       </c>
       <c r="B42" t="n">
-        <v>92816</v>
+        <v>96778</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4691,21 +4691,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>2869</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4715,10 +4715,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>569254</v>
+        <v>569455</v>
       </c>
       <c r="R42" t="n">
-        <v>6949431</v>
+        <v>6949758</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4751,11 +4751,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>1 färskt exemplar</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4782,10 +4777,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129035063</v>
+        <v>129034643</v>
       </c>
       <c r="B43" t="n">
-        <v>96775</v>
+        <v>92819</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4793,21 +4788,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2869</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4817,10 +4812,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>569455</v>
+        <v>569254</v>
       </c>
       <c r="R43" t="n">
-        <v>6949758</v>
+        <v>6949431</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4853,6 +4848,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>1 färskt exemplar</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5086,7 +5086,7 @@
         <v>129034607</v>
       </c>
       <c r="B46" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
         <v>129035041</v>
       </c>
       <c r="B47" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5287,10 +5287,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129035022</v>
+        <v>129035002</v>
       </c>
       <c r="B48" t="n">
-        <v>91808</v>
+        <v>91526</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5298,21 +5298,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5322,10 +5322,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>569423</v>
+        <v>569405</v>
       </c>
       <c r="R48" t="n">
-        <v>6949656</v>
+        <v>6949685</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5387,7 +5387,7 @@
         <v>129034597</v>
       </c>
       <c r="B49" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5486,10 +5486,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129035002</v>
+        <v>129034632</v>
       </c>
       <c r="B50" t="n">
-        <v>91523</v>
+        <v>79035</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5497,21 +5497,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5521,10 +5521,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>569405</v>
+        <v>569237</v>
       </c>
       <c r="R50" t="n">
-        <v>6949685</v>
+        <v>6949442</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5583,32 +5583,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129035016</v>
+        <v>129035062</v>
       </c>
       <c r="B51" t="n">
-        <v>57723</v>
+        <v>96778</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5618,10 +5618,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>569435</v>
+        <v>569478</v>
       </c>
       <c r="R51" t="n">
-        <v>6949665</v>
+        <v>6949666</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5654,11 +5654,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5685,32 +5680,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129034616</v>
+        <v>129035022</v>
       </c>
       <c r="B52" t="n">
-        <v>98656</v>
+        <v>91811</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5720,10 +5715,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>569223</v>
+        <v>569423</v>
       </c>
       <c r="R52" t="n">
-        <v>6949465</v>
+        <v>6949656</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5756,11 +5751,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>10 stycken</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5787,32 +5777,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129035062</v>
+        <v>129035016</v>
       </c>
       <c r="B53" t="n">
-        <v>96775</v>
+        <v>57723</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5822,10 +5812,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>569478</v>
+        <v>569435</v>
       </c>
       <c r="R53" t="n">
-        <v>6949666</v>
+        <v>6949665</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5858,6 +5848,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5884,32 +5879,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129034632</v>
+        <v>129034616</v>
       </c>
       <c r="B54" t="n">
-        <v>79034</v>
+        <v>98659</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5919,10 +5914,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>569237</v>
+        <v>569223</v>
       </c>
       <c r="R54" t="n">
-        <v>6949442</v>
+        <v>6949465</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5955,6 +5950,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>10 stycken</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5984,7 +5984,7 @@
         <v>129034600</v>
       </c>
       <c r="B55" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6083,32 +6083,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129034610</v>
+        <v>129035008</v>
       </c>
       <c r="B56" t="n">
-        <v>98656</v>
+        <v>91526</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6118,10 +6118,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>569282</v>
+        <v>569216</v>
       </c>
       <c r="R56" t="n">
-        <v>6949567</v>
+        <v>6949430</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6154,11 +6154,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ca 100 stycken</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6185,32 +6180,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129034614</v>
+        <v>129034581</v>
       </c>
       <c r="B57" t="n">
-        <v>98656</v>
+        <v>57883</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6220,10 +6215,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>569237</v>
+        <v>569223</v>
       </c>
       <c r="R57" t="n">
-        <v>6949556</v>
+        <v>6949401</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6260,7 +6255,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>5 stycken</t>
+          <t>Sågs och gjorde övriga läten</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6287,10 +6282,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129034581</v>
+        <v>129035028</v>
       </c>
       <c r="B58" t="n">
-        <v>57883</v>
+        <v>91811</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6298,21 +6293,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6322,10 +6317,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>569223</v>
+        <v>569192</v>
       </c>
       <c r="R58" t="n">
-        <v>6949401</v>
+        <v>6949509</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6358,11 +6353,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Sågs och gjorde övriga läten</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6389,32 +6379,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129035028</v>
+        <v>129034610</v>
       </c>
       <c r="B59" t="n">
-        <v>91808</v>
+        <v>98659</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6424,10 +6414,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>569192</v>
+        <v>569282</v>
       </c>
       <c r="R59" t="n">
-        <v>6949509</v>
+        <v>6949567</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6460,6 +6450,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ca 100 stycken</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6486,32 +6481,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129035008</v>
+        <v>129034614</v>
       </c>
       <c r="B60" t="n">
-        <v>91523</v>
+        <v>98659</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6521,10 +6516,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>569216</v>
+        <v>569237</v>
       </c>
       <c r="R60" t="n">
-        <v>6949430</v>
+        <v>6949556</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6557,6 +6552,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>5 stycken</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6586,7 +6586,7 @@
         <v>129034586</v>
       </c>
       <c r="B61" t="n">
-        <v>91978</v>
+        <v>91981</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6683,7 +6683,7 @@
         <v>129035024</v>
       </c>
       <c r="B62" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6777,32 +6777,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129034624</v>
+        <v>129034587</v>
       </c>
       <c r="B63" t="n">
-        <v>105719</v>
+        <v>91811</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221144</v>
+        <v>658</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6812,10 +6812,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>569234</v>
+        <v>569463</v>
       </c>
       <c r="R63" t="n">
-        <v>6949440</v>
+        <v>6949711</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6848,11 +6848,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>9 exemplar</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6879,10 +6874,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129035003</v>
+        <v>129035021</v>
       </c>
       <c r="B64" t="n">
-        <v>91523</v>
+        <v>91811</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6890,21 +6885,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6914,10 +6909,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>569164</v>
+        <v>569446</v>
       </c>
       <c r="R64" t="n">
-        <v>6949559</v>
+        <v>6949629</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6976,10 +6971,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129034587</v>
+        <v>129035003</v>
       </c>
       <c r="B65" t="n">
-        <v>91808</v>
+        <v>91526</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6987,21 +6982,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7011,10 +7006,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>569463</v>
+        <v>569164</v>
       </c>
       <c r="R65" t="n">
-        <v>6949711</v>
+        <v>6949559</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7073,10 +7068,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129035021</v>
+        <v>129034574</v>
       </c>
       <c r="B66" t="n">
-        <v>91808</v>
+        <v>91526</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7084,21 +7079,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7108,10 +7103,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>569446</v>
+        <v>569461</v>
       </c>
       <c r="R66" t="n">
-        <v>6949629</v>
+        <v>6949706</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7170,45 +7165,49 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129034574</v>
+        <v>129027791</v>
       </c>
       <c r="B67" t="n">
-        <v>91523</v>
+        <v>98659</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Sandsjömyran, Mpd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>569461</v>
+        <v>569308</v>
       </c>
       <c r="R67" t="n">
-        <v>6949706</v>
+        <v>6949546</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7267,49 +7266,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129027791</v>
+        <v>129034624</v>
       </c>
       <c r="B68" t="n">
-        <v>98656</v>
+        <v>105722</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Sandsjömyran, Mpd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>569308</v>
+        <v>569234</v>
       </c>
       <c r="R68" t="n">
-        <v>6949546</v>
+        <v>6949440</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7342,6 +7337,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>9 exemplar</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7371,7 +7371,7 @@
         <v>129035035</v>
       </c>
       <c r="B69" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7470,32 +7470,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129035060</v>
+        <v>129035018</v>
       </c>
       <c r="B70" t="n">
-        <v>92816</v>
+        <v>57723</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7505,10 +7505,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>569208</v>
+        <v>569111</v>
       </c>
       <c r="R70" t="n">
-        <v>6949415</v>
+        <v>6949604</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7545,7 +7545,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>20 ex minst</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7572,10 +7572,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129034639</v>
+        <v>129035060</v>
       </c>
       <c r="B71" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7607,10 +7607,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>569398</v>
+        <v>569208</v>
       </c>
       <c r="R71" t="n">
-        <v>6949741</v>
+        <v>6949415</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7647,7 +7647,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>6 äldre exemplar och 1 färsk fruktkropp</t>
+          <t>20 ex minst</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7674,32 +7674,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129034584</v>
+        <v>129034639</v>
       </c>
       <c r="B72" t="n">
-        <v>57720</v>
+        <v>92819</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7709,10 +7709,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>569221</v>
+        <v>569398</v>
       </c>
       <c r="R72" t="n">
-        <v>6949499</v>
+        <v>6949741</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7749,7 +7749,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Förbiflygande från träd till träd</t>
+          <t>6 äldre exemplar och 1 färsk fruktkropp</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7776,10 +7776,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129035018</v>
+        <v>129034584</v>
       </c>
       <c r="B73" t="n">
-        <v>57723</v>
+        <v>57720</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7787,16 +7787,16 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -7811,10 +7811,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>569111</v>
+        <v>569221</v>
       </c>
       <c r="R73" t="n">
-        <v>6949604</v>
+        <v>6949499</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Förbiflygande från träd till träd</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7881,7 +7881,7 @@
         <v>129035037</v>
       </c>
       <c r="B74" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7980,32 +7980,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129026691</v>
+        <v>129034650</v>
       </c>
       <c r="B75" t="n">
-        <v>91808</v>
+        <v>98659</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8015,10 +8015,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>569195</v>
+        <v>569303</v>
       </c>
       <c r="R75" t="n">
-        <v>6949487</v>
+        <v>6949537</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8051,6 +8051,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>30 stycken ( finns eventuellt mer )</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8077,32 +8082,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129034645</v>
+        <v>129034605</v>
       </c>
       <c r="B76" t="n">
-        <v>92816</v>
+        <v>98659</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8112,10 +8117,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>569196</v>
+        <v>569305</v>
       </c>
       <c r="R76" t="n">
-        <v>6949411</v>
+        <v>6949538</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8152,7 +8157,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>4 färska exemplar 3 äldre exemplar</t>
+          <t>21 knärot</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8179,10 +8184,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129034642</v>
+        <v>129034598</v>
       </c>
       <c r="B77" t="n">
-        <v>92816</v>
+        <v>97530</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8190,21 +8195,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8214,10 +8219,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>569283</v>
+        <v>569460</v>
       </c>
       <c r="R77" t="n">
-        <v>6949655</v>
+        <v>6949629</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8250,11 +8255,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>7 äldre exemplar</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8281,32 +8281,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129034650</v>
+        <v>129034645</v>
       </c>
       <c r="B78" t="n">
-        <v>98656</v>
+        <v>92819</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8316,10 +8316,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>569303</v>
+        <v>569196</v>
       </c>
       <c r="R78" t="n">
-        <v>6949537</v>
+        <v>6949411</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>30 stycken ( finns eventuellt mer )</t>
+          <t>4 färska exemplar 3 äldre exemplar</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8383,32 +8383,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129034605</v>
+        <v>129034642</v>
       </c>
       <c r="B79" t="n">
-        <v>98656</v>
+        <v>92819</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8418,10 +8418,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>569305</v>
+        <v>569283</v>
       </c>
       <c r="R79" t="n">
-        <v>6949538</v>
+        <v>6949655</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8458,7 +8458,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>21 knärot</t>
+          <t>7 äldre exemplar</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8485,32 +8485,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129034598</v>
+        <v>129026691</v>
       </c>
       <c r="B80" t="n">
-        <v>97527</v>
+        <v>91811</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8520,10 +8520,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>569460</v>
+        <v>569195</v>
       </c>
       <c r="R80" t="n">
-        <v>6949629</v>
+        <v>6949487</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8582,10 +8582,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129035061</v>
+        <v>129034640</v>
       </c>
       <c r="B81" t="n">
-        <v>96775</v>
+        <v>92819</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8593,21 +8593,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2869</v>
+        <v>4364</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8617,10 +8617,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>569333</v>
+        <v>569213</v>
       </c>
       <c r="R81" t="n">
-        <v>6949607</v>
+        <v>6949414</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8653,6 +8653,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>16 exemplar</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8679,32 +8684,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129034640</v>
+        <v>129035007</v>
       </c>
       <c r="B82" t="n">
-        <v>92816</v>
+        <v>91526</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8714,10 +8719,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>569213</v>
+        <v>569225</v>
       </c>
       <c r="R82" t="n">
-        <v>6949414</v>
+        <v>6949424</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8750,11 +8755,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>16 exemplar</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8781,32 +8781,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129035001</v>
+        <v>129035057</v>
       </c>
       <c r="B83" t="n">
-        <v>91488</v>
+        <v>79035</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8816,10 +8816,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>569232</v>
+        <v>569464</v>
       </c>
       <c r="R83" t="n">
-        <v>6949444</v>
+        <v>6949648</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8878,32 +8878,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129035012</v>
+        <v>129035061</v>
       </c>
       <c r="B84" t="n">
-        <v>57723</v>
+        <v>96778</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8913,10 +8913,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>569435</v>
+        <v>569333</v>
       </c>
       <c r="R84" t="n">
-        <v>6949783</v>
+        <v>6949607</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8949,11 +8949,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8980,32 +8975,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129035007</v>
+        <v>129035001</v>
       </c>
       <c r="B85" t="n">
-        <v>91523</v>
+        <v>91491</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9015,10 +9010,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>569225</v>
+        <v>569232</v>
       </c>
       <c r="R85" t="n">
-        <v>6949424</v>
+        <v>6949444</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9077,10 +9072,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129035057</v>
+        <v>129035012</v>
       </c>
       <c r="B86" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9088,21 +9083,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9112,10 +9107,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>569464</v>
+        <v>569435</v>
       </c>
       <c r="R86" t="n">
-        <v>6949648</v>
+        <v>6949783</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9148,6 +9143,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9177,7 +9177,7 @@
         <v>129035047</v>
       </c>
       <c r="B87" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         <v>129034604</v>
       </c>
       <c r="B88" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9381,7 +9381,7 @@
         <v>129034618</v>
       </c>
       <c r="B89" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9483,7 +9483,7 @@
         <v>129035023</v>
       </c>
       <c r="B90" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         <v>129035027</v>
       </c>
       <c r="B91" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         <v>129034589</v>
       </c>
       <c r="B92" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9774,7 +9774,7 @@
         <v>129035029</v>
       </c>
       <c r="B93" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9871,7 +9871,7 @@
         <v>129035038</v>
       </c>
       <c r="B94" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9973,7 +9973,7 @@
         <v>129035050</v>
       </c>
       <c r="B95" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10075,7 +10075,7 @@
         <v>129034621</v>
       </c>
       <c r="B96" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>129034635</v>
       </c>
       <c r="B97" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10475,32 +10475,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129035056</v>
+        <v>129034609</v>
       </c>
       <c r="B100" t="n">
-        <v>105719</v>
+        <v>98659</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10510,10 +10510,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>569201</v>
+        <v>569458</v>
       </c>
       <c r="R100" t="n">
-        <v>6949530</v>
+        <v>6949777</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10546,6 +10546,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>48 stycken</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10572,10 +10577,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129034609</v>
+        <v>129035036</v>
       </c>
       <c r="B101" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10607,10 +10612,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>569458</v>
+        <v>569330</v>
       </c>
       <c r="R101" t="n">
-        <v>6949777</v>
+        <v>6949564</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10647,7 +10652,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>48 stycken</t>
+          <t>8 ex</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10674,10 +10679,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129035036</v>
+        <v>129035052</v>
       </c>
       <c r="B102" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10709,10 +10714,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>569330</v>
+        <v>569405</v>
       </c>
       <c r="R102" t="n">
-        <v>6949564</v>
+        <v>6949641</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10749,7 +10754,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>8 ex</t>
+          <t>70 ex</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10776,32 +10781,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129035052</v>
+        <v>129035056</v>
       </c>
       <c r="B103" t="n">
-        <v>98656</v>
+        <v>105722</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10811,10 +10816,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>569405</v>
+        <v>569201</v>
       </c>
       <c r="R103" t="n">
-        <v>6949641</v>
+        <v>6949530</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10847,11 +10852,6 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>70 ex</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10878,10 +10878,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129035026</v>
+        <v>129035006</v>
       </c>
       <c r="B104" t="n">
-        <v>91808</v>
+        <v>91526</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10889,21 +10889,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10913,10 +10913,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>569175</v>
+        <v>569217</v>
       </c>
       <c r="R104" t="n">
-        <v>6949549</v>
+        <v>6949470</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10975,10 +10975,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129035006</v>
+        <v>129027886</v>
       </c>
       <c r="B105" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11010,10 +11010,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>569217</v>
+        <v>569305</v>
       </c>
       <c r="R105" t="n">
-        <v>6949470</v>
+        <v>6949566</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11072,10 +11072,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129027886</v>
+        <v>129035026</v>
       </c>
       <c r="B106" t="n">
-        <v>91523</v>
+        <v>91811</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11083,21 +11083,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11107,10 +11107,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>569305</v>
+        <v>569175</v>
       </c>
       <c r="R106" t="n">
-        <v>6949566</v>
+        <v>6949549</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11172,7 +11172,7 @@
         <v>129035048</v>
       </c>
       <c r="B107" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11274,7 +11274,7 @@
         <v>129035053</v>
       </c>
       <c r="B108" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>129035049</v>
       </c>
       <c r="B109" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11478,7 +11478,7 @@
         <v>129035044</v>
       </c>
       <c r="B110" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
         <v>129035033</v>
       </c>
       <c r="B111" t="n">
-        <v>91724</v>
+        <v>91727</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11677,7 +11677,7 @@
         <v>129035032</v>
       </c>
       <c r="B112" t="n">
-        <v>91724</v>
+        <v>91727</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>

--- a/artfynd/A 45833-2025 artfynd.xlsx
+++ b/artfynd/A 45833-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129034612</v>
+        <v>129034627</v>
       </c>
       <c r="B2" t="n">
-        <v>98659</v>
+        <v>79035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569243</v>
+        <v>569482</v>
       </c>
       <c r="R2" t="n">
-        <v>6949558</v>
+        <v>6949676</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>30  exemplar ca</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129035046</v>
+        <v>129034612</v>
       </c>
       <c r="B3" t="n">
         <v>98659</v>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569127</v>
+        <v>569243</v>
       </c>
       <c r="R3" t="n">
-        <v>6949602</v>
+        <v>6949558</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +847,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>13 ex</t>
+          <t>30  exemplar ca</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,7 +874,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129035043</v>
+        <v>129035046</v>
       </c>
       <c r="B4" t="n">
         <v>98659</v>
@@ -914,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569204</v>
+        <v>569127</v>
       </c>
       <c r="R4" t="n">
-        <v>6949533</v>
+        <v>6949602</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,7 +949,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>10 ex</t>
+          <t>13 ex</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,32 +976,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129034627</v>
+        <v>129035043</v>
       </c>
       <c r="B5" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569482</v>
+        <v>569204</v>
       </c>
       <c r="R5" t="n">
-        <v>6949676</v>
+        <v>6949533</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1052,6 +1047,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1078,32 +1078,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129035039</v>
+        <v>129035030</v>
       </c>
       <c r="B6" t="n">
-        <v>98659</v>
+        <v>97530</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>569394</v>
+        <v>569424</v>
       </c>
       <c r="R6" t="n">
-        <v>6949664</v>
+        <v>6949671</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1149,11 +1149,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1180,32 +1175,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129035030</v>
+        <v>129035039</v>
       </c>
       <c r="B7" t="n">
-        <v>97530</v>
+        <v>98659</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>569424</v>
+        <v>569394</v>
       </c>
       <c r="R7" t="n">
-        <v>6949671</v>
+        <v>6949664</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1251,6 +1246,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1277,32 +1277,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129035054</v>
+        <v>129035013</v>
       </c>
       <c r="B8" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>569126</v>
+        <v>569455</v>
       </c>
       <c r="R8" t="n">
-        <v>6949570</v>
+        <v>6949716</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>13 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1379,7 +1379,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129035013</v>
+        <v>129035014</v>
       </c>
       <c r="B9" t="n">
         <v>57723</v>
@@ -1417,7 +1417,7 @@
         <v>569455</v>
       </c>
       <c r="R9" t="n">
-        <v>6949716</v>
+        <v>6949703</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1481,32 +1481,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129035014</v>
+        <v>129035054</v>
       </c>
       <c r="B10" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>569455</v>
+        <v>569126</v>
       </c>
       <c r="R10" t="n">
-        <v>6949703</v>
+        <v>6949570</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>13 ex</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1583,32 +1583,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129034648</v>
+        <v>129034630</v>
       </c>
       <c r="B11" t="n">
-        <v>96778</v>
+        <v>79035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>569279</v>
+        <v>569231</v>
       </c>
       <c r="R11" t="n">
-        <v>6949401</v>
+        <v>6949559</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1680,32 +1680,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129034630</v>
+        <v>129034648</v>
       </c>
       <c r="B12" t="n">
-        <v>79035</v>
+        <v>96778</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1715,10 +1715,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569231</v>
+        <v>569279</v>
       </c>
       <c r="R12" t="n">
-        <v>6949559</v>
+        <v>6949401</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1777,10 +1777,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129034577</v>
+        <v>129034594</v>
       </c>
       <c r="B13" t="n">
-        <v>57723</v>
+        <v>91811</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1788,21 +1788,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1812,10 +1812,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569496</v>
+        <v>569203</v>
       </c>
       <c r="R13" t="n">
-        <v>6949627</v>
+        <v>6949498</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på tall</t>
+          <t>11 exemplar</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1879,32 +1879,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129035055</v>
+        <v>129034577</v>
       </c>
       <c r="B14" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1914,10 +1914,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569221</v>
+        <v>569496</v>
       </c>
       <c r="R14" t="n">
-        <v>6949406</v>
+        <v>6949627</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>25 ex</t>
+          <t>Äldre ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1981,7 +1981,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129035042</v>
+        <v>129035055</v>
       </c>
       <c r="B15" t="n">
         <v>98659</v>
@@ -2016,10 +2016,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>569200</v>
+        <v>569221</v>
       </c>
       <c r="R15" t="n">
-        <v>6949533</v>
+        <v>6949406</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>30 ex</t>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2083,32 +2083,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129034594</v>
+        <v>129035042</v>
       </c>
       <c r="B16" t="n">
-        <v>91811</v>
+        <v>98659</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>569203</v>
+        <v>569200</v>
       </c>
       <c r="R16" t="n">
-        <v>6949498</v>
+        <v>6949533</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>11 exemplar</t>
+          <t>30 ex</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2185,32 +2185,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129034629</v>
+        <v>129034620</v>
       </c>
       <c r="B17" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2220,10 +2220,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>569247</v>
+        <v>569195</v>
       </c>
       <c r="R17" t="n">
-        <v>6949558</v>
+        <v>6949410</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2256,6 +2256,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Blommande knärot 1 exemplar + 21 övriga exemplar blommar ej</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2282,32 +2287,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129034620</v>
+        <v>129035059</v>
       </c>
       <c r="B18" t="n">
-        <v>98659</v>
+        <v>92819</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2317,10 +2322,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>569195</v>
+        <v>569273</v>
       </c>
       <c r="R18" t="n">
-        <v>6949410</v>
+        <v>6949537</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2353,11 +2358,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Blommande knärot 1 exemplar + 21 övriga exemplar blommar ej</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2384,32 +2384,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129035059</v>
+        <v>129034629</v>
       </c>
       <c r="B19" t="n">
-        <v>92819</v>
+        <v>79035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>569273</v>
+        <v>569247</v>
       </c>
       <c r="R19" t="n">
-        <v>6949537</v>
+        <v>6949558</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2787,10 +2787,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129034625</v>
+        <v>129034592</v>
       </c>
       <c r="B23" t="n">
-        <v>79035</v>
+        <v>91811</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2798,21 +2798,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569479</v>
+        <v>569205</v>
       </c>
       <c r="R23" t="n">
-        <v>6949657</v>
+        <v>6949497</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2858,6 +2858,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>1 x</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2884,7 +2889,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129034592</v>
+        <v>129034591</v>
       </c>
       <c r="B24" t="n">
         <v>91811</v>
@@ -2919,10 +2924,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569205</v>
+        <v>569203</v>
       </c>
       <c r="R24" t="n">
-        <v>6949497</v>
+        <v>6949513</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2959,7 +2964,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>1 x</t>
+          <t>11 ex</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2986,10 +2991,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129034591</v>
+        <v>129034647</v>
       </c>
       <c r="B25" t="n">
-        <v>91811</v>
+        <v>88926</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2997,21 +3002,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3021,10 +3026,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569203</v>
+        <v>569247</v>
       </c>
       <c r="R25" t="n">
-        <v>6949513</v>
+        <v>6949558</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3057,11 +3062,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>11 ex</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3088,10 +3088,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129034647</v>
+        <v>129035004</v>
       </c>
       <c r="B26" t="n">
-        <v>88926</v>
+        <v>91526</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3099,21 +3099,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3123,10 +3123,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569247</v>
+        <v>569152</v>
       </c>
       <c r="R26" t="n">
-        <v>6949558</v>
+        <v>6949557</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3282,7 +3282,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129035004</v>
+        <v>129035005</v>
       </c>
       <c r="B28" t="n">
         <v>91526</v>
@@ -3317,10 +3317,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>569152</v>
+        <v>569188</v>
       </c>
       <c r="R28" t="n">
-        <v>6949557</v>
+        <v>6949496</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3379,10 +3379,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129035005</v>
+        <v>129034625</v>
       </c>
       <c r="B29" t="n">
-        <v>91526</v>
+        <v>79035</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3390,21 +3390,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3414,10 +3414,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>569188</v>
+        <v>569479</v>
       </c>
       <c r="R29" t="n">
-        <v>6949496</v>
+        <v>6949657</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3772,10 +3772,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129035031</v>
+        <v>129034578</v>
       </c>
       <c r="B33" t="n">
-        <v>80140</v>
+        <v>57723</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3783,21 +3783,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3807,10 +3807,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>569125</v>
+        <v>569420</v>
       </c>
       <c r="R33" t="n">
-        <v>6949570</v>
+        <v>6949723</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3843,6 +3843,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3869,32 +3874,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129034578</v>
+        <v>129035051</v>
       </c>
       <c r="B34" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3904,10 +3909,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>569420</v>
+        <v>569222</v>
       </c>
       <c r="R34" t="n">
-        <v>6949723</v>
+        <v>6949414</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3944,7 +3949,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på Tall</t>
+          <t>30 ex</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3971,32 +3976,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129035051</v>
+        <v>129035031</v>
       </c>
       <c r="B35" t="n">
-        <v>98659</v>
+        <v>80140</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4006,10 +4011,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>569222</v>
+        <v>569125</v>
       </c>
       <c r="R35" t="n">
-        <v>6949414</v>
+        <v>6949570</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4042,11 +4047,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>30 ex</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4073,32 +4073,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129035020</v>
+        <v>129034602</v>
       </c>
       <c r="B36" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4108,10 +4108,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>569171</v>
+        <v>569301</v>
       </c>
       <c r="R36" t="n">
-        <v>6949543</v>
+        <v>6949480</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Äldre ringhack på granhögstubbe</t>
+          <t>22 stycken</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4175,32 +4175,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129035015</v>
+        <v>129035040</v>
       </c>
       <c r="B37" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4210,10 +4210,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>569454</v>
+        <v>569386</v>
       </c>
       <c r="R37" t="n">
-        <v>6949698</v>
+        <v>6949657</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4250,7 +4250,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>9 ex</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4277,32 +4277,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129034634</v>
+        <v>129035045</v>
       </c>
       <c r="B38" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4312,10 +4312,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>569200</v>
+        <v>569130</v>
       </c>
       <c r="R38" t="n">
-        <v>6949411</v>
+        <v>6949603</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4348,6 +4348,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>14 ex</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4374,32 +4379,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129034602</v>
+        <v>129034634</v>
       </c>
       <c r="B39" t="n">
-        <v>98659</v>
+        <v>79035</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4409,10 +4414,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>569301</v>
+        <v>569200</v>
       </c>
       <c r="R39" t="n">
-        <v>6949480</v>
+        <v>6949411</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4445,11 +4450,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>22 stycken</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4476,32 +4476,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129035040</v>
+        <v>129035020</v>
       </c>
       <c r="B40" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4511,10 +4511,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>569386</v>
+        <v>569171</v>
       </c>
       <c r="R40" t="n">
-        <v>6949657</v>
+        <v>6949543</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4551,7 +4551,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>9 ex</t>
+          <t>Äldre ringhack på granhögstubbe</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4578,32 +4578,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129035045</v>
+        <v>129035015</v>
       </c>
       <c r="B41" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4613,10 +4613,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>569130</v>
+        <v>569454</v>
       </c>
       <c r="R41" t="n">
-        <v>6949603</v>
+        <v>6949698</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4653,7 +4653,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>14 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4680,10 +4680,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129035063</v>
+        <v>129034643</v>
       </c>
       <c r="B42" t="n">
-        <v>96778</v>
+        <v>92819</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4691,21 +4691,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2869</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4715,10 +4715,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>569455</v>
+        <v>569254</v>
       </c>
       <c r="R42" t="n">
-        <v>6949758</v>
+        <v>6949431</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4751,6 +4751,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>1 färskt exemplar</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4777,10 +4782,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129034643</v>
+        <v>129035063</v>
       </c>
       <c r="B43" t="n">
-        <v>92819</v>
+        <v>96778</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4788,21 +4793,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>2869</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4812,10 +4817,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>569254</v>
+        <v>569455</v>
       </c>
       <c r="R43" t="n">
-        <v>6949431</v>
+        <v>6949758</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4848,11 +4853,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>1 färskt exemplar</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4879,32 +4879,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129034575</v>
+        <v>129034607</v>
       </c>
       <c r="B44" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4914,10 +4914,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>569448</v>
+        <v>569317</v>
       </c>
       <c r="R44" t="n">
-        <v>6949625</v>
+        <v>6949549</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Färska ringhack på Tall av tretåig hackspett</t>
+          <t>31 stycken</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4981,32 +4981,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129035011</v>
+        <v>129035041</v>
       </c>
       <c r="B45" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5016,10 +5016,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>569442</v>
+        <v>569262</v>
       </c>
       <c r="R45" t="n">
-        <v>6949783</v>
+        <v>6949524</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5083,32 +5083,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129034607</v>
+        <v>129034575</v>
       </c>
       <c r="B46" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5118,10 +5118,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>569317</v>
+        <v>569448</v>
       </c>
       <c r="R46" t="n">
-        <v>6949549</v>
+        <v>6949625</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>31 stycken</t>
+          <t>Färska ringhack på Tall av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5185,32 +5185,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129035041</v>
+        <v>129035011</v>
       </c>
       <c r="B47" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5220,10 +5220,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>569262</v>
+        <v>569442</v>
       </c>
       <c r="R47" t="n">
-        <v>6949524</v>
+        <v>6949783</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5260,7 +5260,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>5 ex</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5287,10 +5287,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129035002</v>
+        <v>129035022</v>
       </c>
       <c r="B48" t="n">
-        <v>91526</v>
+        <v>91811</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5298,21 +5298,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5322,10 +5322,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>569405</v>
+        <v>569423</v>
       </c>
       <c r="R48" t="n">
-        <v>6949685</v>
+        <v>6949656</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5486,10 +5486,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129034632</v>
+        <v>129035002</v>
       </c>
       <c r="B50" t="n">
-        <v>79035</v>
+        <v>91526</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5497,21 +5497,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5521,10 +5521,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>569237</v>
+        <v>569405</v>
       </c>
       <c r="R50" t="n">
-        <v>6949442</v>
+        <v>6949685</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5583,32 +5583,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129035062</v>
+        <v>129035016</v>
       </c>
       <c r="B51" t="n">
-        <v>96778</v>
+        <v>57723</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5618,10 +5618,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>569478</v>
+        <v>569435</v>
       </c>
       <c r="R51" t="n">
-        <v>6949666</v>
+        <v>6949665</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5654,6 +5654,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5680,10 +5685,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129035022</v>
+        <v>129034632</v>
       </c>
       <c r="B52" t="n">
-        <v>91811</v>
+        <v>79035</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5691,21 +5696,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5715,10 +5720,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>569423</v>
+        <v>569237</v>
       </c>
       <c r="R52" t="n">
-        <v>6949656</v>
+        <v>6949442</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5777,32 +5782,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129035016</v>
+        <v>129035062</v>
       </c>
       <c r="B53" t="n">
-        <v>57723</v>
+        <v>96778</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5812,10 +5817,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>569435</v>
+        <v>569478</v>
       </c>
       <c r="R53" t="n">
-        <v>6949665</v>
+        <v>6949666</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5848,11 +5853,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6083,32 +6083,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129035008</v>
+        <v>129034610</v>
       </c>
       <c r="B56" t="n">
-        <v>91526</v>
+        <v>98659</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6118,10 +6118,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>569216</v>
+        <v>569282</v>
       </c>
       <c r="R56" t="n">
-        <v>6949430</v>
+        <v>6949567</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6154,6 +6154,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ca 100 stycken</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6180,32 +6185,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129034581</v>
+        <v>129034614</v>
       </c>
       <c r="B57" t="n">
-        <v>57883</v>
+        <v>98659</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6215,10 +6220,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>569223</v>
+        <v>569237</v>
       </c>
       <c r="R57" t="n">
-        <v>6949401</v>
+        <v>6949556</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6255,7 +6260,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Sågs och gjorde övriga läten</t>
+          <t>5 stycken</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6379,32 +6384,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129034610</v>
+        <v>129035008</v>
       </c>
       <c r="B59" t="n">
-        <v>98659</v>
+        <v>91526</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6414,10 +6419,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>569282</v>
+        <v>569216</v>
       </c>
       <c r="R59" t="n">
-        <v>6949567</v>
+        <v>6949430</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6450,11 +6455,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ca 100 stycken</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6481,32 +6481,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129034614</v>
+        <v>129034581</v>
       </c>
       <c r="B60" t="n">
-        <v>98659</v>
+        <v>57883</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6516,10 +6516,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>569237</v>
+        <v>569223</v>
       </c>
       <c r="R60" t="n">
-        <v>6949556</v>
+        <v>6949401</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6556,7 +6556,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>5 stycken</t>
+          <t>Sågs och gjorde övriga läten</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6777,10 +6777,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129034587</v>
+        <v>129035003</v>
       </c>
       <c r="B63" t="n">
-        <v>91811</v>
+        <v>91526</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6788,21 +6788,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6812,10 +6812,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>569463</v>
+        <v>569164</v>
       </c>
       <c r="R63" t="n">
-        <v>6949711</v>
+        <v>6949559</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6874,7 +6874,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129035021</v>
+        <v>129034587</v>
       </c>
       <c r="B64" t="n">
         <v>91811</v>
@@ -6909,10 +6909,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>569446</v>
+        <v>569463</v>
       </c>
       <c r="R64" t="n">
-        <v>6949629</v>
+        <v>6949711</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6971,10 +6971,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129035003</v>
+        <v>129035021</v>
       </c>
       <c r="B65" t="n">
-        <v>91526</v>
+        <v>91811</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6982,21 +6982,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7006,10 +7006,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>569164</v>
+        <v>569446</v>
       </c>
       <c r="R65" t="n">
-        <v>6949559</v>
+        <v>6949629</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7165,49 +7165,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129027791</v>
+        <v>129034624</v>
       </c>
       <c r="B67" t="n">
-        <v>98659</v>
+        <v>105722</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Sandsjömyran, Mpd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>569308</v>
+        <v>569234</v>
       </c>
       <c r="R67" t="n">
-        <v>6949546</v>
+        <v>6949440</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7240,6 +7236,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>9 exemplar</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7266,45 +7267,49 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129034624</v>
+        <v>129027791</v>
       </c>
       <c r="B68" t="n">
-        <v>105722</v>
+        <v>98659</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Sandsjömyran, Mpd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>569234</v>
+        <v>569308</v>
       </c>
       <c r="R68" t="n">
-        <v>6949440</v>
+        <v>6949546</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7337,11 +7342,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>9 exemplar</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7470,32 +7470,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129035018</v>
+        <v>129035060</v>
       </c>
       <c r="B70" t="n">
-        <v>57723</v>
+        <v>92819</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7505,10 +7505,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>569111</v>
+        <v>569208</v>
       </c>
       <c r="R70" t="n">
-        <v>6949604</v>
+        <v>6949415</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7545,7 +7545,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>20 ex minst</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7572,7 +7572,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129035060</v>
+        <v>129034639</v>
       </c>
       <c r="B71" t="n">
         <v>92819</v>
@@ -7607,10 +7607,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>569208</v>
+        <v>569398</v>
       </c>
       <c r="R71" t="n">
-        <v>6949415</v>
+        <v>6949741</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7647,7 +7647,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>20 ex minst</t>
+          <t>6 äldre exemplar och 1 färsk fruktkropp</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7674,32 +7674,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129034639</v>
+        <v>129034584</v>
       </c>
       <c r="B72" t="n">
-        <v>92819</v>
+        <v>57720</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7709,10 +7709,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>569398</v>
+        <v>569221</v>
       </c>
       <c r="R72" t="n">
-        <v>6949741</v>
+        <v>6949499</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7749,7 +7749,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>6 äldre exemplar och 1 färsk fruktkropp</t>
+          <t>Förbiflygande från träd till träd</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7776,10 +7776,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129034584</v>
+        <v>129035018</v>
       </c>
       <c r="B73" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7787,16 +7787,16 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -7811,10 +7811,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>569221</v>
+        <v>569111</v>
       </c>
       <c r="R73" t="n">
-        <v>6949499</v>
+        <v>6949604</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Förbiflygande från träd till träd</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7980,32 +7980,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129034650</v>
+        <v>129026691</v>
       </c>
       <c r="B75" t="n">
-        <v>98659</v>
+        <v>91811</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8015,10 +8015,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>569303</v>
+        <v>569195</v>
       </c>
       <c r="R75" t="n">
-        <v>6949537</v>
+        <v>6949487</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8051,11 +8051,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>30 stycken ( finns eventuellt mer )</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8082,32 +8077,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129034605</v>
+        <v>129034598</v>
       </c>
       <c r="B76" t="n">
-        <v>98659</v>
+        <v>97530</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8117,10 +8112,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>569305</v>
+        <v>569460</v>
       </c>
       <c r="R76" t="n">
-        <v>6949538</v>
+        <v>6949629</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8153,11 +8148,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>21 knärot</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8184,10 +8174,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129034598</v>
+        <v>129034645</v>
       </c>
       <c r="B77" t="n">
-        <v>97530</v>
+        <v>92819</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8195,21 +8185,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8219,10 +8209,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>569460</v>
+        <v>569196</v>
       </c>
       <c r="R77" t="n">
-        <v>6949629</v>
+        <v>6949411</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8255,6 +8245,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>4 färska exemplar 3 äldre exemplar</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8281,7 +8276,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129034645</v>
+        <v>129034642</v>
       </c>
       <c r="B78" t="n">
         <v>92819</v>
@@ -8316,10 +8311,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>569196</v>
+        <v>569283</v>
       </c>
       <c r="R78" t="n">
-        <v>6949411</v>
+        <v>6949655</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8356,7 +8351,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>4 färska exemplar 3 äldre exemplar</t>
+          <t>7 äldre exemplar</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8383,32 +8378,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129034642</v>
+        <v>129034650</v>
       </c>
       <c r="B79" t="n">
-        <v>92819</v>
+        <v>98659</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8418,10 +8413,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>569283</v>
+        <v>569303</v>
       </c>
       <c r="R79" t="n">
-        <v>6949655</v>
+        <v>6949537</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8458,7 +8453,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>7 äldre exemplar</t>
+          <t>30 stycken ( finns eventuellt mer )</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8485,32 +8480,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129026691</v>
+        <v>129034605</v>
       </c>
       <c r="B80" t="n">
-        <v>91811</v>
+        <v>98659</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8520,10 +8515,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>569195</v>
+        <v>569305</v>
       </c>
       <c r="R80" t="n">
-        <v>6949487</v>
+        <v>6949538</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8556,6 +8551,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>21 knärot</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8582,32 +8582,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129034640</v>
+        <v>129035007</v>
       </c>
       <c r="B81" t="n">
-        <v>92819</v>
+        <v>91526</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8617,10 +8617,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>569213</v>
+        <v>569225</v>
       </c>
       <c r="R81" t="n">
-        <v>6949414</v>
+        <v>6949424</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8653,11 +8653,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>16 exemplar</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8684,10 +8679,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129035007</v>
+        <v>129035012</v>
       </c>
       <c r="B82" t="n">
-        <v>91526</v>
+        <v>57723</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8695,21 +8690,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8719,10 +8714,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>569225</v>
+        <v>569435</v>
       </c>
       <c r="R82" t="n">
-        <v>6949424</v>
+        <v>6949783</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8755,6 +8750,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8781,32 +8781,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129035057</v>
+        <v>129035047</v>
       </c>
       <c r="B83" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8816,10 +8816,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>569464</v>
+        <v>569162</v>
       </c>
       <c r="R83" t="n">
-        <v>6949648</v>
+        <v>6949566</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8852,6 +8852,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8878,32 +8883,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129035061</v>
+        <v>129034604</v>
       </c>
       <c r="B84" t="n">
-        <v>96778</v>
+        <v>98659</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8913,10 +8918,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>569333</v>
+        <v>569303</v>
       </c>
       <c r="R84" t="n">
-        <v>6949607</v>
+        <v>6949536</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8949,6 +8954,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8975,32 +8985,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129035001</v>
+        <v>129034618</v>
       </c>
       <c r="B85" t="n">
-        <v>91491</v>
+        <v>98659</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9010,10 +9020,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>569232</v>
+        <v>569235</v>
       </c>
       <c r="R85" t="n">
-        <v>6949444</v>
+        <v>6949411</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9046,6 +9056,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9072,32 +9087,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129035012</v>
+        <v>129034640</v>
       </c>
       <c r="B86" t="n">
-        <v>57723</v>
+        <v>92819</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9107,10 +9122,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>569435</v>
+        <v>569213</v>
       </c>
       <c r="R86" t="n">
-        <v>6949783</v>
+        <v>6949414</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9147,7 +9162,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>16 exemplar</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9174,32 +9189,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129035047</v>
+        <v>129035001</v>
       </c>
       <c r="B87" t="n">
-        <v>98659</v>
+        <v>91491</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9209,10 +9224,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>569162</v>
+        <v>569232</v>
       </c>
       <c r="R87" t="n">
-        <v>6949566</v>
+        <v>6949444</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9245,11 +9260,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>50 ex</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9276,32 +9286,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129034604</v>
+        <v>129035057</v>
       </c>
       <c r="B88" t="n">
-        <v>98659</v>
+        <v>79035</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9311,10 +9321,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>569303</v>
+        <v>569464</v>
       </c>
       <c r="R88" t="n">
-        <v>6949536</v>
+        <v>6949648</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9347,11 +9357,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9378,32 +9383,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129034618</v>
+        <v>129035061</v>
       </c>
       <c r="B89" t="n">
-        <v>98659</v>
+        <v>96778</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9413,10 +9418,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>569235</v>
+        <v>569333</v>
       </c>
       <c r="R89" t="n">
-        <v>6949411</v>
+        <v>6949607</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9449,11 +9454,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9480,32 +9480,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129035023</v>
+        <v>129035038</v>
       </c>
       <c r="B90" t="n">
-        <v>91811</v>
+        <v>98659</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>569415</v>
+        <v>569406</v>
       </c>
       <c r="R90" t="n">
-        <v>6949677</v>
+        <v>6949664</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9551,6 +9551,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9577,32 +9582,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129035027</v>
+        <v>129035050</v>
       </c>
       <c r="B91" t="n">
-        <v>91811</v>
+        <v>98659</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9612,10 +9617,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>569169</v>
+        <v>569236</v>
       </c>
       <c r="R91" t="n">
-        <v>6949533</v>
+        <v>6949440</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9648,6 +9653,11 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>4 ex</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9674,32 +9684,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129034589</v>
+        <v>129034621</v>
       </c>
       <c r="B92" t="n">
-        <v>91811</v>
+        <v>98659</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9709,10 +9719,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>569365</v>
+        <v>569247</v>
       </c>
       <c r="R92" t="n">
-        <v>6949661</v>
+        <v>6949434</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9745,6 +9755,11 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>10 stycken knärot</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9771,7 +9786,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129035029</v>
+        <v>129035023</v>
       </c>
       <c r="B93" t="n">
         <v>91811</v>
@@ -9806,10 +9821,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>569217</v>
+        <v>569415</v>
       </c>
       <c r="R93" t="n">
-        <v>6949427</v>
+        <v>6949677</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9868,32 +9883,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129035038</v>
+        <v>129035027</v>
       </c>
       <c r="B94" t="n">
-        <v>98659</v>
+        <v>91811</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9903,10 +9918,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>569406</v>
+        <v>569169</v>
       </c>
       <c r="R94" t="n">
-        <v>6949664</v>
+        <v>6949533</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9939,11 +9954,6 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>20 ex</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -9970,32 +9980,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129035050</v>
+        <v>129034589</v>
       </c>
       <c r="B95" t="n">
-        <v>98659</v>
+        <v>91811</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10005,10 +10015,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>569236</v>
+        <v>569365</v>
       </c>
       <c r="R95" t="n">
-        <v>6949440</v>
+        <v>6949661</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10041,11 +10051,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>4 ex</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10072,32 +10077,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129034621</v>
+        <v>129035029</v>
       </c>
       <c r="B96" t="n">
-        <v>98659</v>
+        <v>91811</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10107,10 +10112,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>569247</v>
+        <v>569217</v>
       </c>
       <c r="R96" t="n">
-        <v>6949434</v>
+        <v>6949427</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10143,11 +10148,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>10 stycken knärot</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10475,32 +10475,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129034609</v>
+        <v>129035056</v>
       </c>
       <c r="B100" t="n">
-        <v>98659</v>
+        <v>105722</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10510,10 +10510,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>569458</v>
+        <v>569201</v>
       </c>
       <c r="R100" t="n">
-        <v>6949777</v>
+        <v>6949530</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10546,11 +10546,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>48 stycken</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10577,7 +10572,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129035036</v>
+        <v>129034609</v>
       </c>
       <c r="B101" t="n">
         <v>98659</v>
@@ -10612,10 +10607,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>569330</v>
+        <v>569458</v>
       </c>
       <c r="R101" t="n">
-        <v>6949564</v>
+        <v>6949777</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10652,7 +10647,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>8 ex</t>
+          <t>48 stycken</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10679,7 +10674,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129035052</v>
+        <v>129035036</v>
       </c>
       <c r="B102" t="n">
         <v>98659</v>
@@ -10714,10 +10709,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>569405</v>
+        <v>569330</v>
       </c>
       <c r="R102" t="n">
-        <v>6949641</v>
+        <v>6949564</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10754,7 +10749,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>70 ex</t>
+          <t>8 ex</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10781,32 +10776,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129035056</v>
+        <v>129035052</v>
       </c>
       <c r="B103" t="n">
-        <v>105722</v>
+        <v>98659</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10816,10 +10811,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>569201</v>
+        <v>569405</v>
       </c>
       <c r="R103" t="n">
-        <v>6949530</v>
+        <v>6949641</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10852,6 +10847,11 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>70 ex</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10878,10 +10878,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129035006</v>
+        <v>129035026</v>
       </c>
       <c r="B104" t="n">
-        <v>91526</v>
+        <v>91811</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10889,21 +10889,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10913,10 +10913,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>569217</v>
+        <v>569175</v>
       </c>
       <c r="R104" t="n">
-        <v>6949470</v>
+        <v>6949549</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10975,7 +10975,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129027886</v>
+        <v>129035006</v>
       </c>
       <c r="B105" t="n">
         <v>91526</v>
@@ -11010,10 +11010,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>569305</v>
+        <v>569217</v>
       </c>
       <c r="R105" t="n">
-        <v>6949566</v>
+        <v>6949470</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11072,10 +11072,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129035026</v>
+        <v>129027886</v>
       </c>
       <c r="B106" t="n">
-        <v>91811</v>
+        <v>91526</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11083,21 +11083,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11107,10 +11107,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>569175</v>
+        <v>569305</v>
       </c>
       <c r="R106" t="n">
-        <v>6949549</v>
+        <v>6949566</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>

--- a/artfynd/A 45833-2025 artfynd.xlsx
+++ b/artfynd/A 45833-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129034627</v>
+        <v>129034612</v>
       </c>
       <c r="B2" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569482</v>
+        <v>569243</v>
       </c>
       <c r="R2" t="n">
-        <v>6949676</v>
+        <v>6949558</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>30  exemplar ca</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129034612</v>
+        <v>129035046</v>
       </c>
       <c r="B3" t="n">
         <v>98659</v>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569243</v>
+        <v>569127</v>
       </c>
       <c r="R3" t="n">
-        <v>6949558</v>
+        <v>6949602</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>30  exemplar ca</t>
+          <t>13 ex</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129035046</v>
+        <v>129035043</v>
       </c>
       <c r="B4" t="n">
         <v>98659</v>
@@ -909,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569127</v>
+        <v>569204</v>
       </c>
       <c r="R4" t="n">
-        <v>6949602</v>
+        <v>6949533</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,7 +954,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>13 ex</t>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,32 +981,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129035043</v>
+        <v>129034627</v>
       </c>
       <c r="B5" t="n">
-        <v>98659</v>
+        <v>79035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569204</v>
+        <v>569482</v>
       </c>
       <c r="R5" t="n">
-        <v>6949533</v>
+        <v>6949676</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1047,11 +1052,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>10 ex</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1078,32 +1078,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129035030</v>
+        <v>129035039</v>
       </c>
       <c r="B6" t="n">
-        <v>97530</v>
+        <v>98659</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>569424</v>
+        <v>569394</v>
       </c>
       <c r="R6" t="n">
-        <v>6949671</v>
+        <v>6949664</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1149,6 +1149,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1175,32 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129035039</v>
+        <v>129035030</v>
       </c>
       <c r="B7" t="n">
-        <v>98659</v>
+        <v>97530</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>569394</v>
+        <v>569424</v>
       </c>
       <c r="R7" t="n">
-        <v>6949664</v>
+        <v>6949671</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1246,11 +1251,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1583,10 +1583,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129034630</v>
+        <v>129034594</v>
       </c>
       <c r="B11" t="n">
-        <v>79035</v>
+        <v>91811</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1594,21 +1594,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>569231</v>
+        <v>569203</v>
       </c>
       <c r="R11" t="n">
-        <v>6949559</v>
+        <v>6949498</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1654,6 +1654,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>11 exemplar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1680,32 +1685,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129034648</v>
+        <v>129034630</v>
       </c>
       <c r="B12" t="n">
-        <v>96778</v>
+        <v>79035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1715,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569279</v>
+        <v>569231</v>
       </c>
       <c r="R12" t="n">
-        <v>6949401</v>
+        <v>6949559</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1777,32 +1782,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129034594</v>
+        <v>129034648</v>
       </c>
       <c r="B13" t="n">
-        <v>91811</v>
+        <v>96778</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>2869</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1812,10 +1817,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569203</v>
+        <v>569279</v>
       </c>
       <c r="R13" t="n">
-        <v>6949498</v>
+        <v>6949401</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1848,11 +1853,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>11 exemplar</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2185,32 +2185,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129034620</v>
+        <v>129035059</v>
       </c>
       <c r="B17" t="n">
-        <v>98659</v>
+        <v>92819</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2220,10 +2220,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>569195</v>
+        <v>569273</v>
       </c>
       <c r="R17" t="n">
-        <v>6949410</v>
+        <v>6949537</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2256,11 +2256,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Blommande knärot 1 exemplar + 21 övriga exemplar blommar ej</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2287,32 +2282,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129035059</v>
+        <v>129034629</v>
       </c>
       <c r="B18" t="n">
-        <v>92819</v>
+        <v>79035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2322,10 +2317,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>569273</v>
+        <v>569247</v>
       </c>
       <c r="R18" t="n">
-        <v>6949537</v>
+        <v>6949558</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2384,10 +2379,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129034629</v>
+        <v>129035009</v>
       </c>
       <c r="B19" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2395,21 +2390,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2419,10 +2414,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>569247</v>
+        <v>569314</v>
       </c>
       <c r="R19" t="n">
-        <v>6949558</v>
+        <v>6949502</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2455,6 +2450,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2481,7 +2481,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129035009</v>
+        <v>129034580</v>
       </c>
       <c r="B20" t="n">
         <v>57723</v>
@@ -2516,10 +2516,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>569314</v>
+        <v>569396</v>
       </c>
       <c r="R20" t="n">
-        <v>6949502</v>
+        <v>6949738</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Äldre ringhack på Tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2583,7 +2583,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129034580</v>
+        <v>129035019</v>
       </c>
       <c r="B21" t="n">
         <v>57723</v>
@@ -2618,10 +2618,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>569396</v>
+        <v>569117</v>
       </c>
       <c r="R21" t="n">
-        <v>6949738</v>
+        <v>6949581</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Äldre ringhack på Tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2685,32 +2685,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129035019</v>
+        <v>129034620</v>
       </c>
       <c r="B22" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2720,10 +2720,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>569117</v>
+        <v>569195</v>
       </c>
       <c r="R22" t="n">
-        <v>6949581</v>
+        <v>6949410</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2760,7 +2760,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Blommande knärot 1 exemplar + 21 övriga exemplar blommar ej</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3578,32 +3578,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129034637</v>
+        <v>129034578</v>
       </c>
       <c r="B31" t="n">
-        <v>92819</v>
+        <v>57723</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>569229</v>
+        <v>569420</v>
       </c>
       <c r="R31" t="n">
-        <v>6949400</v>
+        <v>6949723</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3649,6 +3649,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3675,32 +3680,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129035058</v>
+        <v>129034637</v>
       </c>
       <c r="B32" t="n">
-        <v>79035</v>
+        <v>92819</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3710,10 +3715,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>569388</v>
+        <v>569229</v>
       </c>
       <c r="R32" t="n">
-        <v>6949647</v>
+        <v>6949400</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3772,10 +3777,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129034578</v>
+        <v>129035058</v>
       </c>
       <c r="B33" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3783,21 +3788,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3807,10 +3812,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>569420</v>
+        <v>569388</v>
       </c>
       <c r="R33" t="n">
-        <v>6949723</v>
+        <v>6949647</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3843,11 +3848,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3874,32 +3874,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129035051</v>
+        <v>129035031</v>
       </c>
       <c r="B34" t="n">
-        <v>98659</v>
+        <v>80140</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3909,10 +3909,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>569222</v>
+        <v>569125</v>
       </c>
       <c r="R34" t="n">
-        <v>6949414</v>
+        <v>6949570</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3945,11 +3945,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>30 ex</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3976,32 +3971,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129035031</v>
+        <v>129035051</v>
       </c>
       <c r="B35" t="n">
-        <v>80140</v>
+        <v>98659</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4011,10 +4006,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>569125</v>
+        <v>569222</v>
       </c>
       <c r="R35" t="n">
-        <v>6949570</v>
+        <v>6949414</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4047,6 +4042,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>30 ex</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -7165,45 +7165,49 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129034624</v>
+        <v>129027791</v>
       </c>
       <c r="B67" t="n">
-        <v>105722</v>
+        <v>98659</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Sandsjömyran, Mpd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>569234</v>
+        <v>569308</v>
       </c>
       <c r="R67" t="n">
-        <v>6949440</v>
+        <v>6949546</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7236,11 +7240,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>9 exemplar</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7267,7 +7266,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129027791</v>
+        <v>129035035</v>
       </c>
       <c r="B68" t="n">
         <v>98659</v>
@@ -7295,21 +7294,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Sandsjömyran, Mpd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>569308</v>
+        <v>569317</v>
       </c>
       <c r="R68" t="n">
-        <v>6949546</v>
+        <v>6949469</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7342,6 +7337,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7368,32 +7368,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129035035</v>
+        <v>129034624</v>
       </c>
       <c r="B69" t="n">
-        <v>98659</v>
+        <v>105722</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7403,10 +7403,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>569317</v>
+        <v>569234</v>
       </c>
       <c r="R69" t="n">
-        <v>6949469</v>
+        <v>6949440</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7443,7 +7443,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>5 ex</t>
+          <t>9 exemplar</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7980,32 +7980,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129026691</v>
+        <v>129034598</v>
       </c>
       <c r="B75" t="n">
-        <v>91811</v>
+        <v>97530</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8015,10 +8015,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>569195</v>
+        <v>569460</v>
       </c>
       <c r="R75" t="n">
-        <v>6949487</v>
+        <v>6949629</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8077,32 +8077,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129034598</v>
+        <v>129034650</v>
       </c>
       <c r="B76" t="n">
-        <v>97530</v>
+        <v>98659</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8112,10 +8112,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>569460</v>
+        <v>569303</v>
       </c>
       <c r="R76" t="n">
-        <v>6949629</v>
+        <v>6949537</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8148,6 +8148,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>30 stycken ( finns eventuellt mer )</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8174,32 +8179,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129034645</v>
+        <v>129034605</v>
       </c>
       <c r="B77" t="n">
-        <v>92819</v>
+        <v>98659</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8209,10 +8214,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>569196</v>
+        <v>569305</v>
       </c>
       <c r="R77" t="n">
-        <v>6949411</v>
+        <v>6949538</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8249,7 +8254,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>4 färska exemplar 3 äldre exemplar</t>
+          <t>21 knärot</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8276,32 +8281,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129034642</v>
+        <v>129026691</v>
       </c>
       <c r="B78" t="n">
-        <v>92819</v>
+        <v>91811</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8311,10 +8316,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>569283</v>
+        <v>569195</v>
       </c>
       <c r="R78" t="n">
-        <v>6949655</v>
+        <v>6949487</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8347,11 +8352,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>7 äldre exemplar</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8378,32 +8378,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129034650</v>
+        <v>129034645</v>
       </c>
       <c r="B79" t="n">
-        <v>98659</v>
+        <v>92819</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8413,10 +8413,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>569303</v>
+        <v>569196</v>
       </c>
       <c r="R79" t="n">
-        <v>6949537</v>
+        <v>6949411</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8453,7 +8453,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>30 stycken ( finns eventuellt mer )</t>
+          <t>4 färska exemplar 3 äldre exemplar</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8480,32 +8480,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129034605</v>
+        <v>129034642</v>
       </c>
       <c r="B80" t="n">
-        <v>98659</v>
+        <v>92819</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8515,10 +8515,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>569305</v>
+        <v>569283</v>
       </c>
       <c r="R80" t="n">
-        <v>6949538</v>
+        <v>6949655</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8555,7 +8555,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>21 knärot</t>
+          <t>7 äldre exemplar</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9480,32 +9480,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129035038</v>
+        <v>129035023</v>
       </c>
       <c r="B90" t="n">
-        <v>98659</v>
+        <v>91811</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>569406</v>
+        <v>569415</v>
       </c>
       <c r="R90" t="n">
-        <v>6949664</v>
+        <v>6949677</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9551,11 +9551,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>20 ex</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9582,32 +9577,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129035050</v>
+        <v>129035027</v>
       </c>
       <c r="B91" t="n">
-        <v>98659</v>
+        <v>91811</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9617,10 +9612,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>569236</v>
+        <v>569169</v>
       </c>
       <c r="R91" t="n">
-        <v>6949440</v>
+        <v>6949533</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9653,11 +9648,6 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>4 ex</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9684,32 +9674,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129034621</v>
+        <v>129034589</v>
       </c>
       <c r="B92" t="n">
-        <v>98659</v>
+        <v>91811</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9719,10 +9709,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>569247</v>
+        <v>569365</v>
       </c>
       <c r="R92" t="n">
-        <v>6949434</v>
+        <v>6949661</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9755,11 +9745,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>10 stycken knärot</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9786,7 +9771,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129035023</v>
+        <v>129035029</v>
       </c>
       <c r="B93" t="n">
         <v>91811</v>
@@ -9821,10 +9806,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>569415</v>
+        <v>569217</v>
       </c>
       <c r="R93" t="n">
-        <v>6949677</v>
+        <v>6949427</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9883,32 +9868,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129035027</v>
+        <v>129035038</v>
       </c>
       <c r="B94" t="n">
-        <v>91811</v>
+        <v>98659</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9918,10 +9903,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>569169</v>
+        <v>569406</v>
       </c>
       <c r="R94" t="n">
-        <v>6949533</v>
+        <v>6949664</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9954,6 +9939,11 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -9980,32 +9970,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129034589</v>
+        <v>129035050</v>
       </c>
       <c r="B95" t="n">
-        <v>91811</v>
+        <v>98659</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10015,10 +10005,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>569365</v>
+        <v>569236</v>
       </c>
       <c r="R95" t="n">
-        <v>6949661</v>
+        <v>6949440</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10051,6 +10041,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>4 ex</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10077,32 +10072,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129035029</v>
+        <v>129034621</v>
       </c>
       <c r="B96" t="n">
-        <v>91811</v>
+        <v>98659</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10112,10 +10107,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>569217</v>
+        <v>569247</v>
       </c>
       <c r="R96" t="n">
-        <v>6949427</v>
+        <v>6949434</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10148,6 +10143,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>10 stycken knärot</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10878,32 +10878,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129035026</v>
+        <v>129035048</v>
       </c>
       <c r="B104" t="n">
-        <v>91811</v>
+        <v>98659</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10913,10 +10913,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>569175</v>
+        <v>569176</v>
       </c>
       <c r="R104" t="n">
-        <v>6949549</v>
+        <v>6949507</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10949,6 +10949,11 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>30 ex</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -10975,32 +10980,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129035006</v>
+        <v>129035053</v>
       </c>
       <c r="B105" t="n">
-        <v>91526</v>
+        <v>98659</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11010,10 +11015,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>569217</v>
+        <v>569459</v>
       </c>
       <c r="R105" t="n">
-        <v>6949470</v>
+        <v>6949662</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11046,6 +11051,11 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>14 ex</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11072,32 +11082,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129027886</v>
+        <v>129035049</v>
       </c>
       <c r="B106" t="n">
-        <v>91526</v>
+        <v>98659</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11107,10 +11117,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>569305</v>
+        <v>569219</v>
       </c>
       <c r="R106" t="n">
-        <v>6949566</v>
+        <v>6949489</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11143,6 +11153,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>35 ex</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11169,7 +11184,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129035048</v>
+        <v>129035044</v>
       </c>
       <c r="B107" t="n">
         <v>98659</v>
@@ -11204,10 +11219,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>569176</v>
+        <v>569191</v>
       </c>
       <c r="R107" t="n">
-        <v>6949507</v>
+        <v>6949579</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11244,7 +11259,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>30 ex</t>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11271,32 +11286,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129035053</v>
+        <v>129035026</v>
       </c>
       <c r="B108" t="n">
-        <v>98659</v>
+        <v>91811</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11306,10 +11321,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>569459</v>
+        <v>569175</v>
       </c>
       <c r="R108" t="n">
-        <v>6949662</v>
+        <v>6949549</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11342,11 +11357,6 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>14 ex</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11373,32 +11383,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129035049</v>
+        <v>129035006</v>
       </c>
       <c r="B109" t="n">
-        <v>98659</v>
+        <v>91526</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11408,10 +11418,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>569219</v>
+        <v>569217</v>
       </c>
       <c r="R109" t="n">
-        <v>6949489</v>
+        <v>6949470</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11444,11 +11454,6 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>35 ex</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11475,32 +11480,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129035044</v>
+        <v>129027886</v>
       </c>
       <c r="B110" t="n">
-        <v>98659</v>
+        <v>91526</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11510,10 +11515,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>569191</v>
+        <v>569305</v>
       </c>
       <c r="R110" t="n">
-        <v>6949579</v>
+        <v>6949566</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11546,11 +11551,6 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>50 ex</t>
         </is>
       </c>
       <c r="AD110" t="b">

--- a/artfynd/A 45833-2025 artfynd.xlsx
+++ b/artfynd/A 45833-2025 artfynd.xlsx
@@ -1078,32 +1078,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129035039</v>
+        <v>129035030</v>
       </c>
       <c r="B6" t="n">
-        <v>98659</v>
+        <v>97530</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>569394</v>
+        <v>569424</v>
       </c>
       <c r="R6" t="n">
-        <v>6949664</v>
+        <v>6949671</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1149,11 +1149,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1180,32 +1175,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129035030</v>
+        <v>129035039</v>
       </c>
       <c r="B7" t="n">
-        <v>97530</v>
+        <v>98659</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>569424</v>
+        <v>569394</v>
       </c>
       <c r="R7" t="n">
-        <v>6949671</v>
+        <v>6949664</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1251,6 +1246,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1379,32 +1379,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129035014</v>
+        <v>129035054</v>
       </c>
       <c r="B9" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>569455</v>
+        <v>569126</v>
       </c>
       <c r="R9" t="n">
-        <v>6949703</v>
+        <v>6949570</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>13 ex</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1481,32 +1481,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129035054</v>
+        <v>129035014</v>
       </c>
       <c r="B10" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>569126</v>
+        <v>569455</v>
       </c>
       <c r="R10" t="n">
-        <v>6949570</v>
+        <v>6949703</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>13 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1583,10 +1583,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129034594</v>
+        <v>129034630</v>
       </c>
       <c r="B11" t="n">
-        <v>91811</v>
+        <v>79035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1594,21 +1594,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>569203</v>
+        <v>569231</v>
       </c>
       <c r="R11" t="n">
-        <v>6949498</v>
+        <v>6949559</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1654,11 +1654,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>11 exemplar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1685,32 +1680,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129034630</v>
+        <v>129035055</v>
       </c>
       <c r="B12" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1720,10 +1715,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569231</v>
+        <v>569221</v>
       </c>
       <c r="R12" t="n">
-        <v>6949559</v>
+        <v>6949406</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1756,6 +1751,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1782,32 +1782,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129034648</v>
+        <v>129035042</v>
       </c>
       <c r="B13" t="n">
-        <v>96778</v>
+        <v>98659</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1817,10 +1817,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569279</v>
+        <v>569200</v>
       </c>
       <c r="R13" t="n">
-        <v>6949401</v>
+        <v>6949533</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1853,6 +1853,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>30 ex</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1879,10 +1884,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129034577</v>
+        <v>129034594</v>
       </c>
       <c r="B14" t="n">
-        <v>57723</v>
+        <v>91811</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1890,21 +1895,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1914,10 +1919,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569496</v>
+        <v>569203</v>
       </c>
       <c r="R14" t="n">
-        <v>6949627</v>
+        <v>6949498</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1954,7 +1959,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på tall</t>
+          <t>11 exemplar</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1981,32 +1986,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129035055</v>
+        <v>129034648</v>
       </c>
       <c r="B15" t="n">
-        <v>98659</v>
+        <v>96778</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2016,10 +2021,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>569221</v>
+        <v>569279</v>
       </c>
       <c r="R15" t="n">
-        <v>6949406</v>
+        <v>6949401</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2052,11 +2057,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>25 ex</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2083,32 +2083,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129035042</v>
+        <v>129034577</v>
       </c>
       <c r="B16" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>569200</v>
+        <v>569496</v>
       </c>
       <c r="R16" t="n">
-        <v>6949533</v>
+        <v>6949627</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>30 ex</t>
+          <t>Äldre ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2185,32 +2185,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129035059</v>
+        <v>129034629</v>
       </c>
       <c r="B17" t="n">
-        <v>92819</v>
+        <v>79035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2220,10 +2220,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>569273</v>
+        <v>569247</v>
       </c>
       <c r="R17" t="n">
-        <v>6949537</v>
+        <v>6949558</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2282,32 +2282,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129034629</v>
+        <v>129035059</v>
       </c>
       <c r="B18" t="n">
-        <v>79035</v>
+        <v>92819</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2317,10 +2317,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>569247</v>
+        <v>569273</v>
       </c>
       <c r="R18" t="n">
-        <v>6949558</v>
+        <v>6949537</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2379,7 +2379,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129035009</v>
+        <v>129034580</v>
       </c>
       <c r="B19" t="n">
         <v>57723</v>
@@ -2414,10 +2414,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>569314</v>
+        <v>569396</v>
       </c>
       <c r="R19" t="n">
-        <v>6949502</v>
+        <v>6949738</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Äldre ringhack på Tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2481,7 +2481,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129034580</v>
+        <v>129035009</v>
       </c>
       <c r="B20" t="n">
         <v>57723</v>
@@ -2516,10 +2516,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>569396</v>
+        <v>569314</v>
       </c>
       <c r="R20" t="n">
-        <v>6949738</v>
+        <v>6949502</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Äldre ringhack på Tall</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2787,10 +2787,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129034592</v>
+        <v>129035004</v>
       </c>
       <c r="B23" t="n">
-        <v>91811</v>
+        <v>91526</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2798,21 +2798,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569205</v>
+        <v>569152</v>
       </c>
       <c r="R23" t="n">
-        <v>6949497</v>
+        <v>6949557</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2858,11 +2858,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>1 x</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2889,10 +2884,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129034591</v>
+        <v>129035005</v>
       </c>
       <c r="B24" t="n">
-        <v>91811</v>
+        <v>91526</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2900,21 +2895,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2924,10 +2919,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569203</v>
+        <v>569188</v>
       </c>
       <c r="R24" t="n">
-        <v>6949513</v>
+        <v>6949496</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2960,11 +2955,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>11 ex</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3088,10 +3078,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129035004</v>
+        <v>129034592</v>
       </c>
       <c r="B26" t="n">
-        <v>91526</v>
+        <v>91811</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3099,21 +3089,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3123,10 +3113,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569152</v>
+        <v>569205</v>
       </c>
       <c r="R26" t="n">
-        <v>6949557</v>
+        <v>6949497</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3159,6 +3149,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>1 x</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3185,7 +3180,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129035025</v>
+        <v>129034591</v>
       </c>
       <c r="B27" t="n">
         <v>91811</v>
@@ -3220,10 +3215,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>569388</v>
+        <v>569203</v>
       </c>
       <c r="R27" t="n">
-        <v>6949665</v>
+        <v>6949513</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3256,6 +3251,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>11 ex</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3282,10 +3282,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129035005</v>
+        <v>129035025</v>
       </c>
       <c r="B28" t="n">
-        <v>91526</v>
+        <v>91811</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3293,21 +3293,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3317,10 +3317,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>569188</v>
+        <v>569388</v>
       </c>
       <c r="R28" t="n">
-        <v>6949496</v>
+        <v>6949665</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3578,10 +3578,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129034578</v>
+        <v>129035058</v>
       </c>
       <c r="B31" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3589,21 +3589,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>569420</v>
+        <v>569388</v>
       </c>
       <c r="R31" t="n">
-        <v>6949723</v>
+        <v>6949647</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3649,11 +3649,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3680,32 +3675,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129034637</v>
+        <v>129035031</v>
       </c>
       <c r="B32" t="n">
-        <v>92819</v>
+        <v>80140</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3715,10 +3710,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>569229</v>
+        <v>569125</v>
       </c>
       <c r="R32" t="n">
-        <v>6949400</v>
+        <v>6949570</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3777,32 +3772,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129035058</v>
+        <v>129034637</v>
       </c>
       <c r="B33" t="n">
-        <v>79035</v>
+        <v>92819</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3812,10 +3807,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>569388</v>
+        <v>569229</v>
       </c>
       <c r="R33" t="n">
-        <v>6949647</v>
+        <v>6949400</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3874,10 +3869,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129035031</v>
+        <v>129034578</v>
       </c>
       <c r="B34" t="n">
-        <v>80140</v>
+        <v>57723</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3885,21 +3880,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3909,10 +3904,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>569125</v>
+        <v>569420</v>
       </c>
       <c r="R34" t="n">
-        <v>6949570</v>
+        <v>6949723</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3945,6 +3940,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4073,32 +4073,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129034602</v>
+        <v>129034634</v>
       </c>
       <c r="B36" t="n">
-        <v>98659</v>
+        <v>79035</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4108,10 +4108,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>569301</v>
+        <v>569200</v>
       </c>
       <c r="R36" t="n">
-        <v>6949480</v>
+        <v>6949411</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4144,11 +4144,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>22 stycken</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4175,32 +4170,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129035040</v>
+        <v>129035015</v>
       </c>
       <c r="B37" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4210,10 +4205,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>569386</v>
+        <v>569454</v>
       </c>
       <c r="R37" t="n">
-        <v>6949657</v>
+        <v>6949698</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4250,7 +4245,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>9 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4277,32 +4272,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129035045</v>
+        <v>129035020</v>
       </c>
       <c r="B38" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4312,10 +4307,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>569130</v>
+        <v>569171</v>
       </c>
       <c r="R38" t="n">
-        <v>6949603</v>
+        <v>6949543</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4352,7 +4347,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>14 ex</t>
+          <t>Äldre ringhack på granhögstubbe</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4379,32 +4374,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129034634</v>
+        <v>129034602</v>
       </c>
       <c r="B39" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4414,10 +4409,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>569200</v>
+        <v>569301</v>
       </c>
       <c r="R39" t="n">
-        <v>6949411</v>
+        <v>6949480</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4450,6 +4445,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>22 stycken</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4476,32 +4476,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129035020</v>
+        <v>129035040</v>
       </c>
       <c r="B40" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4511,10 +4511,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>569171</v>
+        <v>569386</v>
       </c>
       <c r="R40" t="n">
-        <v>6949543</v>
+        <v>6949657</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4551,7 +4551,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Äldre ringhack på granhögstubbe</t>
+          <t>9 ex</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4578,32 +4578,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129035015</v>
+        <v>129035045</v>
       </c>
       <c r="B41" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4613,10 +4613,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>569454</v>
+        <v>569130</v>
       </c>
       <c r="R41" t="n">
-        <v>6949698</v>
+        <v>6949603</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4653,7 +4653,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>14 ex</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4879,32 +4879,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129034607</v>
+        <v>129035011</v>
       </c>
       <c r="B44" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4914,10 +4914,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>569317</v>
+        <v>569442</v>
       </c>
       <c r="R44" t="n">
-        <v>6949549</v>
+        <v>6949783</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>31 stycken</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4981,32 +4981,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129035041</v>
+        <v>129034575</v>
       </c>
       <c r="B45" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5016,10 +5016,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>569262</v>
+        <v>569448</v>
       </c>
       <c r="R45" t="n">
-        <v>6949524</v>
+        <v>6949625</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>5 ex</t>
+          <t>Färska ringhack på Tall av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5083,32 +5083,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129034575</v>
+        <v>129034607</v>
       </c>
       <c r="B46" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5118,10 +5118,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>569448</v>
+        <v>569317</v>
       </c>
       <c r="R46" t="n">
-        <v>6949625</v>
+        <v>6949549</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Färska ringhack på Tall av tretåig hackspett</t>
+          <t>31 stycken</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5185,32 +5185,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129035011</v>
+        <v>129035041</v>
       </c>
       <c r="B47" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5220,10 +5220,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>569442</v>
+        <v>569262</v>
       </c>
       <c r="R47" t="n">
-        <v>6949783</v>
+        <v>6949524</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5260,7 +5260,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5287,32 +5287,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129035022</v>
+        <v>129034616</v>
       </c>
       <c r="B48" t="n">
-        <v>91811</v>
+        <v>98659</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5322,10 +5322,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>569423</v>
+        <v>569223</v>
       </c>
       <c r="R48" t="n">
-        <v>6949656</v>
+        <v>6949465</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5358,6 +5358,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>10 stycken</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5384,7 +5389,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129034597</v>
+        <v>129035022</v>
       </c>
       <c r="B49" t="n">
         <v>91811</v>
@@ -5419,10 +5424,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>569221</v>
+        <v>569423</v>
       </c>
       <c r="R49" t="n">
-        <v>6949499</v>
+        <v>6949656</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5455,11 +5460,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>8 exemplar</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5486,10 +5486,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129035002</v>
+        <v>129034597</v>
       </c>
       <c r="B50" t="n">
-        <v>91526</v>
+        <v>91811</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5497,21 +5497,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5521,10 +5521,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>569405</v>
+        <v>569221</v>
       </c>
       <c r="R50" t="n">
-        <v>6949685</v>
+        <v>6949499</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5557,6 +5557,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>8 exemplar</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5583,10 +5588,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129035016</v>
+        <v>129035002</v>
       </c>
       <c r="B51" t="n">
-        <v>57723</v>
+        <v>91526</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5594,21 +5599,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5618,10 +5623,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>569435</v>
+        <v>569405</v>
       </c>
       <c r="R51" t="n">
-        <v>6949665</v>
+        <v>6949685</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5654,11 +5659,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5685,32 +5685,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129034632</v>
+        <v>129035062</v>
       </c>
       <c r="B52" t="n">
-        <v>79035</v>
+        <v>96778</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5720,10 +5720,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>569237</v>
+        <v>569478</v>
       </c>
       <c r="R52" t="n">
-        <v>6949442</v>
+        <v>6949666</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5782,32 +5782,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129035062</v>
+        <v>129034632</v>
       </c>
       <c r="B53" t="n">
-        <v>96778</v>
+        <v>79035</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5817,10 +5817,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>569478</v>
+        <v>569237</v>
       </c>
       <c r="R53" t="n">
-        <v>6949666</v>
+        <v>6949442</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5879,32 +5879,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129034616</v>
+        <v>129035016</v>
       </c>
       <c r="B54" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5914,10 +5914,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>569223</v>
+        <v>569435</v>
       </c>
       <c r="R54" t="n">
-        <v>6949465</v>
+        <v>6949665</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5954,7 +5954,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>10 stycken</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5981,10 +5981,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129034600</v>
+        <v>129034581</v>
       </c>
       <c r="B55" t="n">
-        <v>80140</v>
+        <v>57883</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5992,21 +5992,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6016,10 +6016,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>569481</v>
+        <v>569223</v>
       </c>
       <c r="R55" t="n">
-        <v>6949674</v>
+        <v>6949401</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Apothecier antal 1</t>
+          <t>Sågs och gjorde övriga läten</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6083,32 +6083,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129034610</v>
+        <v>129035028</v>
       </c>
       <c r="B56" t="n">
-        <v>98659</v>
+        <v>91811</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6118,10 +6118,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>569282</v>
+        <v>569192</v>
       </c>
       <c r="R56" t="n">
-        <v>6949567</v>
+        <v>6949509</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6154,11 +6154,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ca 100 stycken</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6185,32 +6180,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129034614</v>
+        <v>129035008</v>
       </c>
       <c r="B57" t="n">
-        <v>98659</v>
+        <v>91526</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6220,10 +6215,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>569237</v>
+        <v>569216</v>
       </c>
       <c r="R57" t="n">
-        <v>6949556</v>
+        <v>6949430</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6256,11 +6251,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>5 stycken</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6287,10 +6277,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129035028</v>
+        <v>129034600</v>
       </c>
       <c r="B58" t="n">
-        <v>91811</v>
+        <v>80140</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6298,21 +6288,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6322,10 +6312,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>569192</v>
+        <v>569481</v>
       </c>
       <c r="R58" t="n">
-        <v>6949509</v>
+        <v>6949674</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6358,6 +6348,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Apothecier antal 1</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6384,32 +6379,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129035008</v>
+        <v>129034610</v>
       </c>
       <c r="B59" t="n">
-        <v>91526</v>
+        <v>98659</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6419,10 +6414,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>569216</v>
+        <v>569282</v>
       </c>
       <c r="R59" t="n">
-        <v>6949430</v>
+        <v>6949567</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6455,6 +6450,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ca 100 stycken</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6481,32 +6481,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129034581</v>
+        <v>129034614</v>
       </c>
       <c r="B60" t="n">
-        <v>57883</v>
+        <v>98659</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6516,10 +6516,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>569223</v>
+        <v>569237</v>
       </c>
       <c r="R60" t="n">
-        <v>6949401</v>
+        <v>6949556</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6556,7 +6556,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Sågs och gjorde övriga läten</t>
+          <t>5 stycken</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6583,32 +6583,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129034586</v>
+        <v>129035024</v>
       </c>
       <c r="B61" t="n">
-        <v>91981</v>
+        <v>91811</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6618,10 +6618,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>569220</v>
+        <v>569404</v>
       </c>
       <c r="R61" t="n">
-        <v>6949500</v>
+        <v>6949660</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6680,32 +6680,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129035024</v>
+        <v>129034586</v>
       </c>
       <c r="B62" t="n">
-        <v>91811</v>
+        <v>91981</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6715,10 +6715,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>569404</v>
+        <v>569220</v>
       </c>
       <c r="R62" t="n">
-        <v>6949660</v>
+        <v>6949500</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6777,10 +6777,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129035003</v>
+        <v>129035021</v>
       </c>
       <c r="B63" t="n">
-        <v>91526</v>
+        <v>91811</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6788,21 +6788,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6812,10 +6812,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>569164</v>
+        <v>569446</v>
       </c>
       <c r="R63" t="n">
-        <v>6949559</v>
+        <v>6949629</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6874,10 +6874,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129034587</v>
+        <v>129035003</v>
       </c>
       <c r="B64" t="n">
-        <v>91811</v>
+        <v>91526</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6885,21 +6885,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6909,10 +6909,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>569463</v>
+        <v>569164</v>
       </c>
       <c r="R64" t="n">
-        <v>6949711</v>
+        <v>6949559</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6971,10 +6971,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129035021</v>
+        <v>129034574</v>
       </c>
       <c r="B65" t="n">
-        <v>91811</v>
+        <v>91526</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6982,21 +6982,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7006,10 +7006,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>569446</v>
+        <v>569461</v>
       </c>
       <c r="R65" t="n">
-        <v>6949629</v>
+        <v>6949706</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7068,10 +7068,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129034574</v>
+        <v>129034587</v>
       </c>
       <c r="B66" t="n">
-        <v>91526</v>
+        <v>91811</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7079,21 +7079,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7103,10 +7103,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>569461</v>
+        <v>569463</v>
       </c>
       <c r="R66" t="n">
-        <v>6949706</v>
+        <v>6949711</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7165,49 +7165,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129027791</v>
+        <v>129034624</v>
       </c>
       <c r="B67" t="n">
-        <v>98659</v>
+        <v>105722</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Sandsjömyran, Mpd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>569308</v>
+        <v>569234</v>
       </c>
       <c r="R67" t="n">
-        <v>6949546</v>
+        <v>6949440</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7240,6 +7236,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>9 exemplar</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7266,7 +7267,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129035035</v>
+        <v>129027791</v>
       </c>
       <c r="B68" t="n">
         <v>98659</v>
@@ -7294,17 +7295,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Sandsjömyran, Mpd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>569317</v>
+        <v>569308</v>
       </c>
       <c r="R68" t="n">
-        <v>6949469</v>
+        <v>6949546</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7337,11 +7342,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>5 ex</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7368,32 +7368,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129034624</v>
+        <v>129035035</v>
       </c>
       <c r="B69" t="n">
-        <v>105722</v>
+        <v>98659</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7403,10 +7403,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>569234</v>
+        <v>569317</v>
       </c>
       <c r="R69" t="n">
-        <v>6949440</v>
+        <v>6949469</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7443,7 +7443,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>9 exemplar</t>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7980,10 +7980,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129034598</v>
+        <v>129034645</v>
       </c>
       <c r="B75" t="n">
-        <v>97530</v>
+        <v>92819</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7991,21 +7991,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8015,10 +8015,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>569460</v>
+        <v>569196</v>
       </c>
       <c r="R75" t="n">
-        <v>6949629</v>
+        <v>6949411</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8051,6 +8051,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>4 färska exemplar 3 äldre exemplar</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8077,32 +8082,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129034650</v>
+        <v>129034642</v>
       </c>
       <c r="B76" t="n">
-        <v>98659</v>
+        <v>92819</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8112,10 +8117,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>569303</v>
+        <v>569283</v>
       </c>
       <c r="R76" t="n">
-        <v>6949537</v>
+        <v>6949655</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8152,7 +8157,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>30 stycken ( finns eventuellt mer )</t>
+          <t>7 äldre exemplar</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8179,32 +8184,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129034605</v>
+        <v>129026691</v>
       </c>
       <c r="B77" t="n">
-        <v>98659</v>
+        <v>91811</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8214,10 +8219,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>569305</v>
+        <v>569195</v>
       </c>
       <c r="R77" t="n">
-        <v>6949538</v>
+        <v>6949487</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8250,11 +8255,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>21 knärot</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8281,32 +8281,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129026691</v>
+        <v>129034598</v>
       </c>
       <c r="B78" t="n">
-        <v>91811</v>
+        <v>97530</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8316,10 +8316,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>569195</v>
+        <v>569460</v>
       </c>
       <c r="R78" t="n">
-        <v>6949487</v>
+        <v>6949629</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8378,32 +8378,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129034645</v>
+        <v>129034650</v>
       </c>
       <c r="B79" t="n">
-        <v>92819</v>
+        <v>98659</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8413,10 +8413,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>569196</v>
+        <v>569303</v>
       </c>
       <c r="R79" t="n">
-        <v>6949411</v>
+        <v>6949537</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8453,7 +8453,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>4 färska exemplar 3 äldre exemplar</t>
+          <t>30 stycken ( finns eventuellt mer )</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8480,32 +8480,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129034642</v>
+        <v>129034605</v>
       </c>
       <c r="B80" t="n">
-        <v>92819</v>
+        <v>98659</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8515,10 +8515,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>569283</v>
+        <v>569305</v>
       </c>
       <c r="R80" t="n">
-        <v>6949655</v>
+        <v>6949538</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8555,7 +8555,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>7 äldre exemplar</t>
+          <t>21 knärot</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8582,32 +8582,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129035007</v>
+        <v>129035061</v>
       </c>
       <c r="B81" t="n">
-        <v>91526</v>
+        <v>96778</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>2869</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8617,10 +8617,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>569225</v>
+        <v>569333</v>
       </c>
       <c r="R81" t="n">
-        <v>6949424</v>
+        <v>6949607</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8679,32 +8679,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129035012</v>
+        <v>129035001</v>
       </c>
       <c r="B82" t="n">
-        <v>57723</v>
+        <v>91491</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8714,10 +8714,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>569435</v>
+        <v>569232</v>
       </c>
       <c r="R82" t="n">
-        <v>6949783</v>
+        <v>6949444</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8750,11 +8750,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8781,32 +8776,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129035047</v>
+        <v>129035007</v>
       </c>
       <c r="B83" t="n">
-        <v>98659</v>
+        <v>91526</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8816,10 +8811,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>569162</v>
+        <v>569225</v>
       </c>
       <c r="R83" t="n">
-        <v>6949566</v>
+        <v>6949424</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8852,11 +8847,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>50 ex</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8883,32 +8873,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129034604</v>
+        <v>129034640</v>
       </c>
       <c r="B84" t="n">
-        <v>98659</v>
+        <v>92819</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8918,10 +8908,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>569303</v>
+        <v>569213</v>
       </c>
       <c r="R84" t="n">
-        <v>6949536</v>
+        <v>6949414</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8958,7 +8948,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>40 stycken</t>
+          <t>16 exemplar</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8985,32 +8975,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129034618</v>
+        <v>129035057</v>
       </c>
       <c r="B85" t="n">
-        <v>98659</v>
+        <v>79035</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9020,10 +9010,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>569235</v>
+        <v>569464</v>
       </c>
       <c r="R85" t="n">
-        <v>6949411</v>
+        <v>6949648</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9056,11 +9046,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9087,32 +9072,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129034640</v>
+        <v>129035012</v>
       </c>
       <c r="B86" t="n">
-        <v>92819</v>
+        <v>57723</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9122,10 +9107,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>569213</v>
+        <v>569435</v>
       </c>
       <c r="R86" t="n">
-        <v>6949414</v>
+        <v>6949783</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9162,7 +9147,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>16 exemplar</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9189,32 +9174,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129035001</v>
+        <v>129035047</v>
       </c>
       <c r="B87" t="n">
-        <v>91491</v>
+        <v>98659</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9224,10 +9209,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>569232</v>
+        <v>569162</v>
       </c>
       <c r="R87" t="n">
-        <v>6949444</v>
+        <v>6949566</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9260,6 +9245,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9286,32 +9276,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129035057</v>
+        <v>129034604</v>
       </c>
       <c r="B88" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9321,10 +9311,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>569464</v>
+        <v>569303</v>
       </c>
       <c r="R88" t="n">
-        <v>6949648</v>
+        <v>6949536</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9357,6 +9347,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9383,32 +9378,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129035061</v>
+        <v>129034618</v>
       </c>
       <c r="B89" t="n">
-        <v>96778</v>
+        <v>98659</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9418,10 +9413,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>569333</v>
+        <v>569235</v>
       </c>
       <c r="R89" t="n">
-        <v>6949607</v>
+        <v>6949411</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9454,6 +9449,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9480,32 +9480,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129035023</v>
+        <v>129035038</v>
       </c>
       <c r="B90" t="n">
-        <v>91811</v>
+        <v>98659</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>569415</v>
+        <v>569406</v>
       </c>
       <c r="R90" t="n">
-        <v>6949677</v>
+        <v>6949664</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9551,6 +9551,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9577,32 +9582,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129035027</v>
+        <v>129035050</v>
       </c>
       <c r="B91" t="n">
-        <v>91811</v>
+        <v>98659</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9612,10 +9617,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>569169</v>
+        <v>569236</v>
       </c>
       <c r="R91" t="n">
-        <v>6949533</v>
+        <v>6949440</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9648,6 +9653,11 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>4 ex</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9674,32 +9684,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129034589</v>
+        <v>129034621</v>
       </c>
       <c r="B92" t="n">
-        <v>91811</v>
+        <v>98659</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9709,10 +9719,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>569365</v>
+        <v>569247</v>
       </c>
       <c r="R92" t="n">
-        <v>6949661</v>
+        <v>6949434</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9745,6 +9755,11 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>10 stycken knärot</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9868,32 +9883,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129035038</v>
+        <v>129035023</v>
       </c>
       <c r="B94" t="n">
-        <v>98659</v>
+        <v>91811</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9903,10 +9918,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>569406</v>
+        <v>569415</v>
       </c>
       <c r="R94" t="n">
-        <v>6949664</v>
+        <v>6949677</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9939,11 +9954,6 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>20 ex</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -9970,32 +9980,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129035050</v>
+        <v>129034589</v>
       </c>
       <c r="B95" t="n">
-        <v>98659</v>
+        <v>91811</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10005,10 +10015,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>569236</v>
+        <v>569365</v>
       </c>
       <c r="R95" t="n">
-        <v>6949440</v>
+        <v>6949661</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10041,11 +10051,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>4 ex</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10072,32 +10077,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129034621</v>
+        <v>129035027</v>
       </c>
       <c r="B96" t="n">
-        <v>98659</v>
+        <v>91811</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10107,10 +10112,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>569247</v>
+        <v>569169</v>
       </c>
       <c r="R96" t="n">
-        <v>6949434</v>
+        <v>6949533</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10143,11 +10148,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>10 stycken knärot</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10475,32 +10475,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129035056</v>
+        <v>129034609</v>
       </c>
       <c r="B100" t="n">
-        <v>105722</v>
+        <v>98659</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10510,10 +10510,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>569201</v>
+        <v>569458</v>
       </c>
       <c r="R100" t="n">
-        <v>6949530</v>
+        <v>6949777</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10546,6 +10546,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>48 stycken</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10572,7 +10577,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129034609</v>
+        <v>129035036</v>
       </c>
       <c r="B101" t="n">
         <v>98659</v>
@@ -10607,10 +10612,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>569458</v>
+        <v>569330</v>
       </c>
       <c r="R101" t="n">
-        <v>6949777</v>
+        <v>6949564</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10647,7 +10652,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>48 stycken</t>
+          <t>8 ex</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10674,7 +10679,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129035036</v>
+        <v>129035052</v>
       </c>
       <c r="B102" t="n">
         <v>98659</v>
@@ -10709,10 +10714,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>569330</v>
+        <v>569405</v>
       </c>
       <c r="R102" t="n">
-        <v>6949564</v>
+        <v>6949641</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10749,7 +10754,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>8 ex</t>
+          <t>70 ex</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10776,32 +10781,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129035052</v>
+        <v>129035056</v>
       </c>
       <c r="B103" t="n">
-        <v>98659</v>
+        <v>105722</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10811,10 +10816,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>569405</v>
+        <v>569201</v>
       </c>
       <c r="R103" t="n">
-        <v>6949641</v>
+        <v>6949530</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10847,11 +10852,6 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>70 ex</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10878,32 +10878,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129035048</v>
+        <v>129035006</v>
       </c>
       <c r="B104" t="n">
-        <v>98659</v>
+        <v>91526</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10913,10 +10913,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>569176</v>
+        <v>569217</v>
       </c>
       <c r="R104" t="n">
-        <v>6949507</v>
+        <v>6949470</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10949,11 +10949,6 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>30 ex</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -10980,32 +10975,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129035053</v>
+        <v>129027886</v>
       </c>
       <c r="B105" t="n">
-        <v>98659</v>
+        <v>91526</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11015,10 +11010,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>569459</v>
+        <v>569305</v>
       </c>
       <c r="R105" t="n">
-        <v>6949662</v>
+        <v>6949566</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11051,11 +11046,6 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>14 ex</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11082,32 +11072,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129035049</v>
+        <v>129035026</v>
       </c>
       <c r="B106" t="n">
-        <v>98659</v>
+        <v>91811</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11117,10 +11107,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>569219</v>
+        <v>569175</v>
       </c>
       <c r="R106" t="n">
-        <v>6949489</v>
+        <v>6949549</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11153,11 +11143,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>35 ex</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11184,7 +11169,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129035044</v>
+        <v>129035048</v>
       </c>
       <c r="B107" t="n">
         <v>98659</v>
@@ -11219,10 +11204,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>569191</v>
+        <v>569176</v>
       </c>
       <c r="R107" t="n">
-        <v>6949579</v>
+        <v>6949507</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11259,7 +11244,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>50 ex</t>
+          <t>30 ex</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11286,32 +11271,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129035026</v>
+        <v>129035053</v>
       </c>
       <c r="B108" t="n">
-        <v>91811</v>
+        <v>98659</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11321,10 +11306,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>569175</v>
+        <v>569459</v>
       </c>
       <c r="R108" t="n">
-        <v>6949549</v>
+        <v>6949662</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11357,6 +11342,11 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>14 ex</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11383,32 +11373,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129035006</v>
+        <v>129035049</v>
       </c>
       <c r="B109" t="n">
-        <v>91526</v>
+        <v>98659</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11418,10 +11408,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>569217</v>
+        <v>569219</v>
       </c>
       <c r="R109" t="n">
-        <v>6949470</v>
+        <v>6949489</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11454,6 +11444,11 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>35 ex</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11480,32 +11475,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129027886</v>
+        <v>129035044</v>
       </c>
       <c r="B110" t="n">
-        <v>91526</v>
+        <v>98659</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11515,10 +11510,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>569305</v>
+        <v>569191</v>
       </c>
       <c r="R110" t="n">
-        <v>6949566</v>
+        <v>6949579</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11551,6 +11546,11 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD110" t="b">

--- a/artfynd/A 45833-2025 artfynd.xlsx
+++ b/artfynd/A 45833-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129034612</v>
+        <v>129034627</v>
       </c>
       <c r="B2" t="n">
-        <v>98659</v>
+        <v>79039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569243</v>
+        <v>569482</v>
       </c>
       <c r="R2" t="n">
-        <v>6949558</v>
+        <v>6949676</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>30  exemplar ca</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129035046</v>
+        <v>129034612</v>
       </c>
       <c r="B3" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569127</v>
+        <v>569243</v>
       </c>
       <c r="R3" t="n">
-        <v>6949602</v>
+        <v>6949558</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +847,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>13 ex</t>
+          <t>30  exemplar ca</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,7 +877,7 @@
         <v>129035043</v>
       </c>
       <c r="B4" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,32 +976,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129034627</v>
+        <v>129035046</v>
       </c>
       <c r="B5" t="n">
-        <v>79035</v>
+        <v>98669</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569482</v>
+        <v>569127</v>
       </c>
       <c r="R5" t="n">
-        <v>6949676</v>
+        <v>6949602</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1052,6 +1047,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>13 ex</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1078,32 +1078,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129035030</v>
+        <v>129035039</v>
       </c>
       <c r="B6" t="n">
-        <v>97530</v>
+        <v>98669</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>569424</v>
+        <v>569394</v>
       </c>
       <c r="R6" t="n">
-        <v>6949671</v>
+        <v>6949664</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1149,6 +1149,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1175,32 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129035039</v>
+        <v>129035030</v>
       </c>
       <c r="B7" t="n">
-        <v>98659</v>
+        <v>97540</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>569394</v>
+        <v>569424</v>
       </c>
       <c r="R7" t="n">
-        <v>6949664</v>
+        <v>6949671</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1246,11 +1251,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1277,32 +1277,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129035013</v>
+        <v>129035054</v>
       </c>
       <c r="B8" t="n">
-        <v>57723</v>
+        <v>98669</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>569455</v>
+        <v>569126</v>
       </c>
       <c r="R8" t="n">
-        <v>6949716</v>
+        <v>6949570</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>13 ex</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1379,32 +1379,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129035054</v>
+        <v>129035014</v>
       </c>
       <c r="B9" t="n">
-        <v>98659</v>
+        <v>57725</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>569126</v>
+        <v>569455</v>
       </c>
       <c r="R9" t="n">
-        <v>6949570</v>
+        <v>6949703</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>13 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1481,10 +1481,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129035014</v>
+        <v>129035013</v>
       </c>
       <c r="B10" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>569455</v>
       </c>
       <c r="R10" t="n">
-        <v>6949703</v>
+        <v>6949716</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1583,10 +1583,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129034630</v>
+        <v>129034594</v>
       </c>
       <c r="B11" t="n">
-        <v>79035</v>
+        <v>91818</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1594,21 +1594,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>569231</v>
+        <v>569203</v>
       </c>
       <c r="R11" t="n">
-        <v>6949559</v>
+        <v>6949498</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1654,6 +1654,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>11 exemplar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1680,32 +1685,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129035055</v>
+        <v>129034648</v>
       </c>
       <c r="B12" t="n">
-        <v>98659</v>
+        <v>96788</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1715,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569221</v>
+        <v>569279</v>
       </c>
       <c r="R12" t="n">
-        <v>6949406</v>
+        <v>6949401</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1751,11 +1756,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>25 ex</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1782,32 +1782,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129035042</v>
+        <v>129034630</v>
       </c>
       <c r="B13" t="n">
-        <v>98659</v>
+        <v>79039</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1817,10 +1817,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569200</v>
+        <v>569231</v>
       </c>
       <c r="R13" t="n">
-        <v>6949533</v>
+        <v>6949559</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1853,11 +1853,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>30 ex</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1884,32 +1879,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129034594</v>
+        <v>129035055</v>
       </c>
       <c r="B14" t="n">
-        <v>91811</v>
+        <v>98669</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1919,10 +1914,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569203</v>
+        <v>569221</v>
       </c>
       <c r="R14" t="n">
-        <v>6949498</v>
+        <v>6949406</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1959,7 +1954,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>11 exemplar</t>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1986,32 +1981,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129034648</v>
+        <v>129035042</v>
       </c>
       <c r="B15" t="n">
-        <v>96778</v>
+        <v>98669</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2021,10 +2016,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>569279</v>
+        <v>569200</v>
       </c>
       <c r="R15" t="n">
-        <v>6949401</v>
+        <v>6949533</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2057,6 +2052,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>30 ex</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2086,7 +2086,7 @@
         <v>129034577</v>
       </c>
       <c r="B16" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2185,32 +2185,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129034629</v>
+        <v>129035059</v>
       </c>
       <c r="B17" t="n">
-        <v>79035</v>
+        <v>92826</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2220,10 +2220,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>569247</v>
+        <v>569273</v>
       </c>
       <c r="R17" t="n">
-        <v>6949558</v>
+        <v>6949537</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2282,32 +2282,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129035059</v>
+        <v>129034629</v>
       </c>
       <c r="B18" t="n">
-        <v>92819</v>
+        <v>79039</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2317,10 +2317,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>569273</v>
+        <v>569247</v>
       </c>
       <c r="R18" t="n">
-        <v>6949537</v>
+        <v>6949558</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2382,7 +2382,7 @@
         <v>129034580</v>
       </c>
       <c r="B19" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2481,10 +2481,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129035009</v>
+        <v>129035019</v>
       </c>
       <c r="B20" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2516,10 +2516,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>569314</v>
+        <v>569117</v>
       </c>
       <c r="R20" t="n">
-        <v>6949502</v>
+        <v>6949581</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2583,10 +2583,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129035019</v>
+        <v>129035009</v>
       </c>
       <c r="B21" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2618,10 +2618,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>569117</v>
+        <v>569314</v>
       </c>
       <c r="R21" t="n">
-        <v>6949581</v>
+        <v>6949502</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2688,7 +2688,7 @@
         <v>129034620</v>
       </c>
       <c r="B22" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2787,10 +2787,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129035004</v>
+        <v>129034592</v>
       </c>
       <c r="B23" t="n">
-        <v>91526</v>
+        <v>91818</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2798,21 +2798,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569152</v>
+        <v>569205</v>
       </c>
       <c r="R23" t="n">
-        <v>6949557</v>
+        <v>6949497</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2858,6 +2858,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>1 x</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2884,10 +2889,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129035005</v>
+        <v>129034591</v>
       </c>
       <c r="B24" t="n">
-        <v>91526</v>
+        <v>91818</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2895,21 +2900,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2919,10 +2924,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569188</v>
+        <v>569203</v>
       </c>
       <c r="R24" t="n">
-        <v>6949496</v>
+        <v>6949513</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2955,6 +2960,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>11 ex</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2984,7 +2994,7 @@
         <v>129034647</v>
       </c>
       <c r="B25" t="n">
-        <v>88926</v>
+        <v>88930</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3078,10 +3088,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129034592</v>
+        <v>129035025</v>
       </c>
       <c r="B26" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3113,10 +3123,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569205</v>
+        <v>569388</v>
       </c>
       <c r="R26" t="n">
-        <v>6949497</v>
+        <v>6949665</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3149,11 +3159,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>1 x</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3180,10 +3185,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129034591</v>
+        <v>129035005</v>
       </c>
       <c r="B27" t="n">
-        <v>91811</v>
+        <v>91533</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3191,21 +3196,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3215,10 +3220,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>569203</v>
+        <v>569188</v>
       </c>
       <c r="R27" t="n">
-        <v>6949513</v>
+        <v>6949496</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3251,11 +3256,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>11 ex</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3282,10 +3282,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129035025</v>
+        <v>129035004</v>
       </c>
       <c r="B28" t="n">
-        <v>91811</v>
+        <v>91533</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3293,21 +3293,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3317,10 +3317,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>569388</v>
+        <v>569152</v>
       </c>
       <c r="R28" t="n">
-        <v>6949665</v>
+        <v>6949557</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3382,7 +3382,7 @@
         <v>129034625</v>
       </c>
       <c r="B29" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>129034623</v>
       </c>
       <c r="B30" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3578,32 +3578,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129035058</v>
+        <v>129034637</v>
       </c>
       <c r="B31" t="n">
-        <v>79035</v>
+        <v>92826</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>569388</v>
+        <v>569229</v>
       </c>
       <c r="R31" t="n">
-        <v>6949647</v>
+        <v>6949400</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3675,10 +3675,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129035031</v>
+        <v>129035058</v>
       </c>
       <c r="B32" t="n">
-        <v>80140</v>
+        <v>79039</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3686,21 +3686,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3710,10 +3710,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>569125</v>
+        <v>569388</v>
       </c>
       <c r="R32" t="n">
-        <v>6949570</v>
+        <v>6949647</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3772,32 +3772,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129034637</v>
+        <v>129035031</v>
       </c>
       <c r="B33" t="n">
-        <v>92819</v>
+        <v>80144</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3807,10 +3807,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>569229</v>
+        <v>569125</v>
       </c>
       <c r="R33" t="n">
-        <v>6949400</v>
+        <v>6949570</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3872,7 +3872,7 @@
         <v>129034578</v>
       </c>
       <c r="B34" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
         <v>129035051</v>
       </c>
       <c r="B35" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4073,32 +4073,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129034634</v>
+        <v>129034602</v>
       </c>
       <c r="B36" t="n">
-        <v>79035</v>
+        <v>98669</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4108,10 +4108,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>569200</v>
+        <v>569301</v>
       </c>
       <c r="R36" t="n">
-        <v>6949411</v>
+        <v>6949480</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4144,6 +4144,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>22 stycken</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4170,32 +4175,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129035015</v>
+        <v>129035040</v>
       </c>
       <c r="B37" t="n">
-        <v>57723</v>
+        <v>98669</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4205,10 +4210,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>569454</v>
+        <v>569386</v>
       </c>
       <c r="R37" t="n">
-        <v>6949698</v>
+        <v>6949657</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4245,7 +4250,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>9 ex</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4272,32 +4277,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129035020</v>
+        <v>129035045</v>
       </c>
       <c r="B38" t="n">
-        <v>57723</v>
+        <v>98669</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4307,10 +4312,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>569171</v>
+        <v>569130</v>
       </c>
       <c r="R38" t="n">
-        <v>6949543</v>
+        <v>6949603</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4347,7 +4352,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Äldre ringhack på granhögstubbe</t>
+          <t>14 ex</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4374,32 +4379,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129034602</v>
+        <v>129035015</v>
       </c>
       <c r="B39" t="n">
-        <v>98659</v>
+        <v>57725</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4409,10 +4414,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>569301</v>
+        <v>569454</v>
       </c>
       <c r="R39" t="n">
-        <v>6949480</v>
+        <v>6949698</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4449,7 +4454,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>22 stycken</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4476,32 +4481,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129035040</v>
+        <v>129035020</v>
       </c>
       <c r="B40" t="n">
-        <v>98659</v>
+        <v>57725</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4511,10 +4516,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>569386</v>
+        <v>569171</v>
       </c>
       <c r="R40" t="n">
-        <v>6949657</v>
+        <v>6949543</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4551,7 +4556,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>9 ex</t>
+          <t>Äldre ringhack på granhögstubbe</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4578,32 +4583,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129035045</v>
+        <v>129034634</v>
       </c>
       <c r="B41" t="n">
-        <v>98659</v>
+        <v>79039</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4613,10 +4618,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>569130</v>
+        <v>569200</v>
       </c>
       <c r="R41" t="n">
-        <v>6949603</v>
+        <v>6949411</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4649,11 +4654,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>14 ex</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4680,10 +4680,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129034643</v>
+        <v>129035063</v>
       </c>
       <c r="B42" t="n">
-        <v>92819</v>
+        <v>96788</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4691,21 +4691,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>2869</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4715,10 +4715,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>569254</v>
+        <v>569455</v>
       </c>
       <c r="R42" t="n">
-        <v>6949431</v>
+        <v>6949758</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4751,11 +4751,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>1 färskt exemplar</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4782,10 +4777,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129035063</v>
+        <v>129034643</v>
       </c>
       <c r="B43" t="n">
-        <v>96778</v>
+        <v>92826</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4793,21 +4788,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2869</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4817,10 +4812,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>569455</v>
+        <v>569254</v>
       </c>
       <c r="R43" t="n">
-        <v>6949758</v>
+        <v>6949431</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4853,6 +4848,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>1 färskt exemplar</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4882,7 +4882,7 @@
         <v>129035011</v>
       </c>
       <c r="B44" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>129034575</v>
       </c>
       <c r="B45" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         <v>129034607</v>
       </c>
       <c r="B46" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
         <v>129035041</v>
       </c>
       <c r="B47" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5287,32 +5287,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129034616</v>
+        <v>129035022</v>
       </c>
       <c r="B48" t="n">
-        <v>98659</v>
+        <v>91818</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5322,10 +5322,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>569223</v>
+        <v>569423</v>
       </c>
       <c r="R48" t="n">
-        <v>6949465</v>
+        <v>6949656</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5358,11 +5358,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>10 stycken</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5389,10 +5384,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129035022</v>
+        <v>129034597</v>
       </c>
       <c r="B49" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5424,10 +5419,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>569423</v>
+        <v>569221</v>
       </c>
       <c r="R49" t="n">
-        <v>6949656</v>
+        <v>6949499</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5460,6 +5455,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>8 exemplar</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5486,10 +5486,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129034597</v>
+        <v>129035002</v>
       </c>
       <c r="B50" t="n">
-        <v>91811</v>
+        <v>91533</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5497,21 +5497,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5521,10 +5521,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>569221</v>
+        <v>569405</v>
       </c>
       <c r="R50" t="n">
-        <v>6949499</v>
+        <v>6949685</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5557,11 +5557,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>8 exemplar</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5588,32 +5583,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129035002</v>
+        <v>129035062</v>
       </c>
       <c r="B51" t="n">
-        <v>91526</v>
+        <v>96788</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>2869</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5623,10 +5618,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>569405</v>
+        <v>569478</v>
       </c>
       <c r="R51" t="n">
-        <v>6949685</v>
+        <v>6949666</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5685,32 +5680,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129035062</v>
+        <v>129034616</v>
       </c>
       <c r="B52" t="n">
-        <v>96778</v>
+        <v>98669</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5720,10 +5715,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>569478</v>
+        <v>569223</v>
       </c>
       <c r="R52" t="n">
-        <v>6949666</v>
+        <v>6949465</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5756,6 +5751,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>10 stycken</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5785,7 +5785,7 @@
         <v>129034632</v>
       </c>
       <c r="B53" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5882,7 +5882,7 @@
         <v>129035016</v>
       </c>
       <c r="B54" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5981,10 +5981,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129034581</v>
+        <v>129035028</v>
       </c>
       <c r="B55" t="n">
-        <v>57883</v>
+        <v>91818</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5992,21 +5992,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6016,10 +6016,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>569223</v>
+        <v>569192</v>
       </c>
       <c r="R55" t="n">
-        <v>6949401</v>
+        <v>6949509</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6052,11 +6052,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Sågs och gjorde övriga läten</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6083,10 +6078,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129035028</v>
+        <v>129035008</v>
       </c>
       <c r="B56" t="n">
-        <v>91811</v>
+        <v>91533</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6094,21 +6089,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6118,10 +6113,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>569192</v>
+        <v>569216</v>
       </c>
       <c r="R56" t="n">
-        <v>6949509</v>
+        <v>6949430</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6180,10 +6175,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129035008</v>
+        <v>129034600</v>
       </c>
       <c r="B57" t="n">
-        <v>91526</v>
+        <v>80144</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6191,21 +6186,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6215,10 +6210,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>569216</v>
+        <v>569481</v>
       </c>
       <c r="R57" t="n">
-        <v>6949430</v>
+        <v>6949674</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6251,6 +6246,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Apothecier antal 1</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6277,10 +6277,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129034600</v>
+        <v>129034581</v>
       </c>
       <c r="B58" t="n">
-        <v>80140</v>
+        <v>57885</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6288,21 +6288,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6312,10 +6312,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>569481</v>
+        <v>569223</v>
       </c>
       <c r="R58" t="n">
-        <v>6949674</v>
+        <v>6949401</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Apothecier antal 1</t>
+          <t>Sågs och gjorde övriga läten</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6382,7 +6382,7 @@
         <v>129034610</v>
       </c>
       <c r="B59" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6484,7 +6484,7 @@
         <v>129034614</v>
       </c>
       <c r="B60" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6586,7 +6586,7 @@
         <v>129035024</v>
       </c>
       <c r="B61" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6683,7 +6683,7 @@
         <v>129034586</v>
       </c>
       <c r="B62" t="n">
-        <v>91981</v>
+        <v>91988</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6777,10 +6777,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129035021</v>
+        <v>129034587</v>
       </c>
       <c r="B63" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6812,10 +6812,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>569446</v>
+        <v>569463</v>
       </c>
       <c r="R63" t="n">
-        <v>6949629</v>
+        <v>6949711</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6874,10 +6874,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129035003</v>
+        <v>129035021</v>
       </c>
       <c r="B64" t="n">
-        <v>91526</v>
+        <v>91818</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6885,21 +6885,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6909,10 +6909,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>569164</v>
+        <v>569446</v>
       </c>
       <c r="R64" t="n">
-        <v>6949559</v>
+        <v>6949629</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6974,7 +6974,7 @@
         <v>129034574</v>
       </c>
       <c r="B65" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7068,10 +7068,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129034587</v>
+        <v>129035003</v>
       </c>
       <c r="B66" t="n">
-        <v>91811</v>
+        <v>91533</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7079,21 +7079,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7103,10 +7103,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>569463</v>
+        <v>569164</v>
       </c>
       <c r="R66" t="n">
-        <v>6949711</v>
+        <v>6949559</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7165,45 +7165,49 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129034624</v>
+        <v>129027791</v>
       </c>
       <c r="B67" t="n">
-        <v>105722</v>
+        <v>98669</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Sandsjömyran, Mpd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>569234</v>
+        <v>569308</v>
       </c>
       <c r="R67" t="n">
-        <v>6949440</v>
+        <v>6949546</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7236,11 +7240,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>9 exemplar</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7267,49 +7266,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129027791</v>
+        <v>129034624</v>
       </c>
       <c r="B68" t="n">
-        <v>98659</v>
+        <v>105732</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Sandsjömyran, Mpd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>569308</v>
+        <v>569234</v>
       </c>
       <c r="R68" t="n">
-        <v>6949546</v>
+        <v>6949440</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7342,6 +7337,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>9 exemplar</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7371,7 +7371,7 @@
         <v>129035035</v>
       </c>
       <c r="B69" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7470,10 +7470,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129035060</v>
+        <v>129034639</v>
       </c>
       <c r="B70" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7505,10 +7505,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>569208</v>
+        <v>569398</v>
       </c>
       <c r="R70" t="n">
-        <v>6949415</v>
+        <v>6949741</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7545,7 +7545,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>20 ex minst</t>
+          <t>6 äldre exemplar och 1 färsk fruktkropp</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7572,10 +7572,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129034639</v>
+        <v>129035060</v>
       </c>
       <c r="B71" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7607,10 +7607,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>569398</v>
+        <v>569208</v>
       </c>
       <c r="R71" t="n">
-        <v>6949741</v>
+        <v>6949415</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7647,7 +7647,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>6 äldre exemplar och 1 färsk fruktkropp</t>
+          <t>20 ex minst</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7674,10 +7674,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129034584</v>
+        <v>129035018</v>
       </c>
       <c r="B72" t="n">
-        <v>57720</v>
+        <v>57725</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7685,16 +7685,16 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -7709,10 +7709,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>569221</v>
+        <v>569111</v>
       </c>
       <c r="R72" t="n">
-        <v>6949499</v>
+        <v>6949604</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7749,7 +7749,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Förbiflygande från träd till träd</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7776,32 +7776,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129035018</v>
+        <v>129035037</v>
       </c>
       <c r="B73" t="n">
-        <v>57723</v>
+        <v>98669</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7811,10 +7811,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>569111</v>
+        <v>569434</v>
       </c>
       <c r="R73" t="n">
-        <v>6949604</v>
+        <v>6949706</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7878,32 +7878,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129035037</v>
+        <v>129034584</v>
       </c>
       <c r="B74" t="n">
-        <v>98659</v>
+        <v>57722</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7913,10 +7913,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>569434</v>
+        <v>569221</v>
       </c>
       <c r="R74" t="n">
-        <v>6949706</v>
+        <v>6949499</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7953,7 +7953,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>20 ex</t>
+          <t>Förbiflygande från träd till träd</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7980,32 +7980,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129034645</v>
+        <v>129034650</v>
       </c>
       <c r="B75" t="n">
-        <v>92819</v>
+        <v>98669</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8015,10 +8015,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>569196</v>
+        <v>569303</v>
       </c>
       <c r="R75" t="n">
-        <v>6949411</v>
+        <v>6949537</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8055,7 +8055,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>4 färska exemplar 3 äldre exemplar</t>
+          <t>30 stycken ( finns eventuellt mer )</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8082,32 +8082,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129034642</v>
+        <v>129034605</v>
       </c>
       <c r="B76" t="n">
-        <v>92819</v>
+        <v>98669</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8117,10 +8117,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>569283</v>
+        <v>569305</v>
       </c>
       <c r="R76" t="n">
-        <v>6949655</v>
+        <v>6949538</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8157,7 +8157,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>7 äldre exemplar</t>
+          <t>21 knärot</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8184,32 +8184,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129026691</v>
+        <v>129034598</v>
       </c>
       <c r="B77" t="n">
-        <v>91811</v>
+        <v>97540</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8219,10 +8219,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>569195</v>
+        <v>569460</v>
       </c>
       <c r="R77" t="n">
-        <v>6949487</v>
+        <v>6949629</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8281,32 +8281,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129034598</v>
+        <v>129026691</v>
       </c>
       <c r="B78" t="n">
-        <v>97530</v>
+        <v>91818</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8316,10 +8316,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>569460</v>
+        <v>569195</v>
       </c>
       <c r="R78" t="n">
-        <v>6949629</v>
+        <v>6949487</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8378,32 +8378,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129034650</v>
+        <v>129034645</v>
       </c>
       <c r="B79" t="n">
-        <v>98659</v>
+        <v>92826</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8413,10 +8413,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>569303</v>
+        <v>569196</v>
       </c>
       <c r="R79" t="n">
-        <v>6949537</v>
+        <v>6949411</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8453,7 +8453,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>30 stycken ( finns eventuellt mer )</t>
+          <t>4 färska exemplar 3 äldre exemplar</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8480,32 +8480,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129034605</v>
+        <v>129034642</v>
       </c>
       <c r="B80" t="n">
-        <v>98659</v>
+        <v>92826</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8515,10 +8515,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>569305</v>
+        <v>569283</v>
       </c>
       <c r="R80" t="n">
-        <v>6949538</v>
+        <v>6949655</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8555,7 +8555,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>21 knärot</t>
+          <t>7 äldre exemplar</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8585,7 +8585,7 @@
         <v>129035061</v>
       </c>
       <c r="B81" t="n">
-        <v>96778</v>
+        <v>96788</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8679,10 +8679,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129035001</v>
+        <v>129034640</v>
       </c>
       <c r="B82" t="n">
-        <v>91491</v>
+        <v>92826</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8690,21 +8690,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8714,10 +8714,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>569232</v>
+        <v>569213</v>
       </c>
       <c r="R82" t="n">
-        <v>6949444</v>
+        <v>6949414</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8750,6 +8750,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>16 exemplar</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8776,10 +8781,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129035007</v>
+        <v>129035057</v>
       </c>
       <c r="B83" t="n">
-        <v>91526</v>
+        <v>79039</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8787,21 +8792,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8811,10 +8816,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>569225</v>
+        <v>569464</v>
       </c>
       <c r="R83" t="n">
-        <v>6949424</v>
+        <v>6949648</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8873,32 +8878,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129034640</v>
+        <v>129035012</v>
       </c>
       <c r="B84" t="n">
-        <v>92819</v>
+        <v>57725</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8908,10 +8913,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>569213</v>
+        <v>569435</v>
       </c>
       <c r="R84" t="n">
-        <v>6949414</v>
+        <v>6949783</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8948,7 +8953,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>16 exemplar</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8975,10 +8980,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129035057</v>
+        <v>129035007</v>
       </c>
       <c r="B85" t="n">
-        <v>79035</v>
+        <v>91533</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8986,21 +8991,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9010,10 +9015,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>569464</v>
+        <v>569225</v>
       </c>
       <c r="R85" t="n">
-        <v>6949648</v>
+        <v>6949424</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9072,32 +9077,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129035012</v>
+        <v>129035001</v>
       </c>
       <c r="B86" t="n">
-        <v>57723</v>
+        <v>91497</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9107,10 +9112,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>569435</v>
+        <v>569232</v>
       </c>
       <c r="R86" t="n">
-        <v>6949783</v>
+        <v>6949444</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9143,11 +9148,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9177,7 +9177,7 @@
         <v>129035047</v>
       </c>
       <c r="B87" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         <v>129034604</v>
       </c>
       <c r="B88" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9381,7 +9381,7 @@
         <v>129034618</v>
       </c>
       <c r="B89" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9480,32 +9480,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129035038</v>
+        <v>129035023</v>
       </c>
       <c r="B90" t="n">
-        <v>98659</v>
+        <v>91818</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>569406</v>
+        <v>569415</v>
       </c>
       <c r="R90" t="n">
-        <v>6949664</v>
+        <v>6949677</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9551,11 +9551,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>20 ex</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9582,32 +9577,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129035050</v>
+        <v>129035027</v>
       </c>
       <c r="B91" t="n">
-        <v>98659</v>
+        <v>91818</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9617,10 +9612,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>569236</v>
+        <v>569169</v>
       </c>
       <c r="R91" t="n">
-        <v>6949440</v>
+        <v>6949533</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9653,11 +9648,6 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>4 ex</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9684,32 +9674,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129034621</v>
+        <v>129034589</v>
       </c>
       <c r="B92" t="n">
-        <v>98659</v>
+        <v>91818</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9719,10 +9709,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>569247</v>
+        <v>569365</v>
       </c>
       <c r="R92" t="n">
-        <v>6949434</v>
+        <v>6949661</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9755,11 +9745,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>10 stycken knärot</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9789,7 +9774,7 @@
         <v>129035029</v>
       </c>
       <c r="B93" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9883,32 +9868,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129035023</v>
+        <v>129035038</v>
       </c>
       <c r="B94" t="n">
-        <v>91811</v>
+        <v>98669</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9918,10 +9903,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>569415</v>
+        <v>569406</v>
       </c>
       <c r="R94" t="n">
-        <v>6949677</v>
+        <v>6949664</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9954,6 +9939,11 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -9980,32 +9970,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129034589</v>
+        <v>129035050</v>
       </c>
       <c r="B95" t="n">
-        <v>91811</v>
+        <v>98669</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10015,10 +10005,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>569365</v>
+        <v>569236</v>
       </c>
       <c r="R95" t="n">
-        <v>6949661</v>
+        <v>6949440</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10051,6 +10041,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>4 ex</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10077,32 +10072,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129035027</v>
+        <v>129034621</v>
       </c>
       <c r="B96" t="n">
-        <v>91811</v>
+        <v>98669</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10112,10 +10107,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>569169</v>
+        <v>569247</v>
       </c>
       <c r="R96" t="n">
-        <v>6949533</v>
+        <v>6949434</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10148,6 +10143,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>10 stycken knärot</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10177,7 +10177,7 @@
         <v>129034635</v>
       </c>
       <c r="B97" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10271,10 +10271,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129035017</v>
+        <v>129035010</v>
       </c>
       <c r="B98" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10306,10 +10306,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>569192</v>
+        <v>569465</v>
       </c>
       <c r="R98" t="n">
-        <v>6949518</v>
+        <v>6949606</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10346,7 +10346,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10373,10 +10373,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129035010</v>
+        <v>129035017</v>
       </c>
       <c r="B99" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10408,10 +10408,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>569465</v>
+        <v>569192</v>
       </c>
       <c r="R99" t="n">
-        <v>6949606</v>
+        <v>6949518</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10448,7 +10448,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10478,7 +10478,7 @@
         <v>129034609</v>
       </c>
       <c r="B100" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10580,7 +10580,7 @@
         <v>129035036</v>
       </c>
       <c r="B101" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10682,7 +10682,7 @@
         <v>129035052</v>
       </c>
       <c r="B102" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10784,7 +10784,7 @@
         <v>129035056</v>
       </c>
       <c r="B103" t="n">
-        <v>105722</v>
+        <v>105732</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10878,32 +10878,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129035006</v>
+        <v>129035048</v>
       </c>
       <c r="B104" t="n">
-        <v>91526</v>
+        <v>98669</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10913,10 +10913,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>569217</v>
+        <v>569176</v>
       </c>
       <c r="R104" t="n">
-        <v>6949470</v>
+        <v>6949507</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10949,6 +10949,11 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>30 ex</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -10975,32 +10980,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129027886</v>
+        <v>129035053</v>
       </c>
       <c r="B105" t="n">
-        <v>91526</v>
+        <v>98669</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11010,10 +11015,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>569305</v>
+        <v>569459</v>
       </c>
       <c r="R105" t="n">
-        <v>6949566</v>
+        <v>6949662</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11046,6 +11051,11 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>14 ex</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11072,32 +11082,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129035026</v>
+        <v>129035049</v>
       </c>
       <c r="B106" t="n">
-        <v>91811</v>
+        <v>98669</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11107,10 +11117,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>569175</v>
+        <v>569219</v>
       </c>
       <c r="R106" t="n">
-        <v>6949549</v>
+        <v>6949489</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11143,6 +11153,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>35 ex</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11169,10 +11184,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129035048</v>
+        <v>129035044</v>
       </c>
       <c r="B107" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11204,10 +11219,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>569176</v>
+        <v>569191</v>
       </c>
       <c r="R107" t="n">
-        <v>6949507</v>
+        <v>6949579</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11244,7 +11259,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>30 ex</t>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11271,32 +11286,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129035053</v>
+        <v>129035026</v>
       </c>
       <c r="B108" t="n">
-        <v>98659</v>
+        <v>91818</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11306,10 +11321,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>569459</v>
+        <v>569175</v>
       </c>
       <c r="R108" t="n">
-        <v>6949662</v>
+        <v>6949549</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11342,11 +11357,6 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>14 ex</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11373,32 +11383,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129035049</v>
+        <v>129027886</v>
       </c>
       <c r="B109" t="n">
-        <v>98659</v>
+        <v>91533</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11408,10 +11418,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>569219</v>
+        <v>569305</v>
       </c>
       <c r="R109" t="n">
-        <v>6949489</v>
+        <v>6949566</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11444,11 +11454,6 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>35 ex</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11475,32 +11480,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129035044</v>
+        <v>129035006</v>
       </c>
       <c r="B110" t="n">
-        <v>98659</v>
+        <v>91533</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11510,10 +11515,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>569191</v>
+        <v>569217</v>
       </c>
       <c r="R110" t="n">
-        <v>6949579</v>
+        <v>6949470</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11546,11 +11551,6 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>50 ex</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11580,7 +11580,7 @@
         <v>129035033</v>
       </c>
       <c r="B111" t="n">
-        <v>91727</v>
+        <v>91734</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11677,7 +11677,7 @@
         <v>129035032</v>
       </c>
       <c r="B112" t="n">
-        <v>91727</v>
+        <v>91734</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>

--- a/artfynd/A 45833-2025 artfynd.xlsx
+++ b/artfynd/A 45833-2025 artfynd.xlsx
@@ -1277,32 +1277,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129035054</v>
+        <v>129035014</v>
       </c>
       <c r="B8" t="n">
-        <v>98669</v>
+        <v>57725</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>569126</v>
+        <v>569455</v>
       </c>
       <c r="R8" t="n">
-        <v>6949570</v>
+        <v>6949703</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>13 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1379,7 +1379,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129035014</v>
+        <v>129035013</v>
       </c>
       <c r="B9" t="n">
         <v>57725</v>
@@ -1417,7 +1417,7 @@
         <v>569455</v>
       </c>
       <c r="R9" t="n">
-        <v>6949703</v>
+        <v>6949716</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1481,32 +1481,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129035013</v>
+        <v>129035054</v>
       </c>
       <c r="B10" t="n">
-        <v>57725</v>
+        <v>98669</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>569455</v>
+        <v>569126</v>
       </c>
       <c r="R10" t="n">
-        <v>6949716</v>
+        <v>6949570</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>13 ex</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2185,32 +2185,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129035059</v>
+        <v>129034580</v>
       </c>
       <c r="B17" t="n">
-        <v>92826</v>
+        <v>57725</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2220,10 +2220,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>569273</v>
+        <v>569396</v>
       </c>
       <c r="R17" t="n">
-        <v>6949537</v>
+        <v>6949738</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2256,6 +2256,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på Tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2282,10 +2287,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129034629</v>
+        <v>129035019</v>
       </c>
       <c r="B18" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2293,21 +2298,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2317,10 +2322,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>569247</v>
+        <v>569117</v>
       </c>
       <c r="R18" t="n">
-        <v>6949558</v>
+        <v>6949581</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2353,6 +2358,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2379,7 +2389,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129034580</v>
+        <v>129035009</v>
       </c>
       <c r="B19" t="n">
         <v>57725</v>
@@ -2414,10 +2424,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>569396</v>
+        <v>569314</v>
       </c>
       <c r="R19" t="n">
-        <v>6949738</v>
+        <v>6949502</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2454,7 +2464,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Äldre ringhack på Tall</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2481,32 +2491,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129035019</v>
+        <v>129035059</v>
       </c>
       <c r="B20" t="n">
-        <v>57725</v>
+        <v>92826</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2516,10 +2526,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>569117</v>
+        <v>569273</v>
       </c>
       <c r="R20" t="n">
-        <v>6949581</v>
+        <v>6949537</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2552,11 +2562,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2583,10 +2588,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129035009</v>
+        <v>129034629</v>
       </c>
       <c r="B21" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2594,21 +2599,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2618,10 +2623,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>569314</v>
+        <v>569247</v>
       </c>
       <c r="R21" t="n">
-        <v>6949502</v>
+        <v>6949558</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2654,11 +2659,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -4680,10 +4680,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129035063</v>
+        <v>129034643</v>
       </c>
       <c r="B42" t="n">
-        <v>96788</v>
+        <v>92826</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4691,21 +4691,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2869</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4715,10 +4715,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>569455</v>
+        <v>569254</v>
       </c>
       <c r="R42" t="n">
-        <v>6949758</v>
+        <v>6949431</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4751,6 +4751,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>1 färskt exemplar</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4777,10 +4782,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129034643</v>
+        <v>129035063</v>
       </c>
       <c r="B43" t="n">
-        <v>92826</v>
+        <v>96788</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4788,21 +4793,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>2869</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4812,10 +4817,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>569254</v>
+        <v>569455</v>
       </c>
       <c r="R43" t="n">
-        <v>6949431</v>
+        <v>6949758</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4848,11 +4853,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>1 färskt exemplar</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4879,32 +4879,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129035011</v>
+        <v>129034607</v>
       </c>
       <c r="B44" t="n">
-        <v>57725</v>
+        <v>98669</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4914,10 +4914,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>569442</v>
+        <v>569317</v>
       </c>
       <c r="R44" t="n">
-        <v>6949783</v>
+        <v>6949549</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>31 stycken</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4981,32 +4981,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129034575</v>
+        <v>129035041</v>
       </c>
       <c r="B45" t="n">
-        <v>57725</v>
+        <v>98669</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5016,10 +5016,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>569448</v>
+        <v>569262</v>
       </c>
       <c r="R45" t="n">
-        <v>6949625</v>
+        <v>6949524</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Färska ringhack på Tall av tretåig hackspett</t>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5083,32 +5083,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129034607</v>
+        <v>129035011</v>
       </c>
       <c r="B46" t="n">
-        <v>98669</v>
+        <v>57725</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5118,10 +5118,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>569317</v>
+        <v>569442</v>
       </c>
       <c r="R46" t="n">
-        <v>6949549</v>
+        <v>6949783</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>31 stycken</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5185,32 +5185,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129035041</v>
+        <v>129034575</v>
       </c>
       <c r="B47" t="n">
-        <v>98669</v>
+        <v>57725</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5220,10 +5220,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>569262</v>
+        <v>569448</v>
       </c>
       <c r="R47" t="n">
-        <v>6949524</v>
+        <v>6949625</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5260,7 +5260,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>5 ex</t>
+          <t>Färska ringhack på Tall av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6777,10 +6777,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129034587</v>
+        <v>129034574</v>
       </c>
       <c r="B63" t="n">
-        <v>91818</v>
+        <v>91533</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6788,21 +6788,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6812,10 +6812,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>569463</v>
+        <v>569461</v>
       </c>
       <c r="R63" t="n">
-        <v>6949711</v>
+        <v>6949706</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6874,10 +6874,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129035021</v>
+        <v>129035003</v>
       </c>
       <c r="B64" t="n">
-        <v>91818</v>
+        <v>91533</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6885,21 +6885,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6909,10 +6909,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>569446</v>
+        <v>569164</v>
       </c>
       <c r="R64" t="n">
-        <v>6949629</v>
+        <v>6949559</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6971,32 +6971,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129034574</v>
+        <v>129035035</v>
       </c>
       <c r="B65" t="n">
-        <v>91533</v>
+        <v>98669</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7006,10 +7006,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>569461</v>
+        <v>569317</v>
       </c>
       <c r="R65" t="n">
-        <v>6949706</v>
+        <v>6949469</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7042,6 +7042,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7068,10 +7073,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129035003</v>
+        <v>129034587</v>
       </c>
       <c r="B66" t="n">
-        <v>91533</v>
+        <v>91818</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7079,21 +7084,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7103,10 +7108,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>569164</v>
+        <v>569463</v>
       </c>
       <c r="R66" t="n">
-        <v>6949559</v>
+        <v>6949711</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7165,49 +7170,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129027791</v>
+        <v>129035021</v>
       </c>
       <c r="B67" t="n">
-        <v>98669</v>
+        <v>91818</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Sandsjömyran, Mpd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>569308</v>
+        <v>569446</v>
       </c>
       <c r="R67" t="n">
-        <v>6949546</v>
+        <v>6949629</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7266,45 +7267,49 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129034624</v>
+        <v>129027791</v>
       </c>
       <c r="B68" t="n">
-        <v>105732</v>
+        <v>98669</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Sandsjömyran, Mpd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>569234</v>
+        <v>569308</v>
       </c>
       <c r="R68" t="n">
-        <v>6949440</v>
+        <v>6949546</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7337,11 +7342,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>9 exemplar</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7368,32 +7368,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129035035</v>
+        <v>129034624</v>
       </c>
       <c r="B69" t="n">
-        <v>98669</v>
+        <v>105732</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7403,10 +7403,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>569317</v>
+        <v>569234</v>
       </c>
       <c r="R69" t="n">
-        <v>6949469</v>
+        <v>6949440</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7443,7 +7443,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>5 ex</t>
+          <t>9 exemplar</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7980,32 +7980,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129034650</v>
+        <v>129026691</v>
       </c>
       <c r="B75" t="n">
-        <v>98669</v>
+        <v>91818</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8015,10 +8015,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>569303</v>
+        <v>569195</v>
       </c>
       <c r="R75" t="n">
-        <v>6949537</v>
+        <v>6949487</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8051,11 +8051,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>30 stycken ( finns eventuellt mer )</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8082,32 +8077,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129034605</v>
+        <v>129034645</v>
       </c>
       <c r="B76" t="n">
-        <v>98669</v>
+        <v>92826</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8117,10 +8112,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>569305</v>
+        <v>569196</v>
       </c>
       <c r="R76" t="n">
-        <v>6949538</v>
+        <v>6949411</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8157,7 +8152,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>21 knärot</t>
+          <t>4 färska exemplar 3 äldre exemplar</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8184,10 +8179,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129034598</v>
+        <v>129034642</v>
       </c>
       <c r="B77" t="n">
-        <v>97540</v>
+        <v>92826</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8195,21 +8190,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8219,10 +8214,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>569460</v>
+        <v>569283</v>
       </c>
       <c r="R77" t="n">
-        <v>6949629</v>
+        <v>6949655</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8255,6 +8250,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>7 äldre exemplar</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8281,32 +8281,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129026691</v>
+        <v>129034650</v>
       </c>
       <c r="B78" t="n">
-        <v>91818</v>
+        <v>98669</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8316,10 +8316,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>569195</v>
+        <v>569303</v>
       </c>
       <c r="R78" t="n">
-        <v>6949487</v>
+        <v>6949537</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8352,6 +8352,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>30 stycken ( finns eventuellt mer )</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8378,32 +8383,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129034645</v>
+        <v>129034605</v>
       </c>
       <c r="B79" t="n">
-        <v>92826</v>
+        <v>98669</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8413,10 +8418,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>569196</v>
+        <v>569305</v>
       </c>
       <c r="R79" t="n">
-        <v>6949411</v>
+        <v>6949538</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8453,7 +8458,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>4 färska exemplar 3 äldre exemplar</t>
+          <t>21 knärot</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8480,10 +8485,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129034642</v>
+        <v>129034598</v>
       </c>
       <c r="B80" t="n">
-        <v>92826</v>
+        <v>97540</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8491,21 +8496,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8515,10 +8520,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>569283</v>
+        <v>569460</v>
       </c>
       <c r="R80" t="n">
-        <v>6949655</v>
+        <v>6949629</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8551,11 +8556,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>7 äldre exemplar</t>
         </is>
       </c>
       <c r="AD80" t="b">

--- a/artfynd/A 45833-2025 artfynd.xlsx
+++ b/artfynd/A 45833-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129034627</v>
+        <v>129034612</v>
       </c>
       <c r="B2" t="n">
-        <v>79039</v>
+        <v>98676</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569482</v>
+        <v>569243</v>
       </c>
       <c r="R2" t="n">
-        <v>6949676</v>
+        <v>6949558</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>30  exemplar ca</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129034612</v>
+        <v>129035046</v>
       </c>
       <c r="B3" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569243</v>
+        <v>569127</v>
       </c>
       <c r="R3" t="n">
-        <v>6949558</v>
+        <v>6949602</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>30  exemplar ca</t>
+          <t>13 ex</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,7 +882,7 @@
         <v>129035043</v>
       </c>
       <c r="B4" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -976,32 +981,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129035046</v>
+        <v>129034627</v>
       </c>
       <c r="B5" t="n">
-        <v>98669</v>
+        <v>79039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569127</v>
+        <v>569482</v>
       </c>
       <c r="R5" t="n">
-        <v>6949602</v>
+        <v>6949676</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1047,11 +1052,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>13 ex</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,7 +1081,7 @@
         <v>129035039</v>
       </c>
       <c r="B6" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>129035030</v>
       </c>
       <c r="B7" t="n">
-        <v>97540</v>
+        <v>97547</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129035014</v>
+        <v>129035013</v>
       </c>
       <c r="B8" t="n">
         <v>57725</v>
@@ -1315,7 +1315,7 @@
         <v>569455</v>
       </c>
       <c r="R8" t="n">
-        <v>6949703</v>
+        <v>6949716</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1379,7 +1379,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129035013</v>
+        <v>129035014</v>
       </c>
       <c r="B9" t="n">
         <v>57725</v>
@@ -1417,7 +1417,7 @@
         <v>569455</v>
       </c>
       <c r="R9" t="n">
-        <v>6949716</v>
+        <v>6949703</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1484,7 +1484,7 @@
         <v>129035054</v>
       </c>
       <c r="B10" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>129034594</v>
       </c>
       <c r="B11" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>129034648</v>
       </c>
       <c r="B12" t="n">
-        <v>96788</v>
+        <v>96795</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1879,32 +1879,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129035055</v>
+        <v>129034577</v>
       </c>
       <c r="B14" t="n">
-        <v>98669</v>
+        <v>57725</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1914,10 +1914,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569221</v>
+        <v>569496</v>
       </c>
       <c r="R14" t="n">
-        <v>6949406</v>
+        <v>6949627</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>25 ex</t>
+          <t>Äldre ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1981,10 +1981,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129035042</v>
+        <v>129035055</v>
       </c>
       <c r="B15" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2016,10 +2016,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>569200</v>
+        <v>569221</v>
       </c>
       <c r="R15" t="n">
-        <v>6949533</v>
+        <v>6949406</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>30 ex</t>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2083,32 +2083,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129034577</v>
+        <v>129035042</v>
       </c>
       <c r="B16" t="n">
-        <v>57725</v>
+        <v>98676</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>569496</v>
+        <v>569200</v>
       </c>
       <c r="R16" t="n">
-        <v>6949627</v>
+        <v>6949533</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på tall</t>
+          <t>30 ex</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2185,7 +2185,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129034580</v>
+        <v>129035009</v>
       </c>
       <c r="B17" t="n">
         <v>57725</v>
@@ -2220,10 +2220,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>569396</v>
+        <v>569314</v>
       </c>
       <c r="R17" t="n">
-        <v>6949738</v>
+        <v>6949502</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Äldre ringhack på Tall</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2287,7 +2287,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129035019</v>
+        <v>129034580</v>
       </c>
       <c r="B18" t="n">
         <v>57725</v>
@@ -2322,10 +2322,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>569117</v>
+        <v>569396</v>
       </c>
       <c r="R18" t="n">
-        <v>6949581</v>
+        <v>6949738</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Äldre ringhack på Tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2389,7 +2389,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129035009</v>
+        <v>129035019</v>
       </c>
       <c r="B19" t="n">
         <v>57725</v>
@@ -2424,10 +2424,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>569314</v>
+        <v>569117</v>
       </c>
       <c r="R19" t="n">
-        <v>6949502</v>
+        <v>6949581</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2464,7 +2464,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2491,32 +2491,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129035059</v>
+        <v>129034620</v>
       </c>
       <c r="B20" t="n">
-        <v>92826</v>
+        <v>98676</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2526,10 +2526,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>569273</v>
+        <v>569195</v>
       </c>
       <c r="R20" t="n">
-        <v>6949537</v>
+        <v>6949410</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2562,6 +2562,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Blommande knärot 1 exemplar + 21 övriga exemplar blommar ej</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2588,32 +2593,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129034629</v>
+        <v>129035059</v>
       </c>
       <c r="B21" t="n">
-        <v>79039</v>
+        <v>92833</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2623,10 +2628,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>569247</v>
+        <v>569273</v>
       </c>
       <c r="R21" t="n">
-        <v>6949558</v>
+        <v>6949537</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2685,32 +2690,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129034620</v>
+        <v>129034629</v>
       </c>
       <c r="B22" t="n">
-        <v>98669</v>
+        <v>79039</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2720,10 +2725,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>569195</v>
+        <v>569247</v>
       </c>
       <c r="R22" t="n">
-        <v>6949410</v>
+        <v>6949558</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2756,11 +2761,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Blommande knärot 1 exemplar + 21 övriga exemplar blommar ej</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2787,32 +2787,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129034592</v>
+        <v>129034623</v>
       </c>
       <c r="B23" t="n">
-        <v>91818</v>
+        <v>98676</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569205</v>
+        <v>569253</v>
       </c>
       <c r="R23" t="n">
-        <v>6949497</v>
+        <v>6949425</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>1 x</t>
+          <t>74 stycken</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2889,10 +2889,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129034591</v>
+        <v>129034592</v>
       </c>
       <c r="B24" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2924,10 +2924,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569203</v>
+        <v>569205</v>
       </c>
       <c r="R24" t="n">
-        <v>6949513</v>
+        <v>6949497</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2964,7 +2964,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>11 ex</t>
+          <t>1 x</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2991,10 +2991,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129034647</v>
+        <v>129034591</v>
       </c>
       <c r="B25" t="n">
-        <v>88930</v>
+        <v>91825</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3002,21 +3002,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3026,10 +3026,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569247</v>
+        <v>569203</v>
       </c>
       <c r="R25" t="n">
-        <v>6949558</v>
+        <v>6949513</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3062,6 +3062,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>11 ex</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3088,10 +3093,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129035025</v>
+        <v>129034647</v>
       </c>
       <c r="B26" t="n">
-        <v>91818</v>
+        <v>88937</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3099,21 +3104,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3123,10 +3128,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569388</v>
+        <v>569247</v>
       </c>
       <c r="R26" t="n">
-        <v>6949665</v>
+        <v>6949558</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3185,10 +3190,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129035005</v>
+        <v>129035004</v>
       </c>
       <c r="B27" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3220,10 +3225,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>569188</v>
+        <v>569152</v>
       </c>
       <c r="R27" t="n">
-        <v>6949496</v>
+        <v>6949557</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3282,10 +3287,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129035004</v>
+        <v>129035025</v>
       </c>
       <c r="B28" t="n">
-        <v>91533</v>
+        <v>91825</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3293,21 +3298,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3317,10 +3322,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>569152</v>
+        <v>569388</v>
       </c>
       <c r="R28" t="n">
-        <v>6949557</v>
+        <v>6949665</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3379,10 +3384,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129034625</v>
+        <v>129035005</v>
       </c>
       <c r="B29" t="n">
-        <v>79039</v>
+        <v>91540</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3390,21 +3395,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3414,10 +3419,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>569479</v>
+        <v>569188</v>
       </c>
       <c r="R29" t="n">
-        <v>6949657</v>
+        <v>6949496</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3476,32 +3481,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129034623</v>
+        <v>129034625</v>
       </c>
       <c r="B30" t="n">
-        <v>98669</v>
+        <v>79039</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3511,10 +3516,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>569253</v>
+        <v>569479</v>
       </c>
       <c r="R30" t="n">
-        <v>6949425</v>
+        <v>6949657</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3547,11 +3552,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>74 stycken</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3581,7 +3581,7 @@
         <v>129034637</v>
       </c>
       <c r="B31" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
         <v>129035051</v>
       </c>
       <c r="B35" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>129034602</v>
       </c>
       <c r="B36" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4178,7 +4178,7 @@
         <v>129035040</v>
       </c>
       <c r="B37" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>129035045</v>
       </c>
       <c r="B38" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4379,10 +4379,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129035015</v>
+        <v>129034634</v>
       </c>
       <c r="B39" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4390,21 +4390,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4414,10 +4414,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>569454</v>
+        <v>569200</v>
       </c>
       <c r="R39" t="n">
-        <v>6949698</v>
+        <v>6949411</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4450,11 +4450,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4583,10 +4578,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129034634</v>
+        <v>129035015</v>
       </c>
       <c r="B41" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4594,21 +4589,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4618,10 +4613,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>569200</v>
+        <v>569454</v>
       </c>
       <c r="R41" t="n">
-        <v>6949411</v>
+        <v>6949698</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4654,6 +4649,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4680,10 +4680,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129034643</v>
+        <v>129035063</v>
       </c>
       <c r="B42" t="n">
-        <v>92826</v>
+        <v>96795</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4691,21 +4691,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>2869</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4715,10 +4715,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>569254</v>
+        <v>569455</v>
       </c>
       <c r="R42" t="n">
-        <v>6949431</v>
+        <v>6949758</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4751,11 +4751,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>1 färskt exemplar</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4782,10 +4777,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129035063</v>
+        <v>129034643</v>
       </c>
       <c r="B43" t="n">
-        <v>96788</v>
+        <v>92833</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4793,21 +4788,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2869</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4817,10 +4812,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>569455</v>
+        <v>569254</v>
       </c>
       <c r="R43" t="n">
-        <v>6949758</v>
+        <v>6949431</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4853,6 +4848,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>1 färskt exemplar</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4879,32 +4879,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129034607</v>
+        <v>129034575</v>
       </c>
       <c r="B44" t="n">
-        <v>98669</v>
+        <v>57725</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4914,10 +4914,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>569317</v>
+        <v>569448</v>
       </c>
       <c r="R44" t="n">
-        <v>6949549</v>
+        <v>6949625</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>31 stycken</t>
+          <t>Färska ringhack på Tall av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4981,32 +4981,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129035041</v>
+        <v>129035011</v>
       </c>
       <c r="B45" t="n">
-        <v>98669</v>
+        <v>57725</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5016,10 +5016,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>569262</v>
+        <v>569442</v>
       </c>
       <c r="R45" t="n">
-        <v>6949524</v>
+        <v>6949783</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>5 ex</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5083,32 +5083,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129035011</v>
+        <v>129034607</v>
       </c>
       <c r="B46" t="n">
-        <v>57725</v>
+        <v>98676</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5118,10 +5118,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>569442</v>
+        <v>569317</v>
       </c>
       <c r="R46" t="n">
-        <v>6949783</v>
+        <v>6949549</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>31 stycken</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5185,32 +5185,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129034575</v>
+        <v>129035041</v>
       </c>
       <c r="B47" t="n">
-        <v>57725</v>
+        <v>98676</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5220,10 +5220,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>569448</v>
+        <v>569262</v>
       </c>
       <c r="R47" t="n">
-        <v>6949625</v>
+        <v>6949524</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5260,7 +5260,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Färska ringhack på Tall av tretåig hackspett</t>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5287,10 +5287,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129035022</v>
+        <v>129034597</v>
       </c>
       <c r="B48" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5322,10 +5322,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>569423</v>
+        <v>569221</v>
       </c>
       <c r="R48" t="n">
-        <v>6949656</v>
+        <v>6949499</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5358,6 +5358,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>8 exemplar</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5384,10 +5389,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129034597</v>
+        <v>129035002</v>
       </c>
       <c r="B49" t="n">
-        <v>91818</v>
+        <v>91540</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5395,21 +5400,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5419,10 +5424,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>569221</v>
+        <v>569405</v>
       </c>
       <c r="R49" t="n">
-        <v>6949499</v>
+        <v>6949685</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5455,11 +5460,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>8 exemplar</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5486,32 +5486,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129035002</v>
+        <v>129034616</v>
       </c>
       <c r="B50" t="n">
-        <v>91533</v>
+        <v>98676</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5521,10 +5521,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>569405</v>
+        <v>569223</v>
       </c>
       <c r="R50" t="n">
-        <v>6949685</v>
+        <v>6949465</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5557,6 +5557,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>10 stycken</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5583,32 +5588,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129035062</v>
+        <v>129035022</v>
       </c>
       <c r="B51" t="n">
-        <v>96788</v>
+        <v>91825</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2869</v>
+        <v>658</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5618,10 +5623,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>569478</v>
+        <v>569423</v>
       </c>
       <c r="R51" t="n">
-        <v>6949666</v>
+        <v>6949656</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5680,32 +5685,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129034616</v>
+        <v>129035062</v>
       </c>
       <c r="B52" t="n">
-        <v>98669</v>
+        <v>96795</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5715,10 +5720,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>569223</v>
+        <v>569478</v>
       </c>
       <c r="R52" t="n">
-        <v>6949465</v>
+        <v>6949666</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5751,11 +5756,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>10 stycken</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5984,7 +5984,7 @@
         <v>129035028</v>
       </c>
       <c r="B55" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         <v>129035008</v>
       </c>
       <c r="B56" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6175,10 +6175,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129034600</v>
+        <v>129034581</v>
       </c>
       <c r="B57" t="n">
-        <v>80144</v>
+        <v>57885</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6186,21 +6186,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6210,10 +6210,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>569481</v>
+        <v>569223</v>
       </c>
       <c r="R57" t="n">
-        <v>6949674</v>
+        <v>6949401</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Apothecier antal 1</t>
+          <t>Sågs och gjorde övriga läten</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6277,32 +6277,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129034581</v>
+        <v>129034614</v>
       </c>
       <c r="B58" t="n">
-        <v>57885</v>
+        <v>98676</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6312,10 +6312,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>569223</v>
+        <v>569237</v>
       </c>
       <c r="R58" t="n">
-        <v>6949401</v>
+        <v>6949556</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Sågs och gjorde övriga läten</t>
+          <t>5 stycken</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6382,7 +6382,7 @@
         <v>129034610</v>
       </c>
       <c r="B59" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6481,32 +6481,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129034614</v>
+        <v>129034600</v>
       </c>
       <c r="B60" t="n">
-        <v>98669</v>
+        <v>80144</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6516,10 +6516,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>569237</v>
+        <v>569481</v>
       </c>
       <c r="R60" t="n">
-        <v>6949556</v>
+        <v>6949674</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6556,7 +6556,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>5 stycken</t>
+          <t>Apothecier antal 1</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6583,32 +6583,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129035024</v>
+        <v>129034586</v>
       </c>
       <c r="B61" t="n">
-        <v>91818</v>
+        <v>91995</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6618,10 +6618,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>569404</v>
+        <v>569220</v>
       </c>
       <c r="R61" t="n">
-        <v>6949660</v>
+        <v>6949500</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6680,32 +6680,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129034586</v>
+        <v>129035024</v>
       </c>
       <c r="B62" t="n">
-        <v>91988</v>
+        <v>91825</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6715,10 +6715,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>569220</v>
+        <v>569404</v>
       </c>
       <c r="R62" t="n">
-        <v>6949500</v>
+        <v>6949660</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6777,10 +6777,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129034574</v>
+        <v>129035003</v>
       </c>
       <c r="B63" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6812,10 +6812,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>569461</v>
+        <v>569164</v>
       </c>
       <c r="R63" t="n">
-        <v>6949706</v>
+        <v>6949559</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6874,10 +6874,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129035003</v>
+        <v>129034587</v>
       </c>
       <c r="B64" t="n">
-        <v>91533</v>
+        <v>91825</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6885,21 +6885,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6909,10 +6909,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>569164</v>
+        <v>569463</v>
       </c>
       <c r="R64" t="n">
-        <v>6949559</v>
+        <v>6949711</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6971,32 +6971,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129035035</v>
+        <v>129035021</v>
       </c>
       <c r="B65" t="n">
-        <v>98669</v>
+        <v>91825</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7006,10 +7006,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>569317</v>
+        <v>569446</v>
       </c>
       <c r="R65" t="n">
-        <v>6949469</v>
+        <v>6949629</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7042,11 +7042,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>5 ex</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7073,10 +7068,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129034587</v>
+        <v>129034574</v>
       </c>
       <c r="B66" t="n">
-        <v>91818</v>
+        <v>91540</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7084,21 +7079,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7108,10 +7103,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>569463</v>
+        <v>569461</v>
       </c>
       <c r="R66" t="n">
-        <v>6949711</v>
+        <v>6949706</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7170,45 +7165,49 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129035021</v>
+        <v>129027791</v>
       </c>
       <c r="B67" t="n">
-        <v>91818</v>
+        <v>98676</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Sandsjömyran, Mpd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>569446</v>
+        <v>569308</v>
       </c>
       <c r="R67" t="n">
-        <v>6949629</v>
+        <v>6949546</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7267,49 +7266,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129027791</v>
+        <v>129034624</v>
       </c>
       <c r="B68" t="n">
-        <v>98669</v>
+        <v>105739</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Sandsjömyran, Mpd</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>569308</v>
+        <v>569234</v>
       </c>
       <c r="R68" t="n">
-        <v>6949546</v>
+        <v>6949440</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7342,6 +7337,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>9 exemplar</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7368,32 +7368,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129034624</v>
+        <v>129035035</v>
       </c>
       <c r="B69" t="n">
-        <v>105732</v>
+        <v>98676</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7403,10 +7403,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>569234</v>
+        <v>569317</v>
       </c>
       <c r="R69" t="n">
-        <v>6949440</v>
+        <v>6949469</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7443,7 +7443,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>9 exemplar</t>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7470,32 +7470,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129034639</v>
+        <v>129035037</v>
       </c>
       <c r="B70" t="n">
-        <v>92826</v>
+        <v>98676</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7505,10 +7505,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>569398</v>
+        <v>569434</v>
       </c>
       <c r="R70" t="n">
-        <v>6949741</v>
+        <v>6949706</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7545,7 +7545,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>6 äldre exemplar och 1 färsk fruktkropp</t>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7575,7 +7575,7 @@
         <v>129035060</v>
       </c>
       <c r="B71" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7674,32 +7674,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129035018</v>
+        <v>129034639</v>
       </c>
       <c r="B72" t="n">
-        <v>57725</v>
+        <v>92833</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7709,10 +7709,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>569111</v>
+        <v>569398</v>
       </c>
       <c r="R72" t="n">
-        <v>6949604</v>
+        <v>6949741</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7749,7 +7749,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>6 äldre exemplar och 1 färsk fruktkropp</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7776,32 +7776,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129035037</v>
+        <v>129034584</v>
       </c>
       <c r="B73" t="n">
-        <v>98669</v>
+        <v>57722</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7811,10 +7811,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>569434</v>
+        <v>569221</v>
       </c>
       <c r="R73" t="n">
-        <v>6949706</v>
+        <v>6949499</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>20 ex</t>
+          <t>Förbiflygande från träd till träd</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7878,10 +7878,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129034584</v>
+        <v>129035018</v>
       </c>
       <c r="B74" t="n">
-        <v>57722</v>
+        <v>57725</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7889,16 +7889,16 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -7913,10 +7913,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>569221</v>
+        <v>569111</v>
       </c>
       <c r="R74" t="n">
-        <v>6949499</v>
+        <v>6949604</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7953,7 +7953,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Förbiflygande från träd till träd</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7980,32 +7980,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129026691</v>
+        <v>129034650</v>
       </c>
       <c r="B75" t="n">
-        <v>91818</v>
+        <v>98676</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8015,10 +8015,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>569195</v>
+        <v>569303</v>
       </c>
       <c r="R75" t="n">
-        <v>6949487</v>
+        <v>6949537</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8051,6 +8051,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>30 stycken ( finns eventuellt mer )</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8077,10 +8082,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129034645</v>
+        <v>129034598</v>
       </c>
       <c r="B76" t="n">
-        <v>92826</v>
+        <v>97547</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8088,21 +8093,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8112,10 +8117,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>569196</v>
+        <v>569460</v>
       </c>
       <c r="R76" t="n">
-        <v>6949411</v>
+        <v>6949629</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8148,11 +8153,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>4 färska exemplar 3 äldre exemplar</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8179,32 +8179,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129034642</v>
+        <v>129034605</v>
       </c>
       <c r="B77" t="n">
-        <v>92826</v>
+        <v>98676</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8214,10 +8214,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>569283</v>
+        <v>569305</v>
       </c>
       <c r="R77" t="n">
-        <v>6949655</v>
+        <v>6949538</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>7 äldre exemplar</t>
+          <t>21 knärot</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8281,32 +8281,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129034650</v>
+        <v>129034645</v>
       </c>
       <c r="B78" t="n">
-        <v>98669</v>
+        <v>92833</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8316,10 +8316,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>569303</v>
+        <v>569196</v>
       </c>
       <c r="R78" t="n">
-        <v>6949537</v>
+        <v>6949411</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>30 stycken ( finns eventuellt mer )</t>
+          <t>4 färska exemplar 3 äldre exemplar</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8383,32 +8383,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129034605</v>
+        <v>129034642</v>
       </c>
       <c r="B79" t="n">
-        <v>98669</v>
+        <v>92833</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8418,10 +8418,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>569305</v>
+        <v>569283</v>
       </c>
       <c r="R79" t="n">
-        <v>6949538</v>
+        <v>6949655</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8458,7 +8458,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>21 knärot</t>
+          <t>7 äldre exemplar</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8485,32 +8485,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129034598</v>
+        <v>129026691</v>
       </c>
       <c r="B80" t="n">
-        <v>97540</v>
+        <v>91825</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8520,10 +8520,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>569460</v>
+        <v>569195</v>
       </c>
       <c r="R80" t="n">
-        <v>6949629</v>
+        <v>6949487</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8582,32 +8582,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129035061</v>
+        <v>129035007</v>
       </c>
       <c r="B81" t="n">
-        <v>96788</v>
+        <v>91540</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2869</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8617,10 +8617,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>569333</v>
+        <v>569225</v>
       </c>
       <c r="R81" t="n">
-        <v>6949607</v>
+        <v>6949424</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8679,10 +8679,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129034640</v>
+        <v>129035061</v>
       </c>
       <c r="B82" t="n">
-        <v>92826</v>
+        <v>96795</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8690,21 +8690,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4364</v>
+        <v>2869</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8714,10 +8714,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>569213</v>
+        <v>569333</v>
       </c>
       <c r="R82" t="n">
-        <v>6949414</v>
+        <v>6949607</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8750,11 +8750,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>16 exemplar</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8781,32 +8776,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129035057</v>
+        <v>129034640</v>
       </c>
       <c r="B83" t="n">
-        <v>79039</v>
+        <v>92833</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8816,10 +8811,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>569464</v>
+        <v>569213</v>
       </c>
       <c r="R83" t="n">
-        <v>6949648</v>
+        <v>6949414</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8852,6 +8847,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>16 exemplar</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8878,10 +8878,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129035012</v>
+        <v>129035057</v>
       </c>
       <c r="B84" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8889,21 +8889,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8913,10 +8913,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>569435</v>
+        <v>569464</v>
       </c>
       <c r="R84" t="n">
-        <v>6949783</v>
+        <v>6949648</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8949,11 +8949,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8980,32 +8975,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129035007</v>
+        <v>129035001</v>
       </c>
       <c r="B85" t="n">
-        <v>91533</v>
+        <v>91504</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9015,10 +9010,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>569225</v>
+        <v>569232</v>
       </c>
       <c r="R85" t="n">
-        <v>6949424</v>
+        <v>6949444</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9077,32 +9072,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129035001</v>
+        <v>129035012</v>
       </c>
       <c r="B86" t="n">
-        <v>91497</v>
+        <v>57725</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9112,10 +9107,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>569232</v>
+        <v>569435</v>
       </c>
       <c r="R86" t="n">
-        <v>6949444</v>
+        <v>6949783</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9148,6 +9143,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9177,7 +9177,7 @@
         <v>129035047</v>
       </c>
       <c r="B87" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         <v>129034604</v>
       </c>
       <c r="B88" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9381,7 +9381,7 @@
         <v>129034618</v>
       </c>
       <c r="B89" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9480,32 +9480,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129035023</v>
+        <v>129035038</v>
       </c>
       <c r="B90" t="n">
-        <v>91818</v>
+        <v>98676</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>569415</v>
+        <v>569406</v>
       </c>
       <c r="R90" t="n">
-        <v>6949677</v>
+        <v>6949664</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9551,6 +9551,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9577,10 +9582,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129035027</v>
+        <v>129035023</v>
       </c>
       <c r="B91" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9612,10 +9617,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>569169</v>
+        <v>569415</v>
       </c>
       <c r="R91" t="n">
-        <v>6949533</v>
+        <v>6949677</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9674,10 +9679,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129034589</v>
+        <v>129035027</v>
       </c>
       <c r="B92" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9709,10 +9714,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>569365</v>
+        <v>569169</v>
       </c>
       <c r="R92" t="n">
-        <v>6949661</v>
+        <v>6949533</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9771,10 +9776,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129035029</v>
+        <v>129034589</v>
       </c>
       <c r="B93" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9806,10 +9811,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>569217</v>
+        <v>569365</v>
       </c>
       <c r="R93" t="n">
-        <v>6949427</v>
+        <v>6949661</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9868,32 +9873,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129035038</v>
+        <v>129035029</v>
       </c>
       <c r="B94" t="n">
-        <v>98669</v>
+        <v>91825</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9903,10 +9908,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>569406</v>
+        <v>569217</v>
       </c>
       <c r="R94" t="n">
-        <v>6949664</v>
+        <v>6949427</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9939,11 +9944,6 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>20 ex</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -9973,7 +9973,7 @@
         <v>129035050</v>
       </c>
       <c r="B95" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10075,7 +10075,7 @@
         <v>129034621</v>
       </c>
       <c r="B96" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10174,10 +10174,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129034635</v>
+        <v>129035017</v>
       </c>
       <c r="B97" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10185,21 +10185,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10209,10 +10209,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>569427</v>
+        <v>569192</v>
       </c>
       <c r="R97" t="n">
-        <v>6949726</v>
+        <v>6949518</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10245,6 +10245,11 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10373,32 +10378,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129035017</v>
+        <v>129034609</v>
       </c>
       <c r="B99" t="n">
-        <v>57725</v>
+        <v>98676</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10408,10 +10413,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>569192</v>
+        <v>569458</v>
       </c>
       <c r="R99" t="n">
-        <v>6949518</v>
+        <v>6949777</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10448,7 +10453,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>48 stycken</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10475,10 +10480,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129034609</v>
+        <v>129035036</v>
       </c>
       <c r="B100" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10510,10 +10515,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>569458</v>
+        <v>569330</v>
       </c>
       <c r="R100" t="n">
-        <v>6949777</v>
+        <v>6949564</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10550,7 +10555,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>48 stycken</t>
+          <t>8 ex</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10577,10 +10582,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129035036</v>
+        <v>129035052</v>
       </c>
       <c r="B101" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10612,10 +10617,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>569330</v>
+        <v>569405</v>
       </c>
       <c r="R101" t="n">
-        <v>6949564</v>
+        <v>6949641</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10652,7 +10657,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>8 ex</t>
+          <t>70 ex</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10679,32 +10684,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129035052</v>
+        <v>129035056</v>
       </c>
       <c r="B102" t="n">
-        <v>98669</v>
+        <v>105739</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10714,10 +10719,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>569405</v>
+        <v>569201</v>
       </c>
       <c r="R102" t="n">
-        <v>6949641</v>
+        <v>6949530</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10750,11 +10755,6 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>70 ex</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10781,32 +10781,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129035056</v>
+        <v>129034635</v>
       </c>
       <c r="B103" t="n">
-        <v>105732</v>
+        <v>79039</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>221144</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10816,10 +10816,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>569201</v>
+        <v>569427</v>
       </c>
       <c r="R103" t="n">
-        <v>6949530</v>
+        <v>6949726</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10878,32 +10878,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129035048</v>
+        <v>129035026</v>
       </c>
       <c r="B104" t="n">
-        <v>98669</v>
+        <v>91825</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10913,10 +10913,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>569176</v>
+        <v>569175</v>
       </c>
       <c r="R104" t="n">
-        <v>6949507</v>
+        <v>6949549</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10949,11 +10949,6 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>30 ex</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -10980,32 +10975,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129035053</v>
+        <v>129035006</v>
       </c>
       <c r="B105" t="n">
-        <v>98669</v>
+        <v>91540</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11015,10 +11010,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>569459</v>
+        <v>569217</v>
       </c>
       <c r="R105" t="n">
-        <v>6949662</v>
+        <v>6949470</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11051,11 +11046,6 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>14 ex</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11082,32 +11072,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129035049</v>
+        <v>129027886</v>
       </c>
       <c r="B106" t="n">
-        <v>98669</v>
+        <v>91540</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11117,10 +11107,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>569219</v>
+        <v>569305</v>
       </c>
       <c r="R106" t="n">
-        <v>6949489</v>
+        <v>6949566</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11153,11 +11143,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>35 ex</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11184,10 +11169,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129035044</v>
+        <v>129035048</v>
       </c>
       <c r="B107" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11219,10 +11204,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>569191</v>
+        <v>569176</v>
       </c>
       <c r="R107" t="n">
-        <v>6949579</v>
+        <v>6949507</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11259,7 +11244,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>50 ex</t>
+          <t>30 ex</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11286,32 +11271,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129035026</v>
+        <v>129035053</v>
       </c>
       <c r="B108" t="n">
-        <v>91818</v>
+        <v>98676</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11321,10 +11306,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>569175</v>
+        <v>569459</v>
       </c>
       <c r="R108" t="n">
-        <v>6949549</v>
+        <v>6949662</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11357,6 +11342,11 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>14 ex</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11383,32 +11373,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129027886</v>
+        <v>129035049</v>
       </c>
       <c r="B109" t="n">
-        <v>91533</v>
+        <v>98676</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11418,10 +11408,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>569305</v>
+        <v>569219</v>
       </c>
       <c r="R109" t="n">
-        <v>6949566</v>
+        <v>6949489</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11454,6 +11444,11 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>35 ex</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11480,32 +11475,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129035006</v>
+        <v>129035044</v>
       </c>
       <c r="B110" t="n">
-        <v>91533</v>
+        <v>98676</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11515,10 +11510,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>569217</v>
+        <v>569191</v>
       </c>
       <c r="R110" t="n">
-        <v>6949470</v>
+        <v>6949579</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11551,6 +11546,11 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11580,7 +11580,7 @@
         <v>129035033</v>
       </c>
       <c r="B111" t="n">
-        <v>91734</v>
+        <v>91741</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11677,7 +11677,7 @@
         <v>129035032</v>
       </c>
       <c r="B112" t="n">
-        <v>91734</v>
+        <v>91741</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>

--- a/artfynd/A 45833-2025 artfynd.xlsx
+++ b/artfynd/A 45833-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129034612</v>
+        <v>129034627</v>
       </c>
       <c r="B2" t="n">
-        <v>98676</v>
+        <v>79041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569243</v>
+        <v>569482</v>
       </c>
       <c r="R2" t="n">
-        <v>6949558</v>
+        <v>6949676</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>30  exemplar ca</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129035046</v>
+        <v>129034612</v>
       </c>
       <c r="B3" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569127</v>
+        <v>569243</v>
       </c>
       <c r="R3" t="n">
-        <v>6949602</v>
+        <v>6949558</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +847,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>13 ex</t>
+          <t>30  exemplar ca</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129035043</v>
+        <v>129035046</v>
       </c>
       <c r="B4" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569204</v>
+        <v>569127</v>
       </c>
       <c r="R4" t="n">
-        <v>6949533</v>
+        <v>6949602</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,7 +949,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>10 ex</t>
+          <t>13 ex</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,32 +976,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129034627</v>
+        <v>129035043</v>
       </c>
       <c r="B5" t="n">
-        <v>79039</v>
+        <v>98678</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569482</v>
+        <v>569204</v>
       </c>
       <c r="R5" t="n">
-        <v>6949676</v>
+        <v>6949533</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1052,6 +1047,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,7 +1081,7 @@
         <v>129035039</v>
       </c>
       <c r="B6" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>129035030</v>
       </c>
       <c r="B7" t="n">
-        <v>97547</v>
+        <v>97549</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>129035013</v>
       </c>
       <c r="B8" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>129035014</v>
       </c>
       <c r="B9" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>129035054</v>
       </c>
       <c r="B10" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,10 +1583,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129034594</v>
+        <v>129034577</v>
       </c>
       <c r="B11" t="n">
-        <v>91825</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1594,21 +1594,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>569203</v>
+        <v>569496</v>
       </c>
       <c r="R11" t="n">
-        <v>6949498</v>
+        <v>6949627</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>11 exemplar</t>
+          <t>Äldre ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1685,32 +1685,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129034648</v>
+        <v>129034630</v>
       </c>
       <c r="B12" t="n">
-        <v>96795</v>
+        <v>79041</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1720,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569279</v>
+        <v>569231</v>
       </c>
       <c r="R12" t="n">
-        <v>6949401</v>
+        <v>6949559</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1782,10 +1782,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129034630</v>
+        <v>129034594</v>
       </c>
       <c r="B13" t="n">
-        <v>79039</v>
+        <v>91827</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1793,21 +1793,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1817,10 +1817,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569231</v>
+        <v>569203</v>
       </c>
       <c r="R13" t="n">
-        <v>6949559</v>
+        <v>6949498</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1853,6 +1853,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>11 exemplar</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1879,32 +1884,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129034577</v>
+        <v>129034648</v>
       </c>
       <c r="B14" t="n">
-        <v>57725</v>
+        <v>96797</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1914,10 +1919,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569496</v>
+        <v>569279</v>
       </c>
       <c r="R14" t="n">
-        <v>6949627</v>
+        <v>6949401</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1950,11 +1955,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Äldre ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1984,7 +1984,7 @@
         <v>129035055</v>
       </c>
       <c r="B15" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>129035042</v>
       </c>
       <c r="B16" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2185,32 +2185,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129035009</v>
+        <v>129035059</v>
       </c>
       <c r="B17" t="n">
-        <v>57725</v>
+        <v>92835</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2220,10 +2220,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>569314</v>
+        <v>569273</v>
       </c>
       <c r="R17" t="n">
-        <v>6949502</v>
+        <v>6949537</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2256,11 +2256,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2287,10 +2282,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129034580</v>
+        <v>129034629</v>
       </c>
       <c r="B18" t="n">
-        <v>57725</v>
+        <v>79041</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2298,21 +2293,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2322,10 +2317,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>569396</v>
+        <v>569247</v>
       </c>
       <c r="R18" t="n">
-        <v>6949738</v>
+        <v>6949558</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2358,11 +2353,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på Tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2389,10 +2379,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129035019</v>
+        <v>129035009</v>
       </c>
       <c r="B19" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2424,10 +2414,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>569117</v>
+        <v>569314</v>
       </c>
       <c r="R19" t="n">
-        <v>6949581</v>
+        <v>6949502</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2464,7 +2454,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2491,32 +2481,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129034620</v>
+        <v>129034580</v>
       </c>
       <c r="B20" t="n">
-        <v>98676</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2526,10 +2516,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>569195</v>
+        <v>569396</v>
       </c>
       <c r="R20" t="n">
-        <v>6949410</v>
+        <v>6949738</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2566,7 +2556,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Blommande knärot 1 exemplar + 21 övriga exemplar blommar ej</t>
+          <t>Äldre ringhack på Tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2593,32 +2583,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129035059</v>
+        <v>129035019</v>
       </c>
       <c r="B21" t="n">
-        <v>92833</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2628,10 +2618,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>569273</v>
+        <v>569117</v>
       </c>
       <c r="R21" t="n">
-        <v>6949537</v>
+        <v>6949581</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2664,6 +2654,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2690,32 +2685,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129034629</v>
+        <v>129034620</v>
       </c>
       <c r="B22" t="n">
-        <v>79039</v>
+        <v>98678</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2725,10 +2720,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>569247</v>
+        <v>569195</v>
       </c>
       <c r="R22" t="n">
-        <v>6949558</v>
+        <v>6949410</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2761,6 +2756,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Blommande knärot 1 exemplar + 21 övriga exemplar blommar ej</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2787,32 +2787,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129034623</v>
+        <v>129034625</v>
       </c>
       <c r="B23" t="n">
-        <v>98676</v>
+        <v>79041</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569253</v>
+        <v>569479</v>
       </c>
       <c r="R23" t="n">
-        <v>6949425</v>
+        <v>6949657</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2858,11 +2858,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>74 stycken</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2892,7 +2887,7 @@
         <v>129034592</v>
       </c>
       <c r="B24" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2994,7 +2989,7 @@
         <v>129034591</v>
       </c>
       <c r="B25" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3093,10 +3088,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129034647</v>
+        <v>129035004</v>
       </c>
       <c r="B26" t="n">
-        <v>88937</v>
+        <v>91542</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3104,21 +3099,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3128,10 +3123,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569247</v>
+        <v>569152</v>
       </c>
       <c r="R26" t="n">
-        <v>6949558</v>
+        <v>6949557</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3190,10 +3185,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129035004</v>
+        <v>129035005</v>
       </c>
       <c r="B27" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3225,10 +3220,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>569152</v>
+        <v>569188</v>
       </c>
       <c r="R27" t="n">
-        <v>6949557</v>
+        <v>6949496</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3287,10 +3282,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129035025</v>
+        <v>129034647</v>
       </c>
       <c r="B28" t="n">
-        <v>91825</v>
+        <v>88939</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3298,21 +3293,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3322,10 +3317,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>569388</v>
+        <v>569247</v>
       </c>
       <c r="R28" t="n">
-        <v>6949665</v>
+        <v>6949558</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3384,10 +3379,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129035005</v>
+        <v>129035025</v>
       </c>
       <c r="B29" t="n">
-        <v>91540</v>
+        <v>91827</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3395,21 +3390,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3419,10 +3414,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>569188</v>
+        <v>569388</v>
       </c>
       <c r="R29" t="n">
-        <v>6949496</v>
+        <v>6949665</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3481,32 +3476,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129034625</v>
+        <v>129034623</v>
       </c>
       <c r="B30" t="n">
-        <v>79039</v>
+        <v>98678</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3516,10 +3511,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>569479</v>
+        <v>569253</v>
       </c>
       <c r="R30" t="n">
-        <v>6949657</v>
+        <v>6949425</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3552,6 +3547,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>74 stycken</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3578,32 +3578,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129034637</v>
+        <v>129035058</v>
       </c>
       <c r="B31" t="n">
-        <v>92833</v>
+        <v>79041</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>569229</v>
+        <v>569388</v>
       </c>
       <c r="R31" t="n">
-        <v>6949400</v>
+        <v>6949647</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3675,10 +3675,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129035058</v>
+        <v>129035031</v>
       </c>
       <c r="B32" t="n">
-        <v>79039</v>
+        <v>80146</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3686,21 +3686,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3710,10 +3710,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>569388</v>
+        <v>569125</v>
       </c>
       <c r="R32" t="n">
-        <v>6949647</v>
+        <v>6949570</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3772,32 +3772,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129035031</v>
+        <v>129035051</v>
       </c>
       <c r="B33" t="n">
-        <v>80144</v>
+        <v>98678</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3807,10 +3807,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>569125</v>
+        <v>569222</v>
       </c>
       <c r="R33" t="n">
-        <v>6949570</v>
+        <v>6949414</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3843,6 +3843,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>30 ex</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3869,32 +3874,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129034578</v>
+        <v>129034637</v>
       </c>
       <c r="B34" t="n">
-        <v>57725</v>
+        <v>92835</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3904,10 +3909,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>569420</v>
+        <v>569229</v>
       </c>
       <c r="R34" t="n">
-        <v>6949723</v>
+        <v>6949400</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3940,11 +3945,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3971,32 +3971,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129035051</v>
+        <v>129034578</v>
       </c>
       <c r="B35" t="n">
-        <v>98676</v>
+        <v>57727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4006,10 +4006,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>569222</v>
+        <v>569420</v>
       </c>
       <c r="R35" t="n">
-        <v>6949414</v>
+        <v>6949723</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>30 ex</t>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4073,32 +4073,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129034602</v>
+        <v>129034634</v>
       </c>
       <c r="B36" t="n">
-        <v>98676</v>
+        <v>79041</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4108,10 +4108,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>569301</v>
+        <v>569200</v>
       </c>
       <c r="R36" t="n">
-        <v>6949480</v>
+        <v>6949411</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4144,11 +4144,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>22 stycken</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4175,10 +4170,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129035040</v>
+        <v>129034602</v>
       </c>
       <c r="B37" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4210,10 +4205,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>569386</v>
+        <v>569301</v>
       </c>
       <c r="R37" t="n">
-        <v>6949657</v>
+        <v>6949480</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4250,7 +4245,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>9 ex</t>
+          <t>22 stycken</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4277,10 +4272,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129035045</v>
+        <v>129035040</v>
       </c>
       <c r="B38" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4312,10 +4307,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>569130</v>
+        <v>569386</v>
       </c>
       <c r="R38" t="n">
-        <v>6949603</v>
+        <v>6949657</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4352,7 +4347,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>14 ex</t>
+          <t>9 ex</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4379,32 +4374,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129034634</v>
+        <v>129035045</v>
       </c>
       <c r="B39" t="n">
-        <v>79039</v>
+        <v>98678</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4414,10 +4409,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>569200</v>
+        <v>569130</v>
       </c>
       <c r="R39" t="n">
-        <v>6949411</v>
+        <v>6949603</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4450,6 +4445,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>14 ex</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4479,7 +4479,7 @@
         <v>129035020</v>
       </c>
       <c r="B40" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4581,7 +4581,7 @@
         <v>129035015</v>
       </c>
       <c r="B41" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4680,10 +4680,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129035063</v>
+        <v>129034643</v>
       </c>
       <c r="B42" t="n">
-        <v>96795</v>
+        <v>92835</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4691,21 +4691,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2869</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4715,10 +4715,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>569455</v>
+        <v>569254</v>
       </c>
       <c r="R42" t="n">
-        <v>6949758</v>
+        <v>6949431</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4751,6 +4751,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>1 färskt exemplar</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4777,10 +4782,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129034643</v>
+        <v>129035063</v>
       </c>
       <c r="B43" t="n">
-        <v>92833</v>
+        <v>96797</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4788,21 +4793,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>2869</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4812,10 +4817,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>569254</v>
+        <v>569455</v>
       </c>
       <c r="R43" t="n">
-        <v>6949431</v>
+        <v>6949758</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4848,11 +4853,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>1 färskt exemplar</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4882,7 +4882,7 @@
         <v>129034575</v>
       </c>
       <c r="B44" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>129035011</v>
       </c>
       <c r="B45" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         <v>129034607</v>
       </c>
       <c r="B46" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
         <v>129035041</v>
       </c>
       <c r="B47" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5287,32 +5287,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129034597</v>
+        <v>129035062</v>
       </c>
       <c r="B48" t="n">
-        <v>91825</v>
+        <v>96797</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>658</v>
+        <v>2869</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5322,10 +5322,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>569221</v>
+        <v>569478</v>
       </c>
       <c r="R48" t="n">
-        <v>6949499</v>
+        <v>6949666</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5358,11 +5358,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>8 exemplar</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5389,10 +5384,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129035002</v>
+        <v>129035022</v>
       </c>
       <c r="B49" t="n">
-        <v>91540</v>
+        <v>91827</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5400,21 +5395,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5424,10 +5419,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>569405</v>
+        <v>569423</v>
       </c>
       <c r="R49" t="n">
-        <v>6949685</v>
+        <v>6949656</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5486,32 +5481,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129034616</v>
+        <v>129035016</v>
       </c>
       <c r="B50" t="n">
-        <v>98676</v>
+        <v>57727</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5521,10 +5516,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>569223</v>
+        <v>569435</v>
       </c>
       <c r="R50" t="n">
-        <v>6949465</v>
+        <v>6949665</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5561,7 +5556,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>10 stycken</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5588,10 +5583,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129035022</v>
+        <v>129034632</v>
       </c>
       <c r="B51" t="n">
-        <v>91825</v>
+        <v>79041</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5599,21 +5594,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5623,10 +5618,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>569423</v>
+        <v>569237</v>
       </c>
       <c r="R51" t="n">
-        <v>6949656</v>
+        <v>6949442</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5685,32 +5680,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129035062</v>
+        <v>129034597</v>
       </c>
       <c r="B52" t="n">
-        <v>96795</v>
+        <v>91827</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2869</v>
+        <v>658</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5720,10 +5715,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>569478</v>
+        <v>569221</v>
       </c>
       <c r="R52" t="n">
-        <v>6949666</v>
+        <v>6949499</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5756,6 +5751,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>8 exemplar</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5782,10 +5782,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129034632</v>
+        <v>129035002</v>
       </c>
       <c r="B53" t="n">
-        <v>79039</v>
+        <v>91542</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5793,21 +5793,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5817,10 +5817,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>569237</v>
+        <v>569405</v>
       </c>
       <c r="R53" t="n">
-        <v>6949442</v>
+        <v>6949685</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5879,32 +5879,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129035016</v>
+        <v>129034616</v>
       </c>
       <c r="B54" t="n">
-        <v>57725</v>
+        <v>98678</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5914,10 +5914,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>569435</v>
+        <v>569223</v>
       </c>
       <c r="R54" t="n">
-        <v>6949665</v>
+        <v>6949465</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5954,7 +5954,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>10 stycken</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5984,7 +5984,7 @@
         <v>129035028</v>
       </c>
       <c r="B55" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6078,10 +6078,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129035008</v>
+        <v>129034600</v>
       </c>
       <c r="B56" t="n">
-        <v>91540</v>
+        <v>80146</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6089,21 +6089,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6113,10 +6113,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>569216</v>
+        <v>569481</v>
       </c>
       <c r="R56" t="n">
-        <v>6949430</v>
+        <v>6949674</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6149,6 +6149,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Apothecier antal 1</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6175,10 +6180,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129034581</v>
+        <v>129035008</v>
       </c>
       <c r="B57" t="n">
-        <v>57885</v>
+        <v>91542</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6186,21 +6191,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6210,10 +6215,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>569223</v>
+        <v>569216</v>
       </c>
       <c r="R57" t="n">
-        <v>6949401</v>
+        <v>6949430</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6246,11 +6251,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Sågs och gjorde övriga läten</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6277,32 +6277,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129034614</v>
+        <v>129034581</v>
       </c>
       <c r="B58" t="n">
-        <v>98676</v>
+        <v>57887</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6312,10 +6312,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>569237</v>
+        <v>569223</v>
       </c>
       <c r="R58" t="n">
-        <v>6949556</v>
+        <v>6949401</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>5 stycken</t>
+          <t>Sågs och gjorde övriga läten</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6382,7 +6382,7 @@
         <v>129034610</v>
       </c>
       <c r="B59" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6481,32 +6481,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129034600</v>
+        <v>129034614</v>
       </c>
       <c r="B60" t="n">
-        <v>80144</v>
+        <v>98678</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6516,10 +6516,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>569481</v>
+        <v>569237</v>
       </c>
       <c r="R60" t="n">
-        <v>6949674</v>
+        <v>6949556</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6556,7 +6556,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Apothecier antal 1</t>
+          <t>5 stycken</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6583,32 +6583,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129034586</v>
+        <v>129035024</v>
       </c>
       <c r="B61" t="n">
-        <v>91995</v>
+        <v>91827</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6618,10 +6618,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>569220</v>
+        <v>569404</v>
       </c>
       <c r="R61" t="n">
-        <v>6949500</v>
+        <v>6949660</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6680,32 +6680,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129035024</v>
+        <v>129034586</v>
       </c>
       <c r="B62" t="n">
-        <v>91825</v>
+        <v>91997</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6715,10 +6715,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>569404</v>
+        <v>569220</v>
       </c>
       <c r="R62" t="n">
-        <v>6949660</v>
+        <v>6949500</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6780,7 +6780,7 @@
         <v>129035003</v>
       </c>
       <c r="B63" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6874,10 +6874,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129034587</v>
+        <v>129034574</v>
       </c>
       <c r="B64" t="n">
-        <v>91825</v>
+        <v>91542</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6885,21 +6885,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6909,10 +6909,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>569463</v>
+        <v>569461</v>
       </c>
       <c r="R64" t="n">
-        <v>6949711</v>
+        <v>6949706</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6971,10 +6971,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129035021</v>
+        <v>129034587</v>
       </c>
       <c r="B65" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7006,10 +7006,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>569446</v>
+        <v>569463</v>
       </c>
       <c r="R65" t="n">
-        <v>6949629</v>
+        <v>6949711</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7068,10 +7068,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129034574</v>
+        <v>129035021</v>
       </c>
       <c r="B66" t="n">
-        <v>91540</v>
+        <v>91827</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7079,21 +7079,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7103,10 +7103,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>569461</v>
+        <v>569446</v>
       </c>
       <c r="R66" t="n">
-        <v>6949706</v>
+        <v>6949629</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7168,7 +7168,7 @@
         <v>129027791</v>
       </c>
       <c r="B67" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         <v>129034624</v>
       </c>
       <c r="B68" t="n">
-        <v>105739</v>
+        <v>105741</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7371,7 +7371,7 @@
         <v>129035035</v>
       </c>
       <c r="B69" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7473,7 +7473,7 @@
         <v>129035037</v>
       </c>
       <c r="B70" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7572,32 +7572,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129035060</v>
+        <v>129034584</v>
       </c>
       <c r="B71" t="n">
-        <v>92833</v>
+        <v>57724</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7607,10 +7607,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>569208</v>
+        <v>569221</v>
       </c>
       <c r="R71" t="n">
-        <v>6949415</v>
+        <v>6949499</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7647,7 +7647,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>20 ex minst</t>
+          <t>Förbiflygande från träd till träd</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7674,32 +7674,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129034639</v>
+        <v>129035018</v>
       </c>
       <c r="B72" t="n">
-        <v>92833</v>
+        <v>57727</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7709,10 +7709,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>569398</v>
+        <v>569111</v>
       </c>
       <c r="R72" t="n">
-        <v>6949741</v>
+        <v>6949604</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7749,7 +7749,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>6 äldre exemplar och 1 färsk fruktkropp</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7776,32 +7776,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129034584</v>
+        <v>129035060</v>
       </c>
       <c r="B73" t="n">
-        <v>57722</v>
+        <v>92835</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7811,10 +7811,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>569221</v>
+        <v>569208</v>
       </c>
       <c r="R73" t="n">
-        <v>6949499</v>
+        <v>6949415</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Förbiflygande från träd till träd</t>
+          <t>20 ex minst</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7878,32 +7878,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129035018</v>
+        <v>129034639</v>
       </c>
       <c r="B74" t="n">
-        <v>57725</v>
+        <v>92835</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7913,10 +7913,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>569111</v>
+        <v>569398</v>
       </c>
       <c r="R74" t="n">
-        <v>6949604</v>
+        <v>6949741</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7953,7 +7953,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>6 äldre exemplar och 1 färsk fruktkropp</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7980,32 +7980,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129034650</v>
+        <v>129026691</v>
       </c>
       <c r="B75" t="n">
-        <v>98676</v>
+        <v>91827</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8015,10 +8015,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>569303</v>
+        <v>569195</v>
       </c>
       <c r="R75" t="n">
-        <v>6949537</v>
+        <v>6949487</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8051,11 +8051,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>30 stycken ( finns eventuellt mer )</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8082,10 +8077,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129034598</v>
+        <v>129034645</v>
       </c>
       <c r="B76" t="n">
-        <v>97547</v>
+        <v>92835</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8093,21 +8088,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8117,10 +8112,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>569460</v>
+        <v>569196</v>
       </c>
       <c r="R76" t="n">
-        <v>6949629</v>
+        <v>6949411</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8153,6 +8148,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>4 färska exemplar 3 äldre exemplar</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8179,32 +8179,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129034605</v>
+        <v>129034642</v>
       </c>
       <c r="B77" t="n">
-        <v>98676</v>
+        <v>92835</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8214,10 +8214,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>569305</v>
+        <v>569283</v>
       </c>
       <c r="R77" t="n">
-        <v>6949538</v>
+        <v>6949655</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>21 knärot</t>
+          <t>7 äldre exemplar</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8281,10 +8281,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129034645</v>
+        <v>129034598</v>
       </c>
       <c r="B78" t="n">
-        <v>92833</v>
+        <v>97549</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8292,21 +8292,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8316,10 +8316,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>569196</v>
+        <v>569460</v>
       </c>
       <c r="R78" t="n">
-        <v>6949411</v>
+        <v>6949629</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8352,11 +8352,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>4 färska exemplar 3 äldre exemplar</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8383,32 +8378,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129034642</v>
+        <v>129034650</v>
       </c>
       <c r="B79" t="n">
-        <v>92833</v>
+        <v>98678</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8418,10 +8413,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>569283</v>
+        <v>569303</v>
       </c>
       <c r="R79" t="n">
-        <v>6949655</v>
+        <v>6949537</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8458,7 +8453,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>7 äldre exemplar</t>
+          <t>30 stycken ( finns eventuellt mer )</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8485,32 +8480,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129026691</v>
+        <v>129034605</v>
       </c>
       <c r="B80" t="n">
-        <v>91825</v>
+        <v>98678</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8520,10 +8515,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>569195</v>
+        <v>569305</v>
       </c>
       <c r="R80" t="n">
-        <v>6949487</v>
+        <v>6949538</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8556,6 +8551,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>21 knärot</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8582,32 +8582,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129035007</v>
+        <v>129035047</v>
       </c>
       <c r="B81" t="n">
-        <v>91540</v>
+        <v>98678</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8617,10 +8617,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>569225</v>
+        <v>569162</v>
       </c>
       <c r="R81" t="n">
-        <v>6949424</v>
+        <v>6949566</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8653,6 +8653,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8679,32 +8684,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129035061</v>
+        <v>129034618</v>
       </c>
       <c r="B82" t="n">
-        <v>96795</v>
+        <v>98678</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8714,10 +8719,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>569333</v>
+        <v>569235</v>
       </c>
       <c r="R82" t="n">
-        <v>6949607</v>
+        <v>6949411</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8750,6 +8755,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8776,32 +8786,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129034640</v>
+        <v>129034604</v>
       </c>
       <c r="B83" t="n">
-        <v>92833</v>
+        <v>98678</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8811,10 +8821,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>569213</v>
+        <v>569303</v>
       </c>
       <c r="R83" t="n">
-        <v>6949414</v>
+        <v>6949536</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8851,7 +8861,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>16 exemplar</t>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8881,7 +8891,7 @@
         <v>129035057</v>
       </c>
       <c r="B84" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8978,7 +8988,7 @@
         <v>129035001</v>
       </c>
       <c r="B85" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9075,7 +9085,7 @@
         <v>129035012</v>
       </c>
       <c r="B86" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9174,32 +9184,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129035047</v>
+        <v>129035007</v>
       </c>
       <c r="B87" t="n">
-        <v>98676</v>
+        <v>91542</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9209,10 +9219,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>569162</v>
+        <v>569225</v>
       </c>
       <c r="R87" t="n">
-        <v>6949566</v>
+        <v>6949424</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9245,11 +9255,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>50 ex</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9276,32 +9281,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129034604</v>
+        <v>129035061</v>
       </c>
       <c r="B88" t="n">
-        <v>98676</v>
+        <v>96797</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9311,10 +9316,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>569303</v>
+        <v>569333</v>
       </c>
       <c r="R88" t="n">
-        <v>6949536</v>
+        <v>6949607</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9347,11 +9352,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9378,32 +9378,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129034618</v>
+        <v>129034640</v>
       </c>
       <c r="B89" t="n">
-        <v>98676</v>
+        <v>92835</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9413,10 +9413,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>569235</v>
+        <v>569213</v>
       </c>
       <c r="R89" t="n">
-        <v>6949411</v>
+        <v>6949414</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9453,7 +9453,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>18 stycken</t>
+          <t>16 exemplar</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9480,32 +9480,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129035038</v>
+        <v>129035027</v>
       </c>
       <c r="B90" t="n">
-        <v>98676</v>
+        <v>91827</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>569406</v>
+        <v>569169</v>
       </c>
       <c r="R90" t="n">
-        <v>6949664</v>
+        <v>6949533</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9551,11 +9551,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>20 ex</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9582,10 +9577,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129035023</v>
+        <v>129034589</v>
       </c>
       <c r="B91" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9617,10 +9612,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>569415</v>
+        <v>569365</v>
       </c>
       <c r="R91" t="n">
-        <v>6949677</v>
+        <v>6949661</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9679,10 +9674,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129035027</v>
+        <v>129035023</v>
       </c>
       <c r="B92" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9714,10 +9709,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>569169</v>
+        <v>569415</v>
       </c>
       <c r="R92" t="n">
-        <v>6949533</v>
+        <v>6949677</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9776,10 +9771,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129034589</v>
+        <v>129035029</v>
       </c>
       <c r="B93" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9811,10 +9806,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>569365</v>
+        <v>569217</v>
       </c>
       <c r="R93" t="n">
-        <v>6949661</v>
+        <v>6949427</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9873,32 +9868,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129035029</v>
+        <v>129035038</v>
       </c>
       <c r="B94" t="n">
-        <v>91825</v>
+        <v>98678</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9908,10 +9903,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>569217</v>
+        <v>569406</v>
       </c>
       <c r="R94" t="n">
-        <v>6949427</v>
+        <v>6949664</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9944,6 +9939,11 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -9973,7 +9973,7 @@
         <v>129035050</v>
       </c>
       <c r="B95" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10075,7 +10075,7 @@
         <v>129034621</v>
       </c>
       <c r="B96" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10174,10 +10174,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129035017</v>
+        <v>129034635</v>
       </c>
       <c r="B97" t="n">
-        <v>57725</v>
+        <v>79041</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10185,21 +10185,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10209,10 +10209,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>569192</v>
+        <v>569427</v>
       </c>
       <c r="R97" t="n">
-        <v>6949518</v>
+        <v>6949726</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10245,11 +10245,6 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10276,10 +10271,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129035010</v>
+        <v>129035017</v>
       </c>
       <c r="B98" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10311,10 +10306,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>569465</v>
+        <v>569192</v>
       </c>
       <c r="R98" t="n">
-        <v>6949606</v>
+        <v>6949518</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10351,7 +10346,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10378,32 +10373,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129034609</v>
+        <v>129035010</v>
       </c>
       <c r="B99" t="n">
-        <v>98676</v>
+        <v>57727</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10413,10 +10408,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>569458</v>
+        <v>569465</v>
       </c>
       <c r="R99" t="n">
-        <v>6949777</v>
+        <v>6949606</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10453,7 +10448,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>48 stycken</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10480,10 +10475,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129035036</v>
+        <v>129034609</v>
       </c>
       <c r="B100" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10515,10 +10510,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>569330</v>
+        <v>569458</v>
       </c>
       <c r="R100" t="n">
-        <v>6949564</v>
+        <v>6949777</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10555,7 +10550,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>8 ex</t>
+          <t>48 stycken</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10582,10 +10577,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129035052</v>
+        <v>129035036</v>
       </c>
       <c r="B101" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10617,10 +10612,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>569405</v>
+        <v>569330</v>
       </c>
       <c r="R101" t="n">
-        <v>6949641</v>
+        <v>6949564</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10657,7 +10652,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>70 ex</t>
+          <t>8 ex</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10684,32 +10679,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129035056</v>
+        <v>129035052</v>
       </c>
       <c r="B102" t="n">
-        <v>105739</v>
+        <v>98678</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10719,10 +10714,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>569201</v>
+        <v>569405</v>
       </c>
       <c r="R102" t="n">
-        <v>6949530</v>
+        <v>6949641</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10755,6 +10750,11 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>70 ex</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10781,32 +10781,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129034635</v>
+        <v>129035056</v>
       </c>
       <c r="B103" t="n">
-        <v>79039</v>
+        <v>105741</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>221144</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10816,10 +10816,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>569427</v>
+        <v>569201</v>
       </c>
       <c r="R103" t="n">
-        <v>6949726</v>
+        <v>6949530</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10881,7 +10881,7 @@
         <v>129035026</v>
       </c>
       <c r="B104" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10975,32 +10975,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129035006</v>
+        <v>129035048</v>
       </c>
       <c r="B105" t="n">
-        <v>91540</v>
+        <v>98678</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11010,10 +11010,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>569217</v>
+        <v>569176</v>
       </c>
       <c r="R105" t="n">
-        <v>6949470</v>
+        <v>6949507</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11046,6 +11046,11 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>30 ex</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11072,32 +11077,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129027886</v>
+        <v>129035053</v>
       </c>
       <c r="B106" t="n">
-        <v>91540</v>
+        <v>98678</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11107,10 +11112,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>569305</v>
+        <v>569459</v>
       </c>
       <c r="R106" t="n">
-        <v>6949566</v>
+        <v>6949662</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11143,6 +11148,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>14 ex</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11169,10 +11179,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129035048</v>
+        <v>129035049</v>
       </c>
       <c r="B107" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11204,10 +11214,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>569176</v>
+        <v>569219</v>
       </c>
       <c r="R107" t="n">
-        <v>6949507</v>
+        <v>6949489</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11244,7 +11254,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>30 ex</t>
+          <t>35 ex</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11271,10 +11281,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129035053</v>
+        <v>129035044</v>
       </c>
       <c r="B108" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11306,10 +11316,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>569459</v>
+        <v>569191</v>
       </c>
       <c r="R108" t="n">
-        <v>6949662</v>
+        <v>6949579</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11346,7 +11356,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>14 ex</t>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11373,32 +11383,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129035049</v>
+        <v>129035006</v>
       </c>
       <c r="B109" t="n">
-        <v>98676</v>
+        <v>91542</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11408,10 +11418,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>569219</v>
+        <v>569217</v>
       </c>
       <c r="R109" t="n">
-        <v>6949489</v>
+        <v>6949470</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11444,11 +11454,6 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>35 ex</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11475,32 +11480,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129035044</v>
+        <v>129027886</v>
       </c>
       <c r="B110" t="n">
-        <v>98676</v>
+        <v>91542</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11510,10 +11515,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>569191</v>
+        <v>569305</v>
       </c>
       <c r="R110" t="n">
-        <v>6949579</v>
+        <v>6949566</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11546,11 +11551,6 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>50 ex</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11580,7 +11580,7 @@
         <v>129035033</v>
       </c>
       <c r="B111" t="n">
-        <v>91741</v>
+        <v>91743</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11677,7 +11677,7 @@
         <v>129035032</v>
       </c>
       <c r="B112" t="n">
-        <v>91741</v>
+        <v>91743</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>

--- a/artfynd/A 45833-2025 artfynd.xlsx
+++ b/artfynd/A 45833-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129034627</v>
+        <v>129034612</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>98678</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569482</v>
+        <v>569243</v>
       </c>
       <c r="R2" t="n">
-        <v>6949676</v>
+        <v>6949558</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>30  exemplar ca</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129034612</v>
+        <v>129035046</v>
       </c>
       <c r="B3" t="n">
         <v>98678</v>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569243</v>
+        <v>569127</v>
       </c>
       <c r="R3" t="n">
-        <v>6949558</v>
+        <v>6949602</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>30  exemplar ca</t>
+          <t>13 ex</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129035046</v>
+        <v>129035043</v>
       </c>
       <c r="B4" t="n">
         <v>98678</v>
@@ -909,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569127</v>
+        <v>569204</v>
       </c>
       <c r="R4" t="n">
-        <v>6949602</v>
+        <v>6949533</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,7 +954,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>13 ex</t>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,32 +981,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129035043</v>
+        <v>129034627</v>
       </c>
       <c r="B5" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569204</v>
+        <v>569482</v>
       </c>
       <c r="R5" t="n">
-        <v>6949533</v>
+        <v>6949676</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1047,11 +1052,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>10 ex</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1078,32 +1078,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129035039</v>
+        <v>129035030</v>
       </c>
       <c r="B6" t="n">
-        <v>98678</v>
+        <v>97549</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>569394</v>
+        <v>569424</v>
       </c>
       <c r="R6" t="n">
-        <v>6949664</v>
+        <v>6949671</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1149,11 +1149,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1180,32 +1175,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129035030</v>
+        <v>129035039</v>
       </c>
       <c r="B7" t="n">
-        <v>97549</v>
+        <v>98678</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>569424</v>
+        <v>569394</v>
       </c>
       <c r="R7" t="n">
-        <v>6949671</v>
+        <v>6949664</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1251,6 +1246,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1583,10 +1583,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129034577</v>
+        <v>129034630</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1594,21 +1594,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>569496</v>
+        <v>569231</v>
       </c>
       <c r="R11" t="n">
-        <v>6949627</v>
+        <v>6949559</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1654,11 +1654,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1685,32 +1680,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129034630</v>
+        <v>129034648</v>
       </c>
       <c r="B12" t="n">
-        <v>79041</v>
+        <v>96797</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1720,10 +1715,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569231</v>
+        <v>569279</v>
       </c>
       <c r="R12" t="n">
-        <v>6949559</v>
+        <v>6949401</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1884,32 +1879,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129034648</v>
+        <v>129034577</v>
       </c>
       <c r="B14" t="n">
-        <v>96797</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1919,10 +1914,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569279</v>
+        <v>569496</v>
       </c>
       <c r="R14" t="n">
-        <v>6949401</v>
+        <v>6949627</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1955,6 +1950,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2787,10 +2787,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129034625</v>
+        <v>129035005</v>
       </c>
       <c r="B23" t="n">
-        <v>79041</v>
+        <v>91542</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2798,21 +2798,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569479</v>
+        <v>569188</v>
       </c>
       <c r="R23" t="n">
-        <v>6949657</v>
+        <v>6949496</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2884,10 +2884,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129034592</v>
+        <v>129035004</v>
       </c>
       <c r="B24" t="n">
-        <v>91827</v>
+        <v>91542</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2895,21 +2895,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2919,10 +2919,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569205</v>
+        <v>569152</v>
       </c>
       <c r="R24" t="n">
-        <v>6949497</v>
+        <v>6949557</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2955,11 +2955,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>1 x</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2986,7 +2981,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129034591</v>
+        <v>129034592</v>
       </c>
       <c r="B25" t="n">
         <v>91827</v>
@@ -3021,10 +3016,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569203</v>
+        <v>569205</v>
       </c>
       <c r="R25" t="n">
-        <v>6949513</v>
+        <v>6949497</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3061,7 +3056,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>11 ex</t>
+          <t>1 x</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3088,10 +3083,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129035004</v>
+        <v>129034591</v>
       </c>
       <c r="B26" t="n">
-        <v>91542</v>
+        <v>91827</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3099,21 +3094,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3123,10 +3118,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569152</v>
+        <v>569203</v>
       </c>
       <c r="R26" t="n">
-        <v>6949557</v>
+        <v>6949513</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3159,6 +3154,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>11 ex</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3185,10 +3185,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129035005</v>
+        <v>129034647</v>
       </c>
       <c r="B27" t="n">
-        <v>91542</v>
+        <v>88939</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3196,21 +3196,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3220,10 +3220,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>569188</v>
+        <v>569247</v>
       </c>
       <c r="R27" t="n">
-        <v>6949496</v>
+        <v>6949558</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3282,10 +3282,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129034647</v>
+        <v>129035025</v>
       </c>
       <c r="B28" t="n">
-        <v>88939</v>
+        <v>91827</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3293,21 +3293,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3317,10 +3317,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>569247</v>
+        <v>569388</v>
       </c>
       <c r="R28" t="n">
-        <v>6949558</v>
+        <v>6949665</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3379,10 +3379,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129035025</v>
+        <v>129034625</v>
       </c>
       <c r="B29" t="n">
-        <v>91827</v>
+        <v>79041</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3390,21 +3390,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3414,10 +3414,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>569388</v>
+        <v>569479</v>
       </c>
       <c r="R29" t="n">
-        <v>6949665</v>
+        <v>6949657</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3578,10 +3578,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129035058</v>
+        <v>129034578</v>
       </c>
       <c r="B31" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3589,21 +3589,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>569388</v>
+        <v>569420</v>
       </c>
       <c r="R31" t="n">
-        <v>6949647</v>
+        <v>6949723</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3649,6 +3649,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3675,32 +3680,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129035031</v>
+        <v>129034637</v>
       </c>
       <c r="B32" t="n">
-        <v>80146</v>
+        <v>92835</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3710,10 +3715,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>569125</v>
+        <v>569229</v>
       </c>
       <c r="R32" t="n">
-        <v>6949570</v>
+        <v>6949400</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3772,32 +3777,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129035051</v>
+        <v>129035058</v>
       </c>
       <c r="B33" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3807,10 +3812,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>569222</v>
+        <v>569388</v>
       </c>
       <c r="R33" t="n">
-        <v>6949414</v>
+        <v>6949647</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3843,11 +3848,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>30 ex</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3874,32 +3874,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129034637</v>
+        <v>129035051</v>
       </c>
       <c r="B34" t="n">
-        <v>92835</v>
+        <v>98678</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3909,10 +3909,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>569229</v>
+        <v>569222</v>
       </c>
       <c r="R34" t="n">
-        <v>6949400</v>
+        <v>6949414</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3945,6 +3945,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>30 ex</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3971,10 +3976,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129034578</v>
+        <v>129035031</v>
       </c>
       <c r="B35" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3982,21 +3987,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4006,10 +4011,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>569420</v>
+        <v>569125</v>
       </c>
       <c r="R35" t="n">
-        <v>6949723</v>
+        <v>6949570</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4042,11 +4047,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4170,32 +4170,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129034602</v>
+        <v>129035020</v>
       </c>
       <c r="B37" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4205,10 +4205,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>569301</v>
+        <v>569171</v>
       </c>
       <c r="R37" t="n">
-        <v>6949480</v>
+        <v>6949543</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>22 stycken</t>
+          <t>Äldre ringhack på granhögstubbe</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4272,32 +4272,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129035040</v>
+        <v>129035015</v>
       </c>
       <c r="B38" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4307,10 +4307,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>569386</v>
+        <v>569454</v>
       </c>
       <c r="R38" t="n">
-        <v>6949657</v>
+        <v>6949698</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>9 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4374,7 +4374,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129035045</v>
+        <v>129034602</v>
       </c>
       <c r="B39" t="n">
         <v>98678</v>
@@ -4409,10 +4409,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>569130</v>
+        <v>569301</v>
       </c>
       <c r="R39" t="n">
-        <v>6949603</v>
+        <v>6949480</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>14 ex</t>
+          <t>22 stycken</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4476,32 +4476,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129035020</v>
+        <v>129035040</v>
       </c>
       <c r="B40" t="n">
-        <v>57727</v>
+        <v>98678</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4511,10 +4511,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>569171</v>
+        <v>569386</v>
       </c>
       <c r="R40" t="n">
-        <v>6949543</v>
+        <v>6949657</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4551,7 +4551,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Äldre ringhack på granhögstubbe</t>
+          <t>9 ex</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4578,32 +4578,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129035015</v>
+        <v>129035045</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>98678</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4613,10 +4613,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>569454</v>
+        <v>569130</v>
       </c>
       <c r="R41" t="n">
-        <v>6949698</v>
+        <v>6949603</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4653,7 +4653,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>14 ex</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4680,10 +4680,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129034643</v>
+        <v>129035063</v>
       </c>
       <c r="B42" t="n">
-        <v>92835</v>
+        <v>96797</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4691,21 +4691,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>2869</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4715,10 +4715,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>569254</v>
+        <v>569455</v>
       </c>
       <c r="R42" t="n">
-        <v>6949431</v>
+        <v>6949758</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4751,11 +4751,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>1 färskt exemplar</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4782,10 +4777,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129035063</v>
+        <v>129034643</v>
       </c>
       <c r="B43" t="n">
-        <v>96797</v>
+        <v>92835</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4793,21 +4788,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2869</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4817,10 +4812,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>569455</v>
+        <v>569254</v>
       </c>
       <c r="R43" t="n">
-        <v>6949758</v>
+        <v>6949431</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4853,6 +4848,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>1 färskt exemplar</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5384,10 +5384,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129035022</v>
+        <v>129035002</v>
       </c>
       <c r="B49" t="n">
-        <v>91827</v>
+        <v>91542</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5395,21 +5395,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5419,10 +5419,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>569423</v>
+        <v>569405</v>
       </c>
       <c r="R49" t="n">
-        <v>6949656</v>
+        <v>6949685</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5481,10 +5481,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129035016</v>
+        <v>129035022</v>
       </c>
       <c r="B50" t="n">
-        <v>57727</v>
+        <v>91827</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5492,21 +5492,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5516,10 +5516,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>569435</v>
+        <v>569423</v>
       </c>
       <c r="R50" t="n">
-        <v>6949665</v>
+        <v>6949656</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5552,11 +5552,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5583,10 +5578,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129034632</v>
+        <v>129034597</v>
       </c>
       <c r="B51" t="n">
-        <v>79041</v>
+        <v>91827</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5594,21 +5589,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5618,10 +5613,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>569237</v>
+        <v>569221</v>
       </c>
       <c r="R51" t="n">
-        <v>6949442</v>
+        <v>6949499</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5654,6 +5649,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>8 exemplar</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5680,10 +5680,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129034597</v>
+        <v>129034632</v>
       </c>
       <c r="B52" t="n">
-        <v>91827</v>
+        <v>79041</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5691,21 +5691,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5715,10 +5715,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>569221</v>
+        <v>569237</v>
       </c>
       <c r="R52" t="n">
-        <v>6949499</v>
+        <v>6949442</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5751,11 +5751,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>8 exemplar</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5782,10 +5777,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129035002</v>
+        <v>129035016</v>
       </c>
       <c r="B53" t="n">
-        <v>91542</v>
+        <v>57727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5793,21 +5788,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5817,10 +5812,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>569405</v>
+        <v>569435</v>
       </c>
       <c r="R53" t="n">
-        <v>6949685</v>
+        <v>6949665</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5853,6 +5848,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5981,10 +5981,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129035028</v>
+        <v>129034581</v>
       </c>
       <c r="B55" t="n">
-        <v>91827</v>
+        <v>57887</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5992,21 +5992,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6016,10 +6016,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>569192</v>
+        <v>569223</v>
       </c>
       <c r="R55" t="n">
-        <v>6949509</v>
+        <v>6949401</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6052,6 +6052,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Sågs och gjorde övriga läten</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6078,32 +6083,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129034600</v>
+        <v>129034610</v>
       </c>
       <c r="B56" t="n">
-        <v>80146</v>
+        <v>98678</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6113,10 +6118,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>569481</v>
+        <v>569282</v>
       </c>
       <c r="R56" t="n">
-        <v>6949674</v>
+        <v>6949567</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6153,7 +6158,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Apothecier antal 1</t>
+          <t>Ca 100 stycken</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6180,32 +6185,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129035008</v>
+        <v>129034614</v>
       </c>
       <c r="B57" t="n">
-        <v>91542</v>
+        <v>98678</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6215,10 +6220,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>569216</v>
+        <v>569237</v>
       </c>
       <c r="R57" t="n">
-        <v>6949430</v>
+        <v>6949556</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6251,6 +6256,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>5 stycken</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6277,10 +6287,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129034581</v>
+        <v>129035008</v>
       </c>
       <c r="B58" t="n">
-        <v>57887</v>
+        <v>91542</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6288,21 +6298,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6312,10 +6322,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>569223</v>
+        <v>569216</v>
       </c>
       <c r="R58" t="n">
-        <v>6949401</v>
+        <v>6949430</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6348,11 +6358,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Sågs och gjorde övriga läten</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6379,32 +6384,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129034610</v>
+        <v>129035028</v>
       </c>
       <c r="B59" t="n">
-        <v>98678</v>
+        <v>91827</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6414,10 +6419,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>569282</v>
+        <v>569192</v>
       </c>
       <c r="R59" t="n">
-        <v>6949567</v>
+        <v>6949509</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6450,11 +6455,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ca 100 stycken</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6481,32 +6481,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129034614</v>
+        <v>129034600</v>
       </c>
       <c r="B60" t="n">
-        <v>98678</v>
+        <v>80146</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6516,10 +6516,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>569237</v>
+        <v>569481</v>
       </c>
       <c r="R60" t="n">
-        <v>6949556</v>
+        <v>6949674</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6556,7 +6556,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>5 stycken</t>
+          <t>Apothecier antal 1</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6583,32 +6583,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129035024</v>
+        <v>129034586</v>
       </c>
       <c r="B61" t="n">
-        <v>91827</v>
+        <v>91997</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6618,10 +6618,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>569404</v>
+        <v>569220</v>
       </c>
       <c r="R61" t="n">
-        <v>6949660</v>
+        <v>6949500</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6680,32 +6680,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129034586</v>
+        <v>129035024</v>
       </c>
       <c r="B62" t="n">
-        <v>91997</v>
+        <v>91827</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6715,10 +6715,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>569220</v>
+        <v>569404</v>
       </c>
       <c r="R62" t="n">
-        <v>6949500</v>
+        <v>6949660</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6777,7 +6777,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129035003</v>
+        <v>129034574</v>
       </c>
       <c r="B63" t="n">
         <v>91542</v>
@@ -6812,10 +6812,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>569164</v>
+        <v>569461</v>
       </c>
       <c r="R63" t="n">
-        <v>6949559</v>
+        <v>6949706</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6874,7 +6874,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129034574</v>
+        <v>129035003</v>
       </c>
       <c r="B64" t="n">
         <v>91542</v>
@@ -6909,10 +6909,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>569461</v>
+        <v>569164</v>
       </c>
       <c r="R64" t="n">
-        <v>6949706</v>
+        <v>6949559</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7470,32 +7470,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129035037</v>
+        <v>129035060</v>
       </c>
       <c r="B70" t="n">
-        <v>98678</v>
+        <v>92835</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7505,10 +7505,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>569434</v>
+        <v>569208</v>
       </c>
       <c r="R70" t="n">
-        <v>6949706</v>
+        <v>6949415</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7545,7 +7545,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>20 ex</t>
+          <t>20 ex minst</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7572,32 +7572,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129034584</v>
+        <v>129034639</v>
       </c>
       <c r="B71" t="n">
-        <v>57724</v>
+        <v>92835</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7607,10 +7607,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>569221</v>
+        <v>569398</v>
       </c>
       <c r="R71" t="n">
-        <v>6949499</v>
+        <v>6949741</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7647,7 +7647,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Förbiflygande från träd till träd</t>
+          <t>6 äldre exemplar och 1 färsk fruktkropp</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7674,32 +7674,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129035018</v>
+        <v>129035037</v>
       </c>
       <c r="B72" t="n">
-        <v>57727</v>
+        <v>98678</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7709,10 +7709,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>569111</v>
+        <v>569434</v>
       </c>
       <c r="R72" t="n">
-        <v>6949604</v>
+        <v>6949706</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7749,7 +7749,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7776,32 +7776,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129035060</v>
+        <v>129034584</v>
       </c>
       <c r="B73" t="n">
-        <v>92835</v>
+        <v>57724</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7811,10 +7811,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>569208</v>
+        <v>569221</v>
       </c>
       <c r="R73" t="n">
-        <v>6949415</v>
+        <v>6949499</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>20 ex minst</t>
+          <t>Förbiflygande från träd till träd</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7878,32 +7878,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129034639</v>
+        <v>129035018</v>
       </c>
       <c r="B74" t="n">
-        <v>92835</v>
+        <v>57727</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7913,10 +7913,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>569398</v>
+        <v>569111</v>
       </c>
       <c r="R74" t="n">
-        <v>6949741</v>
+        <v>6949604</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7953,7 +7953,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>6 äldre exemplar och 1 färsk fruktkropp</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8281,32 +8281,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129034598</v>
+        <v>129034650</v>
       </c>
       <c r="B78" t="n">
-        <v>97549</v>
+        <v>98678</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8316,10 +8316,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>569460</v>
+        <v>569303</v>
       </c>
       <c r="R78" t="n">
-        <v>6949629</v>
+        <v>6949537</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8352,6 +8352,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>30 stycken ( finns eventuellt mer )</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8378,7 +8383,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129034650</v>
+        <v>129034605</v>
       </c>
       <c r="B79" t="n">
         <v>98678</v>
@@ -8413,10 +8418,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>569303</v>
+        <v>569305</v>
       </c>
       <c r="R79" t="n">
-        <v>6949537</v>
+        <v>6949538</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8453,7 +8458,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>30 stycken ( finns eventuellt mer )</t>
+          <t>21 knärot</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8480,32 +8485,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129034605</v>
+        <v>129034598</v>
       </c>
       <c r="B80" t="n">
-        <v>98678</v>
+        <v>97549</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8515,10 +8520,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>569305</v>
+        <v>569460</v>
       </c>
       <c r="R80" t="n">
-        <v>6949538</v>
+        <v>6949629</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8551,11 +8556,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>21 knärot</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8582,32 +8582,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129035047</v>
+        <v>129035057</v>
       </c>
       <c r="B81" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8617,10 +8617,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>569162</v>
+        <v>569464</v>
       </c>
       <c r="R81" t="n">
-        <v>6949566</v>
+        <v>6949648</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8653,11 +8653,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>50 ex</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8684,32 +8679,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129034618</v>
+        <v>129035001</v>
       </c>
       <c r="B82" t="n">
-        <v>98678</v>
+        <v>91506</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8719,10 +8714,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>569235</v>
+        <v>569232</v>
       </c>
       <c r="R82" t="n">
-        <v>6949411</v>
+        <v>6949444</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8755,11 +8750,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8786,32 +8776,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129034604</v>
+        <v>129035061</v>
       </c>
       <c r="B83" t="n">
-        <v>98678</v>
+        <v>96797</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8821,10 +8811,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>569303</v>
+        <v>569333</v>
       </c>
       <c r="R83" t="n">
-        <v>6949536</v>
+        <v>6949607</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8857,11 +8847,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8888,10 +8873,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129035057</v>
+        <v>129035007</v>
       </c>
       <c r="B84" t="n">
-        <v>79041</v>
+        <v>91542</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8899,21 +8884,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8923,10 +8908,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>569464</v>
+        <v>569225</v>
       </c>
       <c r="R84" t="n">
-        <v>6949648</v>
+        <v>6949424</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8985,10 +8970,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129035001</v>
+        <v>129034640</v>
       </c>
       <c r="B85" t="n">
-        <v>91506</v>
+        <v>92835</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8996,21 +8981,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9020,10 +9005,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>569232</v>
+        <v>569213</v>
       </c>
       <c r="R85" t="n">
-        <v>6949444</v>
+        <v>6949414</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9056,6 +9041,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>16 exemplar</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9184,32 +9174,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129035007</v>
+        <v>129035047</v>
       </c>
       <c r="B87" t="n">
-        <v>91542</v>
+        <v>98678</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9219,10 +9209,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>569225</v>
+        <v>569162</v>
       </c>
       <c r="R87" t="n">
-        <v>6949424</v>
+        <v>6949566</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9255,6 +9245,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9281,32 +9276,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129035061</v>
+        <v>129034604</v>
       </c>
       <c r="B88" t="n">
-        <v>96797</v>
+        <v>98678</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9316,10 +9311,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>569333</v>
+        <v>569303</v>
       </c>
       <c r="R88" t="n">
-        <v>6949607</v>
+        <v>6949536</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9352,6 +9347,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9378,32 +9378,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129034640</v>
+        <v>129034618</v>
       </c>
       <c r="B89" t="n">
-        <v>92835</v>
+        <v>98678</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9413,10 +9413,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>569213</v>
+        <v>569235</v>
       </c>
       <c r="R89" t="n">
-        <v>6949414</v>
+        <v>6949411</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9453,7 +9453,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>16 exemplar</t>
+          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9480,7 +9480,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129035027</v>
+        <v>129035023</v>
       </c>
       <c r="B90" t="n">
         <v>91827</v>
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>569169</v>
+        <v>569415</v>
       </c>
       <c r="R90" t="n">
-        <v>6949533</v>
+        <v>6949677</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9577,7 +9577,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129034589</v>
+        <v>129035027</v>
       </c>
       <c r="B91" t="n">
         <v>91827</v>
@@ -9612,10 +9612,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>569365</v>
+        <v>569169</v>
       </c>
       <c r="R91" t="n">
-        <v>6949661</v>
+        <v>6949533</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9674,7 +9674,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129035023</v>
+        <v>129034589</v>
       </c>
       <c r="B92" t="n">
         <v>91827</v>
@@ -9709,10 +9709,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>569415</v>
+        <v>569365</v>
       </c>
       <c r="R92" t="n">
-        <v>6949677</v>
+        <v>6949661</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9868,7 +9868,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129035038</v>
+        <v>129035050</v>
       </c>
       <c r="B94" t="n">
         <v>98678</v>
@@ -9903,10 +9903,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>569406</v>
+        <v>569236</v>
       </c>
       <c r="R94" t="n">
-        <v>6949664</v>
+        <v>6949440</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9943,7 +9943,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>20 ex</t>
+          <t>4 ex</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -9970,7 +9970,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129035050</v>
+        <v>129034621</v>
       </c>
       <c r="B95" t="n">
         <v>98678</v>
@@ -10005,10 +10005,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>569236</v>
+        <v>569247</v>
       </c>
       <c r="R95" t="n">
-        <v>6949440</v>
+        <v>6949434</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10045,7 +10045,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>4 ex</t>
+          <t>10 stycken knärot</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10072,7 +10072,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129034621</v>
+        <v>129035038</v>
       </c>
       <c r="B96" t="n">
         <v>98678</v>
@@ -10107,10 +10107,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>569247</v>
+        <v>569406</v>
       </c>
       <c r="R96" t="n">
-        <v>6949434</v>
+        <v>6949664</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10147,7 +10147,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>10 stycken knärot</t>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10878,10 +10878,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129035026</v>
+        <v>129027886</v>
       </c>
       <c r="B104" t="n">
-        <v>91827</v>
+        <v>91542</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10889,21 +10889,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10913,10 +10913,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>569175</v>
+        <v>569305</v>
       </c>
       <c r="R104" t="n">
-        <v>6949549</v>
+        <v>6949566</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10975,32 +10975,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129035048</v>
+        <v>129035006</v>
       </c>
       <c r="B105" t="n">
-        <v>98678</v>
+        <v>91542</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11010,10 +11010,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>569176</v>
+        <v>569217</v>
       </c>
       <c r="R105" t="n">
-        <v>6949507</v>
+        <v>6949470</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11046,11 +11046,6 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>30 ex</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11077,32 +11072,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129035053</v>
+        <v>129035026</v>
       </c>
       <c r="B106" t="n">
-        <v>98678</v>
+        <v>91827</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11112,10 +11107,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>569459</v>
+        <v>569175</v>
       </c>
       <c r="R106" t="n">
-        <v>6949662</v>
+        <v>6949549</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11148,11 +11143,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>14 ex</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11179,7 +11169,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129035049</v>
+        <v>129035048</v>
       </c>
       <c r="B107" t="n">
         <v>98678</v>
@@ -11214,10 +11204,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>569219</v>
+        <v>569176</v>
       </c>
       <c r="R107" t="n">
-        <v>6949489</v>
+        <v>6949507</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11254,7 +11244,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>35 ex</t>
+          <t>30 ex</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11281,7 +11271,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129035044</v>
+        <v>129035053</v>
       </c>
       <c r="B108" t="n">
         <v>98678</v>
@@ -11316,10 +11306,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>569191</v>
+        <v>569459</v>
       </c>
       <c r="R108" t="n">
-        <v>6949579</v>
+        <v>6949662</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11356,7 +11346,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>50 ex</t>
+          <t>14 ex</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11383,32 +11373,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129035006</v>
+        <v>129035049</v>
       </c>
       <c r="B109" t="n">
-        <v>91542</v>
+        <v>98678</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11418,10 +11408,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>569217</v>
+        <v>569219</v>
       </c>
       <c r="R109" t="n">
-        <v>6949470</v>
+        <v>6949489</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11454,6 +11444,11 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>35 ex</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11480,32 +11475,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129027886</v>
+        <v>129035044</v>
       </c>
       <c r="B110" t="n">
-        <v>91542</v>
+        <v>98678</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11515,10 +11510,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>569305</v>
+        <v>569191</v>
       </c>
       <c r="R110" t="n">
-        <v>6949566</v>
+        <v>6949579</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11551,6 +11546,11 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD110" t="b">

--- a/artfynd/A 45833-2025 artfynd.xlsx
+++ b/artfynd/A 45833-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129034612</v>
+        <v>129034627</v>
       </c>
       <c r="B2" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569243</v>
+        <v>569482</v>
       </c>
       <c r="R2" t="n">
-        <v>6949558</v>
+        <v>6949676</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>30  exemplar ca</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129035046</v>
+        <v>129034612</v>
       </c>
       <c r="B3" t="n">
         <v>98678</v>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569127</v>
+        <v>569243</v>
       </c>
       <c r="R3" t="n">
-        <v>6949602</v>
+        <v>6949558</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +847,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>13 ex</t>
+          <t>30  exemplar ca</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,7 +874,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129035043</v>
+        <v>129035046</v>
       </c>
       <c r="B4" t="n">
         <v>98678</v>
@@ -914,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569204</v>
+        <v>569127</v>
       </c>
       <c r="R4" t="n">
-        <v>6949533</v>
+        <v>6949602</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,7 +949,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>10 ex</t>
+          <t>13 ex</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,32 +976,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129034627</v>
+        <v>129035043</v>
       </c>
       <c r="B5" t="n">
-        <v>79041</v>
+        <v>98678</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569482</v>
+        <v>569204</v>
       </c>
       <c r="R5" t="n">
-        <v>6949676</v>
+        <v>6949533</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1052,6 +1047,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -2787,32 +2787,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129035005</v>
+        <v>129034623</v>
       </c>
       <c r="B23" t="n">
-        <v>91542</v>
+        <v>98678</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569188</v>
+        <v>569253</v>
       </c>
       <c r="R23" t="n">
-        <v>6949496</v>
+        <v>6949425</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2858,6 +2858,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>74 stycken</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2884,7 +2889,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129035004</v>
+        <v>129035005</v>
       </c>
       <c r="B24" t="n">
         <v>91542</v>
@@ -2919,10 +2924,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569152</v>
+        <v>569188</v>
       </c>
       <c r="R24" t="n">
-        <v>6949557</v>
+        <v>6949496</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2981,10 +2986,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129034592</v>
+        <v>129035004</v>
       </c>
       <c r="B25" t="n">
-        <v>91827</v>
+        <v>91542</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2992,21 +2997,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3016,10 +3021,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569205</v>
+        <v>569152</v>
       </c>
       <c r="R25" t="n">
-        <v>6949497</v>
+        <v>6949557</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3052,11 +3057,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>1 x</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3083,7 +3083,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129034591</v>
+        <v>129034592</v>
       </c>
       <c r="B26" t="n">
         <v>91827</v>
@@ -3118,10 +3118,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569203</v>
+        <v>569205</v>
       </c>
       <c r="R26" t="n">
-        <v>6949513</v>
+        <v>6949497</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3158,7 +3158,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>11 ex</t>
+          <t>1 x</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3185,10 +3185,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129034647</v>
+        <v>129034591</v>
       </c>
       <c r="B27" t="n">
-        <v>88939</v>
+        <v>91827</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3196,21 +3196,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3220,10 +3220,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>569247</v>
+        <v>569203</v>
       </c>
       <c r="R27" t="n">
-        <v>6949558</v>
+        <v>6949513</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3256,6 +3256,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>11 ex</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3282,10 +3287,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129035025</v>
+        <v>129034647</v>
       </c>
       <c r="B28" t="n">
-        <v>91827</v>
+        <v>88939</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3293,21 +3298,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3317,10 +3322,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>569388</v>
+        <v>569247</v>
       </c>
       <c r="R28" t="n">
-        <v>6949665</v>
+        <v>6949558</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3379,10 +3384,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129034625</v>
+        <v>129035025</v>
       </c>
       <c r="B29" t="n">
-        <v>79041</v>
+        <v>91827</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3390,21 +3395,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3414,10 +3419,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>569479</v>
+        <v>569388</v>
       </c>
       <c r="R29" t="n">
-        <v>6949657</v>
+        <v>6949665</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3476,32 +3481,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129034623</v>
+        <v>129034625</v>
       </c>
       <c r="B30" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3511,10 +3516,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>569253</v>
+        <v>569479</v>
       </c>
       <c r="R30" t="n">
-        <v>6949425</v>
+        <v>6949657</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3547,11 +3552,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>74 stycken</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3578,32 +3578,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129034578</v>
+        <v>129035051</v>
       </c>
       <c r="B31" t="n">
-        <v>57727</v>
+        <v>98678</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>569420</v>
+        <v>569222</v>
       </c>
       <c r="R31" t="n">
-        <v>6949723</v>
+        <v>6949414</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3653,7 +3653,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på Tall</t>
+          <t>30 ex</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3680,32 +3680,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129034637</v>
+        <v>129034578</v>
       </c>
       <c r="B32" t="n">
-        <v>92835</v>
+        <v>57727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3715,10 +3715,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>569229</v>
+        <v>569420</v>
       </c>
       <c r="R32" t="n">
-        <v>6949400</v>
+        <v>6949723</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3751,6 +3751,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3777,32 +3782,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129035058</v>
+        <v>129034637</v>
       </c>
       <c r="B33" t="n">
-        <v>79041</v>
+        <v>92835</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3812,10 +3817,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>569388</v>
+        <v>569229</v>
       </c>
       <c r="R33" t="n">
-        <v>6949647</v>
+        <v>6949400</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3874,32 +3879,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129035051</v>
+        <v>129035058</v>
       </c>
       <c r="B34" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3909,10 +3914,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>569222</v>
+        <v>569388</v>
       </c>
       <c r="R34" t="n">
-        <v>6949414</v>
+        <v>6949647</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3945,11 +3950,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>30 ex</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5981,10 +5981,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129034581</v>
+        <v>129035008</v>
       </c>
       <c r="B55" t="n">
-        <v>57887</v>
+        <v>91542</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5992,21 +5992,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6016,10 +6016,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>569223</v>
+        <v>569216</v>
       </c>
       <c r="R55" t="n">
-        <v>6949401</v>
+        <v>6949430</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6052,11 +6052,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Sågs och gjorde övriga läten</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6083,32 +6078,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129034610</v>
+        <v>129035028</v>
       </c>
       <c r="B56" t="n">
-        <v>98678</v>
+        <v>91827</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6118,10 +6113,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>569282</v>
+        <v>569192</v>
       </c>
       <c r="R56" t="n">
-        <v>6949567</v>
+        <v>6949509</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6154,11 +6149,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ca 100 stycken</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6185,32 +6175,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129034614</v>
+        <v>129034600</v>
       </c>
       <c r="B57" t="n">
-        <v>98678</v>
+        <v>80146</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6220,10 +6210,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>569237</v>
+        <v>569481</v>
       </c>
       <c r="R57" t="n">
-        <v>6949556</v>
+        <v>6949674</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6260,7 +6250,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>5 stycken</t>
+          <t>Apothecier antal 1</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6287,10 +6277,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129035008</v>
+        <v>129034581</v>
       </c>
       <c r="B58" t="n">
-        <v>91542</v>
+        <v>57887</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6298,21 +6288,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6322,10 +6312,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>569216</v>
+        <v>569223</v>
       </c>
       <c r="R58" t="n">
-        <v>6949430</v>
+        <v>6949401</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6358,6 +6348,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Sågs och gjorde övriga läten</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6384,32 +6379,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129035028</v>
+        <v>129034610</v>
       </c>
       <c r="B59" t="n">
-        <v>91827</v>
+        <v>98678</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6419,10 +6414,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>569192</v>
+        <v>569282</v>
       </c>
       <c r="R59" t="n">
-        <v>6949509</v>
+        <v>6949567</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6455,6 +6450,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ca 100 stycken</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6481,32 +6481,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129034600</v>
+        <v>129034614</v>
       </c>
       <c r="B60" t="n">
-        <v>80146</v>
+        <v>98678</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6516,10 +6516,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>569481</v>
+        <v>569237</v>
       </c>
       <c r="R60" t="n">
-        <v>6949674</v>
+        <v>6949556</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6556,7 +6556,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Apothecier antal 1</t>
+          <t>5 stycken</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7980,32 +7980,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129026691</v>
+        <v>129034598</v>
       </c>
       <c r="B75" t="n">
-        <v>91827</v>
+        <v>97549</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8015,10 +8015,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>569195</v>
+        <v>569460</v>
       </c>
       <c r="R75" t="n">
-        <v>6949487</v>
+        <v>6949629</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8077,32 +8077,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129034645</v>
+        <v>129034650</v>
       </c>
       <c r="B76" t="n">
-        <v>92835</v>
+        <v>98678</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8112,10 +8112,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>569196</v>
+        <v>569303</v>
       </c>
       <c r="R76" t="n">
-        <v>6949411</v>
+        <v>6949537</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8152,7 +8152,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>4 färska exemplar 3 äldre exemplar</t>
+          <t>30 stycken ( finns eventuellt mer )</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8179,32 +8179,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129034642</v>
+        <v>129034605</v>
       </c>
       <c r="B77" t="n">
-        <v>92835</v>
+        <v>98678</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8214,10 +8214,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>569283</v>
+        <v>569305</v>
       </c>
       <c r="R77" t="n">
-        <v>6949655</v>
+        <v>6949538</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>7 äldre exemplar</t>
+          <t>21 knärot</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8281,32 +8281,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129034650</v>
+        <v>129026691</v>
       </c>
       <c r="B78" t="n">
-        <v>98678</v>
+        <v>91827</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8316,10 +8316,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>569303</v>
+        <v>569195</v>
       </c>
       <c r="R78" t="n">
-        <v>6949537</v>
+        <v>6949487</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8352,11 +8352,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>30 stycken ( finns eventuellt mer )</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8383,32 +8378,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129034605</v>
+        <v>129034645</v>
       </c>
       <c r="B79" t="n">
-        <v>98678</v>
+        <v>92835</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8418,10 +8413,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>569305</v>
+        <v>569196</v>
       </c>
       <c r="R79" t="n">
-        <v>6949538</v>
+        <v>6949411</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8458,7 +8453,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>21 knärot</t>
+          <t>4 färska exemplar 3 äldre exemplar</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8485,10 +8480,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129034598</v>
+        <v>129034642</v>
       </c>
       <c r="B80" t="n">
-        <v>97549</v>
+        <v>92835</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8496,21 +8491,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8520,10 +8515,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>569460</v>
+        <v>569283</v>
       </c>
       <c r="R80" t="n">
-        <v>6949629</v>
+        <v>6949655</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8556,6 +8551,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>7 äldre exemplar</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8582,32 +8582,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129035057</v>
+        <v>129035047</v>
       </c>
       <c r="B81" t="n">
-        <v>79041</v>
+        <v>98678</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8617,10 +8617,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>569464</v>
+        <v>569162</v>
       </c>
       <c r="R81" t="n">
-        <v>6949648</v>
+        <v>6949566</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8653,6 +8653,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8679,32 +8684,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129035001</v>
+        <v>129034604</v>
       </c>
       <c r="B82" t="n">
-        <v>91506</v>
+        <v>98678</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8714,10 +8719,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>569232</v>
+        <v>569303</v>
       </c>
       <c r="R82" t="n">
-        <v>6949444</v>
+        <v>6949536</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8750,6 +8755,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8776,32 +8786,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129035061</v>
+        <v>129034618</v>
       </c>
       <c r="B83" t="n">
-        <v>96797</v>
+        <v>98678</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8811,10 +8821,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>569333</v>
+        <v>569235</v>
       </c>
       <c r="R83" t="n">
-        <v>6949607</v>
+        <v>6949411</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8847,6 +8857,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8873,10 +8888,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129035007</v>
+        <v>129035057</v>
       </c>
       <c r="B84" t="n">
-        <v>91542</v>
+        <v>79041</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8884,21 +8899,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8908,10 +8923,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>569225</v>
+        <v>569464</v>
       </c>
       <c r="R84" t="n">
-        <v>6949424</v>
+        <v>6949648</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8970,10 +8985,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129034640</v>
+        <v>129035001</v>
       </c>
       <c r="B85" t="n">
-        <v>92835</v>
+        <v>91506</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8981,21 +8996,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9005,10 +9020,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>569213</v>
+        <v>569232</v>
       </c>
       <c r="R85" t="n">
-        <v>6949414</v>
+        <v>6949444</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9041,11 +9056,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>16 exemplar</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9174,32 +9184,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129035047</v>
+        <v>129035061</v>
       </c>
       <c r="B87" t="n">
-        <v>98678</v>
+        <v>96797</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9209,10 +9219,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>569162</v>
+        <v>569333</v>
       </c>
       <c r="R87" t="n">
-        <v>6949566</v>
+        <v>6949607</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9245,11 +9255,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>50 ex</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9276,32 +9281,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129034604</v>
+        <v>129035007</v>
       </c>
       <c r="B88" t="n">
-        <v>98678</v>
+        <v>91542</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9311,10 +9316,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>569303</v>
+        <v>569225</v>
       </c>
       <c r="R88" t="n">
-        <v>6949536</v>
+        <v>6949424</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9347,11 +9352,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9378,32 +9378,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129034618</v>
+        <v>129034640</v>
       </c>
       <c r="B89" t="n">
-        <v>98678</v>
+        <v>92835</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9413,10 +9413,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>569235</v>
+        <v>569213</v>
       </c>
       <c r="R89" t="n">
-        <v>6949411</v>
+        <v>6949414</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9453,7 +9453,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>18 stycken</t>
+          <t>16 exemplar</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10174,32 +10174,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129034635</v>
+        <v>129034609</v>
       </c>
       <c r="B97" t="n">
-        <v>79041</v>
+        <v>98678</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10209,10 +10209,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>569427</v>
+        <v>569458</v>
       </c>
       <c r="R97" t="n">
-        <v>6949726</v>
+        <v>6949777</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10245,6 +10245,11 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>48 stycken</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10271,32 +10276,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129035017</v>
+        <v>129035036</v>
       </c>
       <c r="B98" t="n">
-        <v>57727</v>
+        <v>98678</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10306,10 +10311,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>569192</v>
+        <v>569330</v>
       </c>
       <c r="R98" t="n">
-        <v>6949518</v>
+        <v>6949564</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10346,7 +10351,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>8 ex</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10373,32 +10378,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129035010</v>
+        <v>129035052</v>
       </c>
       <c r="B99" t="n">
-        <v>57727</v>
+        <v>98678</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10408,10 +10413,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>569465</v>
+        <v>569405</v>
       </c>
       <c r="R99" t="n">
-        <v>6949606</v>
+        <v>6949641</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10448,7 +10453,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>70 ex</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10475,32 +10480,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129034609</v>
+        <v>129035056</v>
       </c>
       <c r="B100" t="n">
-        <v>98678</v>
+        <v>105741</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10510,10 +10515,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>569458</v>
+        <v>569201</v>
       </c>
       <c r="R100" t="n">
-        <v>6949777</v>
+        <v>6949530</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10546,11 +10551,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>48 stycken</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10577,32 +10577,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129035036</v>
+        <v>129035017</v>
       </c>
       <c r="B101" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10612,10 +10612,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>569330</v>
+        <v>569192</v>
       </c>
       <c r="R101" t="n">
-        <v>6949564</v>
+        <v>6949518</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10652,7 +10652,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>8 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10679,32 +10679,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129035052</v>
+        <v>129035010</v>
       </c>
       <c r="B102" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10714,10 +10714,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>569405</v>
+        <v>569465</v>
       </c>
       <c r="R102" t="n">
-        <v>6949641</v>
+        <v>6949606</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10754,7 +10754,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>70 ex</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10781,32 +10781,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129035056</v>
+        <v>129034635</v>
       </c>
       <c r="B103" t="n">
-        <v>105741</v>
+        <v>79041</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>221144</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10816,10 +10816,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>569201</v>
+        <v>569427</v>
       </c>
       <c r="R103" t="n">
-        <v>6949530</v>
+        <v>6949726</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10878,32 +10878,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129027886</v>
+        <v>129035048</v>
       </c>
       <c r="B104" t="n">
-        <v>91542</v>
+        <v>98678</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10913,10 +10913,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>569305</v>
+        <v>569176</v>
       </c>
       <c r="R104" t="n">
-        <v>6949566</v>
+        <v>6949507</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10949,6 +10949,11 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>30 ex</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -10975,32 +10980,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129035006</v>
+        <v>129035053</v>
       </c>
       <c r="B105" t="n">
-        <v>91542</v>
+        <v>98678</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11010,10 +11015,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>569217</v>
+        <v>569459</v>
       </c>
       <c r="R105" t="n">
-        <v>6949470</v>
+        <v>6949662</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11046,6 +11051,11 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>14 ex</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11072,32 +11082,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129035026</v>
+        <v>129035049</v>
       </c>
       <c r="B106" t="n">
-        <v>91827</v>
+        <v>98678</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11107,10 +11117,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>569175</v>
+        <v>569219</v>
       </c>
       <c r="R106" t="n">
-        <v>6949549</v>
+        <v>6949489</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11143,6 +11153,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>35 ex</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11169,7 +11184,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129035048</v>
+        <v>129035044</v>
       </c>
       <c r="B107" t="n">
         <v>98678</v>
@@ -11204,10 +11219,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>569176</v>
+        <v>569191</v>
       </c>
       <c r="R107" t="n">
-        <v>6949507</v>
+        <v>6949579</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11244,7 +11259,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>30 ex</t>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11271,32 +11286,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129035053</v>
+        <v>129027886</v>
       </c>
       <c r="B108" t="n">
-        <v>98678</v>
+        <v>91542</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11306,10 +11321,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>569459</v>
+        <v>569305</v>
       </c>
       <c r="R108" t="n">
-        <v>6949662</v>
+        <v>6949566</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11342,11 +11357,6 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>14 ex</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11373,32 +11383,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129035049</v>
+        <v>129035006</v>
       </c>
       <c r="B109" t="n">
-        <v>98678</v>
+        <v>91542</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11408,10 +11418,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>569219</v>
+        <v>569217</v>
       </c>
       <c r="R109" t="n">
-        <v>6949489</v>
+        <v>6949470</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11444,11 +11454,6 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>35 ex</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11475,32 +11480,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129035044</v>
+        <v>129035026</v>
       </c>
       <c r="B110" t="n">
-        <v>98678</v>
+        <v>91827</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11510,10 +11515,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>569191</v>
+        <v>569175</v>
       </c>
       <c r="R110" t="n">
-        <v>6949579</v>
+        <v>6949549</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11546,11 +11551,6 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>50 ex</t>
         </is>
       </c>
       <c r="AD110" t="b">

--- a/artfynd/A 45833-2025 artfynd.xlsx
+++ b/artfynd/A 45833-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129034627</v>
+        <v>129034612</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>98704</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569482</v>
+        <v>569243</v>
       </c>
       <c r="R2" t="n">
-        <v>6949676</v>
+        <v>6949558</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>30  exemplar ca</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129034612</v>
+        <v>129035046</v>
       </c>
       <c r="B3" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569243</v>
+        <v>569127</v>
       </c>
       <c r="R3" t="n">
-        <v>6949558</v>
+        <v>6949602</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>30  exemplar ca</t>
+          <t>13 ex</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129035046</v>
+        <v>129035043</v>
       </c>
       <c r="B4" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -909,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569127</v>
+        <v>569204</v>
       </c>
       <c r="R4" t="n">
-        <v>6949602</v>
+        <v>6949533</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,7 +954,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>13 ex</t>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,32 +981,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129035043</v>
+        <v>129034627</v>
       </c>
       <c r="B5" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569204</v>
+        <v>569482</v>
       </c>
       <c r="R5" t="n">
-        <v>6949533</v>
+        <v>6949676</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1047,11 +1052,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>10 ex</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1078,32 +1078,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129035030</v>
+        <v>129035039</v>
       </c>
       <c r="B6" t="n">
-        <v>97549</v>
+        <v>98704</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>569424</v>
+        <v>569394</v>
       </c>
       <c r="R6" t="n">
-        <v>6949671</v>
+        <v>6949664</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1149,6 +1149,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1175,32 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129035039</v>
+        <v>129035030</v>
       </c>
       <c r="B7" t="n">
-        <v>98678</v>
+        <v>97575</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>569394</v>
+        <v>569424</v>
       </c>
       <c r="R7" t="n">
-        <v>6949664</v>
+        <v>6949671</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1246,11 +1251,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1484,7 +1484,7 @@
         <v>129035054</v>
       </c>
       <c r="B10" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,10 +1583,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129034630</v>
+        <v>129034594</v>
       </c>
       <c r="B11" t="n">
-        <v>79041</v>
+        <v>91837</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1594,21 +1594,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>569231</v>
+        <v>569203</v>
       </c>
       <c r="R11" t="n">
-        <v>6949559</v>
+        <v>6949498</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1654,6 +1654,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>11 exemplar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1680,32 +1685,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129034648</v>
+        <v>129034577</v>
       </c>
       <c r="B12" t="n">
-        <v>96797</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1715,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569279</v>
+        <v>569496</v>
       </c>
       <c r="R12" t="n">
-        <v>6949401</v>
+        <v>6949627</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1751,6 +1756,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1777,32 +1787,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129034594</v>
+        <v>129035055</v>
       </c>
       <c r="B13" t="n">
-        <v>91827</v>
+        <v>98704</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1812,10 +1822,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569203</v>
+        <v>569221</v>
       </c>
       <c r="R13" t="n">
-        <v>6949498</v>
+        <v>6949406</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1852,7 +1862,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>11 exemplar</t>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1879,32 +1889,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129034577</v>
+        <v>129035042</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>98704</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1914,10 +1924,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569496</v>
+        <v>569200</v>
       </c>
       <c r="R14" t="n">
-        <v>6949627</v>
+        <v>6949533</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1954,7 +1964,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på tall</t>
+          <t>30 ex</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1981,32 +1991,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129035055</v>
+        <v>129034648</v>
       </c>
       <c r="B15" t="n">
-        <v>98678</v>
+        <v>96823</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2016,10 +2026,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>569221</v>
+        <v>569279</v>
       </c>
       <c r="R15" t="n">
-        <v>6949406</v>
+        <v>6949401</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2052,11 +2062,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>25 ex</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2083,32 +2088,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129035042</v>
+        <v>129034630</v>
       </c>
       <c r="B16" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2118,10 +2123,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>569200</v>
+        <v>569231</v>
       </c>
       <c r="R16" t="n">
-        <v>6949533</v>
+        <v>6949559</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2154,11 +2159,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>30 ex</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2188,7 +2188,7 @@
         <v>129035059</v>
       </c>
       <c r="B17" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>129034620</v>
       </c>
       <c r="B22" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2787,32 +2787,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129034623</v>
+        <v>129035004</v>
       </c>
       <c r="B23" t="n">
-        <v>98678</v>
+        <v>91540</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569253</v>
+        <v>569152</v>
       </c>
       <c r="R23" t="n">
-        <v>6949425</v>
+        <v>6949557</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2858,11 +2858,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>74 stycken</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2892,7 +2887,7 @@
         <v>129035005</v>
       </c>
       <c r="B24" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2986,10 +2981,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129035004</v>
+        <v>129034625</v>
       </c>
       <c r="B25" t="n">
-        <v>91542</v>
+        <v>79041</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2997,21 +2992,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3021,10 +3016,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569152</v>
+        <v>569479</v>
       </c>
       <c r="R25" t="n">
-        <v>6949557</v>
+        <v>6949657</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3086,7 +3081,7 @@
         <v>129034592</v>
       </c>
       <c r="B26" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3188,7 +3183,7 @@
         <v>129034591</v>
       </c>
       <c r="B27" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3290,7 +3285,7 @@
         <v>129034647</v>
       </c>
       <c r="B28" t="n">
-        <v>88939</v>
+        <v>88940</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3387,7 +3382,7 @@
         <v>129035025</v>
       </c>
       <c r="B29" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3481,32 +3476,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129034625</v>
+        <v>129034623</v>
       </c>
       <c r="B30" t="n">
-        <v>79041</v>
+        <v>98704</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3516,10 +3511,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>569479</v>
+        <v>569253</v>
       </c>
       <c r="R30" t="n">
-        <v>6949657</v>
+        <v>6949425</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3552,6 +3547,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>74 stycken</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3578,32 +3578,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129035051</v>
+        <v>129034637</v>
       </c>
       <c r="B31" t="n">
-        <v>98678</v>
+        <v>92821</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>569222</v>
+        <v>569229</v>
       </c>
       <c r="R31" t="n">
-        <v>6949414</v>
+        <v>6949400</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3649,11 +3649,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>30 ex</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3680,10 +3675,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129034578</v>
+        <v>129035058</v>
       </c>
       <c r="B32" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3691,21 +3686,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3715,10 +3710,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>569420</v>
+        <v>569388</v>
       </c>
       <c r="R32" t="n">
-        <v>6949723</v>
+        <v>6949647</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3751,11 +3746,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3782,32 +3772,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129034637</v>
+        <v>129035031</v>
       </c>
       <c r="B33" t="n">
-        <v>92835</v>
+        <v>80146</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3817,10 +3807,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>569229</v>
+        <v>569125</v>
       </c>
       <c r="R33" t="n">
-        <v>6949400</v>
+        <v>6949570</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3879,10 +3869,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129035058</v>
+        <v>129034578</v>
       </c>
       <c r="B34" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3890,21 +3880,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3914,10 +3904,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>569388</v>
+        <v>569420</v>
       </c>
       <c r="R34" t="n">
-        <v>6949647</v>
+        <v>6949723</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3950,6 +3940,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3976,32 +3971,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129035031</v>
+        <v>129035051</v>
       </c>
       <c r="B35" t="n">
-        <v>80146</v>
+        <v>98704</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4011,10 +4006,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>569125</v>
+        <v>569222</v>
       </c>
       <c r="R35" t="n">
-        <v>6949570</v>
+        <v>6949414</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4047,6 +4042,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>30 ex</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4170,32 +4170,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129035020</v>
+        <v>129034602</v>
       </c>
       <c r="B37" t="n">
-        <v>57727</v>
+        <v>98704</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4205,10 +4205,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>569171</v>
+        <v>569301</v>
       </c>
       <c r="R37" t="n">
-        <v>6949543</v>
+        <v>6949480</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Äldre ringhack på granhögstubbe</t>
+          <t>22 stycken</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4272,32 +4272,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129035015</v>
+        <v>129035040</v>
       </c>
       <c r="B38" t="n">
-        <v>57727</v>
+        <v>98704</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4307,10 +4307,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>569454</v>
+        <v>569386</v>
       </c>
       <c r="R38" t="n">
-        <v>6949698</v>
+        <v>6949657</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>9 ex</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4374,10 +4374,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129034602</v>
+        <v>129035045</v>
       </c>
       <c r="B39" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4409,10 +4409,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>569301</v>
+        <v>569130</v>
       </c>
       <c r="R39" t="n">
-        <v>6949480</v>
+        <v>6949603</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>22 stycken</t>
+          <t>14 ex</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4476,32 +4476,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129035040</v>
+        <v>129035020</v>
       </c>
       <c r="B40" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4511,10 +4511,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>569386</v>
+        <v>569171</v>
       </c>
       <c r="R40" t="n">
-        <v>6949657</v>
+        <v>6949543</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4551,7 +4551,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>9 ex</t>
+          <t>Äldre ringhack på granhögstubbe</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4578,32 +4578,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129035045</v>
+        <v>129035015</v>
       </c>
       <c r="B41" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4613,10 +4613,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>569130</v>
+        <v>569454</v>
       </c>
       <c r="R41" t="n">
-        <v>6949603</v>
+        <v>6949698</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4653,7 +4653,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>14 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4683,7 +4683,7 @@
         <v>129035063</v>
       </c>
       <c r="B42" t="n">
-        <v>96797</v>
+        <v>96823</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>129034643</v>
       </c>
       <c r="B43" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129034575</v>
+        <v>129035011</v>
       </c>
       <c r="B44" t="n">
         <v>57727</v>
@@ -4914,10 +4914,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>569448</v>
+        <v>569442</v>
       </c>
       <c r="R44" t="n">
-        <v>6949625</v>
+        <v>6949783</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Färska ringhack på Tall av tretåig hackspett</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4981,7 +4981,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129035011</v>
+        <v>129034575</v>
       </c>
       <c r="B45" t="n">
         <v>57727</v>
@@ -5016,10 +5016,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>569442</v>
+        <v>569448</v>
       </c>
       <c r="R45" t="n">
-        <v>6949783</v>
+        <v>6949625</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på Tall av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5086,7 +5086,7 @@
         <v>129034607</v>
       </c>
       <c r="B46" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
         <v>129035041</v>
       </c>
       <c r="B47" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>129035062</v>
       </c>
       <c r="B48" t="n">
-        <v>96797</v>
+        <v>96823</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5384,10 +5384,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129035002</v>
+        <v>129034632</v>
       </c>
       <c r="B49" t="n">
-        <v>91542</v>
+        <v>79041</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5395,21 +5395,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5419,10 +5419,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>569405</v>
+        <v>569237</v>
       </c>
       <c r="R49" t="n">
-        <v>6949685</v>
+        <v>6949442</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5481,10 +5481,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129035022</v>
+        <v>129035002</v>
       </c>
       <c r="B50" t="n">
-        <v>91827</v>
+        <v>91540</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5492,21 +5492,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5516,10 +5516,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>569423</v>
+        <v>569405</v>
       </c>
       <c r="R50" t="n">
-        <v>6949656</v>
+        <v>6949685</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5578,10 +5578,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129034597</v>
+        <v>129035022</v>
       </c>
       <c r="B51" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5613,10 +5613,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>569221</v>
+        <v>569423</v>
       </c>
       <c r="R51" t="n">
-        <v>6949499</v>
+        <v>6949656</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5649,11 +5649,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>8 exemplar</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5680,10 +5675,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129034632</v>
+        <v>129034597</v>
       </c>
       <c r="B52" t="n">
-        <v>79041</v>
+        <v>91837</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5691,21 +5686,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5715,10 +5710,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>569237</v>
+        <v>569221</v>
       </c>
       <c r="R52" t="n">
-        <v>6949442</v>
+        <v>6949499</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5751,6 +5746,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>8 exemplar</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5882,7 +5882,7 @@
         <v>129034616</v>
       </c>
       <c r="B54" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5981,10 +5981,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129035008</v>
+        <v>129035028</v>
       </c>
       <c r="B55" t="n">
-        <v>91542</v>
+        <v>91837</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5992,21 +5992,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6016,10 +6016,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>569216</v>
+        <v>569192</v>
       </c>
       <c r="R55" t="n">
-        <v>6949430</v>
+        <v>6949509</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6078,10 +6078,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129035028</v>
+        <v>129034581</v>
       </c>
       <c r="B56" t="n">
-        <v>91827</v>
+        <v>57887</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6089,21 +6089,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6113,10 +6113,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>569192</v>
+        <v>569223</v>
       </c>
       <c r="R56" t="n">
-        <v>6949509</v>
+        <v>6949401</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6149,6 +6149,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Sågs och gjorde övriga läten</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6175,32 +6180,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129034600</v>
+        <v>129034610</v>
       </c>
       <c r="B57" t="n">
-        <v>80146</v>
+        <v>98704</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6210,10 +6215,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>569481</v>
+        <v>569282</v>
       </c>
       <c r="R57" t="n">
-        <v>6949674</v>
+        <v>6949567</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6250,7 +6255,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Apothecier antal 1</t>
+          <t>Ca 100 stycken</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6277,32 +6282,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129034581</v>
+        <v>129034614</v>
       </c>
       <c r="B58" t="n">
-        <v>57887</v>
+        <v>98704</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6312,10 +6317,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>569223</v>
+        <v>569237</v>
       </c>
       <c r="R58" t="n">
-        <v>6949401</v>
+        <v>6949556</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6352,7 +6357,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Sågs och gjorde övriga läten</t>
+          <t>5 stycken</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6379,32 +6384,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129034610</v>
+        <v>129035008</v>
       </c>
       <c r="B59" t="n">
-        <v>98678</v>
+        <v>91540</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6414,10 +6419,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>569282</v>
+        <v>569216</v>
       </c>
       <c r="R59" t="n">
-        <v>6949567</v>
+        <v>6949430</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6450,11 +6455,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ca 100 stycken</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6481,32 +6481,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129034614</v>
+        <v>129034600</v>
       </c>
       <c r="B60" t="n">
-        <v>98678</v>
+        <v>80146</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6516,10 +6516,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>569237</v>
+        <v>569481</v>
       </c>
       <c r="R60" t="n">
-        <v>6949556</v>
+        <v>6949674</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6556,7 +6556,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>5 stycken</t>
+          <t>Apothecier antal 1</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6583,32 +6583,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129034586</v>
+        <v>129035024</v>
       </c>
       <c r="B61" t="n">
-        <v>91997</v>
+        <v>91837</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6618,10 +6618,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>569220</v>
+        <v>569404</v>
       </c>
       <c r="R61" t="n">
-        <v>6949500</v>
+        <v>6949660</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6680,32 +6680,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129035024</v>
+        <v>129034586</v>
       </c>
       <c r="B62" t="n">
-        <v>91827</v>
+        <v>91992</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6715,10 +6715,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>569404</v>
+        <v>569220</v>
       </c>
       <c r="R62" t="n">
-        <v>6949660</v>
+        <v>6949500</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6777,10 +6777,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129034574</v>
+        <v>129035003</v>
       </c>
       <c r="B63" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6812,10 +6812,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>569461</v>
+        <v>569164</v>
       </c>
       <c r="R63" t="n">
-        <v>6949706</v>
+        <v>6949559</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6874,10 +6874,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129035003</v>
+        <v>129034574</v>
       </c>
       <c r="B64" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6909,10 +6909,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>569164</v>
+        <v>569461</v>
       </c>
       <c r="R64" t="n">
-        <v>6949559</v>
+        <v>6949706</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6971,45 +6971,49 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129034587</v>
+        <v>129027791</v>
       </c>
       <c r="B65" t="n">
-        <v>91827</v>
+        <v>98704</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Sandsjömyran, Mpd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>569463</v>
+        <v>569308</v>
       </c>
       <c r="R65" t="n">
-        <v>6949711</v>
+        <v>6949546</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7068,32 +7072,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129035021</v>
+        <v>129034624</v>
       </c>
       <c r="B66" t="n">
-        <v>91827</v>
+        <v>105767</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>658</v>
+        <v>221144</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7103,10 +7107,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>569446</v>
+        <v>569234</v>
       </c>
       <c r="R66" t="n">
-        <v>6949629</v>
+        <v>6949440</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7139,6 +7143,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>9 exemplar</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7165,10 +7174,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129027791</v>
+        <v>129035035</v>
       </c>
       <c r="B67" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7193,21 +7202,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Sandsjömyran, Mpd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>569308</v>
+        <v>569317</v>
       </c>
       <c r="R67" t="n">
-        <v>6949546</v>
+        <v>6949469</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7240,6 +7245,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7266,32 +7276,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129034624</v>
+        <v>129034587</v>
       </c>
       <c r="B68" t="n">
-        <v>105741</v>
+        <v>91837</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221144</v>
+        <v>658</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7301,10 +7311,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>569234</v>
+        <v>569463</v>
       </c>
       <c r="R68" t="n">
-        <v>6949440</v>
+        <v>6949711</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7337,11 +7347,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>9 exemplar</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7368,32 +7373,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129035035</v>
+        <v>129035021</v>
       </c>
       <c r="B69" t="n">
-        <v>98678</v>
+        <v>91837</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7403,10 +7408,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>569317</v>
+        <v>569446</v>
       </c>
       <c r="R69" t="n">
-        <v>6949469</v>
+        <v>6949629</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7439,11 +7444,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>5 ex</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7470,32 +7470,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129035060</v>
+        <v>129035018</v>
       </c>
       <c r="B70" t="n">
-        <v>92835</v>
+        <v>57727</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7505,10 +7505,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>569208</v>
+        <v>569111</v>
       </c>
       <c r="R70" t="n">
-        <v>6949415</v>
+        <v>6949604</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7545,7 +7545,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>20 ex minst</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7572,10 +7572,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129034639</v>
+        <v>129035060</v>
       </c>
       <c r="B71" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7607,10 +7607,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>569398</v>
+        <v>569208</v>
       </c>
       <c r="R71" t="n">
-        <v>6949741</v>
+        <v>6949415</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7647,7 +7647,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>6 äldre exemplar och 1 färsk fruktkropp</t>
+          <t>20 ex minst</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7674,32 +7674,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129035037</v>
+        <v>129034639</v>
       </c>
       <c r="B72" t="n">
-        <v>98678</v>
+        <v>92821</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7709,10 +7709,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>569434</v>
+        <v>569398</v>
       </c>
       <c r="R72" t="n">
-        <v>6949706</v>
+        <v>6949741</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7749,7 +7749,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>20 ex</t>
+          <t>6 äldre exemplar och 1 färsk fruktkropp</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7878,32 +7878,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129035018</v>
+        <v>129035037</v>
       </c>
       <c r="B74" t="n">
-        <v>57727</v>
+        <v>98704</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7913,10 +7913,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>569111</v>
+        <v>569434</v>
       </c>
       <c r="R74" t="n">
-        <v>6949604</v>
+        <v>6949706</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7953,7 +7953,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7980,10 +7980,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129034598</v>
+        <v>129034645</v>
       </c>
       <c r="B75" t="n">
-        <v>97549</v>
+        <v>92821</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7991,21 +7991,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8015,10 +8015,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>569460</v>
+        <v>569196</v>
       </c>
       <c r="R75" t="n">
-        <v>6949629</v>
+        <v>6949411</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8051,6 +8051,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>4 färska exemplar 3 äldre exemplar</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8077,32 +8082,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129034650</v>
+        <v>129034642</v>
       </c>
       <c r="B76" t="n">
-        <v>98678</v>
+        <v>92821</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8112,10 +8117,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>569303</v>
+        <v>569283</v>
       </c>
       <c r="R76" t="n">
-        <v>6949537</v>
+        <v>6949655</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8152,7 +8157,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>30 stycken ( finns eventuellt mer )</t>
+          <t>7 äldre exemplar</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8182,7 +8187,7 @@
         <v>129034605</v>
       </c>
       <c r="B77" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8281,32 +8286,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129026691</v>
+        <v>129034598</v>
       </c>
       <c r="B78" t="n">
-        <v>91827</v>
+        <v>97575</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8316,10 +8321,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>569195</v>
+        <v>569460</v>
       </c>
       <c r="R78" t="n">
-        <v>6949487</v>
+        <v>6949629</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8378,32 +8383,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129034645</v>
+        <v>129026691</v>
       </c>
       <c r="B79" t="n">
-        <v>92835</v>
+        <v>91837</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8413,10 +8418,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>569196</v>
+        <v>569195</v>
       </c>
       <c r="R79" t="n">
-        <v>6949411</v>
+        <v>6949487</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8449,11 +8454,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>4 färska exemplar 3 äldre exemplar</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8480,32 +8480,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129034642</v>
+        <v>129034650</v>
       </c>
       <c r="B80" t="n">
-        <v>92835</v>
+        <v>98704</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8515,10 +8515,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>569283</v>
+        <v>569303</v>
       </c>
       <c r="R80" t="n">
-        <v>6949655</v>
+        <v>6949537</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8555,7 +8555,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>7 äldre exemplar</t>
+          <t>30 stycken ( finns eventuellt mer )</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8582,32 +8582,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129035047</v>
+        <v>129034640</v>
       </c>
       <c r="B81" t="n">
-        <v>98678</v>
+        <v>92821</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8617,10 +8617,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>569162</v>
+        <v>569213</v>
       </c>
       <c r="R81" t="n">
-        <v>6949566</v>
+        <v>6949414</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8657,7 +8657,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>50 ex</t>
+          <t>16 exemplar</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8684,32 +8684,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129034604</v>
+        <v>129035001</v>
       </c>
       <c r="B82" t="n">
-        <v>98678</v>
+        <v>91504</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8719,10 +8719,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>569303</v>
+        <v>569232</v>
       </c>
       <c r="R82" t="n">
-        <v>6949536</v>
+        <v>6949444</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8755,11 +8755,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8786,32 +8781,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129034618</v>
+        <v>129035061</v>
       </c>
       <c r="B83" t="n">
-        <v>98678</v>
+        <v>96823</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8821,10 +8816,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>569235</v>
+        <v>569333</v>
       </c>
       <c r="R83" t="n">
-        <v>6949411</v>
+        <v>6949607</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8857,11 +8852,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8985,32 +8975,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129035001</v>
+        <v>129035007</v>
       </c>
       <c r="B85" t="n">
-        <v>91506</v>
+        <v>91540</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9020,10 +9010,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>569232</v>
+        <v>569225</v>
       </c>
       <c r="R85" t="n">
-        <v>6949444</v>
+        <v>6949424</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9184,32 +9174,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129035061</v>
+        <v>129035047</v>
       </c>
       <c r="B87" t="n">
-        <v>96797</v>
+        <v>98704</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9219,10 +9209,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>569333</v>
+        <v>569162</v>
       </c>
       <c r="R87" t="n">
-        <v>6949607</v>
+        <v>6949566</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9255,6 +9245,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9281,32 +9276,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129035007</v>
+        <v>129034604</v>
       </c>
       <c r="B88" t="n">
-        <v>91542</v>
+        <v>98704</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9316,10 +9311,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>569225</v>
+        <v>569303</v>
       </c>
       <c r="R88" t="n">
-        <v>6949424</v>
+        <v>6949536</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9352,6 +9347,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9378,32 +9378,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129034640</v>
+        <v>129034618</v>
       </c>
       <c r="B89" t="n">
-        <v>92835</v>
+        <v>98704</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9413,10 +9413,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>569213</v>
+        <v>569235</v>
       </c>
       <c r="R89" t="n">
-        <v>6949414</v>
+        <v>6949411</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9453,7 +9453,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>16 exemplar</t>
+          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9480,32 +9480,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129035023</v>
+        <v>129035038</v>
       </c>
       <c r="B90" t="n">
-        <v>91827</v>
+        <v>98704</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>569415</v>
+        <v>569406</v>
       </c>
       <c r="R90" t="n">
-        <v>6949677</v>
+        <v>6949664</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9551,6 +9551,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9577,32 +9582,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129035027</v>
+        <v>129034621</v>
       </c>
       <c r="B91" t="n">
-        <v>91827</v>
+        <v>98704</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9612,10 +9617,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>569169</v>
+        <v>569247</v>
       </c>
       <c r="R91" t="n">
-        <v>6949533</v>
+        <v>6949434</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9648,6 +9653,11 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>10 stycken knärot</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9674,10 +9684,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129034589</v>
+        <v>129035023</v>
       </c>
       <c r="B92" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9709,10 +9719,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>569365</v>
+        <v>569415</v>
       </c>
       <c r="R92" t="n">
-        <v>6949661</v>
+        <v>6949677</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9771,10 +9781,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129035029</v>
+        <v>129035027</v>
       </c>
       <c r="B93" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9806,10 +9816,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>569217</v>
+        <v>569169</v>
       </c>
       <c r="R93" t="n">
-        <v>6949427</v>
+        <v>6949533</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9868,32 +9878,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129035050</v>
+        <v>129034589</v>
       </c>
       <c r="B94" t="n">
-        <v>98678</v>
+        <v>91837</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9903,10 +9913,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>569236</v>
+        <v>569365</v>
       </c>
       <c r="R94" t="n">
-        <v>6949440</v>
+        <v>6949661</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9939,11 +9949,6 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>4 ex</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -9970,32 +9975,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129034621</v>
+        <v>129035029</v>
       </c>
       <c r="B95" t="n">
-        <v>98678</v>
+        <v>91837</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10005,10 +10010,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>569247</v>
+        <v>569217</v>
       </c>
       <c r="R95" t="n">
-        <v>6949434</v>
+        <v>6949427</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10041,11 +10046,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>10 stycken knärot</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10072,10 +10072,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129035038</v>
+        <v>129035050</v>
       </c>
       <c r="B96" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10107,10 +10107,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>569406</v>
+        <v>569236</v>
       </c>
       <c r="R96" t="n">
-        <v>6949664</v>
+        <v>6949440</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10147,7 +10147,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>20 ex</t>
+          <t>4 ex</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10174,32 +10174,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129034609</v>
+        <v>129034635</v>
       </c>
       <c r="B97" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10209,10 +10209,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>569458</v>
+        <v>569427</v>
       </c>
       <c r="R97" t="n">
-        <v>6949777</v>
+        <v>6949726</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10245,11 +10245,6 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>48 stycken</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10276,32 +10271,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129035036</v>
+        <v>129035017</v>
       </c>
       <c r="B98" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10311,10 +10306,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>569330</v>
+        <v>569192</v>
       </c>
       <c r="R98" t="n">
-        <v>6949564</v>
+        <v>6949518</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10351,7 +10346,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>8 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10378,32 +10373,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129035052</v>
+        <v>129035010</v>
       </c>
       <c r="B99" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10413,10 +10408,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>569405</v>
+        <v>569465</v>
       </c>
       <c r="R99" t="n">
-        <v>6949641</v>
+        <v>6949606</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10453,7 +10448,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>70 ex</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10480,32 +10475,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129035056</v>
+        <v>129034609</v>
       </c>
       <c r="B100" t="n">
-        <v>105741</v>
+        <v>98704</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10515,10 +10510,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>569201</v>
+        <v>569458</v>
       </c>
       <c r="R100" t="n">
-        <v>6949530</v>
+        <v>6949777</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10551,6 +10546,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>48 stycken</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10577,32 +10577,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129035017</v>
+        <v>129035036</v>
       </c>
       <c r="B101" t="n">
-        <v>57727</v>
+        <v>98704</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10612,10 +10612,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>569192</v>
+        <v>569330</v>
       </c>
       <c r="R101" t="n">
-        <v>6949518</v>
+        <v>6949564</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10652,7 +10652,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>8 ex</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10679,32 +10679,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129035010</v>
+        <v>129035052</v>
       </c>
       <c r="B102" t="n">
-        <v>57727</v>
+        <v>98704</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10714,10 +10714,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>569465</v>
+        <v>569405</v>
       </c>
       <c r="R102" t="n">
-        <v>6949606</v>
+        <v>6949641</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10754,7 +10754,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>70 ex</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10781,32 +10781,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129034635</v>
+        <v>129035056</v>
       </c>
       <c r="B103" t="n">
-        <v>79041</v>
+        <v>105767</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>221144</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10816,10 +10816,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>569427</v>
+        <v>569201</v>
       </c>
       <c r="R103" t="n">
-        <v>6949726</v>
+        <v>6949530</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10881,7 +10881,7 @@
         <v>129035048</v>
       </c>
       <c r="B104" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10983,7 +10983,7 @@
         <v>129035053</v>
       </c>
       <c r="B105" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11085,7 +11085,7 @@
         <v>129035049</v>
       </c>
       <c r="B106" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11187,7 +11187,7 @@
         <v>129035044</v>
       </c>
       <c r="B107" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11289,7 +11289,7 @@
         <v>129027886</v>
       </c>
       <c r="B108" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11383,10 +11383,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129035006</v>
+        <v>129035026</v>
       </c>
       <c r="B109" t="n">
-        <v>91542</v>
+        <v>91837</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11394,21 +11394,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11418,10 +11418,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>569217</v>
+        <v>569175</v>
       </c>
       <c r="R109" t="n">
-        <v>6949470</v>
+        <v>6949549</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11480,10 +11480,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129035026</v>
+        <v>129035006</v>
       </c>
       <c r="B110" t="n">
-        <v>91827</v>
+        <v>91540</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11491,21 +11491,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11515,10 +11515,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>569175</v>
+        <v>569217</v>
       </c>
       <c r="R110" t="n">
-        <v>6949549</v>
+        <v>6949470</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11580,7 +11580,7 @@
         <v>129035033</v>
       </c>
       <c r="B111" t="n">
-        <v>91743</v>
+        <v>91752</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11677,7 +11677,7 @@
         <v>129035032</v>
       </c>
       <c r="B112" t="n">
-        <v>91743</v>
+        <v>91752</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>

--- a/artfynd/A 45833-2025 artfynd.xlsx
+++ b/artfynd/A 45833-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129034612</v>
       </c>
       <c r="B2" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129035046</v>
+        <v>129035043</v>
       </c>
       <c r="B3" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569127</v>
+        <v>569204</v>
       </c>
       <c r="R3" t="n">
-        <v>6949602</v>
+        <v>6949533</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>13 ex</t>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129035043</v>
+        <v>129035046</v>
       </c>
       <c r="B4" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569204</v>
+        <v>569127</v>
       </c>
       <c r="R4" t="n">
-        <v>6949533</v>
+        <v>6949602</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,7 +954,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>10 ex</t>
+          <t>13 ex</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1078,32 +1078,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129035039</v>
+        <v>129035030</v>
       </c>
       <c r="B6" t="n">
-        <v>98704</v>
+        <v>97576</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>569394</v>
+        <v>569424</v>
       </c>
       <c r="R6" t="n">
-        <v>6949664</v>
+        <v>6949671</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1149,11 +1149,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1180,32 +1175,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129035030</v>
+        <v>129035039</v>
       </c>
       <c r="B7" t="n">
-        <v>97575</v>
+        <v>98705</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>569424</v>
+        <v>569394</v>
       </c>
       <c r="R7" t="n">
-        <v>6949671</v>
+        <v>6949664</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1251,6 +1246,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1484,7 +1484,7 @@
         <v>129035054</v>
       </c>
       <c r="B10" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>129034594</v>
       </c>
       <c r="B11" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1685,32 +1685,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129034577</v>
+        <v>129034648</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>96824</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1720,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569496</v>
+        <v>569279</v>
       </c>
       <c r="R12" t="n">
-        <v>6949627</v>
+        <v>6949401</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1756,11 +1756,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1787,32 +1782,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129035055</v>
+        <v>129034630</v>
       </c>
       <c r="B13" t="n">
-        <v>98704</v>
+        <v>79041</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1822,10 +1817,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569221</v>
+        <v>569231</v>
       </c>
       <c r="R13" t="n">
-        <v>6949406</v>
+        <v>6949559</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1858,11 +1853,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>25 ex</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1889,32 +1879,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129035042</v>
+        <v>129034577</v>
       </c>
       <c r="B14" t="n">
-        <v>98704</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1924,10 +1914,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569200</v>
+        <v>569496</v>
       </c>
       <c r="R14" t="n">
-        <v>6949533</v>
+        <v>6949627</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1964,7 +1954,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>30 ex</t>
+          <t>Äldre ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1991,32 +1981,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129034648</v>
+        <v>129035042</v>
       </c>
       <c r="B15" t="n">
-        <v>96823</v>
+        <v>98705</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2026,10 +2016,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>569279</v>
+        <v>569200</v>
       </c>
       <c r="R15" t="n">
-        <v>6949401</v>
+        <v>6949533</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2062,6 +2052,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>30 ex</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2088,32 +2083,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129034630</v>
+        <v>129035055</v>
       </c>
       <c r="B16" t="n">
-        <v>79041</v>
+        <v>98705</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2123,10 +2118,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>569231</v>
+        <v>569221</v>
       </c>
       <c r="R16" t="n">
-        <v>6949559</v>
+        <v>6949406</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2159,6 +2154,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2188,7 +2188,7 @@
         <v>129035059</v>
       </c>
       <c r="B17" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>129034620</v>
       </c>
       <c r="B22" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2787,32 +2787,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129035004</v>
+        <v>129034623</v>
       </c>
       <c r="B23" t="n">
-        <v>91540</v>
+        <v>98705</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569152</v>
+        <v>569253</v>
       </c>
       <c r="R23" t="n">
-        <v>6949557</v>
+        <v>6949425</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2858,6 +2858,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>74 stycken</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2884,10 +2889,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129035005</v>
+        <v>129034592</v>
       </c>
       <c r="B24" t="n">
-        <v>91540</v>
+        <v>91838</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2895,21 +2900,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2919,10 +2924,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569188</v>
+        <v>569205</v>
       </c>
       <c r="R24" t="n">
-        <v>6949496</v>
+        <v>6949497</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2955,6 +2960,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>1 x</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2981,10 +2991,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129034625</v>
+        <v>129034591</v>
       </c>
       <c r="B25" t="n">
-        <v>79041</v>
+        <v>91838</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2992,21 +3002,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3016,10 +3026,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569479</v>
+        <v>569203</v>
       </c>
       <c r="R25" t="n">
-        <v>6949657</v>
+        <v>6949513</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3052,6 +3062,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>11 ex</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3078,10 +3093,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129034592</v>
+        <v>129034647</v>
       </c>
       <c r="B26" t="n">
-        <v>91837</v>
+        <v>88940</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3089,21 +3104,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3113,10 +3128,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569205</v>
+        <v>569247</v>
       </c>
       <c r="R26" t="n">
-        <v>6949497</v>
+        <v>6949558</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3149,11 +3164,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>1 x</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3180,10 +3190,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129034591</v>
+        <v>129035004</v>
       </c>
       <c r="B27" t="n">
-        <v>91837</v>
+        <v>91540</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3191,21 +3201,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3215,10 +3225,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>569203</v>
+        <v>569152</v>
       </c>
       <c r="R27" t="n">
-        <v>6949513</v>
+        <v>6949557</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3251,11 +3261,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>11 ex</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3282,10 +3287,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129034647</v>
+        <v>129035025</v>
       </c>
       <c r="B28" t="n">
-        <v>88940</v>
+        <v>91838</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3293,21 +3298,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3317,10 +3322,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>569247</v>
+        <v>569388</v>
       </c>
       <c r="R28" t="n">
-        <v>6949558</v>
+        <v>6949665</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3379,10 +3384,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129035025</v>
+        <v>129035005</v>
       </c>
       <c r="B29" t="n">
-        <v>91837</v>
+        <v>91540</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3390,21 +3395,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3414,10 +3419,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>569388</v>
+        <v>569188</v>
       </c>
       <c r="R29" t="n">
-        <v>6949665</v>
+        <v>6949496</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3476,32 +3481,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129034623</v>
+        <v>129034625</v>
       </c>
       <c r="B30" t="n">
-        <v>98704</v>
+        <v>79041</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3511,10 +3516,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>569253</v>
+        <v>569479</v>
       </c>
       <c r="R30" t="n">
-        <v>6949425</v>
+        <v>6949657</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3547,11 +3552,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>74 stycken</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3578,32 +3578,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129034637</v>
+        <v>129035051</v>
       </c>
       <c r="B31" t="n">
-        <v>92821</v>
+        <v>98705</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>569229</v>
+        <v>569222</v>
       </c>
       <c r="R31" t="n">
-        <v>6949400</v>
+        <v>6949414</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3649,6 +3649,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>30 ex</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3675,32 +3680,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129035058</v>
+        <v>129034637</v>
       </c>
       <c r="B32" t="n">
-        <v>79041</v>
+        <v>92822</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3710,10 +3715,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>569388</v>
+        <v>569229</v>
       </c>
       <c r="R32" t="n">
-        <v>6949647</v>
+        <v>6949400</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3772,10 +3777,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129035031</v>
+        <v>129035058</v>
       </c>
       <c r="B33" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3783,21 +3788,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3807,10 +3812,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>569125</v>
+        <v>569388</v>
       </c>
       <c r="R33" t="n">
-        <v>6949570</v>
+        <v>6949647</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3869,10 +3874,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129034578</v>
+        <v>129035031</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3880,21 +3885,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3904,10 +3909,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>569420</v>
+        <v>569125</v>
       </c>
       <c r="R34" t="n">
-        <v>6949723</v>
+        <v>6949570</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3940,11 +3945,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3971,32 +3971,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129035051</v>
+        <v>129034578</v>
       </c>
       <c r="B35" t="n">
-        <v>98704</v>
+        <v>57727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4006,10 +4006,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>569222</v>
+        <v>569420</v>
       </c>
       <c r="R35" t="n">
-        <v>6949414</v>
+        <v>6949723</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>30 ex</t>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4170,32 +4170,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129034602</v>
+        <v>129035015</v>
       </c>
       <c r="B37" t="n">
-        <v>98704</v>
+        <v>57727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4205,10 +4205,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>569301</v>
+        <v>569454</v>
       </c>
       <c r="R37" t="n">
-        <v>6949480</v>
+        <v>6949698</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>22 stycken</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4272,32 +4272,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129035040</v>
+        <v>129035020</v>
       </c>
       <c r="B38" t="n">
-        <v>98704</v>
+        <v>57727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4307,10 +4307,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>569386</v>
+        <v>569171</v>
       </c>
       <c r="R38" t="n">
-        <v>6949657</v>
+        <v>6949543</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>9 ex</t>
+          <t>Äldre ringhack på granhögstubbe</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4374,10 +4374,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129035045</v>
+        <v>129034602</v>
       </c>
       <c r="B39" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4409,10 +4409,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>569130</v>
+        <v>569301</v>
       </c>
       <c r="R39" t="n">
-        <v>6949603</v>
+        <v>6949480</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>14 ex</t>
+          <t>22 stycken</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4476,32 +4476,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129035020</v>
+        <v>129035040</v>
       </c>
       <c r="B40" t="n">
-        <v>57727</v>
+        <v>98705</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4511,10 +4511,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>569171</v>
+        <v>569386</v>
       </c>
       <c r="R40" t="n">
-        <v>6949543</v>
+        <v>6949657</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4551,7 +4551,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Äldre ringhack på granhögstubbe</t>
+          <t>9 ex</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4578,32 +4578,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129035015</v>
+        <v>129035045</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>98705</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4613,10 +4613,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>569454</v>
+        <v>569130</v>
       </c>
       <c r="R41" t="n">
-        <v>6949698</v>
+        <v>6949603</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4653,7 +4653,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>14 ex</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4680,10 +4680,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129035063</v>
+        <v>129034643</v>
       </c>
       <c r="B42" t="n">
-        <v>96823</v>
+        <v>92822</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4691,21 +4691,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2869</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4715,10 +4715,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>569455</v>
+        <v>569254</v>
       </c>
       <c r="R42" t="n">
-        <v>6949758</v>
+        <v>6949431</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4751,6 +4751,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>1 färskt exemplar</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4777,10 +4782,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129034643</v>
+        <v>129035063</v>
       </c>
       <c r="B43" t="n">
-        <v>92821</v>
+        <v>96824</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4788,21 +4793,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>2869</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4812,10 +4817,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>569254</v>
+        <v>569455</v>
       </c>
       <c r="R43" t="n">
-        <v>6949431</v>
+        <v>6949758</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4848,11 +4853,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>1 färskt exemplar</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4879,32 +4879,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129035011</v>
+        <v>129035041</v>
       </c>
       <c r="B44" t="n">
-        <v>57727</v>
+        <v>98705</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4914,10 +4914,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>569442</v>
+        <v>569262</v>
       </c>
       <c r="R44" t="n">
-        <v>6949783</v>
+        <v>6949524</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5083,32 +5083,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129034607</v>
+        <v>129035011</v>
       </c>
       <c r="B46" t="n">
-        <v>98704</v>
+        <v>57727</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5118,10 +5118,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>569317</v>
+        <v>569442</v>
       </c>
       <c r="R46" t="n">
-        <v>6949549</v>
+        <v>6949783</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>31 stycken</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5185,10 +5185,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129035041</v>
+        <v>129034607</v>
       </c>
       <c r="B47" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5220,10 +5220,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>569262</v>
+        <v>569317</v>
       </c>
       <c r="R47" t="n">
-        <v>6949524</v>
+        <v>6949549</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5260,7 +5260,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>5 ex</t>
+          <t>31 stycken</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5287,32 +5287,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129035062</v>
+        <v>129035022</v>
       </c>
       <c r="B48" t="n">
-        <v>96823</v>
+        <v>91838</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2869</v>
+        <v>658</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5322,10 +5322,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>569478</v>
+        <v>569423</v>
       </c>
       <c r="R48" t="n">
-        <v>6949666</v>
+        <v>6949656</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5384,10 +5384,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129034632</v>
+        <v>129034597</v>
       </c>
       <c r="B49" t="n">
-        <v>79041</v>
+        <v>91838</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5395,21 +5395,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5419,10 +5419,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>569237</v>
+        <v>569221</v>
       </c>
       <c r="R49" t="n">
-        <v>6949442</v>
+        <v>6949499</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5455,6 +5455,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>8 exemplar</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5578,10 +5583,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129035022</v>
+        <v>129034632</v>
       </c>
       <c r="B51" t="n">
-        <v>91837</v>
+        <v>79041</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5589,21 +5594,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5613,10 +5618,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>569423</v>
+        <v>569237</v>
       </c>
       <c r="R51" t="n">
-        <v>6949656</v>
+        <v>6949442</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5675,10 +5680,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129034597</v>
+        <v>129035016</v>
       </c>
       <c r="B52" t="n">
-        <v>91837</v>
+        <v>57727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5686,21 +5691,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5710,10 +5715,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>569221</v>
+        <v>569435</v>
       </c>
       <c r="R52" t="n">
-        <v>6949499</v>
+        <v>6949665</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5750,7 +5755,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>8 exemplar</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5777,32 +5782,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129035016</v>
+        <v>129034616</v>
       </c>
       <c r="B53" t="n">
-        <v>57727</v>
+        <v>98705</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5812,10 +5817,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>569435</v>
+        <v>569223</v>
       </c>
       <c r="R53" t="n">
-        <v>6949665</v>
+        <v>6949465</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5852,7 +5857,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>10 stycken</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5879,32 +5884,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129034616</v>
+        <v>129035062</v>
       </c>
       <c r="B54" t="n">
-        <v>98704</v>
+        <v>96824</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5914,10 +5919,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>569223</v>
+        <v>569478</v>
       </c>
       <c r="R54" t="n">
-        <v>6949465</v>
+        <v>6949666</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5950,11 +5955,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>10 stycken</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5984,7 +5984,7 @@
         <v>129035028</v>
       </c>
       <c r="B55" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6078,10 +6078,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129034581</v>
+        <v>129035008</v>
       </c>
       <c r="B56" t="n">
-        <v>57887</v>
+        <v>91540</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6089,21 +6089,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6113,10 +6113,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>569223</v>
+        <v>569216</v>
       </c>
       <c r="R56" t="n">
-        <v>6949401</v>
+        <v>6949430</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6149,11 +6149,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Sågs och gjorde övriga läten</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6183,7 +6178,7 @@
         <v>129034610</v>
       </c>
       <c r="B57" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6285,7 +6280,7 @@
         <v>129034614</v>
       </c>
       <c r="B58" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6384,10 +6379,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129035008</v>
+        <v>129034600</v>
       </c>
       <c r="B59" t="n">
-        <v>91540</v>
+        <v>80146</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6395,21 +6390,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6419,10 +6414,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>569216</v>
+        <v>569481</v>
       </c>
       <c r="R59" t="n">
-        <v>6949430</v>
+        <v>6949674</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6455,6 +6450,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Apothecier antal 1</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6481,10 +6481,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129034600</v>
+        <v>129034581</v>
       </c>
       <c r="B60" t="n">
-        <v>80146</v>
+        <v>57887</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6492,21 +6492,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6516,10 +6516,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>569481</v>
+        <v>569223</v>
       </c>
       <c r="R60" t="n">
-        <v>6949674</v>
+        <v>6949401</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6556,7 +6556,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Apothecier antal 1</t>
+          <t>Sågs och gjorde övriga läten</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6583,32 +6583,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129035024</v>
+        <v>129034586</v>
       </c>
       <c r="B61" t="n">
-        <v>91837</v>
+        <v>91993</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6618,10 +6618,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>569404</v>
+        <v>569220</v>
       </c>
       <c r="R61" t="n">
-        <v>6949660</v>
+        <v>6949500</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6680,32 +6680,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129034586</v>
+        <v>129035024</v>
       </c>
       <c r="B62" t="n">
-        <v>91992</v>
+        <v>91838</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6715,10 +6715,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>569220</v>
+        <v>569404</v>
       </c>
       <c r="R62" t="n">
-        <v>6949500</v>
+        <v>6949660</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6874,10 +6874,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129034574</v>
+        <v>129034587</v>
       </c>
       <c r="B64" t="n">
-        <v>91540</v>
+        <v>91838</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6885,21 +6885,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6909,10 +6909,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>569461</v>
+        <v>569463</v>
       </c>
       <c r="R64" t="n">
-        <v>6949706</v>
+        <v>6949711</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6971,49 +6971,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129027791</v>
+        <v>129035021</v>
       </c>
       <c r="B65" t="n">
-        <v>98704</v>
+        <v>91838</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Sandsjömyran, Mpd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>569308</v>
+        <v>569446</v>
       </c>
       <c r="R65" t="n">
-        <v>6949546</v>
+        <v>6949629</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7072,32 +7068,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129034624</v>
+        <v>129034574</v>
       </c>
       <c r="B66" t="n">
-        <v>105767</v>
+        <v>91540</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7107,10 +7103,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>569234</v>
+        <v>569461</v>
       </c>
       <c r="R66" t="n">
-        <v>6949440</v>
+        <v>6949706</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7143,11 +7139,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>9 exemplar</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7174,32 +7165,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129035035</v>
+        <v>129034624</v>
       </c>
       <c r="B67" t="n">
-        <v>98704</v>
+        <v>105769</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7209,10 +7200,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>569317</v>
+        <v>569234</v>
       </c>
       <c r="R67" t="n">
-        <v>6949469</v>
+        <v>6949440</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7249,7 +7240,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>5 ex</t>
+          <t>9 exemplar</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7276,32 +7267,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129034587</v>
+        <v>129035035</v>
       </c>
       <c r="B68" t="n">
-        <v>91837</v>
+        <v>98705</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7311,10 +7302,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>569463</v>
+        <v>569317</v>
       </c>
       <c r="R68" t="n">
-        <v>6949711</v>
+        <v>6949469</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7347,6 +7338,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7373,45 +7369,49 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129035021</v>
+        <v>129027791</v>
       </c>
       <c r="B69" t="n">
-        <v>91837</v>
+        <v>98705</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Sandsjömyran, Mpd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>569446</v>
+        <v>569308</v>
       </c>
       <c r="R69" t="n">
-        <v>6949629</v>
+        <v>6949546</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7470,32 +7470,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129035018</v>
+        <v>129035060</v>
       </c>
       <c r="B70" t="n">
-        <v>57727</v>
+        <v>92822</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7505,10 +7505,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>569111</v>
+        <v>569208</v>
       </c>
       <c r="R70" t="n">
-        <v>6949604</v>
+        <v>6949415</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7545,7 +7545,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>20 ex minst</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7572,10 +7572,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129035060</v>
+        <v>129034639</v>
       </c>
       <c r="B71" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7607,10 +7607,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>569208</v>
+        <v>569398</v>
       </c>
       <c r="R71" t="n">
-        <v>6949415</v>
+        <v>6949741</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7647,7 +7647,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>20 ex minst</t>
+          <t>6 äldre exemplar och 1 färsk fruktkropp</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7674,32 +7674,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129034639</v>
+        <v>129034584</v>
       </c>
       <c r="B72" t="n">
-        <v>92821</v>
+        <v>57724</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7709,10 +7709,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>569398</v>
+        <v>569221</v>
       </c>
       <c r="R72" t="n">
-        <v>6949741</v>
+        <v>6949499</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7749,7 +7749,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>6 äldre exemplar och 1 färsk fruktkropp</t>
+          <t>Förbiflygande från träd till träd</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7776,10 +7776,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129034584</v>
+        <v>129035018</v>
       </c>
       <c r="B73" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7787,16 +7787,16 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -7811,10 +7811,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>569221</v>
+        <v>569111</v>
       </c>
       <c r="R73" t="n">
-        <v>6949499</v>
+        <v>6949604</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Förbiflygande från träd till träd</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7881,7 +7881,7 @@
         <v>129035037</v>
       </c>
       <c r="B74" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7980,32 +7980,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129034645</v>
+        <v>129026691</v>
       </c>
       <c r="B75" t="n">
-        <v>92821</v>
+        <v>91838</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8015,10 +8015,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>569196</v>
+        <v>569195</v>
       </c>
       <c r="R75" t="n">
-        <v>6949411</v>
+        <v>6949487</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8051,11 +8051,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>4 färska exemplar 3 äldre exemplar</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8082,10 +8077,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129034642</v>
+        <v>129034645</v>
       </c>
       <c r="B76" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8117,10 +8112,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>569283</v>
+        <v>569196</v>
       </c>
       <c r="R76" t="n">
-        <v>6949655</v>
+        <v>6949411</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8157,7 +8152,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>7 äldre exemplar</t>
+          <t>4 färska exemplar 3 äldre exemplar</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8184,32 +8179,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129034605</v>
+        <v>129034642</v>
       </c>
       <c r="B77" t="n">
-        <v>98704</v>
+        <v>92822</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8219,10 +8214,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>569305</v>
+        <v>569283</v>
       </c>
       <c r="R77" t="n">
-        <v>6949538</v>
+        <v>6949655</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8259,7 +8254,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>21 knärot</t>
+          <t>7 äldre exemplar</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8286,32 +8281,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129034598</v>
+        <v>129034650</v>
       </c>
       <c r="B78" t="n">
-        <v>97575</v>
+        <v>98705</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8321,10 +8316,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>569460</v>
+        <v>569303</v>
       </c>
       <c r="R78" t="n">
-        <v>6949629</v>
+        <v>6949537</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8357,6 +8352,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>30 stycken ( finns eventuellt mer )</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8383,32 +8383,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129026691</v>
+        <v>129034605</v>
       </c>
       <c r="B79" t="n">
-        <v>91837</v>
+        <v>98705</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8418,10 +8418,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>569195</v>
+        <v>569305</v>
       </c>
       <c r="R79" t="n">
-        <v>6949487</v>
+        <v>6949538</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8454,6 +8454,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>21 knärot</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8480,32 +8485,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129034650</v>
+        <v>129034598</v>
       </c>
       <c r="B80" t="n">
-        <v>98704</v>
+        <v>97576</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8515,10 +8520,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>569303</v>
+        <v>569460</v>
       </c>
       <c r="R80" t="n">
-        <v>6949537</v>
+        <v>6949629</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8551,11 +8556,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>30 stycken ( finns eventuellt mer )</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8582,32 +8582,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129034640</v>
+        <v>129035007</v>
       </c>
       <c r="B81" t="n">
-        <v>92821</v>
+        <v>91540</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8617,10 +8617,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>569213</v>
+        <v>569225</v>
       </c>
       <c r="R81" t="n">
-        <v>6949414</v>
+        <v>6949424</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8653,11 +8653,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>16 exemplar</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8684,10 +8679,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129035001</v>
+        <v>129034640</v>
       </c>
       <c r="B82" t="n">
-        <v>91504</v>
+        <v>92822</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8695,21 +8690,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8719,10 +8714,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>569232</v>
+        <v>569213</v>
       </c>
       <c r="R82" t="n">
-        <v>6949444</v>
+        <v>6949414</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8755,6 +8750,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>16 exemplar</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8784,7 +8784,7 @@
         <v>129035061</v>
       </c>
       <c r="B83" t="n">
-        <v>96823</v>
+        <v>96824</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8975,10 +8975,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129035007</v>
+        <v>129035012</v>
       </c>
       <c r="B85" t="n">
-        <v>91540</v>
+        <v>57727</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8986,21 +8986,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9010,10 +9010,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>569225</v>
+        <v>569435</v>
       </c>
       <c r="R85" t="n">
-        <v>6949424</v>
+        <v>6949783</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9046,6 +9046,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9072,32 +9077,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129035012</v>
+        <v>129034618</v>
       </c>
       <c r="B86" t="n">
-        <v>57727</v>
+        <v>98705</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9107,10 +9112,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>569435</v>
+        <v>569235</v>
       </c>
       <c r="R86" t="n">
-        <v>6949783</v>
+        <v>6949411</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9147,7 +9152,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9177,7 +9182,7 @@
         <v>129035047</v>
       </c>
       <c r="B87" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9279,7 +9284,7 @@
         <v>129034604</v>
       </c>
       <c r="B88" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9378,32 +9383,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129034618</v>
+        <v>129035001</v>
       </c>
       <c r="B89" t="n">
-        <v>98704</v>
+        <v>91504</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9413,10 +9418,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>569235</v>
+        <v>569232</v>
       </c>
       <c r="R89" t="n">
-        <v>6949411</v>
+        <v>6949444</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9449,11 +9454,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9480,32 +9480,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129035038</v>
+        <v>129035023</v>
       </c>
       <c r="B90" t="n">
-        <v>98704</v>
+        <v>91838</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>569406</v>
+        <v>569415</v>
       </c>
       <c r="R90" t="n">
-        <v>6949664</v>
+        <v>6949677</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9551,11 +9551,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>20 ex</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9582,32 +9577,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129034621</v>
+        <v>129035027</v>
       </c>
       <c r="B91" t="n">
-        <v>98704</v>
+        <v>91838</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9617,10 +9612,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>569247</v>
+        <v>569169</v>
       </c>
       <c r="R91" t="n">
-        <v>6949434</v>
+        <v>6949533</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9653,11 +9648,6 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>10 stycken knärot</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9684,10 +9674,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129035023</v>
+        <v>129034589</v>
       </c>
       <c r="B92" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9719,10 +9709,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>569415</v>
+        <v>569365</v>
       </c>
       <c r="R92" t="n">
-        <v>6949677</v>
+        <v>6949661</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9781,10 +9771,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129035027</v>
+        <v>129035029</v>
       </c>
       <c r="B93" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9816,10 +9806,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>569169</v>
+        <v>569217</v>
       </c>
       <c r="R93" t="n">
-        <v>6949533</v>
+        <v>6949427</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9878,32 +9868,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129034589</v>
+        <v>129034621</v>
       </c>
       <c r="B94" t="n">
-        <v>91837</v>
+        <v>98705</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9913,10 +9903,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>569365</v>
+        <v>569247</v>
       </c>
       <c r="R94" t="n">
-        <v>6949661</v>
+        <v>6949434</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9949,6 +9939,11 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>10 stycken knärot</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -9975,32 +9970,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129035029</v>
+        <v>129035038</v>
       </c>
       <c r="B95" t="n">
-        <v>91837</v>
+        <v>98705</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10010,10 +10005,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>569217</v>
+        <v>569406</v>
       </c>
       <c r="R95" t="n">
-        <v>6949427</v>
+        <v>6949664</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10046,6 +10041,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10075,7 +10075,7 @@
         <v>129035050</v>
       </c>
       <c r="B96" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10373,32 +10373,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129035010</v>
+        <v>129034609</v>
       </c>
       <c r="B99" t="n">
-        <v>57727</v>
+        <v>98705</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10408,10 +10408,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>569465</v>
+        <v>569458</v>
       </c>
       <c r="R99" t="n">
-        <v>6949606</v>
+        <v>6949777</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10448,7 +10448,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>48 stycken</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10475,32 +10475,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129034609</v>
+        <v>129035010</v>
       </c>
       <c r="B100" t="n">
-        <v>98704</v>
+        <v>57727</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10510,10 +10510,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>569458</v>
+        <v>569465</v>
       </c>
       <c r="R100" t="n">
-        <v>6949777</v>
+        <v>6949606</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10550,7 +10550,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>48 stycken</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10580,7 +10580,7 @@
         <v>129035036</v>
       </c>
       <c r="B101" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10682,7 +10682,7 @@
         <v>129035052</v>
       </c>
       <c r="B102" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10784,7 +10784,7 @@
         <v>129035056</v>
       </c>
       <c r="B103" t="n">
-        <v>105767</v>
+        <v>105769</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10878,32 +10878,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129035048</v>
+        <v>129035026</v>
       </c>
       <c r="B104" t="n">
-        <v>98704</v>
+        <v>91838</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10913,10 +10913,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>569176</v>
+        <v>569175</v>
       </c>
       <c r="R104" t="n">
-        <v>6949507</v>
+        <v>6949549</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10949,11 +10949,6 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>30 ex</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -10980,32 +10975,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129035053</v>
+        <v>129035006</v>
       </c>
       <c r="B105" t="n">
-        <v>98704</v>
+        <v>91540</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11015,10 +11010,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>569459</v>
+        <v>569217</v>
       </c>
       <c r="R105" t="n">
-        <v>6949662</v>
+        <v>6949470</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11051,11 +11046,6 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>14 ex</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11082,32 +11072,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129035049</v>
+        <v>129027886</v>
       </c>
       <c r="B106" t="n">
-        <v>98704</v>
+        <v>91540</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11117,10 +11107,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>569219</v>
+        <v>569305</v>
       </c>
       <c r="R106" t="n">
-        <v>6949489</v>
+        <v>6949566</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11153,11 +11143,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>35 ex</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11184,10 +11169,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129035044</v>
+        <v>129035048</v>
       </c>
       <c r="B107" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11219,10 +11204,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>569191</v>
+        <v>569176</v>
       </c>
       <c r="R107" t="n">
-        <v>6949579</v>
+        <v>6949507</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11259,7 +11244,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>50 ex</t>
+          <t>30 ex</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11286,32 +11271,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129027886</v>
+        <v>129035053</v>
       </c>
       <c r="B108" t="n">
-        <v>91540</v>
+        <v>98705</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11321,10 +11306,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>569305</v>
+        <v>569459</v>
       </c>
       <c r="R108" t="n">
-        <v>6949566</v>
+        <v>6949662</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11357,6 +11342,11 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>14 ex</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11383,32 +11373,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129035026</v>
+        <v>129035049</v>
       </c>
       <c r="B109" t="n">
-        <v>91837</v>
+        <v>98705</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11418,10 +11408,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>569175</v>
+        <v>569219</v>
       </c>
       <c r="R109" t="n">
-        <v>6949549</v>
+        <v>6949489</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11454,6 +11444,11 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>35 ex</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11480,32 +11475,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129035006</v>
+        <v>129035044</v>
       </c>
       <c r="B110" t="n">
-        <v>91540</v>
+        <v>98705</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11515,10 +11510,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>569217</v>
+        <v>569191</v>
       </c>
       <c r="R110" t="n">
-        <v>6949470</v>
+        <v>6949579</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11551,6 +11546,11 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11580,7 +11580,7 @@
         <v>129035033</v>
       </c>
       <c r="B111" t="n">
-        <v>91752</v>
+        <v>91753</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11677,7 +11677,7 @@
         <v>129035032</v>
       </c>
       <c r="B112" t="n">
-        <v>91752</v>
+        <v>91753</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>

--- a/artfynd/A 45833-2025 artfynd.xlsx
+++ b/artfynd/A 45833-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129034612</v>
       </c>
       <c r="B2" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129035043</v>
+        <v>129035046</v>
       </c>
       <c r="B3" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569204</v>
+        <v>569127</v>
       </c>
       <c r="R3" t="n">
-        <v>6949533</v>
+        <v>6949602</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>10 ex</t>
+          <t>13 ex</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129035046</v>
+        <v>129035043</v>
       </c>
       <c r="B4" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569127</v>
+        <v>569204</v>
       </c>
       <c r="R4" t="n">
-        <v>6949602</v>
+        <v>6949533</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,7 +954,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>13 ex</t>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1078,32 +1078,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129035030</v>
+        <v>129035039</v>
       </c>
       <c r="B6" t="n">
-        <v>97576</v>
+        <v>98706</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>569424</v>
+        <v>569394</v>
       </c>
       <c r="R6" t="n">
-        <v>6949671</v>
+        <v>6949664</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1149,6 +1149,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1175,32 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129035039</v>
+        <v>129035030</v>
       </c>
       <c r="B7" t="n">
-        <v>98705</v>
+        <v>97577</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>569394</v>
+        <v>569424</v>
       </c>
       <c r="R7" t="n">
-        <v>6949664</v>
+        <v>6949671</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1246,11 +1251,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1277,7 +1277,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129035013</v>
+        <v>129035014</v>
       </c>
       <c r="B8" t="n">
         <v>57727</v>
@@ -1315,7 +1315,7 @@
         <v>569455</v>
       </c>
       <c r="R8" t="n">
-        <v>6949716</v>
+        <v>6949703</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1379,7 +1379,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129035014</v>
+        <v>129035013</v>
       </c>
       <c r="B9" t="n">
         <v>57727</v>
@@ -1417,7 +1417,7 @@
         <v>569455</v>
       </c>
       <c r="R9" t="n">
-        <v>6949703</v>
+        <v>6949716</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1484,7 +1484,7 @@
         <v>129035054</v>
       </c>
       <c r="B10" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1685,32 +1685,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129034648</v>
+        <v>129034630</v>
       </c>
       <c r="B12" t="n">
-        <v>96824</v>
+        <v>79041</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1720,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569279</v>
+        <v>569231</v>
       </c>
       <c r="R12" t="n">
-        <v>6949401</v>
+        <v>6949559</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1782,32 +1782,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129034630</v>
+        <v>129035055</v>
       </c>
       <c r="B13" t="n">
-        <v>79041</v>
+        <v>98706</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1817,10 +1817,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569231</v>
+        <v>569221</v>
       </c>
       <c r="R13" t="n">
-        <v>6949559</v>
+        <v>6949406</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1853,6 +1853,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1879,32 +1884,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129034577</v>
+        <v>129035042</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>98706</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1914,10 +1919,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569496</v>
+        <v>569200</v>
       </c>
       <c r="R14" t="n">
-        <v>6949627</v>
+        <v>6949533</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1954,7 +1959,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på tall</t>
+          <t>30 ex</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1981,32 +1986,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129035042</v>
+        <v>129034577</v>
       </c>
       <c r="B15" t="n">
-        <v>98705</v>
+        <v>57727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2016,10 +2021,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>569200</v>
+        <v>569496</v>
       </c>
       <c r="R15" t="n">
-        <v>6949533</v>
+        <v>6949627</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2056,7 +2061,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>30 ex</t>
+          <t>Äldre ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2083,32 +2088,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129035055</v>
+        <v>129034648</v>
       </c>
       <c r="B16" t="n">
-        <v>98705</v>
+        <v>96825</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2118,10 +2123,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>569221</v>
+        <v>569279</v>
       </c>
       <c r="R16" t="n">
-        <v>6949406</v>
+        <v>6949401</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2154,11 +2159,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>25 ex</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2185,32 +2185,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129035059</v>
+        <v>129034620</v>
       </c>
       <c r="B17" t="n">
-        <v>92822</v>
+        <v>98706</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2220,10 +2220,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>569273</v>
+        <v>569195</v>
       </c>
       <c r="R17" t="n">
-        <v>6949537</v>
+        <v>6949410</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2256,6 +2256,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Blommande knärot 1 exemplar + 21 övriga exemplar blommar ej</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2379,7 +2384,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129035009</v>
+        <v>129034580</v>
       </c>
       <c r="B19" t="n">
         <v>57727</v>
@@ -2414,10 +2419,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>569314</v>
+        <v>569396</v>
       </c>
       <c r="R19" t="n">
-        <v>6949502</v>
+        <v>6949738</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2454,7 +2459,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Äldre ringhack på Tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2481,7 +2486,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129034580</v>
+        <v>129035019</v>
       </c>
       <c r="B20" t="n">
         <v>57727</v>
@@ -2516,10 +2521,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>569396</v>
+        <v>569117</v>
       </c>
       <c r="R20" t="n">
-        <v>6949738</v>
+        <v>6949581</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2556,7 +2561,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Äldre ringhack på Tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2583,7 +2588,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129035019</v>
+        <v>129035009</v>
       </c>
       <c r="B21" t="n">
         <v>57727</v>
@@ -2618,10 +2623,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>569117</v>
+        <v>569314</v>
       </c>
       <c r="R21" t="n">
-        <v>6949581</v>
+        <v>6949502</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2658,7 +2663,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2685,32 +2690,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129034620</v>
+        <v>129035059</v>
       </c>
       <c r="B22" t="n">
-        <v>98705</v>
+        <v>92822</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2720,10 +2725,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>569195</v>
+        <v>569273</v>
       </c>
       <c r="R22" t="n">
-        <v>6949410</v>
+        <v>6949537</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2756,11 +2761,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Blommande knärot 1 exemplar + 21 övriga exemplar blommar ej</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2790,7 +2790,7 @@
         <v>129034623</v>
       </c>
       <c r="B23" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2889,10 +2889,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129034592</v>
+        <v>129035005</v>
       </c>
       <c r="B24" t="n">
-        <v>91838</v>
+        <v>91540</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2900,21 +2900,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2924,10 +2924,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569205</v>
+        <v>569188</v>
       </c>
       <c r="R24" t="n">
-        <v>6949497</v>
+        <v>6949496</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2960,11 +2960,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>1 x</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2991,10 +2986,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129034591</v>
+        <v>129035004</v>
       </c>
       <c r="B25" t="n">
-        <v>91838</v>
+        <v>91540</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3002,21 +2997,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3026,10 +3021,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569203</v>
+        <v>569152</v>
       </c>
       <c r="R25" t="n">
-        <v>6949513</v>
+        <v>6949557</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3062,11 +3057,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>11 ex</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3093,10 +3083,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129034647</v>
+        <v>129034592</v>
       </c>
       <c r="B26" t="n">
-        <v>88940</v>
+        <v>91838</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3104,21 +3094,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3128,10 +3118,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569247</v>
+        <v>569205</v>
       </c>
       <c r="R26" t="n">
-        <v>6949558</v>
+        <v>6949497</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3164,6 +3154,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>1 x</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3190,10 +3185,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129035004</v>
+        <v>129034591</v>
       </c>
       <c r="B27" t="n">
-        <v>91540</v>
+        <v>91838</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3201,21 +3196,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3225,10 +3220,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>569152</v>
+        <v>569203</v>
       </c>
       <c r="R27" t="n">
-        <v>6949557</v>
+        <v>6949513</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3261,6 +3256,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>11 ex</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3287,10 +3287,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129035025</v>
+        <v>129034647</v>
       </c>
       <c r="B28" t="n">
-        <v>91838</v>
+        <v>88940</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3298,21 +3298,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3322,10 +3322,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>569388</v>
+        <v>569247</v>
       </c>
       <c r="R28" t="n">
-        <v>6949665</v>
+        <v>6949558</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3384,10 +3384,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129035005</v>
+        <v>129035025</v>
       </c>
       <c r="B29" t="n">
-        <v>91540</v>
+        <v>91838</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3395,21 +3395,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3419,10 +3419,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>569188</v>
+        <v>569388</v>
       </c>
       <c r="R29" t="n">
-        <v>6949496</v>
+        <v>6949665</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3578,32 +3578,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129035051</v>
+        <v>129035058</v>
       </c>
       <c r="B31" t="n">
-        <v>98705</v>
+        <v>79041</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>569222</v>
+        <v>569388</v>
       </c>
       <c r="R31" t="n">
-        <v>6949414</v>
+        <v>6949647</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3649,11 +3649,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>30 ex</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3680,32 +3675,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129034637</v>
+        <v>129035031</v>
       </c>
       <c r="B32" t="n">
-        <v>92822</v>
+        <v>80146</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3715,10 +3710,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>569229</v>
+        <v>569125</v>
       </c>
       <c r="R32" t="n">
-        <v>6949400</v>
+        <v>6949570</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3777,10 +3772,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129035058</v>
+        <v>129034578</v>
       </c>
       <c r="B33" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3788,21 +3783,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3812,10 +3807,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>569388</v>
+        <v>569420</v>
       </c>
       <c r="R33" t="n">
-        <v>6949647</v>
+        <v>6949723</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3848,6 +3843,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3874,32 +3874,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129035031</v>
+        <v>129034637</v>
       </c>
       <c r="B34" t="n">
-        <v>80146</v>
+        <v>92822</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3909,10 +3909,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>569125</v>
+        <v>569229</v>
       </c>
       <c r="R34" t="n">
-        <v>6949570</v>
+        <v>6949400</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3971,32 +3971,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129034578</v>
+        <v>129035051</v>
       </c>
       <c r="B35" t="n">
-        <v>57727</v>
+        <v>98706</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4006,10 +4006,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>569420</v>
+        <v>569222</v>
       </c>
       <c r="R35" t="n">
-        <v>6949723</v>
+        <v>6949414</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på Tall</t>
+          <t>30 ex</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4073,10 +4073,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129034634</v>
+        <v>129035015</v>
       </c>
       <c r="B36" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4084,21 +4084,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4108,10 +4108,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>569200</v>
+        <v>569454</v>
       </c>
       <c r="R36" t="n">
-        <v>6949411</v>
+        <v>6949698</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4144,6 +4144,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4170,7 +4175,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129035015</v>
+        <v>129035020</v>
       </c>
       <c r="B37" t="n">
         <v>57727</v>
@@ -4205,10 +4210,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>569454</v>
+        <v>569171</v>
       </c>
       <c r="R37" t="n">
-        <v>6949698</v>
+        <v>6949543</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4245,7 +4250,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på granhögstubbe</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4272,10 +4277,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129035020</v>
+        <v>129034634</v>
       </c>
       <c r="B38" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4283,21 +4288,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4307,10 +4312,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>569171</v>
+        <v>569200</v>
       </c>
       <c r="R38" t="n">
-        <v>6949543</v>
+        <v>6949411</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4343,11 +4348,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på granhögstubbe</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4377,7 +4377,7 @@
         <v>129034602</v>
       </c>
       <c r="B39" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         <v>129035040</v>
       </c>
       <c r="B40" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4581,7 +4581,7 @@
         <v>129035045</v>
       </c>
       <c r="B41" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4785,7 +4785,7 @@
         <v>129035063</v>
       </c>
       <c r="B43" t="n">
-        <v>96824</v>
+        <v>96825</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4879,32 +4879,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129035041</v>
+        <v>129035011</v>
       </c>
       <c r="B44" t="n">
-        <v>98705</v>
+        <v>57727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4914,10 +4914,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>569262</v>
+        <v>569442</v>
       </c>
       <c r="R44" t="n">
-        <v>6949524</v>
+        <v>6949783</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>5 ex</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5083,32 +5083,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129035011</v>
+        <v>129034607</v>
       </c>
       <c r="B46" t="n">
-        <v>57727</v>
+        <v>98706</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5118,10 +5118,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>569442</v>
+        <v>569317</v>
       </c>
       <c r="R46" t="n">
-        <v>6949783</v>
+        <v>6949549</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>31 stycken</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5185,10 +5185,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129034607</v>
+        <v>129035041</v>
       </c>
       <c r="B47" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5220,10 +5220,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>569317</v>
+        <v>569262</v>
       </c>
       <c r="R47" t="n">
-        <v>6949549</v>
+        <v>6949524</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5260,7 +5260,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>31 stycken</t>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5583,10 +5583,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129034632</v>
+        <v>129035016</v>
       </c>
       <c r="B51" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5594,21 +5594,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5618,10 +5618,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>569237</v>
+        <v>569435</v>
       </c>
       <c r="R51" t="n">
-        <v>6949442</v>
+        <v>6949665</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5654,6 +5654,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5680,10 +5685,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129035016</v>
+        <v>129034632</v>
       </c>
       <c r="B52" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5691,21 +5696,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5715,10 +5720,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>569435</v>
+        <v>569237</v>
       </c>
       <c r="R52" t="n">
-        <v>6949665</v>
+        <v>6949442</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5751,11 +5756,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5782,32 +5782,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129034616</v>
+        <v>129035062</v>
       </c>
       <c r="B53" t="n">
-        <v>98705</v>
+        <v>96825</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5817,10 +5817,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>569223</v>
+        <v>569478</v>
       </c>
       <c r="R53" t="n">
-        <v>6949465</v>
+        <v>6949666</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5853,11 +5853,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>10 stycken</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5884,32 +5879,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129035062</v>
+        <v>129034616</v>
       </c>
       <c r="B54" t="n">
-        <v>96824</v>
+        <v>98706</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5919,10 +5914,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>569478</v>
+        <v>569223</v>
       </c>
       <c r="R54" t="n">
-        <v>6949666</v>
+        <v>6949465</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5955,6 +5950,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>10 stycken</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5981,10 +5981,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129035028</v>
+        <v>129035008</v>
       </c>
       <c r="B55" t="n">
-        <v>91838</v>
+        <v>91540</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5992,21 +5992,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6016,10 +6016,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>569192</v>
+        <v>569216</v>
       </c>
       <c r="R55" t="n">
-        <v>6949509</v>
+        <v>6949430</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6078,10 +6078,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129035008</v>
+        <v>129034581</v>
       </c>
       <c r="B56" t="n">
-        <v>91540</v>
+        <v>57887</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6089,21 +6089,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6113,10 +6113,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>569216</v>
+        <v>569223</v>
       </c>
       <c r="R56" t="n">
-        <v>6949430</v>
+        <v>6949401</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6149,6 +6149,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Sågs och gjorde övriga läten</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6178,7 +6183,7 @@
         <v>129034610</v>
       </c>
       <c r="B57" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6280,7 +6285,7 @@
         <v>129034614</v>
       </c>
       <c r="B58" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6379,10 +6384,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129034600</v>
+        <v>129035028</v>
       </c>
       <c r="B59" t="n">
-        <v>80146</v>
+        <v>91838</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6390,21 +6395,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6414,10 +6419,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>569481</v>
+        <v>569192</v>
       </c>
       <c r="R59" t="n">
-        <v>6949674</v>
+        <v>6949509</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6450,11 +6455,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Apothecier antal 1</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6481,10 +6481,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129034581</v>
+        <v>129034600</v>
       </c>
       <c r="B60" t="n">
-        <v>57887</v>
+        <v>80146</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6492,21 +6492,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6516,10 +6516,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>569223</v>
+        <v>569481</v>
       </c>
       <c r="R60" t="n">
-        <v>6949401</v>
+        <v>6949674</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6556,7 +6556,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Sågs och gjorde övriga läten</t>
+          <t>Apothecier antal 1</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6777,10 +6777,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129035003</v>
+        <v>129034587</v>
       </c>
       <c r="B63" t="n">
-        <v>91540</v>
+        <v>91838</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6788,21 +6788,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6812,10 +6812,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>569164</v>
+        <v>569463</v>
       </c>
       <c r="R63" t="n">
-        <v>6949559</v>
+        <v>6949711</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6874,7 +6874,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129034587</v>
+        <v>129035021</v>
       </c>
       <c r="B64" t="n">
         <v>91838</v>
@@ -6909,10 +6909,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>569463</v>
+        <v>569446</v>
       </c>
       <c r="R64" t="n">
-        <v>6949711</v>
+        <v>6949629</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6971,45 +6971,49 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129035021</v>
+        <v>129027791</v>
       </c>
       <c r="B65" t="n">
-        <v>91838</v>
+        <v>98706</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Sandsjömyran, Mpd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>569446</v>
+        <v>569308</v>
       </c>
       <c r="R65" t="n">
-        <v>6949629</v>
+        <v>6949546</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7068,32 +7072,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129034574</v>
+        <v>129034624</v>
       </c>
       <c r="B66" t="n">
-        <v>91540</v>
+        <v>105770</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7103,10 +7107,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>569461</v>
+        <v>569234</v>
       </c>
       <c r="R66" t="n">
-        <v>6949706</v>
+        <v>6949440</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7139,6 +7143,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>9 exemplar</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7165,32 +7174,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129034624</v>
+        <v>129035035</v>
       </c>
       <c r="B67" t="n">
-        <v>105769</v>
+        <v>98706</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7200,10 +7209,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>569234</v>
+        <v>569317</v>
       </c>
       <c r="R67" t="n">
-        <v>6949440</v>
+        <v>6949469</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7240,7 +7249,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>9 exemplar</t>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7267,32 +7276,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129035035</v>
+        <v>129034574</v>
       </c>
       <c r="B68" t="n">
-        <v>98705</v>
+        <v>91540</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7302,10 +7311,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>569317</v>
+        <v>569461</v>
       </c>
       <c r="R68" t="n">
-        <v>6949469</v>
+        <v>6949706</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7338,11 +7347,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>5 ex</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7369,49 +7373,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129027791</v>
+        <v>129035003</v>
       </c>
       <c r="B69" t="n">
-        <v>98705</v>
+        <v>91540</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Sandsjömyran, Mpd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>569308</v>
+        <v>569164</v>
       </c>
       <c r="R69" t="n">
-        <v>6949546</v>
+        <v>6949559</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7470,7 +7470,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129035060</v>
+        <v>129034639</v>
       </c>
       <c r="B70" t="n">
         <v>92822</v>
@@ -7505,10 +7505,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>569208</v>
+        <v>569398</v>
       </c>
       <c r="R70" t="n">
-        <v>6949415</v>
+        <v>6949741</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7545,7 +7545,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>20 ex minst</t>
+          <t>6 äldre exemplar och 1 färsk fruktkropp</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7572,7 +7572,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129034639</v>
+        <v>129035060</v>
       </c>
       <c r="B71" t="n">
         <v>92822</v>
@@ -7607,10 +7607,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>569398</v>
+        <v>569208</v>
       </c>
       <c r="R71" t="n">
-        <v>6949741</v>
+        <v>6949415</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7647,7 +7647,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>6 äldre exemplar och 1 färsk fruktkropp</t>
+          <t>20 ex minst</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7881,7 +7881,7 @@
         <v>129035037</v>
       </c>
       <c r="B74" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7980,32 +7980,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129026691</v>
+        <v>129034645</v>
       </c>
       <c r="B75" t="n">
-        <v>91838</v>
+        <v>92822</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8015,10 +8015,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>569195</v>
+        <v>569196</v>
       </c>
       <c r="R75" t="n">
-        <v>6949487</v>
+        <v>6949411</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8051,6 +8051,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>4 färska exemplar 3 äldre exemplar</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8077,7 +8082,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129034645</v>
+        <v>129034642</v>
       </c>
       <c r="B76" t="n">
         <v>92822</v>
@@ -8112,10 +8117,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>569196</v>
+        <v>569283</v>
       </c>
       <c r="R76" t="n">
-        <v>6949411</v>
+        <v>6949655</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8152,7 +8157,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>4 färska exemplar 3 äldre exemplar</t>
+          <t>7 äldre exemplar</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8179,32 +8184,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129034642</v>
+        <v>129026691</v>
       </c>
       <c r="B77" t="n">
-        <v>92822</v>
+        <v>91838</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8214,10 +8219,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>569283</v>
+        <v>569195</v>
       </c>
       <c r="R77" t="n">
-        <v>6949655</v>
+        <v>6949487</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8250,11 +8255,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>7 äldre exemplar</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8281,32 +8281,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129034650</v>
+        <v>129034598</v>
       </c>
       <c r="B78" t="n">
-        <v>98705</v>
+        <v>97577</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8316,10 +8316,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>569303</v>
+        <v>569460</v>
       </c>
       <c r="R78" t="n">
-        <v>6949537</v>
+        <v>6949629</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8352,11 +8352,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>30 stycken ( finns eventuellt mer )</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8383,10 +8378,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129034605</v>
+        <v>129034650</v>
       </c>
       <c r="B79" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8418,10 +8413,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>569305</v>
+        <v>569303</v>
       </c>
       <c r="R79" t="n">
-        <v>6949538</v>
+        <v>6949537</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8458,7 +8453,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>21 knärot</t>
+          <t>30 stycken ( finns eventuellt mer )</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8485,32 +8480,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129034598</v>
+        <v>129034605</v>
       </c>
       <c r="B80" t="n">
-        <v>97576</v>
+        <v>98706</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8520,10 +8515,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>569460</v>
+        <v>569305</v>
       </c>
       <c r="R80" t="n">
-        <v>6949629</v>
+        <v>6949538</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8556,6 +8551,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>21 knärot</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8582,32 +8582,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129035007</v>
+        <v>129034640</v>
       </c>
       <c r="B81" t="n">
-        <v>91540</v>
+        <v>92822</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8617,10 +8617,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>569225</v>
+        <v>569213</v>
       </c>
       <c r="R81" t="n">
-        <v>6949424</v>
+        <v>6949414</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8653,6 +8653,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>16 exemplar</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8679,32 +8684,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129034640</v>
+        <v>129035007</v>
       </c>
       <c r="B82" t="n">
-        <v>92822</v>
+        <v>91540</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8714,10 +8719,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>569213</v>
+        <v>569225</v>
       </c>
       <c r="R82" t="n">
-        <v>6949414</v>
+        <v>6949424</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8750,11 +8755,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>16 exemplar</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8781,32 +8781,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129035061</v>
+        <v>129035057</v>
       </c>
       <c r="B83" t="n">
-        <v>96824</v>
+        <v>79041</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8816,10 +8816,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>569333</v>
+        <v>569464</v>
       </c>
       <c r="R83" t="n">
-        <v>6949607</v>
+        <v>6949648</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8878,10 +8878,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129035057</v>
+        <v>129035012</v>
       </c>
       <c r="B84" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8889,21 +8889,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8913,10 +8913,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>569464</v>
+        <v>569435</v>
       </c>
       <c r="R84" t="n">
-        <v>6949648</v>
+        <v>6949783</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8949,6 +8949,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8975,32 +8980,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129035012</v>
+        <v>129035061</v>
       </c>
       <c r="B85" t="n">
-        <v>57727</v>
+        <v>96825</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9010,10 +9015,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>569435</v>
+        <v>569333</v>
       </c>
       <c r="R85" t="n">
-        <v>6949783</v>
+        <v>6949607</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9046,11 +9051,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9077,32 +9077,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129034618</v>
+        <v>129035001</v>
       </c>
       <c r="B86" t="n">
-        <v>98705</v>
+        <v>91504</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9112,10 +9112,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>569235</v>
+        <v>569232</v>
       </c>
       <c r="R86" t="n">
-        <v>6949411</v>
+        <v>6949444</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9148,11 +9148,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9182,7 +9177,7 @@
         <v>129035047</v>
       </c>
       <c r="B87" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9284,7 +9279,7 @@
         <v>129034604</v>
       </c>
       <c r="B88" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9383,32 +9378,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129035001</v>
+        <v>129034618</v>
       </c>
       <c r="B89" t="n">
-        <v>91504</v>
+        <v>98706</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9418,10 +9413,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>569232</v>
+        <v>569235</v>
       </c>
       <c r="R89" t="n">
-        <v>6949444</v>
+        <v>6949411</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9454,6 +9449,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9771,32 +9771,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129035029</v>
+        <v>129035038</v>
       </c>
       <c r="B93" t="n">
-        <v>91838</v>
+        <v>98706</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9806,10 +9806,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>569217</v>
+        <v>569406</v>
       </c>
       <c r="R93" t="n">
-        <v>6949427</v>
+        <v>6949664</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9842,6 +9842,11 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9868,10 +9873,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129034621</v>
+        <v>129035050</v>
       </c>
       <c r="B94" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9903,10 +9908,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>569247</v>
+        <v>569236</v>
       </c>
       <c r="R94" t="n">
-        <v>6949434</v>
+        <v>6949440</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9943,7 +9948,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>10 stycken knärot</t>
+          <t>4 ex</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -9970,10 +9975,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129035038</v>
+        <v>129034621</v>
       </c>
       <c r="B95" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10005,10 +10010,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>569406</v>
+        <v>569247</v>
       </c>
       <c r="R95" t="n">
-        <v>6949664</v>
+        <v>6949434</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10045,7 +10050,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>20 ex</t>
+          <t>10 stycken knärot</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10072,32 +10077,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129035050</v>
+        <v>129035029</v>
       </c>
       <c r="B96" t="n">
-        <v>98705</v>
+        <v>91838</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10107,10 +10112,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>569236</v>
+        <v>569217</v>
       </c>
       <c r="R96" t="n">
-        <v>6949440</v>
+        <v>6949427</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10143,11 +10148,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>4 ex</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10174,32 +10174,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129034635</v>
+        <v>129034609</v>
       </c>
       <c r="B97" t="n">
-        <v>79041</v>
+        <v>98706</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10209,10 +10209,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>569427</v>
+        <v>569458</v>
       </c>
       <c r="R97" t="n">
-        <v>6949726</v>
+        <v>6949777</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10245,6 +10245,11 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>48 stycken</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10271,32 +10276,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129035017</v>
+        <v>129035036</v>
       </c>
       <c r="B98" t="n">
-        <v>57727</v>
+        <v>98706</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10306,10 +10311,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>569192</v>
+        <v>569330</v>
       </c>
       <c r="R98" t="n">
-        <v>6949518</v>
+        <v>6949564</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10346,7 +10351,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>8 ex</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10373,32 +10378,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129034609</v>
+        <v>129034635</v>
       </c>
       <c r="B99" t="n">
-        <v>98705</v>
+        <v>79041</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10408,10 +10413,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>569458</v>
+        <v>569427</v>
       </c>
       <c r="R99" t="n">
-        <v>6949777</v>
+        <v>6949726</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10444,11 +10449,6 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>48 stycken</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10577,32 +10577,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129035036</v>
+        <v>129035017</v>
       </c>
       <c r="B101" t="n">
-        <v>98705</v>
+        <v>57727</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10612,10 +10612,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>569330</v>
+        <v>569192</v>
       </c>
       <c r="R101" t="n">
-        <v>6949564</v>
+        <v>6949518</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10652,7 +10652,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>8 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10682,7 +10682,7 @@
         <v>129035052</v>
       </c>
       <c r="B102" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10784,7 +10784,7 @@
         <v>129035056</v>
       </c>
       <c r="B103" t="n">
-        <v>105769</v>
+        <v>105770</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10878,10 +10878,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129035026</v>
+        <v>129027886</v>
       </c>
       <c r="B104" t="n">
-        <v>91838</v>
+        <v>91540</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10889,21 +10889,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10913,10 +10913,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>569175</v>
+        <v>569305</v>
       </c>
       <c r="R104" t="n">
-        <v>6949549</v>
+        <v>6949566</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11072,10 +11072,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129027886</v>
+        <v>129035026</v>
       </c>
       <c r="B106" t="n">
-        <v>91540</v>
+        <v>91838</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11083,21 +11083,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11107,10 +11107,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>569305</v>
+        <v>569175</v>
       </c>
       <c r="R106" t="n">
-        <v>6949566</v>
+        <v>6949549</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11172,7 +11172,7 @@
         <v>129035048</v>
       </c>
       <c r="B107" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11274,7 +11274,7 @@
         <v>129035053</v>
       </c>
       <c r="B108" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>129035049</v>
       </c>
       <c r="B109" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11478,7 +11478,7 @@
         <v>129035044</v>
       </c>
       <c r="B110" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>

--- a/artfynd/A 45833-2025 artfynd.xlsx
+++ b/artfynd/A 45833-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129034612</v>
+        <v>129034627</v>
       </c>
       <c r="B2" t="n">
-        <v>98706</v>
+        <v>79043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569243</v>
+        <v>569482</v>
       </c>
       <c r="R2" t="n">
-        <v>6949558</v>
+        <v>6949676</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>30  exemplar ca</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129035046</v>
+        <v>129034612</v>
       </c>
       <c r="B3" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569127</v>
+        <v>569243</v>
       </c>
       <c r="R3" t="n">
-        <v>6949602</v>
+        <v>6949558</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +847,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>13 ex</t>
+          <t>30  exemplar ca</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129035043</v>
+        <v>129035046</v>
       </c>
       <c r="B4" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569204</v>
+        <v>569127</v>
       </c>
       <c r="R4" t="n">
-        <v>6949533</v>
+        <v>6949602</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,7 +949,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>10 ex</t>
+          <t>13 ex</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,32 +976,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129034627</v>
+        <v>129035043</v>
       </c>
       <c r="B5" t="n">
-        <v>79041</v>
+        <v>98710</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569482</v>
+        <v>569204</v>
       </c>
       <c r="R5" t="n">
-        <v>6949676</v>
+        <v>6949533</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1052,6 +1047,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1078,32 +1078,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129035039</v>
+        <v>129035030</v>
       </c>
       <c r="B6" t="n">
-        <v>98706</v>
+        <v>97581</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>569394</v>
+        <v>569424</v>
       </c>
       <c r="R6" t="n">
-        <v>6949664</v>
+        <v>6949671</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1149,11 +1149,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1180,32 +1175,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129035030</v>
+        <v>129035039</v>
       </c>
       <c r="B7" t="n">
-        <v>97577</v>
+        <v>98710</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>569424</v>
+        <v>569394</v>
       </c>
       <c r="R7" t="n">
-        <v>6949671</v>
+        <v>6949664</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1251,6 +1246,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1277,32 +1277,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129035014</v>
+        <v>129035054</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>98710</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>569455</v>
+        <v>569126</v>
       </c>
       <c r="R8" t="n">
-        <v>6949703</v>
+        <v>6949570</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>13 ex</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1481,32 +1481,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129035054</v>
+        <v>129035014</v>
       </c>
       <c r="B10" t="n">
-        <v>98706</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>569126</v>
+        <v>569455</v>
       </c>
       <c r="R10" t="n">
-        <v>6949570</v>
+        <v>6949703</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>13 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1583,32 +1583,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129034594</v>
+        <v>129035055</v>
       </c>
       <c r="B11" t="n">
-        <v>91838</v>
+        <v>98710</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>569203</v>
+        <v>569221</v>
       </c>
       <c r="R11" t="n">
-        <v>6949498</v>
+        <v>6949406</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>11 exemplar</t>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1685,32 +1685,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129034630</v>
+        <v>129035042</v>
       </c>
       <c r="B12" t="n">
-        <v>79041</v>
+        <v>98710</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1720,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569231</v>
+        <v>569200</v>
       </c>
       <c r="R12" t="n">
-        <v>6949559</v>
+        <v>6949533</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1756,6 +1756,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>30 ex</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1782,32 +1787,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129035055</v>
+        <v>129034630</v>
       </c>
       <c r="B13" t="n">
-        <v>98706</v>
+        <v>79043</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1817,10 +1822,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569221</v>
+        <v>569231</v>
       </c>
       <c r="R13" t="n">
-        <v>6949406</v>
+        <v>6949559</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1853,11 +1858,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>25 ex</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1884,32 +1884,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129035042</v>
+        <v>129034648</v>
       </c>
       <c r="B14" t="n">
-        <v>98706</v>
+        <v>96829</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1919,10 +1919,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569200</v>
+        <v>569279</v>
       </c>
       <c r="R14" t="n">
-        <v>6949533</v>
+        <v>6949401</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1955,11 +1955,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>30 ex</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1986,10 +1981,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129034577</v>
+        <v>129034594</v>
       </c>
       <c r="B15" t="n">
-        <v>57727</v>
+        <v>91841</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1997,21 +1992,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2021,10 +2016,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>569496</v>
+        <v>569203</v>
       </c>
       <c r="R15" t="n">
-        <v>6949627</v>
+        <v>6949498</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2061,7 +2056,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på tall</t>
+          <t>11 exemplar</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2088,32 +2083,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129034648</v>
+        <v>129034577</v>
       </c>
       <c r="B16" t="n">
-        <v>96825</v>
+        <v>57727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2123,10 +2118,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>569279</v>
+        <v>569496</v>
       </c>
       <c r="R16" t="n">
-        <v>6949401</v>
+        <v>6949627</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2159,6 +2154,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2185,32 +2185,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129034620</v>
+        <v>129035059</v>
       </c>
       <c r="B17" t="n">
-        <v>98706</v>
+        <v>92825</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2220,10 +2220,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>569195</v>
+        <v>569273</v>
       </c>
       <c r="R17" t="n">
-        <v>6949410</v>
+        <v>6949537</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2256,11 +2256,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Blommande knärot 1 exemplar + 21 övriga exemplar blommar ej</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2287,10 +2282,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129034629</v>
+        <v>129035009</v>
       </c>
       <c r="B18" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2298,21 +2293,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2322,10 +2317,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>569247</v>
+        <v>569314</v>
       </c>
       <c r="R18" t="n">
-        <v>6949558</v>
+        <v>6949502</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2358,6 +2353,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2588,10 +2588,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129035009</v>
+        <v>129034629</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2599,21 +2599,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>569314</v>
+        <v>569247</v>
       </c>
       <c r="R21" t="n">
-        <v>6949502</v>
+        <v>6949558</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2659,11 +2659,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2690,32 +2685,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129035059</v>
+        <v>129034620</v>
       </c>
       <c r="B22" t="n">
-        <v>92822</v>
+        <v>98710</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2725,10 +2720,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>569273</v>
+        <v>569195</v>
       </c>
       <c r="R22" t="n">
-        <v>6949537</v>
+        <v>6949410</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2761,6 +2756,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Blommande knärot 1 exemplar + 21 övriga exemplar blommar ej</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2787,32 +2787,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129034623</v>
+        <v>129035004</v>
       </c>
       <c r="B23" t="n">
-        <v>98706</v>
+        <v>91543</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569253</v>
+        <v>569152</v>
       </c>
       <c r="R23" t="n">
-        <v>6949425</v>
+        <v>6949557</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2858,11 +2858,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>74 stycken</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2892,7 +2887,7 @@
         <v>129035005</v>
       </c>
       <c r="B24" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2986,32 +2981,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129035004</v>
+        <v>129034623</v>
       </c>
       <c r="B25" t="n">
-        <v>91540</v>
+        <v>98710</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3021,10 +3016,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569152</v>
+        <v>569253</v>
       </c>
       <c r="R25" t="n">
-        <v>6949557</v>
+        <v>6949425</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3057,6 +3052,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>74 stycken</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3083,10 +3083,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129034592</v>
+        <v>129034625</v>
       </c>
       <c r="B26" t="n">
-        <v>91838</v>
+        <v>79043</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3094,21 +3094,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3118,10 +3118,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569205</v>
+        <v>569479</v>
       </c>
       <c r="R26" t="n">
-        <v>6949497</v>
+        <v>6949657</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3154,11 +3154,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>1 x</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3185,10 +3180,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129034591</v>
+        <v>129034592</v>
       </c>
       <c r="B27" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3220,10 +3215,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>569203</v>
+        <v>569205</v>
       </c>
       <c r="R27" t="n">
-        <v>6949513</v>
+        <v>6949497</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3260,7 +3255,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>11 ex</t>
+          <t>1 x</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3287,10 +3282,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129034647</v>
+        <v>129034591</v>
       </c>
       <c r="B28" t="n">
-        <v>88940</v>
+        <v>91841</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3298,21 +3293,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3322,10 +3317,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>569247</v>
+        <v>569203</v>
       </c>
       <c r="R28" t="n">
-        <v>6949558</v>
+        <v>6949513</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3358,6 +3353,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>11 ex</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3384,10 +3384,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129035025</v>
+        <v>129034647</v>
       </c>
       <c r="B29" t="n">
-        <v>91838</v>
+        <v>88943</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3395,21 +3395,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3419,10 +3419,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>569388</v>
+        <v>569247</v>
       </c>
       <c r="R29" t="n">
-        <v>6949665</v>
+        <v>6949558</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3481,10 +3481,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129034625</v>
+        <v>129035025</v>
       </c>
       <c r="B30" t="n">
-        <v>79041</v>
+        <v>91841</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3492,21 +3492,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3516,10 +3516,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>569479</v>
+        <v>569388</v>
       </c>
       <c r="R30" t="n">
-        <v>6949657</v>
+        <v>6949665</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3578,32 +3578,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129035058</v>
+        <v>129034637</v>
       </c>
       <c r="B31" t="n">
-        <v>79041</v>
+        <v>92825</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>569388</v>
+        <v>569229</v>
       </c>
       <c r="R31" t="n">
-        <v>6949647</v>
+        <v>6949400</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3678,7 +3678,7 @@
         <v>129035031</v>
       </c>
       <c r="B32" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3874,32 +3874,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129034637</v>
+        <v>129035058</v>
       </c>
       <c r="B34" t="n">
-        <v>92822</v>
+        <v>79043</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3909,10 +3909,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>569229</v>
+        <v>569388</v>
       </c>
       <c r="R34" t="n">
-        <v>6949400</v>
+        <v>6949647</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3974,7 +3974,7 @@
         <v>129035051</v>
       </c>
       <c r="B35" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4073,32 +4073,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129035015</v>
+        <v>129034602</v>
       </c>
       <c r="B36" t="n">
-        <v>57727</v>
+        <v>98710</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4108,10 +4108,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>569454</v>
+        <v>569301</v>
       </c>
       <c r="R36" t="n">
-        <v>6949698</v>
+        <v>6949480</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>22 stycken</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4175,32 +4175,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129035020</v>
+        <v>129035040</v>
       </c>
       <c r="B37" t="n">
-        <v>57727</v>
+        <v>98710</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4210,10 +4210,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>569171</v>
+        <v>569386</v>
       </c>
       <c r="R37" t="n">
-        <v>6949543</v>
+        <v>6949657</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4250,7 +4250,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Äldre ringhack på granhögstubbe</t>
+          <t>9 ex</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4277,32 +4277,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129034634</v>
+        <v>129035045</v>
       </c>
       <c r="B38" t="n">
-        <v>79041</v>
+        <v>98710</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4312,10 +4312,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>569200</v>
+        <v>569130</v>
       </c>
       <c r="R38" t="n">
-        <v>6949411</v>
+        <v>6949603</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4348,6 +4348,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>14 ex</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4374,32 +4379,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129034602</v>
+        <v>129034634</v>
       </c>
       <c r="B39" t="n">
-        <v>98706</v>
+        <v>79043</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4409,10 +4414,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>569301</v>
+        <v>569200</v>
       </c>
       <c r="R39" t="n">
-        <v>6949480</v>
+        <v>6949411</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4445,11 +4450,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>22 stycken</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4476,32 +4476,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129035040</v>
+        <v>129035020</v>
       </c>
       <c r="B40" t="n">
-        <v>98706</v>
+        <v>57727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4511,10 +4511,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>569386</v>
+        <v>569171</v>
       </c>
       <c r="R40" t="n">
-        <v>6949657</v>
+        <v>6949543</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4551,7 +4551,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>9 ex</t>
+          <t>Äldre ringhack på granhögstubbe</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4578,32 +4578,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129035045</v>
+        <v>129035015</v>
       </c>
       <c r="B41" t="n">
-        <v>98706</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4613,10 +4613,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>569130</v>
+        <v>569454</v>
       </c>
       <c r="R41" t="n">
-        <v>6949603</v>
+        <v>6949698</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4653,7 +4653,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>14 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4680,10 +4680,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129034643</v>
+        <v>129035063</v>
       </c>
       <c r="B42" t="n">
-        <v>92822</v>
+        <v>96829</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4691,21 +4691,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>2869</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4715,10 +4715,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>569254</v>
+        <v>569455</v>
       </c>
       <c r="R42" t="n">
-        <v>6949431</v>
+        <v>6949758</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4751,11 +4751,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>1 färskt exemplar</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4782,10 +4777,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129035063</v>
+        <v>129034643</v>
       </c>
       <c r="B43" t="n">
-        <v>96825</v>
+        <v>92825</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4793,21 +4788,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2869</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4817,10 +4812,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>569455</v>
+        <v>569254</v>
       </c>
       <c r="R43" t="n">
-        <v>6949758</v>
+        <v>6949431</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4853,6 +4848,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>1 färskt exemplar</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4879,7 +4879,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129035011</v>
+        <v>129034575</v>
       </c>
       <c r="B44" t="n">
         <v>57727</v>
@@ -4914,10 +4914,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>569442</v>
+        <v>569448</v>
       </c>
       <c r="R44" t="n">
-        <v>6949783</v>
+        <v>6949625</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på Tall av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4981,7 +4981,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129034575</v>
+        <v>129035011</v>
       </c>
       <c r="B45" t="n">
         <v>57727</v>
@@ -5016,10 +5016,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>569448</v>
+        <v>569442</v>
       </c>
       <c r="R45" t="n">
-        <v>6949625</v>
+        <v>6949783</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Färska ringhack på Tall av tretåig hackspett</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5086,7 +5086,7 @@
         <v>129034607</v>
       </c>
       <c r="B46" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
         <v>129035041</v>
       </c>
       <c r="B47" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5287,10 +5287,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129035022</v>
+        <v>129034632</v>
       </c>
       <c r="B48" t="n">
-        <v>91838</v>
+        <v>79043</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5298,21 +5298,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5322,10 +5322,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>569423</v>
+        <v>569237</v>
       </c>
       <c r="R48" t="n">
-        <v>6949656</v>
+        <v>6949442</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5384,32 +5384,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129034597</v>
+        <v>129035062</v>
       </c>
       <c r="B49" t="n">
-        <v>91838</v>
+        <v>96829</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>658</v>
+        <v>2869</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5419,10 +5419,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>569221</v>
+        <v>569478</v>
       </c>
       <c r="R49" t="n">
-        <v>6949499</v>
+        <v>6949666</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5455,11 +5455,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>8 exemplar</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5489,7 +5484,7 @@
         <v>129035002</v>
       </c>
       <c r="B50" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5583,10 +5578,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129035016</v>
+        <v>129035022</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>91841</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5594,21 +5589,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5618,10 +5613,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>569435</v>
+        <v>569423</v>
       </c>
       <c r="R51" t="n">
-        <v>6949665</v>
+        <v>6949656</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5654,11 +5649,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5685,32 +5675,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129034632</v>
+        <v>129034616</v>
       </c>
       <c r="B52" t="n">
-        <v>79041</v>
+        <v>98710</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5720,10 +5710,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>569237</v>
+        <v>569223</v>
       </c>
       <c r="R52" t="n">
-        <v>6949442</v>
+        <v>6949465</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5756,6 +5746,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>10 stycken</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5782,32 +5777,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129035062</v>
+        <v>129034597</v>
       </c>
       <c r="B53" t="n">
-        <v>96825</v>
+        <v>91841</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2869</v>
+        <v>658</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5817,10 +5812,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>569478</v>
+        <v>569221</v>
       </c>
       <c r="R53" t="n">
-        <v>6949666</v>
+        <v>6949499</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5853,6 +5848,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>8 exemplar</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5879,32 +5879,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129034616</v>
+        <v>129035016</v>
       </c>
       <c r="B54" t="n">
-        <v>98706</v>
+        <v>57727</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5914,10 +5914,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>569223</v>
+        <v>569435</v>
       </c>
       <c r="R54" t="n">
-        <v>6949465</v>
+        <v>6949665</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5954,7 +5954,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>10 stycken</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5981,10 +5981,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129035008</v>
+        <v>129035028</v>
       </c>
       <c r="B55" t="n">
-        <v>91540</v>
+        <v>91841</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5992,21 +5992,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6016,10 +6016,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>569216</v>
+        <v>569192</v>
       </c>
       <c r="R55" t="n">
-        <v>6949430</v>
+        <v>6949509</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6078,10 +6078,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129034581</v>
+        <v>129035008</v>
       </c>
       <c r="B56" t="n">
-        <v>57887</v>
+        <v>91543</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6089,21 +6089,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6113,10 +6113,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>569223</v>
+        <v>569216</v>
       </c>
       <c r="R56" t="n">
-        <v>6949401</v>
+        <v>6949430</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6149,11 +6149,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Sågs och gjorde övriga läten</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6180,32 +6175,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129034610</v>
+        <v>129034600</v>
       </c>
       <c r="B57" t="n">
-        <v>98706</v>
+        <v>80148</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6215,10 +6210,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>569282</v>
+        <v>569481</v>
       </c>
       <c r="R57" t="n">
-        <v>6949567</v>
+        <v>6949674</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6255,7 +6250,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ca 100 stycken</t>
+          <t>Apothecier antal 1</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6282,32 +6277,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129034614</v>
+        <v>129034581</v>
       </c>
       <c r="B58" t="n">
-        <v>98706</v>
+        <v>57887</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6317,10 +6312,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>569237</v>
+        <v>569223</v>
       </c>
       <c r="R58" t="n">
-        <v>6949556</v>
+        <v>6949401</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6357,7 +6352,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>5 stycken</t>
+          <t>Sågs och gjorde övriga läten</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6384,32 +6379,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129035028</v>
+        <v>129034610</v>
       </c>
       <c r="B59" t="n">
-        <v>91838</v>
+        <v>98710</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6419,10 +6414,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>569192</v>
+        <v>569282</v>
       </c>
       <c r="R59" t="n">
-        <v>6949509</v>
+        <v>6949567</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6455,6 +6450,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ca 100 stycken</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6481,32 +6481,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129034600</v>
+        <v>129034614</v>
       </c>
       <c r="B60" t="n">
-        <v>80146</v>
+        <v>98710</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6516,10 +6516,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>569481</v>
+        <v>569237</v>
       </c>
       <c r="R60" t="n">
-        <v>6949674</v>
+        <v>6949556</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6556,7 +6556,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Apothecier antal 1</t>
+          <t>5 stycken</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6586,7 +6586,7 @@
         <v>129034586</v>
       </c>
       <c r="B61" t="n">
-        <v>91993</v>
+        <v>91996</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6683,7 +6683,7 @@
         <v>129035024</v>
       </c>
       <c r="B62" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6777,10 +6777,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129034587</v>
+        <v>129035021</v>
       </c>
       <c r="B63" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6812,10 +6812,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>569463</v>
+        <v>569446</v>
       </c>
       <c r="R63" t="n">
-        <v>6949711</v>
+        <v>6949629</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6874,45 +6874,49 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129035021</v>
+        <v>129027791</v>
       </c>
       <c r="B64" t="n">
-        <v>91838</v>
+        <v>98710</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Sandsjömyran, Mpd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>569446</v>
+        <v>569308</v>
       </c>
       <c r="R64" t="n">
-        <v>6949629</v>
+        <v>6949546</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6971,49 +6975,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129027791</v>
+        <v>129034624</v>
       </c>
       <c r="B65" t="n">
-        <v>98706</v>
+        <v>105774</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Sandsjömyran, Mpd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>569308</v>
+        <v>569234</v>
       </c>
       <c r="R65" t="n">
-        <v>6949546</v>
+        <v>6949440</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7046,6 +7046,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>9 exemplar</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7072,32 +7077,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129034624</v>
+        <v>129035035</v>
       </c>
       <c r="B66" t="n">
-        <v>105770</v>
+        <v>98710</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7107,10 +7112,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>569234</v>
+        <v>569317</v>
       </c>
       <c r="R66" t="n">
-        <v>6949440</v>
+        <v>6949469</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7147,7 +7152,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>9 exemplar</t>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7174,32 +7179,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129035035</v>
+        <v>129035003</v>
       </c>
       <c r="B67" t="n">
-        <v>98706</v>
+        <v>91543</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7209,10 +7214,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>569317</v>
+        <v>569164</v>
       </c>
       <c r="R67" t="n">
-        <v>6949469</v>
+        <v>6949559</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7245,11 +7250,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>5 ex</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7279,7 +7279,7 @@
         <v>129034574</v>
       </c>
       <c r="B68" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7373,10 +7373,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129035003</v>
+        <v>129034587</v>
       </c>
       <c r="B69" t="n">
-        <v>91540</v>
+        <v>91841</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7384,21 +7384,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7408,10 +7408,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>569164</v>
+        <v>569463</v>
       </c>
       <c r="R69" t="n">
-        <v>6949559</v>
+        <v>6949711</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7470,32 +7470,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129034639</v>
+        <v>129034584</v>
       </c>
       <c r="B70" t="n">
-        <v>92822</v>
+        <v>57724</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7505,10 +7505,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>569398</v>
+        <v>569221</v>
       </c>
       <c r="R70" t="n">
-        <v>6949741</v>
+        <v>6949499</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7545,7 +7545,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>6 äldre exemplar och 1 färsk fruktkropp</t>
+          <t>Förbiflygande från träd till träd</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7572,32 +7572,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129035060</v>
+        <v>129035018</v>
       </c>
       <c r="B71" t="n">
-        <v>92822</v>
+        <v>57727</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7607,10 +7607,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>569208</v>
+        <v>569111</v>
       </c>
       <c r="R71" t="n">
-        <v>6949415</v>
+        <v>6949604</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7647,7 +7647,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>20 ex minst</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7674,32 +7674,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129034584</v>
+        <v>129035037</v>
       </c>
       <c r="B72" t="n">
-        <v>57724</v>
+        <v>98710</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7709,10 +7709,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>569221</v>
+        <v>569434</v>
       </c>
       <c r="R72" t="n">
-        <v>6949499</v>
+        <v>6949706</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7749,7 +7749,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Förbiflygande från träd till träd</t>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7776,32 +7776,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129035018</v>
+        <v>129035060</v>
       </c>
       <c r="B73" t="n">
-        <v>57727</v>
+        <v>92825</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7811,10 +7811,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>569111</v>
+        <v>569208</v>
       </c>
       <c r="R73" t="n">
-        <v>6949604</v>
+        <v>6949415</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>20 ex minst</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7878,32 +7878,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129035037</v>
+        <v>129034639</v>
       </c>
       <c r="B74" t="n">
-        <v>98706</v>
+        <v>92825</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7913,10 +7913,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>569434</v>
+        <v>569398</v>
       </c>
       <c r="R74" t="n">
-        <v>6949706</v>
+        <v>6949741</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7953,7 +7953,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>20 ex</t>
+          <t>6 äldre exemplar och 1 färsk fruktkropp</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7980,32 +7980,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129034645</v>
+        <v>129034650</v>
       </c>
       <c r="B75" t="n">
-        <v>92822</v>
+        <v>98710</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8015,10 +8015,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>569196</v>
+        <v>569303</v>
       </c>
       <c r="R75" t="n">
-        <v>6949411</v>
+        <v>6949537</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8055,7 +8055,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>4 färska exemplar 3 äldre exemplar</t>
+          <t>30 stycken ( finns eventuellt mer )</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8082,32 +8082,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129034642</v>
+        <v>129034605</v>
       </c>
       <c r="B76" t="n">
-        <v>92822</v>
+        <v>98710</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8117,10 +8117,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>569283</v>
+        <v>569305</v>
       </c>
       <c r="R76" t="n">
-        <v>6949655</v>
+        <v>6949538</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8157,7 +8157,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>7 äldre exemplar</t>
+          <t>21 knärot</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8184,32 +8184,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129026691</v>
+        <v>129034598</v>
       </c>
       <c r="B77" t="n">
-        <v>91838</v>
+        <v>97581</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8219,10 +8219,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>569195</v>
+        <v>569460</v>
       </c>
       <c r="R77" t="n">
-        <v>6949487</v>
+        <v>6949629</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8281,10 +8281,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129034598</v>
+        <v>129034645</v>
       </c>
       <c r="B78" t="n">
-        <v>97577</v>
+        <v>92825</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8292,21 +8292,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8316,10 +8316,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>569460</v>
+        <v>569196</v>
       </c>
       <c r="R78" t="n">
-        <v>6949629</v>
+        <v>6949411</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8352,6 +8352,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>4 färska exemplar 3 äldre exemplar</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8378,32 +8383,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129034650</v>
+        <v>129034642</v>
       </c>
       <c r="B79" t="n">
-        <v>98706</v>
+        <v>92825</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8413,10 +8418,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>569303</v>
+        <v>569283</v>
       </c>
       <c r="R79" t="n">
-        <v>6949537</v>
+        <v>6949655</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8453,7 +8458,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>30 stycken ( finns eventuellt mer )</t>
+          <t>7 äldre exemplar</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8480,32 +8485,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129034605</v>
+        <v>129026691</v>
       </c>
       <c r="B80" t="n">
-        <v>98706</v>
+        <v>91841</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8515,10 +8520,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>569305</v>
+        <v>569195</v>
       </c>
       <c r="R80" t="n">
-        <v>6949538</v>
+        <v>6949487</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8551,11 +8556,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>21 knärot</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8582,32 +8582,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129034640</v>
+        <v>129035057</v>
       </c>
       <c r="B81" t="n">
-        <v>92822</v>
+        <v>79043</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8617,10 +8617,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>569213</v>
+        <v>569464</v>
       </c>
       <c r="R81" t="n">
-        <v>6949414</v>
+        <v>6949648</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8653,11 +8653,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>16 exemplar</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8684,32 +8679,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129035007</v>
+        <v>129035061</v>
       </c>
       <c r="B82" t="n">
-        <v>91540</v>
+        <v>96829</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>2869</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8719,10 +8714,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>569225</v>
+        <v>569333</v>
       </c>
       <c r="R82" t="n">
-        <v>6949424</v>
+        <v>6949607</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8781,10 +8776,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129035057</v>
+        <v>129035007</v>
       </c>
       <c r="B83" t="n">
-        <v>79041</v>
+        <v>91543</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8792,21 +8787,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8816,10 +8811,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>569464</v>
+        <v>569225</v>
       </c>
       <c r="R83" t="n">
-        <v>6949648</v>
+        <v>6949424</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8878,32 +8873,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129035012</v>
+        <v>129035047</v>
       </c>
       <c r="B84" t="n">
-        <v>57727</v>
+        <v>98710</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8913,10 +8908,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>569435</v>
+        <v>569162</v>
       </c>
       <c r="R84" t="n">
-        <v>6949783</v>
+        <v>6949566</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8953,7 +8948,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8980,32 +8975,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129035061</v>
+        <v>129034604</v>
       </c>
       <c r="B85" t="n">
-        <v>96825</v>
+        <v>98710</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9015,10 +9010,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>569333</v>
+        <v>569303</v>
       </c>
       <c r="R85" t="n">
-        <v>6949607</v>
+        <v>6949536</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9051,6 +9046,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9077,32 +9077,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129035001</v>
+        <v>129034618</v>
       </c>
       <c r="B86" t="n">
-        <v>91504</v>
+        <v>98710</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9112,10 +9112,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>569232</v>
+        <v>569235</v>
       </c>
       <c r="R86" t="n">
-        <v>6949444</v>
+        <v>6949411</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9148,6 +9148,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9174,32 +9179,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129035047</v>
+        <v>129035001</v>
       </c>
       <c r="B87" t="n">
-        <v>98706</v>
+        <v>91507</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9209,10 +9214,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>569162</v>
+        <v>569232</v>
       </c>
       <c r="R87" t="n">
-        <v>6949566</v>
+        <v>6949444</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9245,11 +9250,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>50 ex</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9276,32 +9276,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129034604</v>
+        <v>129034640</v>
       </c>
       <c r="B88" t="n">
-        <v>98706</v>
+        <v>92825</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9311,10 +9311,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>569303</v>
+        <v>569213</v>
       </c>
       <c r="R88" t="n">
-        <v>6949536</v>
+        <v>6949414</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9351,7 +9351,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>40 stycken</t>
+          <t>16 exemplar</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9378,32 +9378,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129034618</v>
+        <v>129035012</v>
       </c>
       <c r="B89" t="n">
-        <v>98706</v>
+        <v>57727</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9413,10 +9413,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>569235</v>
+        <v>569435</v>
       </c>
       <c r="R89" t="n">
-        <v>6949411</v>
+        <v>6949783</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9453,7 +9453,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>18 stycken</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9480,32 +9480,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129035023</v>
+        <v>129035038</v>
       </c>
       <c r="B90" t="n">
-        <v>91838</v>
+        <v>98710</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>569415</v>
+        <v>569406</v>
       </c>
       <c r="R90" t="n">
-        <v>6949677</v>
+        <v>6949664</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9551,6 +9551,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9577,32 +9582,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129035027</v>
+        <v>129035050</v>
       </c>
       <c r="B91" t="n">
-        <v>91838</v>
+        <v>98710</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9612,10 +9617,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>569169</v>
+        <v>569236</v>
       </c>
       <c r="R91" t="n">
-        <v>6949533</v>
+        <v>6949440</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9648,6 +9653,11 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>4 ex</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9674,32 +9684,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129034589</v>
+        <v>129034621</v>
       </c>
       <c r="B92" t="n">
-        <v>91838</v>
+        <v>98710</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9709,10 +9719,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>569365</v>
+        <v>569247</v>
       </c>
       <c r="R92" t="n">
-        <v>6949661</v>
+        <v>6949434</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9745,6 +9755,11 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>10 stycken knärot</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9771,32 +9786,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129035038</v>
+        <v>129035023</v>
       </c>
       <c r="B93" t="n">
-        <v>98706</v>
+        <v>91841</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9806,10 +9821,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>569406</v>
+        <v>569415</v>
       </c>
       <c r="R93" t="n">
-        <v>6949664</v>
+        <v>6949677</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9842,11 +9857,6 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>20 ex</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9873,32 +9883,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129035050</v>
+        <v>129035027</v>
       </c>
       <c r="B94" t="n">
-        <v>98706</v>
+        <v>91841</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9908,10 +9918,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>569236</v>
+        <v>569169</v>
       </c>
       <c r="R94" t="n">
-        <v>6949440</v>
+        <v>6949533</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9944,11 +9954,6 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>4 ex</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -9975,32 +9980,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129034621</v>
+        <v>129034589</v>
       </c>
       <c r="B95" t="n">
-        <v>98706</v>
+        <v>91841</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10010,10 +10015,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>569247</v>
+        <v>569365</v>
       </c>
       <c r="R95" t="n">
-        <v>6949434</v>
+        <v>6949661</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10046,11 +10051,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>10 stycken knärot</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10080,7 +10080,7 @@
         <v>129035029</v>
       </c>
       <c r="B96" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10174,32 +10174,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129034609</v>
+        <v>129034635</v>
       </c>
       <c r="B97" t="n">
-        <v>98706</v>
+        <v>79043</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10209,10 +10209,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>569458</v>
+        <v>569427</v>
       </c>
       <c r="R97" t="n">
-        <v>6949777</v>
+        <v>6949726</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10245,11 +10245,6 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>48 stycken</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10276,32 +10271,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129035036</v>
+        <v>129035017</v>
       </c>
       <c r="B98" t="n">
-        <v>98706</v>
+        <v>57727</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10311,10 +10306,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>569330</v>
+        <v>569192</v>
       </c>
       <c r="R98" t="n">
-        <v>6949564</v>
+        <v>6949518</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10351,7 +10346,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>8 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10378,10 +10373,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129034635</v>
+        <v>129035010</v>
       </c>
       <c r="B99" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10389,21 +10384,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10413,10 +10408,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>569427</v>
+        <v>569465</v>
       </c>
       <c r="R99" t="n">
-        <v>6949726</v>
+        <v>6949606</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10449,6 +10444,11 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10475,32 +10475,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129035010</v>
+        <v>129034609</v>
       </c>
       <c r="B100" t="n">
-        <v>57727</v>
+        <v>98710</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10510,10 +10510,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>569465</v>
+        <v>569458</v>
       </c>
       <c r="R100" t="n">
-        <v>6949606</v>
+        <v>6949777</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10550,7 +10550,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>48 stycken</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10577,32 +10577,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129035017</v>
+        <v>129035036</v>
       </c>
       <c r="B101" t="n">
-        <v>57727</v>
+        <v>98710</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10612,10 +10612,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>569192</v>
+        <v>569330</v>
       </c>
       <c r="R101" t="n">
-        <v>6949518</v>
+        <v>6949564</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10652,7 +10652,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>8 ex</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10682,7 +10682,7 @@
         <v>129035052</v>
       </c>
       <c r="B102" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10784,7 +10784,7 @@
         <v>129035056</v>
       </c>
       <c r="B103" t="n">
-        <v>105770</v>
+        <v>105774</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10878,10 +10878,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129027886</v>
+        <v>129035006</v>
       </c>
       <c r="B104" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10913,10 +10913,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>569305</v>
+        <v>569217</v>
       </c>
       <c r="R104" t="n">
-        <v>6949566</v>
+        <v>6949470</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10975,10 +10975,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129035006</v>
+        <v>129027886</v>
       </c>
       <c r="B105" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11010,10 +11010,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>569217</v>
+        <v>569305</v>
       </c>
       <c r="R105" t="n">
-        <v>6949470</v>
+        <v>6949566</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11072,32 +11072,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129035026</v>
+        <v>129035048</v>
       </c>
       <c r="B106" t="n">
-        <v>91838</v>
+        <v>98710</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11107,10 +11107,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>569175</v>
+        <v>569176</v>
       </c>
       <c r="R106" t="n">
-        <v>6949549</v>
+        <v>6949507</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11143,6 +11143,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>30 ex</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11169,10 +11174,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129035048</v>
+        <v>129035053</v>
       </c>
       <c r="B107" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11204,10 +11209,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>569176</v>
+        <v>569459</v>
       </c>
       <c r="R107" t="n">
-        <v>6949507</v>
+        <v>6949662</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11244,7 +11249,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>30 ex</t>
+          <t>14 ex</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11271,10 +11276,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129035053</v>
+        <v>129035049</v>
       </c>
       <c r="B108" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11306,10 +11311,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>569459</v>
+        <v>569219</v>
       </c>
       <c r="R108" t="n">
-        <v>6949662</v>
+        <v>6949489</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11346,7 +11351,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>14 ex</t>
+          <t>35 ex</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11373,10 +11378,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129035049</v>
+        <v>129035044</v>
       </c>
       <c r="B109" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11408,10 +11413,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>569219</v>
+        <v>569191</v>
       </c>
       <c r="R109" t="n">
-        <v>6949489</v>
+        <v>6949579</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11448,7 +11453,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>35 ex</t>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11475,32 +11480,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129035044</v>
+        <v>129035026</v>
       </c>
       <c r="B110" t="n">
-        <v>98706</v>
+        <v>91841</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11510,10 +11515,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>569191</v>
+        <v>569175</v>
       </c>
       <c r="R110" t="n">
-        <v>6949579</v>
+        <v>6949549</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11546,11 +11551,6 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>50 ex</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11580,7 +11580,7 @@
         <v>129035033</v>
       </c>
       <c r="B111" t="n">
-        <v>91753</v>
+        <v>91756</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11677,7 +11677,7 @@
         <v>129035032</v>
       </c>
       <c r="B112" t="n">
-        <v>91753</v>
+        <v>91756</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>

--- a/artfynd/A 45833-2025 artfynd.xlsx
+++ b/artfynd/A 45833-2025 artfynd.xlsx
@@ -1583,32 +1583,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129035055</v>
+        <v>129034630</v>
       </c>
       <c r="B11" t="n">
-        <v>98710</v>
+        <v>79043</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>569221</v>
+        <v>569231</v>
       </c>
       <c r="R11" t="n">
-        <v>6949406</v>
+        <v>6949559</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1654,11 +1654,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>25 ex</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1685,32 +1680,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129035042</v>
+        <v>129034648</v>
       </c>
       <c r="B12" t="n">
-        <v>98710</v>
+        <v>96829</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1720,10 +1715,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569200</v>
+        <v>569279</v>
       </c>
       <c r="R12" t="n">
-        <v>6949533</v>
+        <v>6949401</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1756,11 +1751,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>30 ex</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1787,10 +1777,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129034630</v>
+        <v>129034594</v>
       </c>
       <c r="B13" t="n">
-        <v>79043</v>
+        <v>91841</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1798,21 +1788,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1822,10 +1812,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569231</v>
+        <v>569203</v>
       </c>
       <c r="R13" t="n">
-        <v>6949559</v>
+        <v>6949498</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1858,6 +1848,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>11 exemplar</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1884,32 +1879,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129034648</v>
+        <v>129034577</v>
       </c>
       <c r="B14" t="n">
-        <v>96829</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1919,10 +1914,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569279</v>
+        <v>569496</v>
       </c>
       <c r="R14" t="n">
-        <v>6949401</v>
+        <v>6949627</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1955,6 +1950,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1981,32 +1981,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129034594</v>
+        <v>129035055</v>
       </c>
       <c r="B15" t="n">
-        <v>91841</v>
+        <v>98710</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2016,10 +2016,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>569203</v>
+        <v>569221</v>
       </c>
       <c r="R15" t="n">
-        <v>6949498</v>
+        <v>6949406</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>11 exemplar</t>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2083,32 +2083,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129034577</v>
+        <v>129035042</v>
       </c>
       <c r="B16" t="n">
-        <v>57727</v>
+        <v>98710</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>569496</v>
+        <v>569200</v>
       </c>
       <c r="R16" t="n">
-        <v>6949627</v>
+        <v>6949533</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på tall</t>
+          <t>30 ex</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -4073,32 +4073,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129034602</v>
+        <v>129034634</v>
       </c>
       <c r="B36" t="n">
-        <v>98710</v>
+        <v>79043</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4108,10 +4108,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>569301</v>
+        <v>569200</v>
       </c>
       <c r="R36" t="n">
-        <v>6949480</v>
+        <v>6949411</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4144,11 +4144,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>22 stycken</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4175,32 +4170,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129035040</v>
+        <v>129035020</v>
       </c>
       <c r="B37" t="n">
-        <v>98710</v>
+        <v>57727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4210,10 +4205,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>569386</v>
+        <v>569171</v>
       </c>
       <c r="R37" t="n">
-        <v>6949657</v>
+        <v>6949543</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4250,7 +4245,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>9 ex</t>
+          <t>Äldre ringhack på granhögstubbe</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4277,32 +4272,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129035045</v>
+        <v>129035015</v>
       </c>
       <c r="B38" t="n">
-        <v>98710</v>
+        <v>57727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4312,10 +4307,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>569130</v>
+        <v>569454</v>
       </c>
       <c r="R38" t="n">
-        <v>6949603</v>
+        <v>6949698</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4352,7 +4347,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>14 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4379,32 +4374,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129034634</v>
+        <v>129034602</v>
       </c>
       <c r="B39" t="n">
-        <v>79043</v>
+        <v>98710</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4414,10 +4409,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>569200</v>
+        <v>569301</v>
       </c>
       <c r="R39" t="n">
-        <v>6949411</v>
+        <v>6949480</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4450,6 +4445,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>22 stycken</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4476,32 +4476,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129035020</v>
+        <v>129035040</v>
       </c>
       <c r="B40" t="n">
-        <v>57727</v>
+        <v>98710</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4511,10 +4511,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>569171</v>
+        <v>569386</v>
       </c>
       <c r="R40" t="n">
-        <v>6949543</v>
+        <v>6949657</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4551,7 +4551,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Äldre ringhack på granhögstubbe</t>
+          <t>9 ex</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4578,32 +4578,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129035015</v>
+        <v>129035045</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>98710</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4613,10 +4613,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>569454</v>
+        <v>569130</v>
       </c>
       <c r="R41" t="n">
-        <v>6949698</v>
+        <v>6949603</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4653,7 +4653,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>14 ex</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5675,32 +5675,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129034616</v>
+        <v>129034597</v>
       </c>
       <c r="B52" t="n">
-        <v>98710</v>
+        <v>91841</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5710,10 +5710,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>569223</v>
+        <v>569221</v>
       </c>
       <c r="R52" t="n">
-        <v>6949465</v>
+        <v>6949499</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>10 stycken</t>
+          <t>8 exemplar</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5777,32 +5777,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129034597</v>
+        <v>129034616</v>
       </c>
       <c r="B53" t="n">
-        <v>91841</v>
+        <v>98710</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>569221</v>
+        <v>569223</v>
       </c>
       <c r="R53" t="n">
-        <v>6949499</v>
+        <v>6949465</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5852,7 +5852,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>8 exemplar</t>
+          <t>10 stycken</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6583,32 +6583,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129034586</v>
+        <v>129035024</v>
       </c>
       <c r="B61" t="n">
-        <v>91996</v>
+        <v>91841</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6618,10 +6618,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>569220</v>
+        <v>569404</v>
       </c>
       <c r="R61" t="n">
-        <v>6949500</v>
+        <v>6949660</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6680,32 +6680,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129035024</v>
+        <v>129034586</v>
       </c>
       <c r="B62" t="n">
-        <v>91841</v>
+        <v>91996</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6715,10 +6715,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>569404</v>
+        <v>569220</v>
       </c>
       <c r="R62" t="n">
-        <v>6949660</v>
+        <v>6949500</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7572,32 +7572,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129035018</v>
+        <v>129035060</v>
       </c>
       <c r="B71" t="n">
-        <v>57727</v>
+        <v>92825</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7607,10 +7607,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>569111</v>
+        <v>569208</v>
       </c>
       <c r="R71" t="n">
-        <v>6949604</v>
+        <v>6949415</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7647,7 +7647,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>20 ex minst</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7674,32 +7674,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129035037</v>
+        <v>129034639</v>
       </c>
       <c r="B72" t="n">
-        <v>98710</v>
+        <v>92825</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7709,10 +7709,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>569434</v>
+        <v>569398</v>
       </c>
       <c r="R72" t="n">
-        <v>6949706</v>
+        <v>6949741</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7749,7 +7749,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>20 ex</t>
+          <t>6 äldre exemplar och 1 färsk fruktkropp</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7776,32 +7776,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129035060</v>
+        <v>129035018</v>
       </c>
       <c r="B73" t="n">
-        <v>92825</v>
+        <v>57727</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7811,10 +7811,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>569208</v>
+        <v>569111</v>
       </c>
       <c r="R73" t="n">
-        <v>6949415</v>
+        <v>6949604</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>20 ex minst</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7878,32 +7878,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129034639</v>
+        <v>129035037</v>
       </c>
       <c r="B74" t="n">
-        <v>92825</v>
+        <v>98710</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7913,10 +7913,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>569398</v>
+        <v>569434</v>
       </c>
       <c r="R74" t="n">
-        <v>6949741</v>
+        <v>6949706</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7953,7 +7953,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>6 äldre exemplar och 1 färsk fruktkropp</t>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7980,32 +7980,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129034650</v>
+        <v>129034645</v>
       </c>
       <c r="B75" t="n">
-        <v>98710</v>
+        <v>92825</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8015,10 +8015,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>569303</v>
+        <v>569196</v>
       </c>
       <c r="R75" t="n">
-        <v>6949537</v>
+        <v>6949411</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8055,7 +8055,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>30 stycken ( finns eventuellt mer )</t>
+          <t>4 färska exemplar 3 äldre exemplar</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8082,32 +8082,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129034605</v>
+        <v>129034642</v>
       </c>
       <c r="B76" t="n">
-        <v>98710</v>
+        <v>92825</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8117,10 +8117,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>569305</v>
+        <v>569283</v>
       </c>
       <c r="R76" t="n">
-        <v>6949538</v>
+        <v>6949655</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8157,7 +8157,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>21 knärot</t>
+          <t>7 äldre exemplar</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8281,32 +8281,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129034645</v>
+        <v>129026691</v>
       </c>
       <c r="B78" t="n">
-        <v>92825</v>
+        <v>91841</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8316,10 +8316,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>569196</v>
+        <v>569195</v>
       </c>
       <c r="R78" t="n">
-        <v>6949411</v>
+        <v>6949487</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8352,11 +8352,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>4 färska exemplar 3 äldre exemplar</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8383,32 +8378,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129034642</v>
+        <v>129034650</v>
       </c>
       <c r="B79" t="n">
-        <v>92825</v>
+        <v>98710</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8418,10 +8413,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>569283</v>
+        <v>569303</v>
       </c>
       <c r="R79" t="n">
-        <v>6949655</v>
+        <v>6949537</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8458,7 +8453,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>7 äldre exemplar</t>
+          <t>30 stycken ( finns eventuellt mer )</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8485,32 +8480,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129026691</v>
+        <v>129034605</v>
       </c>
       <c r="B80" t="n">
-        <v>91841</v>
+        <v>98710</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8520,10 +8515,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>569195</v>
+        <v>569305</v>
       </c>
       <c r="R80" t="n">
-        <v>6949487</v>
+        <v>6949538</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8556,6 +8551,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>21 knärot</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8679,32 +8679,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129035061</v>
+        <v>129035007</v>
       </c>
       <c r="B82" t="n">
-        <v>96829</v>
+        <v>91543</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2869</v>
+        <v>1202</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8714,10 +8714,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>569333</v>
+        <v>569225</v>
       </c>
       <c r="R82" t="n">
-        <v>6949607</v>
+        <v>6949424</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8776,32 +8776,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129035007</v>
+        <v>129035001</v>
       </c>
       <c r="B83" t="n">
-        <v>91543</v>
+        <v>91507</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8811,10 +8811,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>569225</v>
+        <v>569232</v>
       </c>
       <c r="R83" t="n">
-        <v>6949424</v>
+        <v>6949444</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8873,32 +8873,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129035047</v>
+        <v>129034640</v>
       </c>
       <c r="B84" t="n">
-        <v>98710</v>
+        <v>92825</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8908,10 +8908,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>569162</v>
+        <v>569213</v>
       </c>
       <c r="R84" t="n">
-        <v>6949566</v>
+        <v>6949414</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8948,7 +8948,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>50 ex</t>
+          <t>16 exemplar</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8975,32 +8975,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129034604</v>
+        <v>129035012</v>
       </c>
       <c r="B85" t="n">
-        <v>98710</v>
+        <v>57727</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9010,10 +9010,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>569303</v>
+        <v>569435</v>
       </c>
       <c r="R85" t="n">
-        <v>6949536</v>
+        <v>6949783</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9050,7 +9050,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>40 stycken</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9077,32 +9077,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129034618</v>
+        <v>129035061</v>
       </c>
       <c r="B86" t="n">
-        <v>98710</v>
+        <v>96829</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9112,10 +9112,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>569235</v>
+        <v>569333</v>
       </c>
       <c r="R86" t="n">
-        <v>6949411</v>
+        <v>6949607</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9148,11 +9148,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9179,32 +9174,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129035001</v>
+        <v>129035047</v>
       </c>
       <c r="B87" t="n">
-        <v>91507</v>
+        <v>98710</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9214,10 +9209,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>569232</v>
+        <v>569162</v>
       </c>
       <c r="R87" t="n">
-        <v>6949444</v>
+        <v>6949566</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9250,6 +9245,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9276,32 +9276,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129034640</v>
+        <v>129034604</v>
       </c>
       <c r="B88" t="n">
-        <v>92825</v>
+        <v>98710</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9311,10 +9311,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>569213</v>
+        <v>569303</v>
       </c>
       <c r="R88" t="n">
-        <v>6949414</v>
+        <v>6949536</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9351,7 +9351,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>16 exemplar</t>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9378,32 +9378,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129035012</v>
+        <v>129034618</v>
       </c>
       <c r="B89" t="n">
-        <v>57727</v>
+        <v>98710</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9413,10 +9413,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>569435</v>
+        <v>569235</v>
       </c>
       <c r="R89" t="n">
-        <v>6949783</v>
+        <v>6949411</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9453,7 +9453,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9480,32 +9480,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129035038</v>
+        <v>129035023</v>
       </c>
       <c r="B90" t="n">
-        <v>98710</v>
+        <v>91841</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>569406</v>
+        <v>569415</v>
       </c>
       <c r="R90" t="n">
-        <v>6949664</v>
+        <v>6949677</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9551,11 +9551,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>20 ex</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9582,32 +9577,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129035050</v>
+        <v>129035027</v>
       </c>
       <c r="B91" t="n">
-        <v>98710</v>
+        <v>91841</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9617,10 +9612,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>569236</v>
+        <v>569169</v>
       </c>
       <c r="R91" t="n">
-        <v>6949440</v>
+        <v>6949533</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9653,11 +9648,6 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>4 ex</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9684,32 +9674,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129034621</v>
+        <v>129035029</v>
       </c>
       <c r="B92" t="n">
-        <v>98710</v>
+        <v>91841</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9719,10 +9709,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>569247</v>
+        <v>569217</v>
       </c>
       <c r="R92" t="n">
-        <v>6949434</v>
+        <v>6949427</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9755,11 +9745,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>10 stycken knärot</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9786,7 +9771,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129035023</v>
+        <v>129034589</v>
       </c>
       <c r="B93" t="n">
         <v>91841</v>
@@ -9821,10 +9806,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>569415</v>
+        <v>569365</v>
       </c>
       <c r="R93" t="n">
-        <v>6949677</v>
+        <v>6949661</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9883,32 +9868,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129035027</v>
+        <v>129035038</v>
       </c>
       <c r="B94" t="n">
-        <v>91841</v>
+        <v>98710</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9918,10 +9903,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>569169</v>
+        <v>569406</v>
       </c>
       <c r="R94" t="n">
-        <v>6949533</v>
+        <v>6949664</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9954,6 +9939,11 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -9980,32 +9970,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129034589</v>
+        <v>129035050</v>
       </c>
       <c r="B95" t="n">
-        <v>91841</v>
+        <v>98710</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10015,10 +10005,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>569365</v>
+        <v>569236</v>
       </c>
       <c r="R95" t="n">
-        <v>6949661</v>
+        <v>6949440</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10051,6 +10041,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>4 ex</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10077,32 +10072,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129035029</v>
+        <v>129034621</v>
       </c>
       <c r="B96" t="n">
-        <v>91841</v>
+        <v>98710</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10112,10 +10107,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>569217</v>
+        <v>569247</v>
       </c>
       <c r="R96" t="n">
-        <v>6949427</v>
+        <v>6949434</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10148,6 +10143,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>10 stycken knärot</t>
         </is>
       </c>
       <c r="AD96" t="b">

--- a/artfynd/A 45833-2025 artfynd.xlsx
+++ b/artfynd/A 45833-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129034627</v>
+        <v>129034612</v>
       </c>
       <c r="B2" t="n">
-        <v>79043</v>
+        <v>98712</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569482</v>
+        <v>569243</v>
       </c>
       <c r="R2" t="n">
-        <v>6949676</v>
+        <v>6949558</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>30  exemplar ca</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129034612</v>
+        <v>129035046</v>
       </c>
       <c r="B3" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569243</v>
+        <v>569127</v>
       </c>
       <c r="R3" t="n">
-        <v>6949558</v>
+        <v>6949602</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>30  exemplar ca</t>
+          <t>13 ex</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129035046</v>
+        <v>129035043</v>
       </c>
       <c r="B4" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -909,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569127</v>
+        <v>569204</v>
       </c>
       <c r="R4" t="n">
-        <v>6949602</v>
+        <v>6949533</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,7 +954,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>13 ex</t>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,32 +981,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129035043</v>
+        <v>129034627</v>
       </c>
       <c r="B5" t="n">
-        <v>98710</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569204</v>
+        <v>569482</v>
       </c>
       <c r="R5" t="n">
-        <v>6949533</v>
+        <v>6949676</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1047,11 +1052,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>10 ex</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1078,32 +1078,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129035030</v>
+        <v>129035039</v>
       </c>
       <c r="B6" t="n">
-        <v>97581</v>
+        <v>98712</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>569424</v>
+        <v>569394</v>
       </c>
       <c r="R6" t="n">
-        <v>6949671</v>
+        <v>6949664</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1149,6 +1149,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1175,32 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129035039</v>
+        <v>129035030</v>
       </c>
       <c r="B7" t="n">
-        <v>98710</v>
+        <v>97583</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>569394</v>
+        <v>569424</v>
       </c>
       <c r="R7" t="n">
-        <v>6949664</v>
+        <v>6949671</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1246,11 +1251,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1277,32 +1277,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129035054</v>
+        <v>129035013</v>
       </c>
       <c r="B8" t="n">
-        <v>98710</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>569126</v>
+        <v>569455</v>
       </c>
       <c r="R8" t="n">
-        <v>6949570</v>
+        <v>6949716</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>13 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1379,7 +1379,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129035013</v>
+        <v>129035014</v>
       </c>
       <c r="B9" t="n">
         <v>57727</v>
@@ -1417,7 +1417,7 @@
         <v>569455</v>
       </c>
       <c r="R9" t="n">
-        <v>6949716</v>
+        <v>6949703</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1481,32 +1481,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129035014</v>
+        <v>129035054</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>98712</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>569455</v>
+        <v>569126</v>
       </c>
       <c r="R10" t="n">
-        <v>6949703</v>
+        <v>6949570</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>13 ex</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1583,32 +1583,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129034630</v>
+        <v>129034648</v>
       </c>
       <c r="B11" t="n">
-        <v>79043</v>
+        <v>96831</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>569231</v>
+        <v>569279</v>
       </c>
       <c r="R11" t="n">
-        <v>6949559</v>
+        <v>6949401</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1680,32 +1680,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129034648</v>
+        <v>129034577</v>
       </c>
       <c r="B12" t="n">
-        <v>96829</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1715,10 +1715,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569279</v>
+        <v>569496</v>
       </c>
       <c r="R12" t="n">
-        <v>6949401</v>
+        <v>6949627</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1751,6 +1751,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1777,10 +1782,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129034594</v>
+        <v>129034630</v>
       </c>
       <c r="B13" t="n">
-        <v>91841</v>
+        <v>79044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1788,21 +1793,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1812,10 +1817,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569203</v>
+        <v>569231</v>
       </c>
       <c r="R13" t="n">
-        <v>6949498</v>
+        <v>6949559</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1848,11 +1853,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>11 exemplar</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1879,10 +1879,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129034577</v>
+        <v>129034594</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>91843</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1890,21 +1890,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1914,10 +1914,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569496</v>
+        <v>569203</v>
       </c>
       <c r="R14" t="n">
-        <v>6949627</v>
+        <v>6949498</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på tall</t>
+          <t>11 exemplar</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1984,7 +1984,7 @@
         <v>129035055</v>
       </c>
       <c r="B15" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>129035042</v>
       </c>
       <c r="B16" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2185,32 +2185,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129035059</v>
+        <v>129034620</v>
       </c>
       <c r="B17" t="n">
-        <v>92825</v>
+        <v>98712</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2220,10 +2220,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>569273</v>
+        <v>569195</v>
       </c>
       <c r="R17" t="n">
-        <v>6949537</v>
+        <v>6949410</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2256,6 +2256,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Blommande knärot 1 exemplar + 21 övriga exemplar blommar ej</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2588,32 +2593,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129034629</v>
+        <v>129035059</v>
       </c>
       <c r="B21" t="n">
-        <v>79043</v>
+        <v>92827</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2623,10 +2628,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>569247</v>
+        <v>569273</v>
       </c>
       <c r="R21" t="n">
-        <v>6949558</v>
+        <v>6949537</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2685,32 +2690,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129034620</v>
+        <v>129034629</v>
       </c>
       <c r="B22" t="n">
-        <v>98710</v>
+        <v>79044</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2720,10 +2725,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>569195</v>
+        <v>569247</v>
       </c>
       <c r="R22" t="n">
-        <v>6949410</v>
+        <v>6949558</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2756,11 +2761,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Blommande knärot 1 exemplar + 21 övriga exemplar blommar ej</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2787,10 +2787,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129035004</v>
+        <v>129034625</v>
       </c>
       <c r="B23" t="n">
-        <v>91543</v>
+        <v>79044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2798,21 +2798,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569152</v>
+        <v>569479</v>
       </c>
       <c r="R23" t="n">
-        <v>6949557</v>
+        <v>6949657</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2887,7 +2887,7 @@
         <v>129035005</v>
       </c>
       <c r="B24" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2981,32 +2981,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129034623</v>
+        <v>129035004</v>
       </c>
       <c r="B25" t="n">
-        <v>98710</v>
+        <v>91545</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3016,10 +3016,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569253</v>
+        <v>569152</v>
       </c>
       <c r="R25" t="n">
-        <v>6949425</v>
+        <v>6949557</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3052,11 +3052,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>74 stycken</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3083,10 +3078,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129034625</v>
+        <v>129034592</v>
       </c>
       <c r="B26" t="n">
-        <v>79043</v>
+        <v>91843</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3094,21 +3089,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3118,10 +3113,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569479</v>
+        <v>569205</v>
       </c>
       <c r="R26" t="n">
-        <v>6949657</v>
+        <v>6949497</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3154,6 +3149,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>1 x</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3180,10 +3180,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129034592</v>
+        <v>129034591</v>
       </c>
       <c r="B27" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3215,10 +3215,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>569205</v>
+        <v>569203</v>
       </c>
       <c r="R27" t="n">
-        <v>6949497</v>
+        <v>6949513</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3255,7 +3255,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>1 x</t>
+          <t>11 ex</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3282,10 +3282,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129034591</v>
+        <v>129034647</v>
       </c>
       <c r="B28" t="n">
-        <v>91841</v>
+        <v>88945</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3293,21 +3293,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3317,10 +3317,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>569203</v>
+        <v>569247</v>
       </c>
       <c r="R28" t="n">
-        <v>6949513</v>
+        <v>6949558</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3353,11 +3353,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>11 ex</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3384,10 +3379,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129034647</v>
+        <v>129035025</v>
       </c>
       <c r="B29" t="n">
-        <v>88943</v>
+        <v>91843</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3395,21 +3390,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3419,10 +3414,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>569247</v>
+        <v>569388</v>
       </c>
       <c r="R29" t="n">
-        <v>6949558</v>
+        <v>6949665</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3481,32 +3476,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129035025</v>
+        <v>129034623</v>
       </c>
       <c r="B30" t="n">
-        <v>91841</v>
+        <v>98712</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3516,10 +3511,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>569388</v>
+        <v>569253</v>
       </c>
       <c r="R30" t="n">
-        <v>6949665</v>
+        <v>6949425</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3552,6 +3547,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>74 stycken</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3581,7 +3581,7 @@
         <v>129034637</v>
       </c>
       <c r="B31" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3675,10 +3675,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129035031</v>
+        <v>129035058</v>
       </c>
       <c r="B32" t="n">
-        <v>80148</v>
+        <v>79044</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3686,21 +3686,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3710,10 +3710,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>569125</v>
+        <v>569388</v>
       </c>
       <c r="R32" t="n">
-        <v>6949570</v>
+        <v>6949647</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3772,10 +3772,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129034578</v>
+        <v>129035031</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3783,21 +3783,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3807,10 +3807,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>569420</v>
+        <v>569125</v>
       </c>
       <c r="R33" t="n">
-        <v>6949723</v>
+        <v>6949570</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3843,11 +3843,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3874,10 +3869,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129035058</v>
+        <v>129034578</v>
       </c>
       <c r="B34" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3885,21 +3880,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3909,10 +3904,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>569388</v>
+        <v>569420</v>
       </c>
       <c r="R34" t="n">
-        <v>6949647</v>
+        <v>6949723</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3945,6 +3940,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3974,7 +3974,7 @@
         <v>129035051</v>
       </c>
       <c r="B35" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>129034634</v>
       </c>
       <c r="B36" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
         <v>129034602</v>
       </c>
       <c r="B39" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         <v>129035040</v>
       </c>
       <c r="B40" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4581,7 +4581,7 @@
         <v>129035045</v>
       </c>
       <c r="B41" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4683,7 +4683,7 @@
         <v>129035063</v>
       </c>
       <c r="B42" t="n">
-        <v>96829</v>
+        <v>96831</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>129034643</v>
       </c>
       <c r="B43" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4879,32 +4879,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129034575</v>
+        <v>129034607</v>
       </c>
       <c r="B44" t="n">
-        <v>57727</v>
+        <v>98712</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4914,10 +4914,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>569448</v>
+        <v>569317</v>
       </c>
       <c r="R44" t="n">
-        <v>6949625</v>
+        <v>6949549</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Färska ringhack på Tall av tretåig hackspett</t>
+          <t>31 stycken</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4981,32 +4981,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129035011</v>
+        <v>129035041</v>
       </c>
       <c r="B45" t="n">
-        <v>57727</v>
+        <v>98712</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5016,10 +5016,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>569442</v>
+        <v>569262</v>
       </c>
       <c r="R45" t="n">
-        <v>6949783</v>
+        <v>6949524</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5083,32 +5083,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129034607</v>
+        <v>129034575</v>
       </c>
       <c r="B46" t="n">
-        <v>98710</v>
+        <v>57727</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5118,10 +5118,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>569317</v>
+        <v>569448</v>
       </c>
       <c r="R46" t="n">
-        <v>6949549</v>
+        <v>6949625</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>31 stycken</t>
+          <t>Färska ringhack på Tall av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5185,32 +5185,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129035041</v>
+        <v>129035011</v>
       </c>
       <c r="B47" t="n">
-        <v>98710</v>
+        <v>57727</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5220,10 +5220,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>569262</v>
+        <v>569442</v>
       </c>
       <c r="R47" t="n">
-        <v>6949524</v>
+        <v>6949783</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5260,7 +5260,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>5 ex</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5287,10 +5287,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129034632</v>
+        <v>129035016</v>
       </c>
       <c r="B48" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5298,21 +5298,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5322,10 +5322,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>569237</v>
+        <v>569435</v>
       </c>
       <c r="R48" t="n">
-        <v>6949442</v>
+        <v>6949665</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5358,6 +5358,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5384,32 +5389,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129035062</v>
+        <v>129034632</v>
       </c>
       <c r="B49" t="n">
-        <v>96829</v>
+        <v>79044</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5419,10 +5424,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>569478</v>
+        <v>569237</v>
       </c>
       <c r="R49" t="n">
-        <v>6949666</v>
+        <v>6949442</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5481,32 +5486,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129035002</v>
+        <v>129035062</v>
       </c>
       <c r="B50" t="n">
-        <v>91543</v>
+        <v>96831</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>2869</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5516,10 +5521,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>569405</v>
+        <v>569478</v>
       </c>
       <c r="R50" t="n">
-        <v>6949685</v>
+        <v>6949666</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5578,10 +5583,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129035022</v>
+        <v>129035002</v>
       </c>
       <c r="B51" t="n">
-        <v>91841</v>
+        <v>91545</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5589,21 +5594,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5613,10 +5618,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>569423</v>
+        <v>569405</v>
       </c>
       <c r="R51" t="n">
-        <v>6949656</v>
+        <v>6949685</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5675,10 +5680,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129034597</v>
+        <v>129035022</v>
       </c>
       <c r="B52" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5710,10 +5715,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>569221</v>
+        <v>569423</v>
       </c>
       <c r="R52" t="n">
-        <v>6949499</v>
+        <v>6949656</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5746,11 +5751,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>8 exemplar</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5777,32 +5777,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129034616</v>
+        <v>129034597</v>
       </c>
       <c r="B53" t="n">
-        <v>98710</v>
+        <v>91843</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>569223</v>
+        <v>569221</v>
       </c>
       <c r="R53" t="n">
-        <v>6949465</v>
+        <v>6949499</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5852,7 +5852,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>10 stycken</t>
+          <t>8 exemplar</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5879,32 +5879,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129035016</v>
+        <v>129034616</v>
       </c>
       <c r="B54" t="n">
-        <v>57727</v>
+        <v>98712</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5914,10 +5914,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>569435</v>
+        <v>569223</v>
       </c>
       <c r="R54" t="n">
-        <v>6949665</v>
+        <v>6949465</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5954,7 +5954,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>10 stycken</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5981,10 +5981,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129035028</v>
+        <v>129035008</v>
       </c>
       <c r="B55" t="n">
-        <v>91841</v>
+        <v>91545</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5992,21 +5992,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6016,10 +6016,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>569192</v>
+        <v>569216</v>
       </c>
       <c r="R55" t="n">
-        <v>6949509</v>
+        <v>6949430</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6078,10 +6078,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129035008</v>
+        <v>129035028</v>
       </c>
       <c r="B56" t="n">
-        <v>91543</v>
+        <v>91843</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6089,21 +6089,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6113,10 +6113,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>569216</v>
+        <v>569192</v>
       </c>
       <c r="R56" t="n">
-        <v>6949430</v>
+        <v>6949509</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6178,7 +6178,7 @@
         <v>129034600</v>
       </c>
       <c r="B57" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
         <v>129034610</v>
       </c>
       <c r="B59" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6484,7 +6484,7 @@
         <v>129034614</v>
       </c>
       <c r="B60" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6583,32 +6583,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129035024</v>
+        <v>129034586</v>
       </c>
       <c r="B61" t="n">
-        <v>91841</v>
+        <v>91998</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6618,10 +6618,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>569404</v>
+        <v>569220</v>
       </c>
       <c r="R61" t="n">
-        <v>6949660</v>
+        <v>6949500</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6680,32 +6680,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129034586</v>
+        <v>129035024</v>
       </c>
       <c r="B62" t="n">
-        <v>91996</v>
+        <v>91843</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6715,10 +6715,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>569220</v>
+        <v>569404</v>
       </c>
       <c r="R62" t="n">
-        <v>6949500</v>
+        <v>6949660</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6777,10 +6777,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129035021</v>
+        <v>129034574</v>
       </c>
       <c r="B63" t="n">
-        <v>91841</v>
+        <v>91545</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6788,21 +6788,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6812,10 +6812,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>569446</v>
+        <v>569461</v>
       </c>
       <c r="R63" t="n">
-        <v>6949629</v>
+        <v>6949706</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6874,49 +6874,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129027791</v>
+        <v>129035003</v>
       </c>
       <c r="B64" t="n">
-        <v>98710</v>
+        <v>91545</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Sandsjömyran, Mpd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>569308</v>
+        <v>569164</v>
       </c>
       <c r="R64" t="n">
-        <v>6949546</v>
+        <v>6949559</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6975,32 +6971,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129034624</v>
+        <v>129035021</v>
       </c>
       <c r="B65" t="n">
-        <v>105774</v>
+        <v>91843</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221144</v>
+        <v>658</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7010,10 +7006,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>569234</v>
+        <v>569446</v>
       </c>
       <c r="R65" t="n">
-        <v>6949440</v>
+        <v>6949629</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7046,11 +7042,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>9 exemplar</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7077,32 +7068,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129035035</v>
+        <v>129034587</v>
       </c>
       <c r="B66" t="n">
-        <v>98710</v>
+        <v>91843</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7112,10 +7103,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>569317</v>
+        <v>569463</v>
       </c>
       <c r="R66" t="n">
-        <v>6949469</v>
+        <v>6949711</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7148,11 +7139,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>5 ex</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7179,32 +7165,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129035003</v>
+        <v>129034624</v>
       </c>
       <c r="B67" t="n">
-        <v>91543</v>
+        <v>105776</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7214,10 +7200,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>569164</v>
+        <v>569234</v>
       </c>
       <c r="R67" t="n">
-        <v>6949559</v>
+        <v>6949440</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7250,6 +7236,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>9 exemplar</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7276,32 +7267,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129034574</v>
+        <v>129035035</v>
       </c>
       <c r="B68" t="n">
-        <v>91543</v>
+        <v>98712</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7311,10 +7302,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>569461</v>
+        <v>569317</v>
       </c>
       <c r="R68" t="n">
-        <v>6949706</v>
+        <v>6949469</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7347,6 +7338,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7373,45 +7369,49 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129034587</v>
+        <v>129027791</v>
       </c>
       <c r="B69" t="n">
-        <v>91841</v>
+        <v>98712</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Sandsjömyran, Mpd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>569463</v>
+        <v>569308</v>
       </c>
       <c r="R69" t="n">
-        <v>6949711</v>
+        <v>6949546</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7470,32 +7470,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129034584</v>
+        <v>129034639</v>
       </c>
       <c r="B70" t="n">
-        <v>57724</v>
+        <v>92827</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7505,10 +7505,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>569221</v>
+        <v>569398</v>
       </c>
       <c r="R70" t="n">
-        <v>6949499</v>
+        <v>6949741</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7545,7 +7545,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Förbiflygande från träd till träd</t>
+          <t>6 äldre exemplar och 1 färsk fruktkropp</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7575,7 +7575,7 @@
         <v>129035060</v>
       </c>
       <c r="B71" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7674,32 +7674,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129034639</v>
+        <v>129034584</v>
       </c>
       <c r="B72" t="n">
-        <v>92825</v>
+        <v>57724</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7709,10 +7709,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>569398</v>
+        <v>569221</v>
       </c>
       <c r="R72" t="n">
-        <v>6949741</v>
+        <v>6949499</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7749,7 +7749,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>6 äldre exemplar och 1 färsk fruktkropp</t>
+          <t>Förbiflygande från träd till träd</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7881,7 +7881,7 @@
         <v>129035037</v>
       </c>
       <c r="B74" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7980,32 +7980,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129034645</v>
+        <v>129034650</v>
       </c>
       <c r="B75" t="n">
-        <v>92825</v>
+        <v>98712</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8015,10 +8015,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>569196</v>
+        <v>569303</v>
       </c>
       <c r="R75" t="n">
-        <v>6949411</v>
+        <v>6949537</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8055,7 +8055,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>4 färska exemplar 3 äldre exemplar</t>
+          <t>30 stycken ( finns eventuellt mer )</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8082,32 +8082,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129034642</v>
+        <v>129034605</v>
       </c>
       <c r="B76" t="n">
-        <v>92825</v>
+        <v>98712</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8117,10 +8117,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>569283</v>
+        <v>569305</v>
       </c>
       <c r="R76" t="n">
-        <v>6949655</v>
+        <v>6949538</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8157,7 +8157,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>7 äldre exemplar</t>
+          <t>21 knärot</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8184,10 +8184,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129034598</v>
+        <v>129034645</v>
       </c>
       <c r="B77" t="n">
-        <v>97581</v>
+        <v>92827</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8195,21 +8195,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8219,10 +8219,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>569460</v>
+        <v>569196</v>
       </c>
       <c r="R77" t="n">
-        <v>6949629</v>
+        <v>6949411</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8255,6 +8255,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>4 färska exemplar 3 äldre exemplar</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8281,32 +8286,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129026691</v>
+        <v>129034642</v>
       </c>
       <c r="B78" t="n">
-        <v>91841</v>
+        <v>92827</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8316,10 +8321,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>569195</v>
+        <v>569283</v>
       </c>
       <c r="R78" t="n">
-        <v>6949487</v>
+        <v>6949655</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8352,6 +8357,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>7 äldre exemplar</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8378,32 +8388,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129034650</v>
+        <v>129026691</v>
       </c>
       <c r="B79" t="n">
-        <v>98710</v>
+        <v>91843</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8413,10 +8423,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>569303</v>
+        <v>569195</v>
       </c>
       <c r="R79" t="n">
-        <v>6949537</v>
+        <v>6949487</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8449,11 +8459,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>30 stycken ( finns eventuellt mer )</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8480,32 +8485,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129034605</v>
+        <v>129034598</v>
       </c>
       <c r="B80" t="n">
-        <v>98710</v>
+        <v>97583</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8515,10 +8520,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>569305</v>
+        <v>569460</v>
       </c>
       <c r="R80" t="n">
-        <v>6949538</v>
+        <v>6949629</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8551,11 +8556,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>21 knärot</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8582,32 +8582,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129035057</v>
+        <v>129035047</v>
       </c>
       <c r="B81" t="n">
-        <v>79043</v>
+        <v>98712</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8617,10 +8617,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>569464</v>
+        <v>569162</v>
       </c>
       <c r="R81" t="n">
-        <v>6949648</v>
+        <v>6949566</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8653,6 +8653,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8679,32 +8684,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129035007</v>
+        <v>129034604</v>
       </c>
       <c r="B82" t="n">
-        <v>91543</v>
+        <v>98712</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8714,10 +8719,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>569225</v>
+        <v>569303</v>
       </c>
       <c r="R82" t="n">
-        <v>6949424</v>
+        <v>6949536</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8750,6 +8755,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8776,32 +8786,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129035001</v>
+        <v>129034618</v>
       </c>
       <c r="B83" t="n">
-        <v>91507</v>
+        <v>98712</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8811,10 +8821,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>569232</v>
+        <v>569235</v>
       </c>
       <c r="R83" t="n">
-        <v>6949444</v>
+        <v>6949411</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8847,6 +8857,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8876,7 +8891,7 @@
         <v>129034640</v>
       </c>
       <c r="B84" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8975,10 +8990,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129035012</v>
+        <v>129035057</v>
       </c>
       <c r="B85" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8986,21 +9001,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9010,10 +9025,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>569435</v>
+        <v>569464</v>
       </c>
       <c r="R85" t="n">
-        <v>6949783</v>
+        <v>6949648</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9046,11 +9061,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9080,7 +9090,7 @@
         <v>129035061</v>
       </c>
       <c r="B86" t="n">
-        <v>96829</v>
+        <v>96831</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9174,32 +9184,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129035047</v>
+        <v>129035007</v>
       </c>
       <c r="B87" t="n">
-        <v>98710</v>
+        <v>91545</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9209,10 +9219,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>569162</v>
+        <v>569225</v>
       </c>
       <c r="R87" t="n">
-        <v>6949566</v>
+        <v>6949424</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9245,11 +9255,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>50 ex</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9276,32 +9281,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129034604</v>
+        <v>129035001</v>
       </c>
       <c r="B88" t="n">
-        <v>98710</v>
+        <v>91509</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9311,10 +9316,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>569303</v>
+        <v>569232</v>
       </c>
       <c r="R88" t="n">
-        <v>6949536</v>
+        <v>6949444</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9347,11 +9352,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9378,32 +9378,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129034618</v>
+        <v>129035012</v>
       </c>
       <c r="B89" t="n">
-        <v>98710</v>
+        <v>57727</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9413,10 +9413,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>569235</v>
+        <v>569435</v>
       </c>
       <c r="R89" t="n">
-        <v>6949411</v>
+        <v>6949783</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9453,7 +9453,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>18 stycken</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9480,32 +9480,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129035023</v>
+        <v>129035038</v>
       </c>
       <c r="B90" t="n">
-        <v>91841</v>
+        <v>98712</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>569415</v>
+        <v>569406</v>
       </c>
       <c r="R90" t="n">
-        <v>6949677</v>
+        <v>6949664</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9551,6 +9551,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9577,32 +9582,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129035027</v>
+        <v>129035050</v>
       </c>
       <c r="B91" t="n">
-        <v>91841</v>
+        <v>98712</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9612,10 +9617,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>569169</v>
+        <v>569236</v>
       </c>
       <c r="R91" t="n">
-        <v>6949533</v>
+        <v>6949440</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9648,6 +9653,11 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>4 ex</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9674,32 +9684,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129035029</v>
+        <v>129034621</v>
       </c>
       <c r="B92" t="n">
-        <v>91841</v>
+        <v>98712</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9709,10 +9719,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>569217</v>
+        <v>569247</v>
       </c>
       <c r="R92" t="n">
-        <v>6949427</v>
+        <v>6949434</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9745,6 +9755,11 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>10 stycken knärot</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9771,10 +9786,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129034589</v>
+        <v>129035023</v>
       </c>
       <c r="B93" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9806,10 +9821,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>569365</v>
+        <v>569415</v>
       </c>
       <c r="R93" t="n">
-        <v>6949661</v>
+        <v>6949677</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9868,32 +9883,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129035038</v>
+        <v>129034589</v>
       </c>
       <c r="B94" t="n">
-        <v>98710</v>
+        <v>91843</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9903,10 +9918,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>569406</v>
+        <v>569365</v>
       </c>
       <c r="R94" t="n">
-        <v>6949664</v>
+        <v>6949661</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9939,11 +9954,6 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>20 ex</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -9970,32 +9980,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129035050</v>
+        <v>129035027</v>
       </c>
       <c r="B95" t="n">
-        <v>98710</v>
+        <v>91843</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10005,10 +10015,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>569236</v>
+        <v>569169</v>
       </c>
       <c r="R95" t="n">
-        <v>6949440</v>
+        <v>6949533</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10041,11 +10051,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>4 ex</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10072,32 +10077,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129034621</v>
+        <v>129035029</v>
       </c>
       <c r="B96" t="n">
-        <v>98710</v>
+        <v>91843</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10107,10 +10112,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>569247</v>
+        <v>569217</v>
       </c>
       <c r="R96" t="n">
-        <v>6949434</v>
+        <v>6949427</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10143,11 +10148,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>10 stycken knärot</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10177,7 +10177,7 @@
         <v>129034635</v>
       </c>
       <c r="B97" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10478,7 +10478,7 @@
         <v>129034609</v>
       </c>
       <c r="B100" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10580,7 +10580,7 @@
         <v>129035036</v>
       </c>
       <c r="B101" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10682,7 +10682,7 @@
         <v>129035052</v>
       </c>
       <c r="B102" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10784,7 +10784,7 @@
         <v>129035056</v>
       </c>
       <c r="B103" t="n">
-        <v>105774</v>
+        <v>105776</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10878,10 +10878,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129035006</v>
+        <v>129027886</v>
       </c>
       <c r="B104" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10913,10 +10913,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>569217</v>
+        <v>569305</v>
       </c>
       <c r="R104" t="n">
-        <v>6949470</v>
+        <v>6949566</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10975,10 +10975,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129027886</v>
+        <v>129035006</v>
       </c>
       <c r="B105" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11010,10 +11010,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>569305</v>
+        <v>569217</v>
       </c>
       <c r="R105" t="n">
-        <v>6949566</v>
+        <v>6949470</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11072,32 +11072,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129035048</v>
+        <v>129035026</v>
       </c>
       <c r="B106" t="n">
-        <v>98710</v>
+        <v>91843</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11107,10 +11107,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>569176</v>
+        <v>569175</v>
       </c>
       <c r="R106" t="n">
-        <v>6949507</v>
+        <v>6949549</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11143,11 +11143,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>30 ex</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11174,10 +11169,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129035053</v>
+        <v>129035048</v>
       </c>
       <c r="B107" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11209,10 +11204,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>569459</v>
+        <v>569176</v>
       </c>
       <c r="R107" t="n">
-        <v>6949662</v>
+        <v>6949507</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11249,7 +11244,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>14 ex</t>
+          <t>30 ex</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11276,10 +11271,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129035049</v>
+        <v>129035053</v>
       </c>
       <c r="B108" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11311,10 +11306,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>569219</v>
+        <v>569459</v>
       </c>
       <c r="R108" t="n">
-        <v>6949489</v>
+        <v>6949662</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11351,7 +11346,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>35 ex</t>
+          <t>14 ex</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11378,10 +11373,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129035044</v>
+        <v>129035049</v>
       </c>
       <c r="B109" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11413,10 +11408,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>569191</v>
+        <v>569219</v>
       </c>
       <c r="R109" t="n">
-        <v>6949579</v>
+        <v>6949489</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11453,7 +11448,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>50 ex</t>
+          <t>35 ex</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11480,32 +11475,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129035026</v>
+        <v>129035044</v>
       </c>
       <c r="B110" t="n">
-        <v>91841</v>
+        <v>98712</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11515,10 +11510,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>569175</v>
+        <v>569191</v>
       </c>
       <c r="R110" t="n">
-        <v>6949549</v>
+        <v>6949579</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11551,6 +11546,11 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11580,7 +11580,7 @@
         <v>129035033</v>
       </c>
       <c r="B111" t="n">
-        <v>91756</v>
+        <v>91758</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11677,7 +11677,7 @@
         <v>129035032</v>
       </c>
       <c r="B112" t="n">
-        <v>91756</v>
+        <v>91758</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>

--- a/artfynd/A 45833-2025 artfynd.xlsx
+++ b/artfynd/A 45833-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129034612</v>
+        <v>129034627</v>
       </c>
       <c r="B2" t="n">
-        <v>98712</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569243</v>
+        <v>569482</v>
       </c>
       <c r="R2" t="n">
-        <v>6949558</v>
+        <v>6949676</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>30  exemplar ca</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129035046</v>
+        <v>129034612</v>
       </c>
       <c r="B3" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569127</v>
+        <v>569243</v>
       </c>
       <c r="R3" t="n">
-        <v>6949602</v>
+        <v>6949558</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +847,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>13 ex</t>
+          <t>30  exemplar ca</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129035043</v>
+        <v>129035046</v>
       </c>
       <c r="B4" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569204</v>
+        <v>569127</v>
       </c>
       <c r="R4" t="n">
-        <v>6949533</v>
+        <v>6949602</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,7 +949,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>10 ex</t>
+          <t>13 ex</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,32 +976,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129034627</v>
+        <v>129035043</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>98716</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569482</v>
+        <v>569204</v>
       </c>
       <c r="R5" t="n">
-        <v>6949676</v>
+        <v>6949533</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1052,6 +1047,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,7 +1081,7 @@
         <v>129035039</v>
       </c>
       <c r="B6" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>129035030</v>
       </c>
       <c r="B7" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>129035054</v>
       </c>
       <c r="B10" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,32 +1583,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129034648</v>
+        <v>129034630</v>
       </c>
       <c r="B11" t="n">
-        <v>96831</v>
+        <v>79044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>569279</v>
+        <v>569231</v>
       </c>
       <c r="R11" t="n">
-        <v>6949401</v>
+        <v>6949559</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1782,32 +1782,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129034630</v>
+        <v>129035055</v>
       </c>
       <c r="B13" t="n">
-        <v>79044</v>
+        <v>98716</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1817,10 +1817,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569231</v>
+        <v>569221</v>
       </c>
       <c r="R13" t="n">
-        <v>6949559</v>
+        <v>6949406</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1853,6 +1853,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1879,32 +1884,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129034594</v>
+        <v>129035042</v>
       </c>
       <c r="B14" t="n">
-        <v>91843</v>
+        <v>98716</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1914,10 +1919,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569203</v>
+        <v>569200</v>
       </c>
       <c r="R14" t="n">
-        <v>6949498</v>
+        <v>6949533</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1954,7 +1959,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>11 exemplar</t>
+          <t>30 ex</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1981,32 +1986,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129035055</v>
+        <v>129034594</v>
       </c>
       <c r="B15" t="n">
-        <v>98712</v>
+        <v>91847</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2016,10 +2021,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>569221</v>
+        <v>569203</v>
       </c>
       <c r="R15" t="n">
-        <v>6949406</v>
+        <v>6949498</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2056,7 +2061,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>25 ex</t>
+          <t>11 exemplar</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2083,32 +2088,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129035042</v>
+        <v>129034648</v>
       </c>
       <c r="B16" t="n">
-        <v>98712</v>
+        <v>96835</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2118,10 +2123,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>569200</v>
+        <v>569279</v>
       </c>
       <c r="R16" t="n">
-        <v>6949533</v>
+        <v>6949401</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2154,11 +2159,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>30 ex</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2188,7 +2188,7 @@
         <v>129034620</v>
       </c>
       <c r="B17" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2287,32 +2287,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129035009</v>
+        <v>129035059</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>92831</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2322,10 +2322,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>569314</v>
+        <v>569273</v>
       </c>
       <c r="R18" t="n">
-        <v>6949502</v>
+        <v>6949537</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2358,11 +2358,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2389,10 +2384,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129034580</v>
+        <v>129034629</v>
       </c>
       <c r="B19" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2400,21 +2395,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2424,10 +2419,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>569396</v>
+        <v>569247</v>
       </c>
       <c r="R19" t="n">
-        <v>6949738</v>
+        <v>6949558</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2460,11 +2455,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på Tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2491,7 +2481,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129035019</v>
+        <v>129035009</v>
       </c>
       <c r="B20" t="n">
         <v>57727</v>
@@ -2526,10 +2516,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>569117</v>
+        <v>569314</v>
       </c>
       <c r="R20" t="n">
-        <v>6949581</v>
+        <v>6949502</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2566,7 +2556,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2593,32 +2583,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129035059</v>
+        <v>129034580</v>
       </c>
       <c r="B21" t="n">
-        <v>92827</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2628,10 +2618,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>569273</v>
+        <v>569396</v>
       </c>
       <c r="R21" t="n">
-        <v>6949537</v>
+        <v>6949738</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2664,6 +2654,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på Tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2690,10 +2685,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129034629</v>
+        <v>129035019</v>
       </c>
       <c r="B22" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2701,21 +2696,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2725,10 +2720,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>569247</v>
+        <v>569117</v>
       </c>
       <c r="R22" t="n">
-        <v>6949558</v>
+        <v>6949581</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2761,6 +2756,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2787,10 +2787,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129034625</v>
+        <v>129035004</v>
       </c>
       <c r="B23" t="n">
-        <v>79044</v>
+        <v>91549</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2798,21 +2798,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569479</v>
+        <v>569152</v>
       </c>
       <c r="R23" t="n">
-        <v>6949657</v>
+        <v>6949557</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2887,7 +2887,7 @@
         <v>129035005</v>
       </c>
       <c r="B24" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2981,10 +2981,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129035004</v>
+        <v>129034647</v>
       </c>
       <c r="B25" t="n">
-        <v>91545</v>
+        <v>88949</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2992,21 +2992,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3016,10 +3016,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569152</v>
+        <v>569247</v>
       </c>
       <c r="R25" t="n">
-        <v>6949557</v>
+        <v>6949558</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3078,10 +3078,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129034592</v>
+        <v>129034591</v>
       </c>
       <c r="B26" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3113,10 +3113,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569205</v>
+        <v>569203</v>
       </c>
       <c r="R26" t="n">
-        <v>6949497</v>
+        <v>6949513</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3153,7 +3153,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>1 x</t>
+          <t>11 ex</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3180,10 +3180,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129034591</v>
+        <v>129034592</v>
       </c>
       <c r="B27" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3215,10 +3215,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>569203</v>
+        <v>569205</v>
       </c>
       <c r="R27" t="n">
-        <v>6949513</v>
+        <v>6949497</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3255,7 +3255,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>11 ex</t>
+          <t>1 x</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3282,10 +3282,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129034647</v>
+        <v>129035025</v>
       </c>
       <c r="B28" t="n">
-        <v>88945</v>
+        <v>91847</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3293,21 +3293,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3317,10 +3317,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>569247</v>
+        <v>569388</v>
       </c>
       <c r="R28" t="n">
-        <v>6949558</v>
+        <v>6949665</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3379,10 +3379,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129035025</v>
+        <v>129034625</v>
       </c>
       <c r="B29" t="n">
-        <v>91843</v>
+        <v>79044</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3390,21 +3390,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3414,10 +3414,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>569388</v>
+        <v>569479</v>
       </c>
       <c r="R29" t="n">
-        <v>6949665</v>
+        <v>6949657</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3479,7 +3479,7 @@
         <v>129034623</v>
       </c>
       <c r="B30" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3578,32 +3578,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129034637</v>
+        <v>129035058</v>
       </c>
       <c r="B31" t="n">
-        <v>92827</v>
+        <v>79044</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>569229</v>
+        <v>569388</v>
       </c>
       <c r="R31" t="n">
-        <v>6949400</v>
+        <v>6949647</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3675,10 +3675,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129035058</v>
+        <v>129035031</v>
       </c>
       <c r="B32" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3686,21 +3686,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3710,10 +3710,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>569388</v>
+        <v>569125</v>
       </c>
       <c r="R32" t="n">
-        <v>6949647</v>
+        <v>6949570</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3772,32 +3772,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129035031</v>
+        <v>129034637</v>
       </c>
       <c r="B33" t="n">
-        <v>80149</v>
+        <v>92831</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3807,10 +3807,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>569125</v>
+        <v>569229</v>
       </c>
       <c r="R33" t="n">
-        <v>6949570</v>
+        <v>6949400</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3974,7 +3974,7 @@
         <v>129035051</v>
       </c>
       <c r="B35" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4073,10 +4073,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129034634</v>
+        <v>129035020</v>
       </c>
       <c r="B36" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4084,21 +4084,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4108,10 +4108,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>569200</v>
+        <v>569171</v>
       </c>
       <c r="R36" t="n">
-        <v>6949411</v>
+        <v>6949543</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4144,6 +4144,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på granhögstubbe</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4170,10 +4175,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129035020</v>
+        <v>129034634</v>
       </c>
       <c r="B37" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4181,21 +4186,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4205,10 +4210,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>569171</v>
+        <v>569200</v>
       </c>
       <c r="R37" t="n">
-        <v>6949543</v>
+        <v>6949411</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4241,11 +4246,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på granhögstubbe</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4377,7 +4377,7 @@
         <v>129034602</v>
       </c>
       <c r="B39" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         <v>129035040</v>
       </c>
       <c r="B40" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4581,7 +4581,7 @@
         <v>129035045</v>
       </c>
       <c r="B41" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4683,7 +4683,7 @@
         <v>129035063</v>
       </c>
       <c r="B42" t="n">
-        <v>96831</v>
+        <v>96835</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>129034643</v>
       </c>
       <c r="B43" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4879,32 +4879,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129034607</v>
+        <v>129034575</v>
       </c>
       <c r="B44" t="n">
-        <v>98712</v>
+        <v>57727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4914,10 +4914,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>569317</v>
+        <v>569448</v>
       </c>
       <c r="R44" t="n">
-        <v>6949549</v>
+        <v>6949625</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>31 stycken</t>
+          <t>Färska ringhack på Tall av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4981,32 +4981,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129035041</v>
+        <v>129035011</v>
       </c>
       <c r="B45" t="n">
-        <v>98712</v>
+        <v>57727</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5016,10 +5016,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>569262</v>
+        <v>569442</v>
       </c>
       <c r="R45" t="n">
-        <v>6949524</v>
+        <v>6949783</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>5 ex</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5083,32 +5083,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129034575</v>
+        <v>129034607</v>
       </c>
       <c r="B46" t="n">
-        <v>57727</v>
+        <v>98716</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5118,10 +5118,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>569448</v>
+        <v>569317</v>
       </c>
       <c r="R46" t="n">
-        <v>6949625</v>
+        <v>6949549</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Färska ringhack på Tall av tretåig hackspett</t>
+          <t>31 stycken</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5185,32 +5185,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129035011</v>
+        <v>129035041</v>
       </c>
       <c r="B47" t="n">
-        <v>57727</v>
+        <v>98716</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5220,10 +5220,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>569442</v>
+        <v>569262</v>
       </c>
       <c r="R47" t="n">
-        <v>6949783</v>
+        <v>6949524</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5260,7 +5260,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5287,32 +5287,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129035016</v>
+        <v>129035062</v>
       </c>
       <c r="B48" t="n">
-        <v>57727</v>
+        <v>96835</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5322,10 +5322,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>569435</v>
+        <v>569478</v>
       </c>
       <c r="R48" t="n">
-        <v>6949665</v>
+        <v>6949666</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5358,11 +5358,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5389,10 +5384,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129034632</v>
+        <v>129035016</v>
       </c>
       <c r="B49" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5400,21 +5395,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5424,10 +5419,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>569237</v>
+        <v>569435</v>
       </c>
       <c r="R49" t="n">
-        <v>6949442</v>
+        <v>6949665</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5460,6 +5455,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5486,32 +5486,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129035062</v>
+        <v>129035002</v>
       </c>
       <c r="B50" t="n">
-        <v>96831</v>
+        <v>91549</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2869</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5521,10 +5521,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>569478</v>
+        <v>569405</v>
       </c>
       <c r="R50" t="n">
-        <v>6949666</v>
+        <v>6949685</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5583,10 +5583,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129035002</v>
+        <v>129034597</v>
       </c>
       <c r="B51" t="n">
-        <v>91545</v>
+        <v>91847</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5594,21 +5594,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5618,10 +5618,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>569405</v>
+        <v>569221</v>
       </c>
       <c r="R51" t="n">
-        <v>6949685</v>
+        <v>6949499</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5654,6 +5654,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>8 exemplar</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5683,7 +5688,7 @@
         <v>129035022</v>
       </c>
       <c r="B52" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5777,10 +5782,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129034597</v>
+        <v>129034632</v>
       </c>
       <c r="B53" t="n">
-        <v>91843</v>
+        <v>79044</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5788,21 +5793,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5812,10 +5817,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>569221</v>
+        <v>569237</v>
       </c>
       <c r="R53" t="n">
-        <v>6949499</v>
+        <v>6949442</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5848,11 +5853,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>8 exemplar</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5882,7 +5882,7 @@
         <v>129034616</v>
       </c>
       <c r="B54" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5981,10 +5981,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129035008</v>
+        <v>129034600</v>
       </c>
       <c r="B55" t="n">
-        <v>91545</v>
+        <v>80149</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5992,21 +5992,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6016,10 +6016,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>569216</v>
+        <v>569481</v>
       </c>
       <c r="R55" t="n">
-        <v>6949430</v>
+        <v>6949674</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6052,6 +6052,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Apothecier antal 1</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6078,10 +6083,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129035028</v>
+        <v>129035008</v>
       </c>
       <c r="B56" t="n">
-        <v>91843</v>
+        <v>91549</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6089,21 +6094,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6113,10 +6118,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>569192</v>
+        <v>569216</v>
       </c>
       <c r="R56" t="n">
-        <v>6949509</v>
+        <v>6949430</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6175,10 +6180,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129034600</v>
+        <v>129035028</v>
       </c>
       <c r="B57" t="n">
-        <v>80149</v>
+        <v>91847</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6186,21 +6191,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6210,10 +6215,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>569481</v>
+        <v>569192</v>
       </c>
       <c r="R57" t="n">
-        <v>6949674</v>
+        <v>6949509</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6246,11 +6251,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Apothecier antal 1</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6277,32 +6277,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129034581</v>
+        <v>129034610</v>
       </c>
       <c r="B58" t="n">
-        <v>57887</v>
+        <v>98716</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6312,10 +6312,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>569223</v>
+        <v>569282</v>
       </c>
       <c r="R58" t="n">
-        <v>6949401</v>
+        <v>6949567</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Sågs och gjorde övriga läten</t>
+          <t>Ca 100 stycken</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6379,10 +6379,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129034610</v>
+        <v>129034614</v>
       </c>
       <c r="B59" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6414,10 +6414,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>569282</v>
+        <v>569237</v>
       </c>
       <c r="R59" t="n">
-        <v>6949567</v>
+        <v>6949556</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ca 100 stycken</t>
+          <t>5 stycken</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6481,32 +6481,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129034614</v>
+        <v>129034581</v>
       </c>
       <c r="B60" t="n">
-        <v>98712</v>
+        <v>57887</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6516,10 +6516,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>569237</v>
+        <v>569223</v>
       </c>
       <c r="R60" t="n">
-        <v>6949556</v>
+        <v>6949401</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6556,7 +6556,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>5 stycken</t>
+          <t>Sågs och gjorde övriga läten</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6586,7 +6586,7 @@
         <v>129034586</v>
       </c>
       <c r="B61" t="n">
-        <v>91998</v>
+        <v>92002</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6683,7 +6683,7 @@
         <v>129035024</v>
       </c>
       <c r="B62" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6777,10 +6777,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129034574</v>
+        <v>129035003</v>
       </c>
       <c r="B63" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6812,10 +6812,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>569461</v>
+        <v>569164</v>
       </c>
       <c r="R63" t="n">
-        <v>6949706</v>
+        <v>6949559</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6874,10 +6874,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129035003</v>
+        <v>129034574</v>
       </c>
       <c r="B64" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6909,10 +6909,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>569164</v>
+        <v>569461</v>
       </c>
       <c r="R64" t="n">
-        <v>6949559</v>
+        <v>6949706</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6971,10 +6971,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129035021</v>
+        <v>129034587</v>
       </c>
       <c r="B65" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7006,10 +7006,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>569446</v>
+        <v>569463</v>
       </c>
       <c r="R65" t="n">
-        <v>6949629</v>
+        <v>6949711</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7068,10 +7068,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129034587</v>
+        <v>129035021</v>
       </c>
       <c r="B66" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7103,10 +7103,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>569463</v>
+        <v>569446</v>
       </c>
       <c r="R66" t="n">
-        <v>6949711</v>
+        <v>6949629</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7165,45 +7165,49 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129034624</v>
+        <v>129027791</v>
       </c>
       <c r="B67" t="n">
-        <v>105776</v>
+        <v>98716</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Sandsjömyran, Mpd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>569234</v>
+        <v>569308</v>
       </c>
       <c r="R67" t="n">
-        <v>6949440</v>
+        <v>6949546</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7236,11 +7240,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>9 exemplar</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7267,32 +7266,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129035035</v>
+        <v>129034624</v>
       </c>
       <c r="B68" t="n">
-        <v>98712</v>
+        <v>105780</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7302,10 +7301,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>569317</v>
+        <v>569234</v>
       </c>
       <c r="R68" t="n">
-        <v>6949469</v>
+        <v>6949440</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7342,7 +7341,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>5 ex</t>
+          <t>9 exemplar</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7369,10 +7368,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129027791</v>
+        <v>129035035</v>
       </c>
       <c r="B69" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7397,21 +7396,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Sandsjömyran, Mpd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>569308</v>
+        <v>569317</v>
       </c>
       <c r="R69" t="n">
-        <v>6949546</v>
+        <v>6949469</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7444,6 +7439,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7470,10 +7470,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129034639</v>
+        <v>129035060</v>
       </c>
       <c r="B70" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7505,10 +7505,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>569398</v>
+        <v>569208</v>
       </c>
       <c r="R70" t="n">
-        <v>6949741</v>
+        <v>6949415</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7545,7 +7545,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>6 äldre exemplar och 1 färsk fruktkropp</t>
+          <t>20 ex minst</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7572,10 +7572,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129035060</v>
+        <v>129034639</v>
       </c>
       <c r="B71" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7607,10 +7607,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>569208</v>
+        <v>569398</v>
       </c>
       <c r="R71" t="n">
-        <v>6949415</v>
+        <v>6949741</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7647,7 +7647,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>20 ex minst</t>
+          <t>6 äldre exemplar och 1 färsk fruktkropp</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7674,32 +7674,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129034584</v>
+        <v>129035037</v>
       </c>
       <c r="B72" t="n">
-        <v>57724</v>
+        <v>98716</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7709,10 +7709,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>569221</v>
+        <v>569434</v>
       </c>
       <c r="R72" t="n">
-        <v>6949499</v>
+        <v>6949706</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7749,7 +7749,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Förbiflygande från träd till träd</t>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7776,10 +7776,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129035018</v>
+        <v>129034584</v>
       </c>
       <c r="B73" t="n">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7787,16 +7787,16 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -7811,10 +7811,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>569111</v>
+        <v>569221</v>
       </c>
       <c r="R73" t="n">
-        <v>6949604</v>
+        <v>6949499</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Förbiflygande från träd till träd</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7878,32 +7878,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129035037</v>
+        <v>129035018</v>
       </c>
       <c r="B74" t="n">
-        <v>98712</v>
+        <v>57727</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7913,10 +7913,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>569434</v>
+        <v>569111</v>
       </c>
       <c r="R74" t="n">
-        <v>6949706</v>
+        <v>6949604</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7953,7 +7953,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>20 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7980,32 +7980,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129034650</v>
+        <v>129026691</v>
       </c>
       <c r="B75" t="n">
-        <v>98712</v>
+        <v>91847</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8015,10 +8015,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>569303</v>
+        <v>569195</v>
       </c>
       <c r="R75" t="n">
-        <v>6949537</v>
+        <v>6949487</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8051,11 +8051,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>30 stycken ( finns eventuellt mer )</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8082,32 +8077,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129034605</v>
+        <v>129034645</v>
       </c>
       <c r="B76" t="n">
-        <v>98712</v>
+        <v>92831</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8117,10 +8112,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>569305</v>
+        <v>569196</v>
       </c>
       <c r="R76" t="n">
-        <v>6949538</v>
+        <v>6949411</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8157,7 +8152,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>21 knärot</t>
+          <t>4 färska exemplar 3 äldre exemplar</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8184,10 +8179,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129034645</v>
+        <v>129034642</v>
       </c>
       <c r="B77" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8219,10 +8214,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>569196</v>
+        <v>569283</v>
       </c>
       <c r="R77" t="n">
-        <v>6949411</v>
+        <v>6949655</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8259,7 +8254,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>4 färska exemplar 3 äldre exemplar</t>
+          <t>7 äldre exemplar</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8286,10 +8281,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129034642</v>
+        <v>129034598</v>
       </c>
       <c r="B78" t="n">
-        <v>92827</v>
+        <v>97587</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8297,21 +8292,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8321,10 +8316,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>569283</v>
+        <v>569460</v>
       </c>
       <c r="R78" t="n">
-        <v>6949655</v>
+        <v>6949629</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8357,11 +8352,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>7 äldre exemplar</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8388,32 +8378,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129026691</v>
+        <v>129034650</v>
       </c>
       <c r="B79" t="n">
-        <v>91843</v>
+        <v>98716</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8423,10 +8413,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>569195</v>
+        <v>569303</v>
       </c>
       <c r="R79" t="n">
-        <v>6949487</v>
+        <v>6949537</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8459,6 +8449,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>30 stycken ( finns eventuellt mer )</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8485,32 +8480,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129034598</v>
+        <v>129034605</v>
       </c>
       <c r="B80" t="n">
-        <v>97583</v>
+        <v>98716</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8520,10 +8515,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>569460</v>
+        <v>569305</v>
       </c>
       <c r="R80" t="n">
-        <v>6949629</v>
+        <v>6949538</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8556,6 +8551,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>21 knärot</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8582,32 +8582,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129035047</v>
+        <v>129034640</v>
       </c>
       <c r="B81" t="n">
-        <v>98712</v>
+        <v>92831</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8617,10 +8617,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>569162</v>
+        <v>569213</v>
       </c>
       <c r="R81" t="n">
-        <v>6949566</v>
+        <v>6949414</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8657,7 +8657,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>50 ex</t>
+          <t>16 exemplar</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8684,32 +8684,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129034604</v>
+        <v>129035001</v>
       </c>
       <c r="B82" t="n">
-        <v>98712</v>
+        <v>91513</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8719,10 +8719,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>569303</v>
+        <v>569232</v>
       </c>
       <c r="R82" t="n">
-        <v>6949536</v>
+        <v>6949444</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8755,11 +8755,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8786,32 +8781,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129034618</v>
+        <v>129035057</v>
       </c>
       <c r="B83" t="n">
-        <v>98712</v>
+        <v>79044</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8821,10 +8816,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>569235</v>
+        <v>569464</v>
       </c>
       <c r="R83" t="n">
-        <v>6949411</v>
+        <v>6949648</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8857,11 +8852,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8888,32 +8878,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129034640</v>
+        <v>129035007</v>
       </c>
       <c r="B84" t="n">
-        <v>92827</v>
+        <v>91549</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8923,10 +8913,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>569213</v>
+        <v>569225</v>
       </c>
       <c r="R84" t="n">
-        <v>6949414</v>
+        <v>6949424</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8959,11 +8949,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>16 exemplar</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8990,32 +8975,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129035057</v>
+        <v>129035061</v>
       </c>
       <c r="B85" t="n">
-        <v>79044</v>
+        <v>96835</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9025,10 +9010,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>569464</v>
+        <v>569333</v>
       </c>
       <c r="R85" t="n">
-        <v>6949648</v>
+        <v>6949607</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9087,32 +9072,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129035061</v>
+        <v>129035012</v>
       </c>
       <c r="B86" t="n">
-        <v>96831</v>
+        <v>57727</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9122,10 +9107,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>569333</v>
+        <v>569435</v>
       </c>
       <c r="R86" t="n">
-        <v>6949607</v>
+        <v>6949783</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9158,6 +9143,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9184,32 +9174,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129035007</v>
+        <v>129035047</v>
       </c>
       <c r="B87" t="n">
-        <v>91545</v>
+        <v>98716</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9219,10 +9209,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>569225</v>
+        <v>569162</v>
       </c>
       <c r="R87" t="n">
-        <v>6949424</v>
+        <v>6949566</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9255,6 +9245,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9281,32 +9276,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129035001</v>
+        <v>129034604</v>
       </c>
       <c r="B88" t="n">
-        <v>91509</v>
+        <v>98716</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9316,10 +9311,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>569232</v>
+        <v>569303</v>
       </c>
       <c r="R88" t="n">
-        <v>6949444</v>
+        <v>6949536</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9352,6 +9347,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9378,32 +9378,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129035012</v>
+        <v>129034618</v>
       </c>
       <c r="B89" t="n">
-        <v>57727</v>
+        <v>98716</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9413,10 +9413,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>569435</v>
+        <v>569235</v>
       </c>
       <c r="R89" t="n">
-        <v>6949783</v>
+        <v>6949411</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9453,7 +9453,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9483,7 +9483,7 @@
         <v>129035038</v>
       </c>
       <c r="B90" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9585,7 +9585,7 @@
         <v>129035050</v>
       </c>
       <c r="B91" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9687,7 +9687,7 @@
         <v>129034621</v>
       </c>
       <c r="B92" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9786,10 +9786,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129035023</v>
+        <v>129035027</v>
       </c>
       <c r="B93" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9821,10 +9821,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>569415</v>
+        <v>569169</v>
       </c>
       <c r="R93" t="n">
-        <v>6949677</v>
+        <v>6949533</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9883,10 +9883,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129034589</v>
+        <v>129035023</v>
       </c>
       <c r="B94" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9918,10 +9918,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>569365</v>
+        <v>569415</v>
       </c>
       <c r="R94" t="n">
-        <v>6949661</v>
+        <v>6949677</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9980,10 +9980,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129035027</v>
+        <v>129034589</v>
       </c>
       <c r="B95" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10015,10 +10015,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>569169</v>
+        <v>569365</v>
       </c>
       <c r="R95" t="n">
-        <v>6949533</v>
+        <v>6949661</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10080,7 +10080,7 @@
         <v>129035029</v>
       </c>
       <c r="B96" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10174,32 +10174,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129034635</v>
+        <v>129034609</v>
       </c>
       <c r="B97" t="n">
-        <v>79044</v>
+        <v>98716</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10209,10 +10209,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>569427</v>
+        <v>569458</v>
       </c>
       <c r="R97" t="n">
-        <v>6949726</v>
+        <v>6949777</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10245,6 +10245,11 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>48 stycken</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10271,32 +10276,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129035017</v>
+        <v>129035036</v>
       </c>
       <c r="B98" t="n">
-        <v>57727</v>
+        <v>98716</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10306,10 +10311,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>569192</v>
+        <v>569330</v>
       </c>
       <c r="R98" t="n">
-        <v>6949518</v>
+        <v>6949564</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10346,7 +10351,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>8 ex</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10373,32 +10378,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129035010</v>
+        <v>129035052</v>
       </c>
       <c r="B99" t="n">
-        <v>57727</v>
+        <v>98716</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10408,10 +10413,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>569465</v>
+        <v>569405</v>
       </c>
       <c r="R99" t="n">
-        <v>6949606</v>
+        <v>6949641</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10448,7 +10453,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>70 ex</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10475,32 +10480,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129034609</v>
+        <v>129035056</v>
       </c>
       <c r="B100" t="n">
-        <v>98712</v>
+        <v>105780</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10510,10 +10515,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>569458</v>
+        <v>569201</v>
       </c>
       <c r="R100" t="n">
-        <v>6949777</v>
+        <v>6949530</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10546,11 +10551,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>48 stycken</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10577,32 +10577,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129035036</v>
+        <v>129034635</v>
       </c>
       <c r="B101" t="n">
-        <v>98712</v>
+        <v>79044</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10612,10 +10612,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>569330</v>
+        <v>569427</v>
       </c>
       <c r="R101" t="n">
-        <v>6949564</v>
+        <v>6949726</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10648,11 +10648,6 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>8 ex</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10679,32 +10674,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129035052</v>
+        <v>129035017</v>
       </c>
       <c r="B102" t="n">
-        <v>98712</v>
+        <v>57727</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10714,10 +10709,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>569405</v>
+        <v>569192</v>
       </c>
       <c r="R102" t="n">
-        <v>6949641</v>
+        <v>6949518</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10754,7 +10749,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>70 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10781,32 +10776,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129035056</v>
+        <v>129035010</v>
       </c>
       <c r="B103" t="n">
-        <v>105776</v>
+        <v>57727</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>221144</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10816,10 +10811,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>569201</v>
+        <v>569465</v>
       </c>
       <c r="R103" t="n">
-        <v>6949530</v>
+        <v>6949606</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10852,6 +10847,11 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10878,10 +10878,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129027886</v>
+        <v>129035006</v>
       </c>
       <c r="B104" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10913,10 +10913,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>569305</v>
+        <v>569217</v>
       </c>
       <c r="R104" t="n">
-        <v>6949566</v>
+        <v>6949470</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10975,10 +10975,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129035006</v>
+        <v>129027886</v>
       </c>
       <c r="B105" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11010,10 +11010,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>569217</v>
+        <v>569305</v>
       </c>
       <c r="R105" t="n">
-        <v>6949470</v>
+        <v>6949566</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11075,7 +11075,7 @@
         <v>129035026</v>
       </c>
       <c r="B106" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
         <v>129035048</v>
       </c>
       <c r="B107" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11274,7 +11274,7 @@
         <v>129035053</v>
       </c>
       <c r="B108" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>129035049</v>
       </c>
       <c r="B109" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11478,7 +11478,7 @@
         <v>129035044</v>
       </c>
       <c r="B110" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
         <v>129035033</v>
       </c>
       <c r="B111" t="n">
-        <v>91758</v>
+        <v>91762</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11677,7 +11677,7 @@
         <v>129035032</v>
       </c>
       <c r="B112" t="n">
-        <v>91758</v>
+        <v>91762</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>

--- a/artfynd/A 45833-2025 artfynd.xlsx
+++ b/artfynd/A 45833-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129034627</v>
+        <v>129035046</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569482</v>
+        <v>569127</v>
       </c>
       <c r="R2" t="n">
-        <v>6949676</v>
+        <v>6949602</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>13 ex</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129034612</v>
+        <v>129035043</v>
       </c>
       <c r="B3" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569243</v>
+        <v>569204</v>
       </c>
       <c r="R3" t="n">
-        <v>6949558</v>
+        <v>6949533</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>30  exemplar ca</t>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129035046</v>
+        <v>129034627</v>
       </c>
       <c r="B4" t="n">
-        <v>98716</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569127</v>
+        <v>569482</v>
       </c>
       <c r="R4" t="n">
-        <v>6949602</v>
+        <v>6949676</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,11 +950,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>13 ex</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129035043</v>
+        <v>129034612</v>
       </c>
       <c r="B5" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569204</v>
+        <v>569243</v>
       </c>
       <c r="R5" t="n">
-        <v>6949533</v>
+        <v>6949558</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>10 ex</t>
+          <t>30  exemplar ca</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1078,32 +1078,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129035039</v>
+        <v>129035030</v>
       </c>
       <c r="B6" t="n">
-        <v>98716</v>
+        <v>97595</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>569394</v>
+        <v>569424</v>
       </c>
       <c r="R6" t="n">
-        <v>6949664</v>
+        <v>6949671</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1149,11 +1149,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1180,32 +1175,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129035030</v>
+        <v>129035039</v>
       </c>
       <c r="B7" t="n">
-        <v>97587</v>
+        <v>98724</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>569424</v>
+        <v>569394</v>
       </c>
       <c r="R7" t="n">
-        <v>6949671</v>
+        <v>6949664</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1251,6 +1246,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1277,32 +1277,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129035013</v>
+        <v>129035054</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>569455</v>
+        <v>569126</v>
       </c>
       <c r="R8" t="n">
-        <v>6949716</v>
+        <v>6949570</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>13 ex</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1379,7 +1379,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129035014</v>
+        <v>129035013</v>
       </c>
       <c r="B9" t="n">
         <v>57727</v>
@@ -1417,7 +1417,7 @@
         <v>569455</v>
       </c>
       <c r="R9" t="n">
-        <v>6949703</v>
+        <v>6949716</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1481,32 +1481,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129035054</v>
+        <v>129035014</v>
       </c>
       <c r="B10" t="n">
-        <v>98716</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>569126</v>
+        <v>569455</v>
       </c>
       <c r="R10" t="n">
-        <v>6949570</v>
+        <v>6949703</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>13 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1583,10 +1583,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129034630</v>
+        <v>129034577</v>
       </c>
       <c r="B11" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1594,21 +1594,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>569231</v>
+        <v>569496</v>
       </c>
       <c r="R11" t="n">
-        <v>6949559</v>
+        <v>6949627</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1654,6 +1654,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1680,32 +1685,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129034577</v>
+        <v>129035042</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1715,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569496</v>
+        <v>569200</v>
       </c>
       <c r="R12" t="n">
-        <v>6949627</v>
+        <v>6949533</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1755,7 +1760,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på tall</t>
+          <t>30 ex</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1782,32 +1787,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129035055</v>
+        <v>129034594</v>
       </c>
       <c r="B13" t="n">
-        <v>98716</v>
+        <v>91848</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1817,10 +1822,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569221</v>
+        <v>569203</v>
       </c>
       <c r="R13" t="n">
-        <v>6949406</v>
+        <v>6949498</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1857,7 +1862,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>25 ex</t>
+          <t>11 exemplar</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1884,32 +1889,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129035042</v>
+        <v>129034648</v>
       </c>
       <c r="B14" t="n">
-        <v>98716</v>
+        <v>96843</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1919,10 +1924,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569200</v>
+        <v>569279</v>
       </c>
       <c r="R14" t="n">
-        <v>6949533</v>
+        <v>6949401</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1955,11 +1960,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>30 ex</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1986,10 +1986,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129034594</v>
+        <v>129034630</v>
       </c>
       <c r="B15" t="n">
-        <v>91847</v>
+        <v>79044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1997,21 +1997,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2021,10 +2021,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>569203</v>
+        <v>569231</v>
       </c>
       <c r="R15" t="n">
-        <v>6949498</v>
+        <v>6949559</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2057,11 +2057,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>11 exemplar</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2088,32 +2083,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129034648</v>
+        <v>129035055</v>
       </c>
       <c r="B16" t="n">
-        <v>96835</v>
+        <v>98724</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2123,10 +2118,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>569279</v>
+        <v>569221</v>
       </c>
       <c r="R16" t="n">
-        <v>6949401</v>
+        <v>6949406</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2159,6 +2154,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2185,32 +2185,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129034620</v>
+        <v>129034629</v>
       </c>
       <c r="B17" t="n">
-        <v>98716</v>
+        <v>79044</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2220,10 +2220,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>569195</v>
+        <v>569247</v>
       </c>
       <c r="R17" t="n">
-        <v>6949410</v>
+        <v>6949558</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2256,11 +2256,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Blommande knärot 1 exemplar + 21 övriga exemplar blommar ej</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2290,7 +2285,7 @@
         <v>129035059</v>
       </c>
       <c r="B18" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2384,32 +2379,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129034629</v>
+        <v>129034620</v>
       </c>
       <c r="B19" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2419,10 +2414,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>569247</v>
+        <v>569195</v>
       </c>
       <c r="R19" t="n">
-        <v>6949558</v>
+        <v>6949410</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2455,6 +2450,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Blommande knärot 1 exemplar + 21 övriga exemplar blommar ej</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2787,10 +2787,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129035004</v>
+        <v>129034592</v>
       </c>
       <c r="B23" t="n">
-        <v>91549</v>
+        <v>91848</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2798,21 +2798,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569152</v>
+        <v>569205</v>
       </c>
       <c r="R23" t="n">
-        <v>6949557</v>
+        <v>6949497</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2858,6 +2858,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>1 x</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2884,10 +2889,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129035005</v>
+        <v>129034591</v>
       </c>
       <c r="B24" t="n">
-        <v>91549</v>
+        <v>91848</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2895,21 +2900,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2919,10 +2924,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569188</v>
+        <v>569203</v>
       </c>
       <c r="R24" t="n">
-        <v>6949496</v>
+        <v>6949513</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2955,6 +2960,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>11 ex</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2984,7 +2994,7 @@
         <v>129034647</v>
       </c>
       <c r="B25" t="n">
-        <v>88949</v>
+        <v>88950</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3078,10 +3088,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129034591</v>
+        <v>129035004</v>
       </c>
       <c r="B26" t="n">
-        <v>91847</v>
+        <v>91550</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3089,21 +3099,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3113,10 +3123,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569203</v>
+        <v>569152</v>
       </c>
       <c r="R26" t="n">
-        <v>6949513</v>
+        <v>6949557</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3149,11 +3159,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>11 ex</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3180,10 +3185,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129034592</v>
+        <v>129035025</v>
       </c>
       <c r="B27" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3215,10 +3220,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>569205</v>
+        <v>569388</v>
       </c>
       <c r="R27" t="n">
-        <v>6949497</v>
+        <v>6949665</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3251,11 +3256,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>1 x</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3282,10 +3282,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129035025</v>
+        <v>129035005</v>
       </c>
       <c r="B28" t="n">
-        <v>91847</v>
+        <v>91550</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3293,21 +3293,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3317,10 +3317,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>569388</v>
+        <v>569188</v>
       </c>
       <c r="R28" t="n">
-        <v>6949665</v>
+        <v>6949496</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3479,7 +3479,7 @@
         <v>129034623</v>
       </c>
       <c r="B30" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3578,32 +3578,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129035058</v>
+        <v>129034637</v>
       </c>
       <c r="B31" t="n">
-        <v>79044</v>
+        <v>92832</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>569388</v>
+        <v>569229</v>
       </c>
       <c r="R31" t="n">
-        <v>6949647</v>
+        <v>6949400</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3772,32 +3772,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129034637</v>
+        <v>129035051</v>
       </c>
       <c r="B33" t="n">
-        <v>92831</v>
+        <v>98724</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3807,10 +3807,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>569229</v>
+        <v>569222</v>
       </c>
       <c r="R33" t="n">
-        <v>6949400</v>
+        <v>6949414</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3843,6 +3843,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>30 ex</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3869,10 +3874,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129034578</v>
+        <v>129035058</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3880,21 +3885,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3904,10 +3909,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>569420</v>
+        <v>569388</v>
       </c>
       <c r="R34" t="n">
-        <v>6949723</v>
+        <v>6949647</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3940,11 +3945,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3971,32 +3971,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129035051</v>
+        <v>129034578</v>
       </c>
       <c r="B35" t="n">
-        <v>98716</v>
+        <v>57727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4006,10 +4006,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>569222</v>
+        <v>569420</v>
       </c>
       <c r="R35" t="n">
-        <v>6949414</v>
+        <v>6949723</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>30 ex</t>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4073,10 +4073,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129035020</v>
+        <v>129034634</v>
       </c>
       <c r="B36" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4084,21 +4084,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4108,10 +4108,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>569171</v>
+        <v>569200</v>
       </c>
       <c r="R36" t="n">
-        <v>6949543</v>
+        <v>6949411</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4144,11 +4144,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på granhögstubbe</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4175,10 +4170,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129034634</v>
+        <v>129035020</v>
       </c>
       <c r="B37" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4186,21 +4181,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4210,10 +4205,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>569200</v>
+        <v>569171</v>
       </c>
       <c r="R37" t="n">
-        <v>6949411</v>
+        <v>6949543</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4246,6 +4241,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på granhögstubbe</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4374,10 +4374,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129034602</v>
+        <v>129035040</v>
       </c>
       <c r="B39" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4409,10 +4409,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>569301</v>
+        <v>569386</v>
       </c>
       <c r="R39" t="n">
-        <v>6949480</v>
+        <v>6949657</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>22 stycken</t>
+          <t>9 ex</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4476,10 +4476,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129035040</v>
+        <v>129035045</v>
       </c>
       <c r="B40" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4511,10 +4511,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>569386</v>
+        <v>569130</v>
       </c>
       <c r="R40" t="n">
-        <v>6949657</v>
+        <v>6949603</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4551,7 +4551,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>9 ex</t>
+          <t>14 ex</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4578,10 +4578,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129035045</v>
+        <v>129034602</v>
       </c>
       <c r="B41" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4613,10 +4613,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>569130</v>
+        <v>569301</v>
       </c>
       <c r="R41" t="n">
-        <v>6949603</v>
+        <v>6949480</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4653,7 +4653,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>14 ex</t>
+          <t>22 stycken</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4680,10 +4680,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129035063</v>
+        <v>129034643</v>
       </c>
       <c r="B42" t="n">
-        <v>96835</v>
+        <v>92832</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4691,21 +4691,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2869</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4715,10 +4715,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>569455</v>
+        <v>569254</v>
       </c>
       <c r="R42" t="n">
-        <v>6949758</v>
+        <v>6949431</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4751,6 +4751,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>1 färskt exemplar</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4777,10 +4782,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129034643</v>
+        <v>129035063</v>
       </c>
       <c r="B43" t="n">
-        <v>92831</v>
+        <v>96843</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4788,21 +4793,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>2869</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4812,10 +4817,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>569254</v>
+        <v>569455</v>
       </c>
       <c r="R43" t="n">
-        <v>6949431</v>
+        <v>6949758</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4848,11 +4853,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>1 färskt exemplar</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5086,7 +5086,7 @@
         <v>129034607</v>
       </c>
       <c r="B46" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
         <v>129035041</v>
       </c>
       <c r="B47" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5287,32 +5287,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129035062</v>
+        <v>129035022</v>
       </c>
       <c r="B48" t="n">
-        <v>96835</v>
+        <v>91848</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2869</v>
+        <v>658</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5322,10 +5322,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>569478</v>
+        <v>569423</v>
       </c>
       <c r="R48" t="n">
-        <v>6949666</v>
+        <v>6949656</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5384,10 +5384,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129035016</v>
+        <v>129034597</v>
       </c>
       <c r="B49" t="n">
-        <v>57727</v>
+        <v>91848</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5395,21 +5395,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5419,10 +5419,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>569435</v>
+        <v>569221</v>
       </c>
       <c r="R49" t="n">
-        <v>6949665</v>
+        <v>6949499</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5459,7 +5459,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>8 exemplar</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5486,32 +5486,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129035002</v>
+        <v>129035062</v>
       </c>
       <c r="B50" t="n">
-        <v>91549</v>
+        <v>96843</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>2869</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5521,10 +5521,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>569405</v>
+        <v>569478</v>
       </c>
       <c r="R50" t="n">
-        <v>6949685</v>
+        <v>6949666</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5583,10 +5583,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129034597</v>
+        <v>129035016</v>
       </c>
       <c r="B51" t="n">
-        <v>91847</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5594,21 +5594,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5618,10 +5618,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>569221</v>
+        <v>569435</v>
       </c>
       <c r="R51" t="n">
-        <v>6949499</v>
+        <v>6949665</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>8 exemplar</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5685,32 +5685,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129035022</v>
+        <v>129034616</v>
       </c>
       <c r="B52" t="n">
-        <v>91847</v>
+        <v>98724</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5720,10 +5720,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>569423</v>
+        <v>569223</v>
       </c>
       <c r="R52" t="n">
-        <v>6949656</v>
+        <v>6949465</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5756,6 +5756,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>10 stycken</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5782,10 +5787,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129034632</v>
+        <v>129035002</v>
       </c>
       <c r="B53" t="n">
-        <v>79044</v>
+        <v>91550</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5793,21 +5798,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5817,10 +5822,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>569237</v>
+        <v>569405</v>
       </c>
       <c r="R53" t="n">
-        <v>6949442</v>
+        <v>6949685</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5879,32 +5884,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129034616</v>
+        <v>129034632</v>
       </c>
       <c r="B54" t="n">
-        <v>98716</v>
+        <v>79044</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5914,10 +5919,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>569223</v>
+        <v>569237</v>
       </c>
       <c r="R54" t="n">
-        <v>6949465</v>
+        <v>6949442</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5950,11 +5955,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>10 stycken</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5981,10 +5981,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129034600</v>
+        <v>129034581</v>
       </c>
       <c r="B55" t="n">
-        <v>80149</v>
+        <v>57887</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5992,21 +5992,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6016,10 +6016,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>569481</v>
+        <v>569223</v>
       </c>
       <c r="R55" t="n">
-        <v>6949674</v>
+        <v>6949401</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Apothecier antal 1</t>
+          <t>Sågs och gjorde övriga läten</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6083,10 +6083,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129035008</v>
+        <v>129035028</v>
       </c>
       <c r="B56" t="n">
-        <v>91549</v>
+        <v>91848</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6094,21 +6094,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6118,10 +6118,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>569216</v>
+        <v>569192</v>
       </c>
       <c r="R56" t="n">
-        <v>6949430</v>
+        <v>6949509</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6180,10 +6180,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129035028</v>
+        <v>129035008</v>
       </c>
       <c r="B57" t="n">
-        <v>91847</v>
+        <v>91550</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6191,21 +6191,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6215,10 +6215,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>569192</v>
+        <v>569216</v>
       </c>
       <c r="R57" t="n">
-        <v>6949509</v>
+        <v>6949430</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6277,32 +6277,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129034610</v>
+        <v>129034600</v>
       </c>
       <c r="B58" t="n">
-        <v>98716</v>
+        <v>80149</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6312,10 +6312,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>569282</v>
+        <v>569481</v>
       </c>
       <c r="R58" t="n">
-        <v>6949567</v>
+        <v>6949674</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ca 100 stycken</t>
+          <t>Apothecier antal 1</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6379,10 +6379,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129034614</v>
+        <v>129034610</v>
       </c>
       <c r="B59" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6414,10 +6414,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>569237</v>
+        <v>569282</v>
       </c>
       <c r="R59" t="n">
-        <v>6949556</v>
+        <v>6949567</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>5 stycken</t>
+          <t>Ca 100 stycken</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6481,32 +6481,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129034581</v>
+        <v>129034614</v>
       </c>
       <c r="B60" t="n">
-        <v>57887</v>
+        <v>98724</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6516,10 +6516,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>569223</v>
+        <v>569237</v>
       </c>
       <c r="R60" t="n">
-        <v>6949401</v>
+        <v>6949556</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6556,7 +6556,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Sågs och gjorde övriga läten</t>
+          <t>5 stycken</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6586,7 +6586,7 @@
         <v>129034586</v>
       </c>
       <c r="B61" t="n">
-        <v>92002</v>
+        <v>92003</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6683,7 +6683,7 @@
         <v>129035024</v>
       </c>
       <c r="B62" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6777,32 +6777,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129035003</v>
+        <v>129035035</v>
       </c>
       <c r="B63" t="n">
-        <v>91549</v>
+        <v>98724</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6812,10 +6812,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>569164</v>
+        <v>569317</v>
       </c>
       <c r="R63" t="n">
-        <v>6949559</v>
+        <v>6949469</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6848,6 +6848,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6874,32 +6879,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129034574</v>
+        <v>129034624</v>
       </c>
       <c r="B64" t="n">
-        <v>91549</v>
+        <v>105790</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6909,10 +6914,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>569461</v>
+        <v>569234</v>
       </c>
       <c r="R64" t="n">
-        <v>6949706</v>
+        <v>6949440</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6945,6 +6950,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>9 exemplar</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6971,10 +6981,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129034587</v>
+        <v>129035003</v>
       </c>
       <c r="B65" t="n">
-        <v>91847</v>
+        <v>91550</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6982,21 +6992,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7006,10 +7016,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>569463</v>
+        <v>569164</v>
       </c>
       <c r="R65" t="n">
-        <v>6949711</v>
+        <v>6949559</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7068,10 +7078,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129035021</v>
+        <v>129034587</v>
       </c>
       <c r="B66" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7103,10 +7113,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>569446</v>
+        <v>569463</v>
       </c>
       <c r="R66" t="n">
-        <v>6949629</v>
+        <v>6949711</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7165,49 +7175,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129027791</v>
+        <v>129035021</v>
       </c>
       <c r="B67" t="n">
-        <v>98716</v>
+        <v>91848</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Sandsjömyran, Mpd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>569308</v>
+        <v>569446</v>
       </c>
       <c r="R67" t="n">
-        <v>6949546</v>
+        <v>6949629</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7266,32 +7272,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129034624</v>
+        <v>129034574</v>
       </c>
       <c r="B68" t="n">
-        <v>105780</v>
+        <v>91550</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7301,10 +7307,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>569234</v>
+        <v>569461</v>
       </c>
       <c r="R68" t="n">
-        <v>6949440</v>
+        <v>6949706</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7337,11 +7343,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>9 exemplar</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7368,10 +7369,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129035035</v>
+        <v>129027791</v>
       </c>
       <c r="B69" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7396,17 +7397,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Sandsjömyran, Mpd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>569317</v>
+        <v>569308</v>
       </c>
       <c r="R69" t="n">
-        <v>6949469</v>
+        <v>6949546</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7439,11 +7444,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>5 ex</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7470,32 +7470,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129035060</v>
+        <v>129034584</v>
       </c>
       <c r="B70" t="n">
-        <v>92831</v>
+        <v>57724</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7505,10 +7505,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>569208</v>
+        <v>569221</v>
       </c>
       <c r="R70" t="n">
-        <v>6949415</v>
+        <v>6949499</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7545,7 +7545,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>20 ex minst</t>
+          <t>Förbiflygande från träd till träd</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7572,32 +7572,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129034639</v>
+        <v>129035018</v>
       </c>
       <c r="B71" t="n">
-        <v>92831</v>
+        <v>57727</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7607,10 +7607,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>569398</v>
+        <v>569111</v>
       </c>
       <c r="R71" t="n">
-        <v>6949741</v>
+        <v>6949604</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7647,7 +7647,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>6 äldre exemplar och 1 färsk fruktkropp</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7677,7 +7677,7 @@
         <v>129035037</v>
       </c>
       <c r="B72" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7776,32 +7776,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129034584</v>
+        <v>129035060</v>
       </c>
       <c r="B73" t="n">
-        <v>57724</v>
+        <v>92832</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7811,10 +7811,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>569221</v>
+        <v>569208</v>
       </c>
       <c r="R73" t="n">
-        <v>6949499</v>
+        <v>6949415</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Förbiflygande från träd till träd</t>
+          <t>20 ex minst</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7878,32 +7878,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129035018</v>
+        <v>129034639</v>
       </c>
       <c r="B74" t="n">
-        <v>57727</v>
+        <v>92832</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7913,10 +7913,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>569111</v>
+        <v>569398</v>
       </c>
       <c r="R74" t="n">
-        <v>6949604</v>
+        <v>6949741</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7953,7 +7953,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>6 äldre exemplar och 1 färsk fruktkropp</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7980,32 +7980,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129026691</v>
+        <v>129034598</v>
       </c>
       <c r="B75" t="n">
-        <v>91847</v>
+        <v>97595</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8015,10 +8015,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>569195</v>
+        <v>569460</v>
       </c>
       <c r="R75" t="n">
-        <v>6949487</v>
+        <v>6949629</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8077,32 +8077,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129034645</v>
+        <v>129034605</v>
       </c>
       <c r="B76" t="n">
-        <v>92831</v>
+        <v>98724</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8112,10 +8112,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>569196</v>
+        <v>569305</v>
       </c>
       <c r="R76" t="n">
-        <v>6949411</v>
+        <v>6949538</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8152,7 +8152,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>4 färska exemplar 3 äldre exemplar</t>
+          <t>21 knärot</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8179,32 +8179,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129034642</v>
+        <v>129026691</v>
       </c>
       <c r="B77" t="n">
-        <v>92831</v>
+        <v>91848</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4364</v>
+        <v>658</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8214,10 +8214,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>569283</v>
+        <v>569195</v>
       </c>
       <c r="R77" t="n">
-        <v>6949655</v>
+        <v>6949487</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8250,11 +8250,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>7 äldre exemplar</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8281,10 +8276,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129034598</v>
+        <v>129034645</v>
       </c>
       <c r="B78" t="n">
-        <v>97587</v>
+        <v>92832</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8292,21 +8287,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8316,10 +8311,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>569460</v>
+        <v>569196</v>
       </c>
       <c r="R78" t="n">
-        <v>6949629</v>
+        <v>6949411</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8352,6 +8347,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>4 färska exemplar 3 äldre exemplar</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8378,32 +8378,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129034650</v>
+        <v>129034642</v>
       </c>
       <c r="B79" t="n">
-        <v>98716</v>
+        <v>92832</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8413,10 +8413,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>569303</v>
+        <v>569283</v>
       </c>
       <c r="R79" t="n">
-        <v>6949537</v>
+        <v>6949655</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8453,7 +8453,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>30 stycken ( finns eventuellt mer )</t>
+          <t>7 äldre exemplar</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8480,10 +8480,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129034605</v>
+        <v>129034650</v>
       </c>
       <c r="B80" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8515,10 +8515,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>569305</v>
+        <v>569303</v>
       </c>
       <c r="R80" t="n">
-        <v>6949538</v>
+        <v>6949537</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8555,7 +8555,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>21 knärot</t>
+          <t>30 stycken ( finns eventuellt mer )</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8582,32 +8582,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129034640</v>
+        <v>129035007</v>
       </c>
       <c r="B81" t="n">
-        <v>92831</v>
+        <v>91550</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8617,10 +8617,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>569213</v>
+        <v>569225</v>
       </c>
       <c r="R81" t="n">
-        <v>6949414</v>
+        <v>6949424</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8653,11 +8653,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>16 exemplar</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8684,10 +8679,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129035001</v>
+        <v>129035061</v>
       </c>
       <c r="B82" t="n">
-        <v>91513</v>
+        <v>96843</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8695,21 +8690,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5447</v>
+        <v>2869</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8719,10 +8714,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>569232</v>
+        <v>569333</v>
       </c>
       <c r="R82" t="n">
-        <v>6949444</v>
+        <v>6949607</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8781,32 +8776,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129035057</v>
+        <v>129035001</v>
       </c>
       <c r="B83" t="n">
-        <v>79044</v>
+        <v>91514</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8816,10 +8811,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>569464</v>
+        <v>569232</v>
       </c>
       <c r="R83" t="n">
-        <v>6949648</v>
+        <v>6949444</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8878,32 +8873,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129035007</v>
+        <v>129034640</v>
       </c>
       <c r="B84" t="n">
-        <v>91549</v>
+        <v>92832</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8913,10 +8908,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>569225</v>
+        <v>569213</v>
       </c>
       <c r="R84" t="n">
-        <v>6949424</v>
+        <v>6949414</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8949,6 +8944,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>16 exemplar</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8975,32 +8975,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129035061</v>
+        <v>129035012</v>
       </c>
       <c r="B85" t="n">
-        <v>96835</v>
+        <v>57727</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9010,10 +9010,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>569333</v>
+        <v>569435</v>
       </c>
       <c r="R85" t="n">
-        <v>6949607</v>
+        <v>6949783</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9046,6 +9046,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9072,32 +9077,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129035012</v>
+        <v>129035047</v>
       </c>
       <c r="B86" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9107,10 +9112,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>569435</v>
+        <v>569162</v>
       </c>
       <c r="R86" t="n">
-        <v>6949783</v>
+        <v>6949566</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9147,7 +9152,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9174,10 +9179,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129035047</v>
+        <v>129034604</v>
       </c>
       <c r="B87" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9209,10 +9214,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>569162</v>
+        <v>569303</v>
       </c>
       <c r="R87" t="n">
-        <v>6949566</v>
+        <v>6949536</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9249,7 +9254,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>50 ex</t>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9276,32 +9281,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129034604</v>
+        <v>129035057</v>
       </c>
       <c r="B88" t="n">
-        <v>98716</v>
+        <v>79044</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9311,10 +9316,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>569303</v>
+        <v>569464</v>
       </c>
       <c r="R88" t="n">
-        <v>6949536</v>
+        <v>6949648</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9347,11 +9352,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9381,7 +9381,7 @@
         <v>129034618</v>
       </c>
       <c r="B89" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9483,7 +9483,7 @@
         <v>129035038</v>
       </c>
       <c r="B90" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9582,10 +9582,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129035050</v>
+        <v>129034621</v>
       </c>
       <c r="B91" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9617,10 +9617,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>569236</v>
+        <v>569247</v>
       </c>
       <c r="R91" t="n">
-        <v>6949440</v>
+        <v>6949434</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9657,7 +9657,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>4 ex</t>
+          <t>10 stycken knärot</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9684,10 +9684,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129034621</v>
+        <v>129035050</v>
       </c>
       <c r="B92" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9719,10 +9719,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>569247</v>
+        <v>569236</v>
       </c>
       <c r="R92" t="n">
-        <v>6949434</v>
+        <v>6949440</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9759,7 +9759,7 @@
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>10 stycken knärot</t>
+          <t>4 ex</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9786,10 +9786,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129035027</v>
+        <v>129035023</v>
       </c>
       <c r="B93" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9821,10 +9821,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>569169</v>
+        <v>569415</v>
       </c>
       <c r="R93" t="n">
-        <v>6949533</v>
+        <v>6949677</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9883,10 +9883,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129035023</v>
+        <v>129035027</v>
       </c>
       <c r="B94" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9918,10 +9918,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>569415</v>
+        <v>569169</v>
       </c>
       <c r="R94" t="n">
-        <v>6949677</v>
+        <v>6949533</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9983,7 +9983,7 @@
         <v>129034589</v>
       </c>
       <c r="B95" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10080,7 +10080,7 @@
         <v>129035029</v>
       </c>
       <c r="B96" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10174,32 +10174,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129034609</v>
+        <v>129034635</v>
       </c>
       <c r="B97" t="n">
-        <v>98716</v>
+        <v>79044</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10209,10 +10209,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>569458</v>
+        <v>569427</v>
       </c>
       <c r="R97" t="n">
-        <v>6949777</v>
+        <v>6949726</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10245,11 +10245,6 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>48 stycken</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10276,10 +10271,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129035036</v>
+        <v>129034609</v>
       </c>
       <c r="B98" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10311,10 +10306,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>569330</v>
+        <v>569458</v>
       </c>
       <c r="R98" t="n">
-        <v>6949564</v>
+        <v>6949777</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10351,7 +10346,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>8 ex</t>
+          <t>48 stycken</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10381,7 +10376,7 @@
         <v>129035052</v>
       </c>
       <c r="B99" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10483,7 +10478,7 @@
         <v>129035056</v>
       </c>
       <c r="B100" t="n">
-        <v>105780</v>
+        <v>105790</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10577,10 +10572,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129034635</v>
+        <v>129035017</v>
       </c>
       <c r="B101" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10588,21 +10583,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10612,10 +10607,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>569427</v>
+        <v>569192</v>
       </c>
       <c r="R101" t="n">
-        <v>6949726</v>
+        <v>6949518</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10648,6 +10643,11 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10674,7 +10674,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129035017</v>
+        <v>129035010</v>
       </c>
       <c r="B102" t="n">
         <v>57727</v>
@@ -10709,10 +10709,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>569192</v>
+        <v>569465</v>
       </c>
       <c r="R102" t="n">
-        <v>6949518</v>
+        <v>6949606</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10749,7 +10749,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10776,32 +10776,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129035010</v>
+        <v>129035036</v>
       </c>
       <c r="B103" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>569465</v>
+        <v>569330</v>
       </c>
       <c r="R103" t="n">
-        <v>6949606</v>
+        <v>6949564</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>8 ex</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10878,10 +10878,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129035006</v>
+        <v>129035026</v>
       </c>
       <c r="B104" t="n">
-        <v>91549</v>
+        <v>91848</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10889,21 +10889,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10913,10 +10913,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>569217</v>
+        <v>569175</v>
       </c>
       <c r="R104" t="n">
-        <v>6949470</v>
+        <v>6949549</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10975,10 +10975,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129027886</v>
+        <v>129035006</v>
       </c>
       <c r="B105" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11010,10 +11010,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>569305</v>
+        <v>569217</v>
       </c>
       <c r="R105" t="n">
-        <v>6949566</v>
+        <v>6949470</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11072,10 +11072,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129035026</v>
+        <v>129027886</v>
       </c>
       <c r="B106" t="n">
-        <v>91847</v>
+        <v>91550</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11083,21 +11083,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11107,10 +11107,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>569175</v>
+        <v>569305</v>
       </c>
       <c r="R106" t="n">
-        <v>6949549</v>
+        <v>6949566</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11172,7 +11172,7 @@
         <v>129035048</v>
       </c>
       <c r="B107" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11271,10 +11271,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129035053</v>
+        <v>129035049</v>
       </c>
       <c r="B108" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11306,10 +11306,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>569459</v>
+        <v>569219</v>
       </c>
       <c r="R108" t="n">
-        <v>6949662</v>
+        <v>6949489</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11346,7 +11346,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>14 ex</t>
+          <t>35 ex</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11373,10 +11373,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129035049</v>
+        <v>129035044</v>
       </c>
       <c r="B109" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11408,10 +11408,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>569219</v>
+        <v>569191</v>
       </c>
       <c r="R109" t="n">
-        <v>6949489</v>
+        <v>6949579</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11448,7 +11448,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>35 ex</t>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11475,10 +11475,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129035044</v>
+        <v>129035053</v>
       </c>
       <c r="B110" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11510,10 +11510,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>569191</v>
+        <v>569459</v>
       </c>
       <c r="R110" t="n">
-        <v>6949579</v>
+        <v>6949662</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11550,7 +11550,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>50 ex</t>
+          <t>14 ex</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11580,7 +11580,7 @@
         <v>129035033</v>
       </c>
       <c r="B111" t="n">
-        <v>91762</v>
+        <v>91763</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11677,7 +11677,7 @@
         <v>129035032</v>
       </c>
       <c r="B112" t="n">
-        <v>91762</v>
+        <v>91763</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>

--- a/artfynd/A 45833-2025 artfynd.xlsx
+++ b/artfynd/A 45833-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129035046</v>
+        <v>129034612</v>
       </c>
       <c r="B2" t="n">
         <v>98724</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569127</v>
+        <v>569243</v>
       </c>
       <c r="R2" t="n">
-        <v>6949602</v>
+        <v>6949558</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>13 ex</t>
+          <t>30  exemplar ca</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129035043</v>
+        <v>129035046</v>
       </c>
       <c r="B3" t="n">
         <v>98724</v>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569204</v>
+        <v>569127</v>
       </c>
       <c r="R3" t="n">
-        <v>6949533</v>
+        <v>6949602</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>10 ex</t>
+          <t>13 ex</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129034627</v>
+        <v>129035043</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569482</v>
+        <v>569204</v>
       </c>
       <c r="R4" t="n">
-        <v>6949676</v>
+        <v>6949533</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -950,6 +950,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,32 +981,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129034612</v>
+        <v>129034627</v>
       </c>
       <c r="B5" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569243</v>
+        <v>569482</v>
       </c>
       <c r="R5" t="n">
-        <v>6949558</v>
+        <v>6949676</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1047,11 +1052,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>30  exemplar ca</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1277,32 +1277,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129035054</v>
+        <v>129035013</v>
       </c>
       <c r="B8" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>569126</v>
+        <v>569455</v>
       </c>
       <c r="R8" t="n">
-        <v>6949570</v>
+        <v>6949716</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>13 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1379,7 +1379,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129035013</v>
+        <v>129035014</v>
       </c>
       <c r="B9" t="n">
         <v>57727</v>
@@ -1417,7 +1417,7 @@
         <v>569455</v>
       </c>
       <c r="R9" t="n">
-        <v>6949716</v>
+        <v>6949703</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1481,32 +1481,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129035014</v>
+        <v>129035054</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>569455</v>
+        <v>569126</v>
       </c>
       <c r="R10" t="n">
-        <v>6949703</v>
+        <v>6949570</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>13 ex</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1583,10 +1583,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129034577</v>
+        <v>129034594</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>91848</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1594,21 +1594,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>569496</v>
+        <v>569203</v>
       </c>
       <c r="R11" t="n">
-        <v>6949627</v>
+        <v>6949498</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på tall</t>
+          <t>11 exemplar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1685,32 +1685,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129035042</v>
+        <v>129034648</v>
       </c>
       <c r="B12" t="n">
-        <v>98724</v>
+        <v>96843</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1720,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569200</v>
+        <v>569279</v>
       </c>
       <c r="R12" t="n">
-        <v>6949533</v>
+        <v>6949401</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1756,11 +1756,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>30 ex</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1787,10 +1782,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129034594</v>
+        <v>129034577</v>
       </c>
       <c r="B13" t="n">
-        <v>91848</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1798,21 +1793,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1822,10 +1817,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569203</v>
+        <v>569496</v>
       </c>
       <c r="R13" t="n">
-        <v>6949498</v>
+        <v>6949627</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1862,7 +1857,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>11 exemplar</t>
+          <t>Äldre ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1889,32 +1884,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129034648</v>
+        <v>129034630</v>
       </c>
       <c r="B14" t="n">
-        <v>96843</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1924,10 +1919,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569279</v>
+        <v>569231</v>
       </c>
       <c r="R14" t="n">
-        <v>6949401</v>
+        <v>6949559</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1986,32 +1981,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129034630</v>
+        <v>129035055</v>
       </c>
       <c r="B15" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2021,10 +2016,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>569231</v>
+        <v>569221</v>
       </c>
       <c r="R15" t="n">
-        <v>6949559</v>
+        <v>6949406</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2057,6 +2052,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2083,7 +2083,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129035055</v>
+        <v>129035042</v>
       </c>
       <c r="B16" t="n">
         <v>98724</v>
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>569221</v>
+        <v>569200</v>
       </c>
       <c r="R16" t="n">
-        <v>6949406</v>
+        <v>6949533</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>25 ex</t>
+          <t>30 ex</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2185,10 +2185,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129034629</v>
+        <v>129035009</v>
       </c>
       <c r="B17" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2196,21 +2196,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2220,10 +2220,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>569247</v>
+        <v>569314</v>
       </c>
       <c r="R17" t="n">
-        <v>6949558</v>
+        <v>6949502</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2256,6 +2256,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2282,32 +2287,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129035059</v>
+        <v>129034580</v>
       </c>
       <c r="B18" t="n">
-        <v>92832</v>
+        <v>57727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2317,10 +2322,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>569273</v>
+        <v>569396</v>
       </c>
       <c r="R18" t="n">
-        <v>6949537</v>
+        <v>6949738</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2353,6 +2358,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på Tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2379,32 +2389,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129034620</v>
+        <v>129035019</v>
       </c>
       <c r="B19" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2414,10 +2424,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>569195</v>
+        <v>569117</v>
       </c>
       <c r="R19" t="n">
-        <v>6949410</v>
+        <v>6949581</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2454,7 +2464,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Blommande knärot 1 exemplar + 21 övriga exemplar blommar ej</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2481,10 +2491,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129035009</v>
+        <v>129034629</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2492,21 +2502,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2516,10 +2526,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>569314</v>
+        <v>569247</v>
       </c>
       <c r="R20" t="n">
-        <v>6949502</v>
+        <v>6949558</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2552,11 +2562,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2583,32 +2588,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129034580</v>
+        <v>129034620</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2618,10 +2623,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>569396</v>
+        <v>569195</v>
       </c>
       <c r="R21" t="n">
-        <v>6949738</v>
+        <v>6949410</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2658,7 +2663,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Äldre ringhack på Tall</t>
+          <t>Blommande knärot 1 exemplar + 21 övriga exemplar blommar ej</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2685,32 +2690,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129035019</v>
+        <v>129035059</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>92832</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2720,10 +2725,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>569117</v>
+        <v>569273</v>
       </c>
       <c r="R22" t="n">
-        <v>6949581</v>
+        <v>6949537</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2756,11 +2761,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2787,10 +2787,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129034592</v>
+        <v>129034647</v>
       </c>
       <c r="B23" t="n">
-        <v>91848</v>
+        <v>88950</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2798,21 +2798,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569205</v>
+        <v>569247</v>
       </c>
       <c r="R23" t="n">
-        <v>6949497</v>
+        <v>6949558</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2858,11 +2858,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>1 x</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2889,7 +2884,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129034591</v>
+        <v>129034592</v>
       </c>
       <c r="B24" t="n">
         <v>91848</v>
@@ -2924,10 +2919,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569203</v>
+        <v>569205</v>
       </c>
       <c r="R24" t="n">
-        <v>6949513</v>
+        <v>6949497</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2964,7 +2959,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>11 ex</t>
+          <t>1 x</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2991,10 +2986,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129034647</v>
+        <v>129034591</v>
       </c>
       <c r="B25" t="n">
-        <v>88950</v>
+        <v>91848</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3002,21 +2997,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3026,10 +3021,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569247</v>
+        <v>569203</v>
       </c>
       <c r="R25" t="n">
-        <v>6949558</v>
+        <v>6949513</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3062,6 +3057,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>11 ex</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3578,32 +3578,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129034637</v>
+        <v>129035031</v>
       </c>
       <c r="B31" t="n">
-        <v>92832</v>
+        <v>80149</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>569229</v>
+        <v>569125</v>
       </c>
       <c r="R31" t="n">
-        <v>6949400</v>
+        <v>6949570</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3675,10 +3675,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129035031</v>
+        <v>129034578</v>
       </c>
       <c r="B32" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3686,21 +3686,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3710,10 +3710,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>569125</v>
+        <v>569420</v>
       </c>
       <c r="R32" t="n">
-        <v>6949570</v>
+        <v>6949723</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3746,6 +3746,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3772,32 +3777,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129035051</v>
+        <v>129035058</v>
       </c>
       <c r="B33" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3807,10 +3812,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>569222</v>
+        <v>569388</v>
       </c>
       <c r="R33" t="n">
-        <v>6949414</v>
+        <v>6949647</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3843,11 +3848,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>30 ex</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3874,32 +3874,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129035058</v>
+        <v>129034637</v>
       </c>
       <c r="B34" t="n">
-        <v>79044</v>
+        <v>92832</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3909,10 +3909,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>569388</v>
+        <v>569229</v>
       </c>
       <c r="R34" t="n">
-        <v>6949647</v>
+        <v>6949400</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3971,32 +3971,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129034578</v>
+        <v>129035051</v>
       </c>
       <c r="B35" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4006,10 +4006,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>569420</v>
+        <v>569222</v>
       </c>
       <c r="R35" t="n">
-        <v>6949723</v>
+        <v>6949414</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på Tall</t>
+          <t>30 ex</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4073,10 +4073,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129034634</v>
+        <v>129035020</v>
       </c>
       <c r="B36" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4084,21 +4084,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4108,10 +4108,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>569200</v>
+        <v>569171</v>
       </c>
       <c r="R36" t="n">
-        <v>6949411</v>
+        <v>6949543</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4144,6 +4144,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på granhögstubbe</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4170,7 +4175,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129035020</v>
+        <v>129035015</v>
       </c>
       <c r="B37" t="n">
         <v>57727</v>
@@ -4205,10 +4210,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>569171</v>
+        <v>569454</v>
       </c>
       <c r="R37" t="n">
-        <v>6949543</v>
+        <v>6949698</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4245,7 +4250,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Äldre ringhack på granhögstubbe</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4272,10 +4277,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129035015</v>
+        <v>129034634</v>
       </c>
       <c r="B38" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4283,21 +4288,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4307,10 +4312,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>569454</v>
+        <v>569200</v>
       </c>
       <c r="R38" t="n">
-        <v>6949698</v>
+        <v>6949411</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4343,11 +4348,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4374,7 +4374,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129035040</v>
+        <v>129034602</v>
       </c>
       <c r="B39" t="n">
         <v>98724</v>
@@ -4409,10 +4409,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>569386</v>
+        <v>569301</v>
       </c>
       <c r="R39" t="n">
-        <v>6949657</v>
+        <v>6949480</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>9 ex</t>
+          <t>22 stycken</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4476,7 +4476,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129035045</v>
+        <v>129035040</v>
       </c>
       <c r="B40" t="n">
         <v>98724</v>
@@ -4511,10 +4511,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>569130</v>
+        <v>569386</v>
       </c>
       <c r="R40" t="n">
-        <v>6949603</v>
+        <v>6949657</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4551,7 +4551,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>14 ex</t>
+          <t>9 ex</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4578,7 +4578,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129034602</v>
+        <v>129035045</v>
       </c>
       <c r="B41" t="n">
         <v>98724</v>
@@ -4613,10 +4613,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>569301</v>
+        <v>569130</v>
       </c>
       <c r="R41" t="n">
-        <v>6949480</v>
+        <v>6949603</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4653,7 +4653,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>22 stycken</t>
+          <t>14 ex</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4680,10 +4680,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129034643</v>
+        <v>129035063</v>
       </c>
       <c r="B42" t="n">
-        <v>92832</v>
+        <v>96843</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4691,21 +4691,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>2869</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4715,10 +4715,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>569254</v>
+        <v>569455</v>
       </c>
       <c r="R42" t="n">
-        <v>6949431</v>
+        <v>6949758</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4751,11 +4751,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>1 färskt exemplar</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4782,10 +4777,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129035063</v>
+        <v>129034643</v>
       </c>
       <c r="B43" t="n">
-        <v>96843</v>
+        <v>92832</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4793,21 +4788,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2869</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4817,10 +4812,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>569455</v>
+        <v>569254</v>
       </c>
       <c r="R43" t="n">
-        <v>6949758</v>
+        <v>6949431</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4853,6 +4848,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>1 färskt exemplar</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4879,32 +4879,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129034575</v>
+        <v>129034607</v>
       </c>
       <c r="B44" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4914,10 +4914,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>569448</v>
+        <v>569317</v>
       </c>
       <c r="R44" t="n">
-        <v>6949625</v>
+        <v>6949549</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Färska ringhack på Tall av tretåig hackspett</t>
+          <t>31 stycken</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4981,32 +4981,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129035011</v>
+        <v>129035041</v>
       </c>
       <c r="B45" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5016,10 +5016,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>569442</v>
+        <v>569262</v>
       </c>
       <c r="R45" t="n">
-        <v>6949783</v>
+        <v>6949524</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5083,32 +5083,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129034607</v>
+        <v>129034575</v>
       </c>
       <c r="B46" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5118,10 +5118,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>569317</v>
+        <v>569448</v>
       </c>
       <c r="R46" t="n">
-        <v>6949549</v>
+        <v>6949625</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>31 stycken</t>
+          <t>Färska ringhack på Tall av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5185,32 +5185,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129035041</v>
+        <v>129035011</v>
       </c>
       <c r="B47" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5220,10 +5220,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>569262</v>
+        <v>569442</v>
       </c>
       <c r="R47" t="n">
-        <v>6949524</v>
+        <v>6949783</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5260,7 +5260,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>5 ex</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5287,10 +5287,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129035022</v>
+        <v>129034632</v>
       </c>
       <c r="B48" t="n">
-        <v>91848</v>
+        <v>79044</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5298,21 +5298,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5322,10 +5322,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>569423</v>
+        <v>569237</v>
       </c>
       <c r="R48" t="n">
-        <v>6949656</v>
+        <v>6949442</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5384,7 +5384,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129034597</v>
+        <v>129035022</v>
       </c>
       <c r="B49" t="n">
         <v>91848</v>
@@ -5419,10 +5419,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>569221</v>
+        <v>569423</v>
       </c>
       <c r="R49" t="n">
-        <v>6949499</v>
+        <v>6949656</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5455,11 +5455,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>8 exemplar</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5486,32 +5481,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129035062</v>
+        <v>129034597</v>
       </c>
       <c r="B50" t="n">
-        <v>96843</v>
+        <v>91848</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2869</v>
+        <v>658</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5521,10 +5516,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>569478</v>
+        <v>569221</v>
       </c>
       <c r="R50" t="n">
-        <v>6949666</v>
+        <v>6949499</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5557,6 +5552,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>8 exemplar</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5583,10 +5583,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129035016</v>
+        <v>129035002</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>91550</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5594,21 +5594,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5618,10 +5618,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>569435</v>
+        <v>569405</v>
       </c>
       <c r="R51" t="n">
-        <v>6949665</v>
+        <v>6949685</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5654,11 +5654,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5685,32 +5680,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129034616</v>
+        <v>129035062</v>
       </c>
       <c r="B52" t="n">
-        <v>98724</v>
+        <v>96843</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5720,10 +5715,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>569223</v>
+        <v>569478</v>
       </c>
       <c r="R52" t="n">
-        <v>6949465</v>
+        <v>6949666</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5756,11 +5751,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>10 stycken</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5787,10 +5777,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129035002</v>
+        <v>129035016</v>
       </c>
       <c r="B53" t="n">
-        <v>91550</v>
+        <v>57727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5798,21 +5788,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5822,10 +5812,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>569405</v>
+        <v>569435</v>
       </c>
       <c r="R53" t="n">
-        <v>6949685</v>
+        <v>6949665</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5858,6 +5848,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5884,32 +5879,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129034632</v>
+        <v>129034616</v>
       </c>
       <c r="B54" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5919,10 +5914,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>569237</v>
+        <v>569223</v>
       </c>
       <c r="R54" t="n">
-        <v>6949442</v>
+        <v>6949465</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5955,6 +5950,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>10 stycken</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5981,10 +5981,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129034581</v>
+        <v>129035028</v>
       </c>
       <c r="B55" t="n">
-        <v>57887</v>
+        <v>91848</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5992,21 +5992,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6016,10 +6016,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>569223</v>
+        <v>569192</v>
       </c>
       <c r="R55" t="n">
-        <v>6949401</v>
+        <v>6949509</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6052,11 +6052,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Sågs och gjorde övriga läten</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6083,10 +6078,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129035028</v>
+        <v>129035008</v>
       </c>
       <c r="B56" t="n">
-        <v>91848</v>
+        <v>91550</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6094,21 +6089,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6118,10 +6113,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>569192</v>
+        <v>569216</v>
       </c>
       <c r="R56" t="n">
-        <v>6949509</v>
+        <v>6949430</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6180,10 +6175,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129035008</v>
+        <v>129034600</v>
       </c>
       <c r="B57" t="n">
-        <v>91550</v>
+        <v>80149</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6191,21 +6186,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6215,10 +6210,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>569216</v>
+        <v>569481</v>
       </c>
       <c r="R57" t="n">
-        <v>6949430</v>
+        <v>6949674</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6251,6 +6246,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Apothecier antal 1</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6277,32 +6277,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129034600</v>
+        <v>129034610</v>
       </c>
       <c r="B58" t="n">
-        <v>80149</v>
+        <v>98724</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6312,10 +6312,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>569481</v>
+        <v>569282</v>
       </c>
       <c r="R58" t="n">
-        <v>6949674</v>
+        <v>6949567</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Apothecier antal 1</t>
+          <t>Ca 100 stycken</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6379,7 +6379,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129034610</v>
+        <v>129034614</v>
       </c>
       <c r="B59" t="n">
         <v>98724</v>
@@ -6414,10 +6414,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>569282</v>
+        <v>569237</v>
       </c>
       <c r="R59" t="n">
-        <v>6949567</v>
+        <v>6949556</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ca 100 stycken</t>
+          <t>5 stycken</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6481,32 +6481,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129034614</v>
+        <v>129034581</v>
       </c>
       <c r="B60" t="n">
-        <v>98724</v>
+        <v>57887</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6516,10 +6516,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>569237</v>
+        <v>569223</v>
       </c>
       <c r="R60" t="n">
-        <v>6949556</v>
+        <v>6949401</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6556,7 +6556,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>5 stycken</t>
+          <t>Sågs och gjorde övriga läten</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6777,7 +6777,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129035035</v>
+        <v>129027791</v>
       </c>
       <c r="B63" t="n">
         <v>98724</v>
@@ -6805,17 +6805,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Sandsjömyran, Mpd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>569317</v>
+        <v>569308</v>
       </c>
       <c r="R63" t="n">
-        <v>6949469</v>
+        <v>6949546</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6848,11 +6852,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>5 ex</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6981,32 +6980,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129035003</v>
+        <v>129035035</v>
       </c>
       <c r="B65" t="n">
-        <v>91550</v>
+        <v>98724</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7016,10 +7015,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>569164</v>
+        <v>569317</v>
       </c>
       <c r="R65" t="n">
-        <v>6949559</v>
+        <v>6949469</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7052,6 +7051,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7078,10 +7082,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129034587</v>
+        <v>129035003</v>
       </c>
       <c r="B66" t="n">
-        <v>91848</v>
+        <v>91550</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7089,21 +7093,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7113,10 +7117,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>569463</v>
+        <v>569164</v>
       </c>
       <c r="R66" t="n">
-        <v>6949711</v>
+        <v>6949559</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7175,7 +7179,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129035021</v>
+        <v>129034587</v>
       </c>
       <c r="B67" t="n">
         <v>91848</v>
@@ -7210,10 +7214,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>569446</v>
+        <v>569463</v>
       </c>
       <c r="R67" t="n">
-        <v>6949629</v>
+        <v>6949711</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7272,10 +7276,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129034574</v>
+        <v>129035021</v>
       </c>
       <c r="B68" t="n">
-        <v>91550</v>
+        <v>91848</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7283,21 +7287,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7307,10 +7311,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>569461</v>
+        <v>569446</v>
       </c>
       <c r="R68" t="n">
-        <v>6949706</v>
+        <v>6949629</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7369,49 +7373,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129027791</v>
+        <v>129034574</v>
       </c>
       <c r="B69" t="n">
-        <v>98724</v>
+        <v>91550</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Sandsjömyran, Mpd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>569308</v>
+        <v>569461</v>
       </c>
       <c r="R69" t="n">
-        <v>6949546</v>
+        <v>6949706</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7470,32 +7470,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129034584</v>
+        <v>129035060</v>
       </c>
       <c r="B70" t="n">
-        <v>57724</v>
+        <v>92832</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7505,10 +7505,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>569221</v>
+        <v>569208</v>
       </c>
       <c r="R70" t="n">
-        <v>6949499</v>
+        <v>6949415</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7545,7 +7545,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Förbiflygande från träd till träd</t>
+          <t>20 ex minst</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7674,32 +7674,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129035037</v>
+        <v>129034584</v>
       </c>
       <c r="B72" t="n">
-        <v>98724</v>
+        <v>57724</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7709,10 +7709,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>569434</v>
+        <v>569221</v>
       </c>
       <c r="R72" t="n">
-        <v>6949706</v>
+        <v>6949499</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7749,7 +7749,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>20 ex</t>
+          <t>Förbiflygande från träd till träd</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7776,32 +7776,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129035060</v>
+        <v>129035037</v>
       </c>
       <c r="B73" t="n">
-        <v>92832</v>
+        <v>98724</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7811,10 +7811,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>569208</v>
+        <v>569434</v>
       </c>
       <c r="R73" t="n">
-        <v>6949415</v>
+        <v>6949706</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>20 ex minst</t>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7980,32 +7980,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129034598</v>
+        <v>129026691</v>
       </c>
       <c r="B75" t="n">
-        <v>97595</v>
+        <v>91848</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8015,10 +8015,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>569460</v>
+        <v>569195</v>
       </c>
       <c r="R75" t="n">
-        <v>6949629</v>
+        <v>6949487</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8077,32 +8077,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129034605</v>
+        <v>129034645</v>
       </c>
       <c r="B76" t="n">
-        <v>98724</v>
+        <v>92832</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8112,10 +8112,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>569305</v>
+        <v>569196</v>
       </c>
       <c r="R76" t="n">
-        <v>6949538</v>
+        <v>6949411</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8152,7 +8152,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>21 knärot</t>
+          <t>4 färska exemplar 3 äldre exemplar</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8179,32 +8179,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129026691</v>
+        <v>129034642</v>
       </c>
       <c r="B77" t="n">
-        <v>91848</v>
+        <v>92832</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8214,10 +8214,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>569195</v>
+        <v>569283</v>
       </c>
       <c r="R77" t="n">
-        <v>6949487</v>
+        <v>6949655</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8250,6 +8250,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>7 äldre exemplar</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8276,10 +8281,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129034645</v>
+        <v>129034598</v>
       </c>
       <c r="B78" t="n">
-        <v>92832</v>
+        <v>97595</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8287,21 +8292,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8311,10 +8316,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>569196</v>
+        <v>569460</v>
       </c>
       <c r="R78" t="n">
-        <v>6949411</v>
+        <v>6949629</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8347,11 +8352,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>4 färska exemplar 3 äldre exemplar</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8378,32 +8378,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129034642</v>
+        <v>129034650</v>
       </c>
       <c r="B79" t="n">
-        <v>92832</v>
+        <v>98724</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8413,10 +8413,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>569283</v>
+        <v>569303</v>
       </c>
       <c r="R79" t="n">
-        <v>6949655</v>
+        <v>6949537</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8453,7 +8453,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>7 äldre exemplar</t>
+          <t>30 stycken ( finns eventuellt mer )</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8480,7 +8480,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129034650</v>
+        <v>129034605</v>
       </c>
       <c r="B80" t="n">
         <v>98724</v>
@@ -8515,10 +8515,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>569303</v>
+        <v>569305</v>
       </c>
       <c r="R80" t="n">
-        <v>6949537</v>
+        <v>6949538</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8555,7 +8555,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>30 stycken ( finns eventuellt mer )</t>
+          <t>21 knärot</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8679,32 +8679,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129035061</v>
+        <v>129035012</v>
       </c>
       <c r="B82" t="n">
-        <v>96843</v>
+        <v>57727</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8714,10 +8714,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>569333</v>
+        <v>569435</v>
       </c>
       <c r="R82" t="n">
-        <v>6949607</v>
+        <v>6949783</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8750,6 +8750,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8776,32 +8781,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129035001</v>
+        <v>129035057</v>
       </c>
       <c r="B83" t="n">
-        <v>91514</v>
+        <v>79044</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8811,10 +8816,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>569232</v>
+        <v>569464</v>
       </c>
       <c r="R83" t="n">
-        <v>6949444</v>
+        <v>6949648</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8873,10 +8878,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129034640</v>
+        <v>129035001</v>
       </c>
       <c r="B84" t="n">
-        <v>92832</v>
+        <v>91514</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8884,21 +8889,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8908,10 +8913,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>569213</v>
+        <v>569232</v>
       </c>
       <c r="R84" t="n">
-        <v>6949414</v>
+        <v>6949444</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8944,11 +8949,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>16 exemplar</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8975,32 +8975,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129035012</v>
+        <v>129035061</v>
       </c>
       <c r="B85" t="n">
-        <v>57727</v>
+        <v>96843</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9010,10 +9010,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>569435</v>
+        <v>569333</v>
       </c>
       <c r="R85" t="n">
-        <v>6949783</v>
+        <v>6949607</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9046,11 +9046,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9077,32 +9072,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129035047</v>
+        <v>129034640</v>
       </c>
       <c r="B86" t="n">
-        <v>98724</v>
+        <v>92832</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9112,10 +9107,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>569162</v>
+        <v>569213</v>
       </c>
       <c r="R86" t="n">
-        <v>6949566</v>
+        <v>6949414</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9152,7 +9147,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>50 ex</t>
+          <t>16 exemplar</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9179,7 +9174,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129034604</v>
+        <v>129035047</v>
       </c>
       <c r="B87" t="n">
         <v>98724</v>
@@ -9214,10 +9209,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>569303</v>
+        <v>569162</v>
       </c>
       <c r="R87" t="n">
-        <v>6949536</v>
+        <v>6949566</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9254,7 +9249,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>40 stycken</t>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9281,32 +9276,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129035057</v>
+        <v>129034604</v>
       </c>
       <c r="B88" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9316,10 +9311,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>569464</v>
+        <v>569303</v>
       </c>
       <c r="R88" t="n">
-        <v>6949648</v>
+        <v>6949536</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9352,6 +9347,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9480,32 +9480,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129035038</v>
+        <v>129035023</v>
       </c>
       <c r="B90" t="n">
-        <v>98724</v>
+        <v>91848</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9515,10 +9515,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>569406</v>
+        <v>569415</v>
       </c>
       <c r="R90" t="n">
-        <v>6949664</v>
+        <v>6949677</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9551,11 +9551,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>20 ex</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9582,32 +9577,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129034621</v>
+        <v>129035027</v>
       </c>
       <c r="B91" t="n">
-        <v>98724</v>
+        <v>91848</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9617,10 +9612,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>569247</v>
+        <v>569169</v>
       </c>
       <c r="R91" t="n">
-        <v>6949434</v>
+        <v>6949533</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9653,11 +9648,6 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>10 stycken knärot</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9684,32 +9674,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129035050</v>
+        <v>129034589</v>
       </c>
       <c r="B92" t="n">
-        <v>98724</v>
+        <v>91848</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9719,10 +9709,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>569236</v>
+        <v>569365</v>
       </c>
       <c r="R92" t="n">
-        <v>6949440</v>
+        <v>6949661</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9755,11 +9745,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>4 ex</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9786,7 +9771,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129035023</v>
+        <v>129035029</v>
       </c>
       <c r="B93" t="n">
         <v>91848</v>
@@ -9821,10 +9806,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>569415</v>
+        <v>569217</v>
       </c>
       <c r="R93" t="n">
-        <v>6949677</v>
+        <v>6949427</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9883,32 +9868,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129035027</v>
+        <v>129035038</v>
       </c>
       <c r="B94" t="n">
-        <v>91848</v>
+        <v>98724</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9918,10 +9903,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>569169</v>
+        <v>569406</v>
       </c>
       <c r="R94" t="n">
-        <v>6949533</v>
+        <v>6949664</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9954,6 +9939,11 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -9980,32 +9970,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129034589</v>
+        <v>129035050</v>
       </c>
       <c r="B95" t="n">
-        <v>91848</v>
+        <v>98724</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10015,10 +10005,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>569365</v>
+        <v>569236</v>
       </c>
       <c r="R95" t="n">
-        <v>6949661</v>
+        <v>6949440</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10051,6 +10041,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>4 ex</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10077,32 +10072,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129035029</v>
+        <v>129034621</v>
       </c>
       <c r="B96" t="n">
-        <v>91848</v>
+        <v>98724</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10112,10 +10107,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>569217</v>
+        <v>569247</v>
       </c>
       <c r="R96" t="n">
-        <v>6949427</v>
+        <v>6949434</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10148,6 +10143,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>10 stycken knärot</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10174,10 +10174,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129034635</v>
+        <v>129035017</v>
       </c>
       <c r="B97" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10185,21 +10185,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10209,10 +10209,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>569427</v>
+        <v>569192</v>
       </c>
       <c r="R97" t="n">
-        <v>6949726</v>
+        <v>6949518</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10245,6 +10245,11 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10271,32 +10276,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129034609</v>
+        <v>129035010</v>
       </c>
       <c r="B98" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10306,10 +10311,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>569458</v>
+        <v>569465</v>
       </c>
       <c r="R98" t="n">
-        <v>6949777</v>
+        <v>6949606</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10346,7 +10351,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>48 stycken</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10373,32 +10378,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129035052</v>
+        <v>129034635</v>
       </c>
       <c r="B99" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10408,10 +10413,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>569405</v>
+        <v>569427</v>
       </c>
       <c r="R99" t="n">
-        <v>6949641</v>
+        <v>6949726</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10444,11 +10449,6 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>70 ex</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10475,32 +10475,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129035056</v>
+        <v>129034609</v>
       </c>
       <c r="B100" t="n">
-        <v>105790</v>
+        <v>98724</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10510,10 +10510,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>569201</v>
+        <v>569458</v>
       </c>
       <c r="R100" t="n">
-        <v>6949530</v>
+        <v>6949777</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10546,6 +10546,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>48 stycken</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10572,32 +10577,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129035017</v>
+        <v>129035036</v>
       </c>
       <c r="B101" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10607,10 +10612,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>569192</v>
+        <v>569330</v>
       </c>
       <c r="R101" t="n">
-        <v>6949518</v>
+        <v>6949564</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10647,7 +10652,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>8 ex</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10674,32 +10679,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129035010</v>
+        <v>129035052</v>
       </c>
       <c r="B102" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10709,10 +10714,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>569465</v>
+        <v>569405</v>
       </c>
       <c r="R102" t="n">
-        <v>6949606</v>
+        <v>6949641</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10749,7 +10754,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>70 ex</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10776,32 +10781,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129035036</v>
+        <v>129035056</v>
       </c>
       <c r="B103" t="n">
-        <v>98724</v>
+        <v>105790</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10811,10 +10816,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>569330</v>
+        <v>569201</v>
       </c>
       <c r="R103" t="n">
-        <v>6949564</v>
+        <v>6949530</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10847,11 +10852,6 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>8 ex</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11271,7 +11271,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129035049</v>
+        <v>129035053</v>
       </c>
       <c r="B108" t="n">
         <v>98724</v>
@@ -11306,10 +11306,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>569219</v>
+        <v>569459</v>
       </c>
       <c r="R108" t="n">
-        <v>6949489</v>
+        <v>6949662</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11346,7 +11346,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>35 ex</t>
+          <t>14 ex</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11373,7 +11373,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129035044</v>
+        <v>129035049</v>
       </c>
       <c r="B109" t="n">
         <v>98724</v>
@@ -11408,10 +11408,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>569191</v>
+        <v>569219</v>
       </c>
       <c r="R109" t="n">
-        <v>6949579</v>
+        <v>6949489</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11448,7 +11448,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>50 ex</t>
+          <t>35 ex</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11475,7 +11475,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129035053</v>
+        <v>129035044</v>
       </c>
       <c r="B110" t="n">
         <v>98724</v>
@@ -11510,10 +11510,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>569459</v>
+        <v>569191</v>
       </c>
       <c r="R110" t="n">
-        <v>6949662</v>
+        <v>6949579</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11550,7 +11550,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>14 ex</t>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD110" t="b">

--- a/artfynd/A 45833-2025 artfynd.xlsx
+++ b/artfynd/A 45833-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY112"/>
+  <dimension ref="A1:AY111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1078,32 +1078,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129035030</v>
+        <v>129035039</v>
       </c>
       <c r="B6" t="n">
-        <v>97595</v>
+        <v>98724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>569424</v>
+        <v>569394</v>
       </c>
       <c r="R6" t="n">
-        <v>6949671</v>
+        <v>6949664</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1149,6 +1149,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1175,32 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129035039</v>
+        <v>129035030</v>
       </c>
       <c r="B7" t="n">
-        <v>98724</v>
+        <v>97595</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>569394</v>
+        <v>569424</v>
       </c>
       <c r="R7" t="n">
-        <v>6949664</v>
+        <v>6949671</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1246,11 +1251,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -2787,10 +2787,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129034647</v>
+        <v>129034592</v>
       </c>
       <c r="B23" t="n">
-        <v>88950</v>
+        <v>91848</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2798,21 +2798,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>569247</v>
+        <v>569205</v>
       </c>
       <c r="R23" t="n">
-        <v>6949558</v>
+        <v>6949497</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2858,6 +2858,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>1 x</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2884,7 +2889,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129034592</v>
+        <v>129034591</v>
       </c>
       <c r="B24" t="n">
         <v>91848</v>
@@ -2919,10 +2924,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>569205</v>
+        <v>569203</v>
       </c>
       <c r="R24" t="n">
-        <v>6949497</v>
+        <v>6949513</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2959,7 +2964,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>1 x</t>
+          <t>11 ex</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2986,10 +2991,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129034591</v>
+        <v>129035004</v>
       </c>
       <c r="B25" t="n">
-        <v>91848</v>
+        <v>91550</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2997,21 +3002,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3021,10 +3026,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569203</v>
+        <v>569152</v>
       </c>
       <c r="R25" t="n">
-        <v>6949513</v>
+        <v>6949557</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3057,11 +3062,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>11 ex</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3088,10 +3088,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129035004</v>
+        <v>129035025</v>
       </c>
       <c r="B26" t="n">
-        <v>91550</v>
+        <v>91848</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3099,21 +3099,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3123,10 +3123,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569152</v>
+        <v>569388</v>
       </c>
       <c r="R26" t="n">
-        <v>6949557</v>
+        <v>6949665</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3185,10 +3185,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129035025</v>
+        <v>129035005</v>
       </c>
       <c r="B27" t="n">
-        <v>91848</v>
+        <v>91550</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3196,21 +3196,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3220,10 +3220,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>569388</v>
+        <v>569188</v>
       </c>
       <c r="R27" t="n">
-        <v>6949665</v>
+        <v>6949496</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3282,10 +3282,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129035005</v>
+        <v>129034625</v>
       </c>
       <c r="B28" t="n">
-        <v>91550</v>
+        <v>79044</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3293,21 +3293,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3317,10 +3317,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>569188</v>
+        <v>569479</v>
       </c>
       <c r="R28" t="n">
-        <v>6949496</v>
+        <v>6949657</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3379,10 +3379,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129034625</v>
+        <v>129034647</v>
       </c>
       <c r="B29" t="n">
-        <v>79044</v>
+        <v>88950</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3390,21 +3390,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3414,10 +3414,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>569479</v>
+        <v>569247</v>
       </c>
       <c r="R29" t="n">
-        <v>6949657</v>
+        <v>6949558</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3675,32 +3675,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129034578</v>
+        <v>129034637</v>
       </c>
       <c r="B32" t="n">
-        <v>57727</v>
+        <v>92832</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3710,10 +3710,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>569420</v>
+        <v>569229</v>
       </c>
       <c r="R32" t="n">
-        <v>6949723</v>
+        <v>6949400</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3746,11 +3746,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3777,10 +3772,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129035058</v>
+        <v>129034578</v>
       </c>
       <c r="B33" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3788,21 +3783,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3812,10 +3807,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>569388</v>
+        <v>569420</v>
       </c>
       <c r="R33" t="n">
-        <v>6949647</v>
+        <v>6949723</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3848,6 +3843,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3874,32 +3874,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129034637</v>
+        <v>129035058</v>
       </c>
       <c r="B34" t="n">
-        <v>92832</v>
+        <v>79044</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3909,10 +3909,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>569229</v>
+        <v>569388</v>
       </c>
       <c r="R34" t="n">
-        <v>6949400</v>
+        <v>6949647</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5083,7 +5083,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129034575</v>
+        <v>129035011</v>
       </c>
       <c r="B46" t="n">
         <v>57727</v>
@@ -5118,10 +5118,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>569448</v>
+        <v>569442</v>
       </c>
       <c r="R46" t="n">
-        <v>6949625</v>
+        <v>6949783</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Färska ringhack på Tall av tretåig hackspett</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5185,7 +5185,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129035011</v>
+        <v>129034575</v>
       </c>
       <c r="B47" t="n">
         <v>57727</v>
@@ -5220,10 +5220,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>569442</v>
+        <v>569448</v>
       </c>
       <c r="R47" t="n">
-        <v>6949783</v>
+        <v>6949625</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5260,7 +5260,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på Tall av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5287,10 +5287,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129034632</v>
+        <v>129035022</v>
       </c>
       <c r="B48" t="n">
-        <v>79044</v>
+        <v>91848</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5298,21 +5298,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5322,10 +5322,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>569237</v>
+        <v>569423</v>
       </c>
       <c r="R48" t="n">
-        <v>6949442</v>
+        <v>6949656</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5384,7 +5384,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129035022</v>
+        <v>129034597</v>
       </c>
       <c r="B49" t="n">
         <v>91848</v>
@@ -5419,10 +5419,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>569423</v>
+        <v>569221</v>
       </c>
       <c r="R49" t="n">
-        <v>6949656</v>
+        <v>6949499</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5455,6 +5455,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>8 exemplar</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5481,10 +5486,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129034597</v>
+        <v>129035002</v>
       </c>
       <c r="B50" t="n">
-        <v>91848</v>
+        <v>91550</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5492,21 +5497,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5516,10 +5521,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>569221</v>
+        <v>569405</v>
       </c>
       <c r="R50" t="n">
-        <v>6949499</v>
+        <v>6949685</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5552,11 +5557,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>8 exemplar</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5583,10 +5583,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129035002</v>
+        <v>129034632</v>
       </c>
       <c r="B51" t="n">
-        <v>91550</v>
+        <v>79044</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5594,21 +5594,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5618,10 +5618,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>569405</v>
+        <v>569237</v>
       </c>
       <c r="R51" t="n">
-        <v>6949685</v>
+        <v>6949442</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -8582,32 +8582,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129035007</v>
+        <v>129035047</v>
       </c>
       <c r="B81" t="n">
-        <v>91550</v>
+        <v>98724</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8617,10 +8617,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>569225</v>
+        <v>569162</v>
       </c>
       <c r="R81" t="n">
-        <v>6949424</v>
+        <v>6949566</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8653,6 +8653,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8679,32 +8684,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129035012</v>
+        <v>129034604</v>
       </c>
       <c r="B82" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8714,10 +8719,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>569435</v>
+        <v>569303</v>
       </c>
       <c r="R82" t="n">
-        <v>6949783</v>
+        <v>6949536</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8754,7 +8759,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8781,32 +8786,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129035057</v>
+        <v>129034618</v>
       </c>
       <c r="B83" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8816,10 +8821,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>569464</v>
+        <v>569235</v>
       </c>
       <c r="R83" t="n">
-        <v>6949648</v>
+        <v>6949411</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8852,6 +8857,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8975,32 +8985,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129035061</v>
+        <v>129035007</v>
       </c>
       <c r="B85" t="n">
-        <v>96843</v>
+        <v>91550</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2869</v>
+        <v>1202</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9010,10 +9020,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>569333</v>
+        <v>569225</v>
       </c>
       <c r="R85" t="n">
-        <v>6949607</v>
+        <v>6949424</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9072,10 +9082,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129034640</v>
+        <v>129035061</v>
       </c>
       <c r="B86" t="n">
-        <v>92832</v>
+        <v>96843</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9083,21 +9093,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4364</v>
+        <v>2869</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9107,10 +9117,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>569213</v>
+        <v>569333</v>
       </c>
       <c r="R86" t="n">
-        <v>6949414</v>
+        <v>6949607</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9143,11 +9153,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>16 exemplar</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9174,32 +9179,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129035047</v>
+        <v>129035012</v>
       </c>
       <c r="B87" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9209,10 +9214,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>569162</v>
+        <v>569435</v>
       </c>
       <c r="R87" t="n">
-        <v>6949566</v>
+        <v>6949783</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9249,7 +9254,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>50 ex</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9276,32 +9281,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129034604</v>
+        <v>129035057</v>
       </c>
       <c r="B88" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9311,10 +9316,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>569303</v>
+        <v>569464</v>
       </c>
       <c r="R88" t="n">
-        <v>6949536</v>
+        <v>6949648</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9347,11 +9352,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9378,32 +9378,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129034618</v>
+        <v>129034640</v>
       </c>
       <c r="B89" t="n">
-        <v>98724</v>
+        <v>92832</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9413,10 +9413,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>569235</v>
+        <v>569213</v>
       </c>
       <c r="R89" t="n">
-        <v>6949411</v>
+        <v>6949414</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9453,7 +9453,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>18 stycken</t>
+          <t>16 exemplar</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10174,32 +10174,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129035017</v>
+        <v>129034609</v>
       </c>
       <c r="B97" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10209,10 +10209,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>569192</v>
+        <v>569458</v>
       </c>
       <c r="R97" t="n">
-        <v>6949518</v>
+        <v>6949777</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10249,7 +10249,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>48 stycken</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10276,32 +10276,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129035010</v>
+        <v>129035036</v>
       </c>
       <c r="B98" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10311,10 +10311,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>569465</v>
+        <v>569330</v>
       </c>
       <c r="R98" t="n">
-        <v>6949606</v>
+        <v>6949564</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10351,7 +10351,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>8 ex</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10378,32 +10378,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129034635</v>
+        <v>129035052</v>
       </c>
       <c r="B99" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10413,10 +10413,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>569427</v>
+        <v>569405</v>
       </c>
       <c r="R99" t="n">
-        <v>6949726</v>
+        <v>6949641</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10449,6 +10449,11 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>70 ex</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10475,32 +10480,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129034609</v>
+        <v>129035056</v>
       </c>
       <c r="B100" t="n">
-        <v>98724</v>
+        <v>105790</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10510,10 +10515,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>569458</v>
+        <v>569201</v>
       </c>
       <c r="R100" t="n">
-        <v>6949777</v>
+        <v>6949530</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10546,11 +10551,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>48 stycken</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10577,32 +10577,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129035036</v>
+        <v>129035017</v>
       </c>
       <c r="B101" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10612,10 +10612,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>569330</v>
+        <v>569192</v>
       </c>
       <c r="R101" t="n">
-        <v>6949564</v>
+        <v>6949518</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10652,7 +10652,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>8 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10679,32 +10679,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129035052</v>
+        <v>129035010</v>
       </c>
       <c r="B102" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10714,10 +10714,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>569405</v>
+        <v>569465</v>
       </c>
       <c r="R102" t="n">
-        <v>6949641</v>
+        <v>6949606</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10754,7 +10754,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>70 ex</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10781,32 +10781,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129035056</v>
+        <v>129034635</v>
       </c>
       <c r="B103" t="n">
-        <v>105790</v>
+        <v>79044</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>221144</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10816,10 +10816,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>569201</v>
+        <v>569427</v>
       </c>
       <c r="R103" t="n">
-        <v>6949530</v>
+        <v>6949726</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11577,45 +11577,43 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129035033</v>
+        <v>129035034</v>
       </c>
       <c r="B111" t="n">
-        <v>91763</v>
+        <v>91969</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>48</v>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>Lappticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Sandsjömyran, Mpd</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>569387</v>
+        <v>569140</v>
       </c>
       <c r="R111" t="n">
-        <v>6949669</v>
+        <v>6949574</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11656,6 +11654,7 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -11671,103 +11670,6 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" t="n">
-        <v>129035032</v>
-      </c>
-      <c r="B112" t="n">
-        <v>91763</v>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E112" t="n">
-        <v>48</v>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>Lappticka</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>Amylocystis lapponica</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr"/>
-      <c r="P112" t="inlineStr">
-        <is>
-          <t>Sandsjömyran, Mpd</t>
-        </is>
-      </c>
-      <c r="Q112" t="n">
-        <v>569462</v>
-      </c>
-      <c r="R112" t="n">
-        <v>6949702</v>
-      </c>
-      <c r="S112" t="n">
-        <v>10</v>
-      </c>
-      <c r="T112" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U112" t="inlineStr">
-        <is>
-          <t>Ånge</t>
-        </is>
-      </c>
-      <c r="V112" t="inlineStr">
-        <is>
-          <t>Medelpad</t>
-        </is>
-      </c>
-      <c r="W112" t="inlineStr">
-        <is>
-          <t>Torp</t>
-        </is>
-      </c>
-      <c r="Y112" t="inlineStr">
-        <is>
-          <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AA112" t="inlineStr">
-        <is>
-          <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AD112" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE112" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG112" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT112" t="inlineStr"/>
-      <c r="AW112" t="inlineStr">
-        <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AX112" t="inlineStr">
-        <is>
-          <t>Joel Helker-Nygren</t>
-        </is>
-      </c>
-      <c r="AY112" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45833-2025 artfynd.xlsx
+++ b/artfynd/A 45833-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129034612</v>
+        <v>129034627</v>
       </c>
       <c r="B2" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569243</v>
+        <v>569482</v>
       </c>
       <c r="R2" t="n">
-        <v>6949558</v>
+        <v>6949676</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>30  exemplar ca</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129035046</v>
+        <v>129034612</v>
       </c>
       <c r="B3" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569127</v>
+        <v>569243</v>
       </c>
       <c r="R3" t="n">
-        <v>6949602</v>
+        <v>6949558</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +847,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>13 ex</t>
+          <t>30  exemplar ca</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129035043</v>
+        <v>129035046</v>
       </c>
       <c r="B4" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569204</v>
+        <v>569127</v>
       </c>
       <c r="R4" t="n">
-        <v>6949533</v>
+        <v>6949602</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,7 +949,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>10 ex</t>
+          <t>13 ex</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,32 +976,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129034627</v>
+        <v>129035043</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569482</v>
+        <v>569204</v>
       </c>
       <c r="R5" t="n">
-        <v>6949676</v>
+        <v>6949533</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1052,6 +1047,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>10 ex</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,7 +1081,7 @@
         <v>129035039</v>
       </c>
       <c r="B6" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>129035030</v>
       </c>
       <c r="B7" t="n">
-        <v>97595</v>
+        <v>97598</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1277,32 +1277,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129035013</v>
+        <v>129035054</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>569455</v>
+        <v>569126</v>
       </c>
       <c r="R8" t="n">
-        <v>6949716</v>
+        <v>6949570</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>13 ex</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1379,7 +1379,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129035014</v>
+        <v>129035013</v>
       </c>
       <c r="B9" t="n">
         <v>57727</v>
@@ -1417,7 +1417,7 @@
         <v>569455</v>
       </c>
       <c r="R9" t="n">
-        <v>6949703</v>
+        <v>6949716</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1481,32 +1481,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129035054</v>
+        <v>129035014</v>
       </c>
       <c r="B10" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>569126</v>
+        <v>569455</v>
       </c>
       <c r="R10" t="n">
-        <v>6949570</v>
+        <v>6949703</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>13 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1583,32 +1583,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129034594</v>
+        <v>129034648</v>
       </c>
       <c r="B11" t="n">
-        <v>91848</v>
+        <v>96846</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>2869</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>569203</v>
+        <v>569279</v>
       </c>
       <c r="R11" t="n">
-        <v>6949498</v>
+        <v>6949401</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1654,11 +1654,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>11 exemplar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1685,32 +1680,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129034648</v>
+        <v>129034630</v>
       </c>
       <c r="B12" t="n">
-        <v>96843</v>
+        <v>79044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1720,10 +1715,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>569279</v>
+        <v>569231</v>
       </c>
       <c r="R12" t="n">
-        <v>6949401</v>
+        <v>6949559</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1782,10 +1777,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129034577</v>
+        <v>129034594</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>91851</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1793,21 +1788,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1817,10 +1812,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>569496</v>
+        <v>569203</v>
       </c>
       <c r="R13" t="n">
-        <v>6949627</v>
+        <v>6949498</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1857,7 +1852,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på tall</t>
+          <t>11 exemplar</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1884,10 +1879,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129034630</v>
+        <v>129034577</v>
       </c>
       <c r="B14" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1895,21 +1890,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1919,10 +1914,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>569231</v>
+        <v>569496</v>
       </c>
       <c r="R14" t="n">
-        <v>6949559</v>
+        <v>6949627</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1955,6 +1950,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1984,7 +1984,7 @@
         <v>129035055</v>
       </c>
       <c r="B15" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>129035042</v>
       </c>
       <c r="B16" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2185,32 +2185,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129035009</v>
+        <v>129035059</v>
       </c>
       <c r="B17" t="n">
-        <v>57727</v>
+        <v>92835</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2220,10 +2220,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>569314</v>
+        <v>569273</v>
       </c>
       <c r="R17" t="n">
-        <v>6949502</v>
+        <v>6949537</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2256,11 +2256,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2287,10 +2282,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129034580</v>
+        <v>129034629</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2298,21 +2293,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2322,10 +2317,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>569396</v>
+        <v>569247</v>
       </c>
       <c r="R18" t="n">
-        <v>6949738</v>
+        <v>6949558</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2358,11 +2353,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på Tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2389,7 +2379,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129035019</v>
+        <v>129035009</v>
       </c>
       <c r="B19" t="n">
         <v>57727</v>
@@ -2424,10 +2414,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>569117</v>
+        <v>569314</v>
       </c>
       <c r="R19" t="n">
-        <v>6949581</v>
+        <v>6949502</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2464,7 +2454,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2491,10 +2481,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129034629</v>
+        <v>129034580</v>
       </c>
       <c r="B20" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2502,21 +2492,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2526,10 +2516,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>569247</v>
+        <v>569396</v>
       </c>
       <c r="R20" t="n">
-        <v>6949558</v>
+        <v>6949738</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2562,6 +2552,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på Tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2588,32 +2583,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129034620</v>
+        <v>129035019</v>
       </c>
       <c r="B21" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2623,10 +2618,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>569195</v>
+        <v>569117</v>
       </c>
       <c r="R21" t="n">
-        <v>6949410</v>
+        <v>6949581</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2663,7 +2658,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Blommande knärot 1 exemplar + 21 övriga exemplar blommar ej</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2690,32 +2685,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129035059</v>
+        <v>129034620</v>
       </c>
       <c r="B22" t="n">
-        <v>92832</v>
+        <v>98727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2725,10 +2720,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>569273</v>
+        <v>569195</v>
       </c>
       <c r="R22" t="n">
-        <v>6949537</v>
+        <v>6949410</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2761,6 +2756,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Blommande knärot 1 exemplar + 21 övriga exemplar blommar ej</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2790,7 +2790,7 @@
         <v>129034592</v>
       </c>
       <c r="B23" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>129034591</v>
       </c>
       <c r="B24" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2991,10 +2991,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129035004</v>
+        <v>129034647</v>
       </c>
       <c r="B25" t="n">
-        <v>91550</v>
+        <v>88952</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3002,21 +3002,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3026,10 +3026,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>569152</v>
+        <v>569247</v>
       </c>
       <c r="R25" t="n">
-        <v>6949557</v>
+        <v>6949558</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3088,10 +3088,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129035025</v>
+        <v>129035004</v>
       </c>
       <c r="B26" t="n">
-        <v>91848</v>
+        <v>91553</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3099,21 +3099,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3123,10 +3123,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>569388</v>
+        <v>569152</v>
       </c>
       <c r="R26" t="n">
-        <v>6949665</v>
+        <v>6949557</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3185,10 +3185,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129035005</v>
+        <v>129035025</v>
       </c>
       <c r="B27" t="n">
-        <v>91550</v>
+        <v>91851</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3196,21 +3196,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3220,10 +3220,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>569188</v>
+        <v>569388</v>
       </c>
       <c r="R27" t="n">
-        <v>6949496</v>
+        <v>6949665</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3282,10 +3282,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129034625</v>
+        <v>129035005</v>
       </c>
       <c r="B28" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3293,21 +3293,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3317,10 +3317,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>569479</v>
+        <v>569188</v>
       </c>
       <c r="R28" t="n">
-        <v>6949657</v>
+        <v>6949496</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3379,10 +3379,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129034647</v>
+        <v>129034625</v>
       </c>
       <c r="B29" t="n">
-        <v>88950</v>
+        <v>79044</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3390,21 +3390,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3414,10 +3414,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>569247</v>
+        <v>569479</v>
       </c>
       <c r="R29" t="n">
-        <v>6949558</v>
+        <v>6949657</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3479,7 +3479,7 @@
         <v>129034623</v>
       </c>
       <c r="B30" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3578,10 +3578,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129035031</v>
+        <v>129034578</v>
       </c>
       <c r="B31" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3589,21 +3589,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>569125</v>
+        <v>569420</v>
       </c>
       <c r="R31" t="n">
-        <v>6949570</v>
+        <v>6949723</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3649,6 +3649,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3675,32 +3680,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129034637</v>
+        <v>129035031</v>
       </c>
       <c r="B32" t="n">
-        <v>92832</v>
+        <v>80149</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3710,10 +3715,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>569229</v>
+        <v>569125</v>
       </c>
       <c r="R32" t="n">
-        <v>6949400</v>
+        <v>6949570</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3772,32 +3777,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129034578</v>
+        <v>129034637</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>92835</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3807,10 +3812,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>569420</v>
+        <v>569229</v>
       </c>
       <c r="R33" t="n">
-        <v>6949723</v>
+        <v>6949400</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3843,11 +3848,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3974,7 +3974,7 @@
         <v>129035051</v>
       </c>
       <c r="B35" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4277,32 +4277,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129034634</v>
+        <v>129035040</v>
       </c>
       <c r="B38" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4312,10 +4312,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>569200</v>
+        <v>569386</v>
       </c>
       <c r="R38" t="n">
-        <v>6949411</v>
+        <v>6949657</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4348,6 +4348,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>9 ex</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4374,10 +4379,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129034602</v>
+        <v>129035045</v>
       </c>
       <c r="B39" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4409,10 +4414,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>569301</v>
+        <v>569130</v>
       </c>
       <c r="R39" t="n">
-        <v>6949480</v>
+        <v>6949603</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4449,7 +4454,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>22 stycken</t>
+          <t>14 ex</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4476,32 +4481,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129035040</v>
+        <v>129034634</v>
       </c>
       <c r="B40" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4511,10 +4516,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>569386</v>
+        <v>569200</v>
       </c>
       <c r="R40" t="n">
-        <v>6949657</v>
+        <v>6949411</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4547,11 +4552,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>9 ex</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4578,10 +4578,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129035045</v>
+        <v>129034602</v>
       </c>
       <c r="B41" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4613,10 +4613,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>569130</v>
+        <v>569301</v>
       </c>
       <c r="R41" t="n">
-        <v>6949603</v>
+        <v>6949480</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4653,7 +4653,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>14 ex</t>
+          <t>22 stycken</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4680,10 +4680,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129035063</v>
+        <v>129034643</v>
       </c>
       <c r="B42" t="n">
-        <v>96843</v>
+        <v>92835</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4691,21 +4691,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2869</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4715,10 +4715,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>569455</v>
+        <v>569254</v>
       </c>
       <c r="R42" t="n">
-        <v>6949758</v>
+        <v>6949431</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4751,6 +4751,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>1 färskt exemplar</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4777,10 +4782,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129034643</v>
+        <v>129035063</v>
       </c>
       <c r="B43" t="n">
-        <v>92832</v>
+        <v>96846</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4788,21 +4793,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>2869</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4812,10 +4817,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>569254</v>
+        <v>569455</v>
       </c>
       <c r="R43" t="n">
-        <v>6949431</v>
+        <v>6949758</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4848,11 +4853,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>1 färskt exemplar</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4882,7 +4882,7 @@
         <v>129034607</v>
       </c>
       <c r="B44" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>129035041</v>
       </c>
       <c r="B45" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129035011</v>
+        <v>129034575</v>
       </c>
       <c r="B46" t="n">
         <v>57727</v>
@@ -5118,10 +5118,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>569442</v>
+        <v>569448</v>
       </c>
       <c r="R46" t="n">
-        <v>6949783</v>
+        <v>6949625</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på Tall av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5185,7 +5185,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129034575</v>
+        <v>129035011</v>
       </c>
       <c r="B47" t="n">
         <v>57727</v>
@@ -5220,10 +5220,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>569448</v>
+        <v>569442</v>
       </c>
       <c r="R47" t="n">
-        <v>6949625</v>
+        <v>6949783</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5260,7 +5260,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Färska ringhack på Tall av tretåig hackspett</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5290,7 +5290,7 @@
         <v>129035022</v>
       </c>
       <c r="B48" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>129034597</v>
       </c>
       <c r="B49" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         <v>129035002</v>
       </c>
       <c r="B50" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5583,32 +5583,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129034632</v>
+        <v>129035062</v>
       </c>
       <c r="B51" t="n">
-        <v>79044</v>
+        <v>96846</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5618,10 +5618,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>569237</v>
+        <v>569478</v>
       </c>
       <c r="R51" t="n">
-        <v>6949442</v>
+        <v>6949666</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5680,32 +5680,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129035062</v>
+        <v>129034632</v>
       </c>
       <c r="B52" t="n">
-        <v>96843</v>
+        <v>79044</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5715,10 +5715,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>569478</v>
+        <v>569237</v>
       </c>
       <c r="R52" t="n">
-        <v>6949666</v>
+        <v>6949442</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5882,7 +5882,7 @@
         <v>129034616</v>
       </c>
       <c r="B54" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>129035028</v>
       </c>
       <c r="B55" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         <v>129035008</v>
       </c>
       <c r="B56" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6277,32 +6277,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129034610</v>
+        <v>129034581</v>
       </c>
       <c r="B58" t="n">
-        <v>98724</v>
+        <v>57887</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6312,10 +6312,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>569282</v>
+        <v>569223</v>
       </c>
       <c r="R58" t="n">
-        <v>6949567</v>
+        <v>6949401</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ca 100 stycken</t>
+          <t>Sågs och gjorde övriga läten</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6379,10 +6379,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129034614</v>
+        <v>129034610</v>
       </c>
       <c r="B59" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6414,10 +6414,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>569237</v>
+        <v>569282</v>
       </c>
       <c r="R59" t="n">
-        <v>6949556</v>
+        <v>6949567</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>5 stycken</t>
+          <t>Ca 100 stycken</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6481,32 +6481,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129034581</v>
+        <v>129034614</v>
       </c>
       <c r="B60" t="n">
-        <v>57887</v>
+        <v>98727</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6516,10 +6516,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>569223</v>
+        <v>569237</v>
       </c>
       <c r="R60" t="n">
-        <v>6949401</v>
+        <v>6949556</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6556,7 +6556,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Sågs och gjorde övriga läten</t>
+          <t>5 stycken</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6586,7 +6586,7 @@
         <v>129034586</v>
       </c>
       <c r="B61" t="n">
-        <v>92003</v>
+        <v>92006</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6683,7 +6683,7 @@
         <v>129035024</v>
       </c>
       <c r="B62" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6777,49 +6777,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129027791</v>
+        <v>129035003</v>
       </c>
       <c r="B63" t="n">
-        <v>98724</v>
+        <v>91553</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Sandsjömyran, Mpd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>569308</v>
+        <v>569164</v>
       </c>
       <c r="R63" t="n">
-        <v>6949546</v>
+        <v>6949559</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6878,32 +6874,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129034624</v>
+        <v>129034587</v>
       </c>
       <c r="B64" t="n">
-        <v>105790</v>
+        <v>91851</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221144</v>
+        <v>658</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6913,10 +6909,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>569234</v>
+        <v>569463</v>
       </c>
       <c r="R64" t="n">
-        <v>6949440</v>
+        <v>6949711</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6949,11 +6945,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>9 exemplar</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6980,32 +6971,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129035035</v>
+        <v>129035021</v>
       </c>
       <c r="B65" t="n">
-        <v>98724</v>
+        <v>91851</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7015,10 +7006,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>569317</v>
+        <v>569446</v>
       </c>
       <c r="R65" t="n">
-        <v>6949469</v>
+        <v>6949629</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7051,11 +7042,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>5 ex</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7082,10 +7068,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129035003</v>
+        <v>129034574</v>
       </c>
       <c r="B66" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7117,10 +7103,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>569164</v>
+        <v>569461</v>
       </c>
       <c r="R66" t="n">
-        <v>6949559</v>
+        <v>6949706</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7179,45 +7165,49 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129034587</v>
+        <v>129027791</v>
       </c>
       <c r="B67" t="n">
-        <v>91848</v>
+        <v>98727</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Sandsjömyran, Mpd</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>569463</v>
+        <v>569308</v>
       </c>
       <c r="R67" t="n">
-        <v>6949711</v>
+        <v>6949546</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7276,32 +7266,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129035021</v>
+        <v>129035035</v>
       </c>
       <c r="B68" t="n">
-        <v>91848</v>
+        <v>98727</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7311,10 +7301,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>569446</v>
+        <v>569317</v>
       </c>
       <c r="R68" t="n">
-        <v>6949629</v>
+        <v>6949469</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7347,6 +7337,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7373,32 +7368,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129034574</v>
+        <v>129034624</v>
       </c>
       <c r="B69" t="n">
-        <v>91550</v>
+        <v>105793</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7408,10 +7403,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>569461</v>
+        <v>569234</v>
       </c>
       <c r="R69" t="n">
-        <v>6949706</v>
+        <v>6949440</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7444,6 +7439,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>9 exemplar</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7470,32 +7470,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129035060</v>
+        <v>129034584</v>
       </c>
       <c r="B70" t="n">
-        <v>92832</v>
+        <v>57724</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7505,10 +7505,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>569208</v>
+        <v>569221</v>
       </c>
       <c r="R70" t="n">
-        <v>6949415</v>
+        <v>6949499</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7545,7 +7545,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>20 ex minst</t>
+          <t>Förbiflygande från träd till träd</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7572,32 +7572,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129035018</v>
+        <v>129035037</v>
       </c>
       <c r="B71" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7607,10 +7607,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>569111</v>
+        <v>569434</v>
       </c>
       <c r="R71" t="n">
-        <v>6949604</v>
+        <v>6949706</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7647,7 +7647,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>20 ex</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7674,32 +7674,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129034584</v>
+        <v>129034639</v>
       </c>
       <c r="B72" t="n">
-        <v>57724</v>
+        <v>92835</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7709,10 +7709,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>569221</v>
+        <v>569398</v>
       </c>
       <c r="R72" t="n">
-        <v>6949499</v>
+        <v>6949741</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7749,7 +7749,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Förbiflygande från träd till träd</t>
+          <t>6 äldre exemplar och 1 färsk fruktkropp</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7776,32 +7776,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129035037</v>
+        <v>129035060</v>
       </c>
       <c r="B73" t="n">
-        <v>98724</v>
+        <v>92835</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7811,10 +7811,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>569434</v>
+        <v>569208</v>
       </c>
       <c r="R73" t="n">
-        <v>6949706</v>
+        <v>6949415</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>20 ex</t>
+          <t>20 ex minst</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7878,32 +7878,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129034639</v>
+        <v>129035018</v>
       </c>
       <c r="B74" t="n">
-        <v>92832</v>
+        <v>57727</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7913,10 +7913,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>569398</v>
+        <v>569111</v>
       </c>
       <c r="R74" t="n">
-        <v>6949741</v>
+        <v>6949604</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7953,7 +7953,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>6 äldre exemplar och 1 färsk fruktkropp</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7980,32 +7980,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129026691</v>
+        <v>129034645</v>
       </c>
       <c r="B75" t="n">
-        <v>91848</v>
+        <v>92835</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8015,10 +8015,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>569195</v>
+        <v>569196</v>
       </c>
       <c r="R75" t="n">
-        <v>6949487</v>
+        <v>6949411</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8051,6 +8051,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>4 färska exemplar 3 äldre exemplar</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8077,10 +8082,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129034645</v>
+        <v>129034642</v>
       </c>
       <c r="B76" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8112,10 +8117,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>569196</v>
+        <v>569283</v>
       </c>
       <c r="R76" t="n">
-        <v>6949411</v>
+        <v>6949655</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8152,7 +8157,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>4 färska exemplar 3 äldre exemplar</t>
+          <t>7 äldre exemplar</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8179,32 +8184,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129034642</v>
+        <v>129034650</v>
       </c>
       <c r="B77" t="n">
-        <v>92832</v>
+        <v>98727</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8214,10 +8219,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>569283</v>
+        <v>569303</v>
       </c>
       <c r="R77" t="n">
-        <v>6949655</v>
+        <v>6949537</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8254,7 +8259,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>7 äldre exemplar</t>
+          <t>30 stycken ( finns eventuellt mer )</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8281,32 +8286,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129034598</v>
+        <v>129034605</v>
       </c>
       <c r="B78" t="n">
-        <v>97595</v>
+        <v>98727</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8316,10 +8321,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>569460</v>
+        <v>569305</v>
       </c>
       <c r="R78" t="n">
-        <v>6949629</v>
+        <v>6949538</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8352,6 +8357,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>21 knärot</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8378,32 +8388,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129034650</v>
+        <v>129026691</v>
       </c>
       <c r="B79" t="n">
-        <v>98724</v>
+        <v>91851</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8413,10 +8423,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>569303</v>
+        <v>569195</v>
       </c>
       <c r="R79" t="n">
-        <v>6949537</v>
+        <v>6949487</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8449,11 +8459,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>30 stycken ( finns eventuellt mer )</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8480,32 +8485,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129034605</v>
+        <v>129034598</v>
       </c>
       <c r="B80" t="n">
-        <v>98724</v>
+        <v>97598</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8515,10 +8520,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>569305</v>
+        <v>569460</v>
       </c>
       <c r="R80" t="n">
-        <v>6949538</v>
+        <v>6949629</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8551,11 +8556,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>21 knärot</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8582,32 +8582,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129035047</v>
+        <v>129035007</v>
       </c>
       <c r="B81" t="n">
-        <v>98724</v>
+        <v>91553</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8617,10 +8617,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>569162</v>
+        <v>569225</v>
       </c>
       <c r="R81" t="n">
-        <v>6949566</v>
+        <v>6949424</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8653,11 +8653,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>50 ex</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8684,32 +8679,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129034604</v>
+        <v>129035061</v>
       </c>
       <c r="B82" t="n">
-        <v>98724</v>
+        <v>96846</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8719,10 +8714,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>569303</v>
+        <v>569333</v>
       </c>
       <c r="R82" t="n">
-        <v>6949536</v>
+        <v>6949607</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8755,11 +8750,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8786,32 +8776,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129034618</v>
+        <v>129035057</v>
       </c>
       <c r="B83" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8821,10 +8811,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>569235</v>
+        <v>569464</v>
       </c>
       <c r="R83" t="n">
-        <v>6949411</v>
+        <v>6949648</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8857,11 +8847,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8888,32 +8873,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129035001</v>
+        <v>129035012</v>
       </c>
       <c r="B84" t="n">
-        <v>91514</v>
+        <v>57727</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8923,10 +8908,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>569232</v>
+        <v>569435</v>
       </c>
       <c r="R84" t="n">
-        <v>6949444</v>
+        <v>6949783</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8959,6 +8944,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8985,32 +8975,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129035007</v>
+        <v>129035047</v>
       </c>
       <c r="B85" t="n">
-        <v>91550</v>
+        <v>98727</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9020,10 +9010,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>569225</v>
+        <v>569162</v>
       </c>
       <c r="R85" t="n">
-        <v>6949424</v>
+        <v>6949566</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9056,6 +9046,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9082,10 +9077,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129035061</v>
+        <v>129034640</v>
       </c>
       <c r="B86" t="n">
-        <v>96843</v>
+        <v>92835</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9093,21 +9088,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2869</v>
+        <v>4364</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9117,10 +9112,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>569333</v>
+        <v>569213</v>
       </c>
       <c r="R86" t="n">
-        <v>6949607</v>
+        <v>6949414</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9153,6 +9148,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>16 exemplar</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9179,32 +9179,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129035012</v>
+        <v>129035001</v>
       </c>
       <c r="B87" t="n">
-        <v>57727</v>
+        <v>91517</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9214,10 +9214,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>569435</v>
+        <v>569232</v>
       </c>
       <c r="R87" t="n">
-        <v>6949783</v>
+        <v>6949444</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9250,11 +9250,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9281,32 +9276,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129035057</v>
+        <v>129034604</v>
       </c>
       <c r="B88" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9316,10 +9311,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>569464</v>
+        <v>569303</v>
       </c>
       <c r="R88" t="n">
-        <v>6949648</v>
+        <v>6949536</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9352,6 +9347,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>40 stycken</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9378,32 +9378,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129034640</v>
+        <v>129034618</v>
       </c>
       <c r="B89" t="n">
-        <v>92832</v>
+        <v>98727</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9413,10 +9413,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>569213</v>
+        <v>569235</v>
       </c>
       <c r="R89" t="n">
-        <v>6949414</v>
+        <v>6949411</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9453,7 +9453,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>16 exemplar</t>
+          <t>18 stycken</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9483,7 +9483,7 @@
         <v>129035023</v>
       </c>
       <c r="B90" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         <v>129035027</v>
       </c>
       <c r="B91" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         <v>129034589</v>
       </c>
       <c r="B92" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9774,7 +9774,7 @@
         <v>129035029</v>
       </c>
       <c r="B93" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9871,7 +9871,7 @@
         <v>129035038</v>
       </c>
       <c r="B94" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9973,7 +9973,7 @@
         <v>129035050</v>
       </c>
       <c r="B95" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10075,7 +10075,7 @@
         <v>129034621</v>
       </c>
       <c r="B96" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>129034609</v>
       </c>
       <c r="B97" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10279,7 +10279,7 @@
         <v>129035036</v>
       </c>
       <c r="B98" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10381,7 +10381,7 @@
         <v>129035052</v>
       </c>
       <c r="B99" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10483,7 +10483,7 @@
         <v>129035056</v>
       </c>
       <c r="B100" t="n">
-        <v>105790</v>
+        <v>105793</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10577,10 +10577,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129035017</v>
+        <v>129034635</v>
       </c>
       <c r="B101" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10588,21 +10588,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10612,10 +10612,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>569192</v>
+        <v>569427</v>
       </c>
       <c r="R101" t="n">
-        <v>6949518</v>
+        <v>6949726</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10648,11 +10648,6 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-10-10</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10679,7 +10674,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129035010</v>
+        <v>129035017</v>
       </c>
       <c r="B102" t="n">
         <v>57727</v>
@@ -10714,10 +10709,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>569465</v>
+        <v>569192</v>
       </c>
       <c r="R102" t="n">
-        <v>6949606</v>
+        <v>6949518</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10754,7 +10749,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10781,10 +10776,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129034635</v>
+        <v>129035010</v>
       </c>
       <c r="B103" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10792,21 +10787,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10816,10 +10811,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>569427</v>
+        <v>569465</v>
       </c>
       <c r="R103" t="n">
-        <v>6949726</v>
+        <v>6949606</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10852,6 +10847,11 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10878,32 +10878,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129035026</v>
+        <v>129035048</v>
       </c>
       <c r="B104" t="n">
-        <v>91848</v>
+        <v>98727</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10913,10 +10913,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>569175</v>
+        <v>569176</v>
       </c>
       <c r="R104" t="n">
-        <v>6949549</v>
+        <v>6949507</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10949,6 +10949,11 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>30 ex</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -10975,32 +10980,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129035006</v>
+        <v>129035053</v>
       </c>
       <c r="B105" t="n">
-        <v>91550</v>
+        <v>98727</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11010,10 +11015,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>569217</v>
+        <v>569459</v>
       </c>
       <c r="R105" t="n">
-        <v>6949470</v>
+        <v>6949662</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11046,6 +11051,11 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>14 ex</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11072,32 +11082,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129027886</v>
+        <v>129035049</v>
       </c>
       <c r="B106" t="n">
-        <v>91550</v>
+        <v>98727</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11107,10 +11117,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>569305</v>
+        <v>569219</v>
       </c>
       <c r="R106" t="n">
-        <v>6949566</v>
+        <v>6949489</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11143,6 +11153,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>35 ex</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11169,10 +11184,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129035048</v>
+        <v>129035044</v>
       </c>
       <c r="B107" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11204,10 +11219,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>569176</v>
+        <v>569191</v>
       </c>
       <c r="R107" t="n">
-        <v>6949507</v>
+        <v>6949579</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11244,7 +11259,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>30 ex</t>
+          <t>50 ex</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11271,32 +11286,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129035053</v>
+        <v>129035026</v>
       </c>
       <c r="B108" t="n">
-        <v>98724</v>
+        <v>91851</v>
       </c>
       <